--- a/AfterToken/Configs/GameConfig/Datas/__beans__.xlsx
+++ b/AfterToken/Configs/GameConfig/Datas/__beans__.xlsx
@@ -1025,7 +1025,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P279"/>
+  <dimension ref="A1:P284"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col width="20.625" customWidth="1" style="1" min="2" max="4"/>
@@ -2321,34 +2321,34 @@
       </c>
     </row>
     <row r="71">
-      <c r="J71" t="inlineStr">
+      <c r="J71" s="0" t="inlineStr">
         <is>
           <t>rewardGold</t>
         </is>
       </c>
-      <c r="L71" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="N71" t="inlineStr">
+      <c r="L71" s="0" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="N71" s="0" t="inlineStr">
         <is>
           <t>通关奖励金币</t>
         </is>
       </c>
     </row>
     <row r="72">
-      <c r="J72" t="inlineStr">
+      <c r="J72" s="0" t="inlineStr">
         <is>
           <t>rewardExp</t>
         </is>
       </c>
-      <c r="L72" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="N72" t="inlineStr">
+      <c r="L72" s="0" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="N72" s="0" t="inlineStr">
         <is>
           <t>通关奖励经验</t>
         </is>
@@ -5465,7 +5465,6 @@
         </is>
       </c>
     </row>
-    <row r="256"/>
     <row r="257">
       <c r="B257" s="0" t="inlineStr">
         <is>
@@ -5555,7 +5554,6 @@
         </is>
       </c>
     </row>
-    <row r="264"/>
     <row r="265">
       <c r="B265" s="0" t="inlineStr">
         <is>
@@ -5626,189 +5624,274 @@
       </c>
     </row>
     <row r="269">
-      <c r="B269" t="inlineStr">
+      <c r="B269" s="0" t="inlineStr">
         <is>
           <t>cfg.PlayerLevel</t>
         </is>
       </c>
-      <c r="G269" t="inlineStr">
+      <c r="G269" s="0" t="inlineStr">
         <is>
           <t>玩家等级经验表</t>
         </is>
       </c>
-      <c r="I269" t="inlineStr">
+      <c r="I269" s="0" t="inlineStr">
         <is>
           <t>c</t>
         </is>
       </c>
     </row>
     <row r="270">
-      <c r="J270" t="inlineStr">
+      <c r="J270" s="0" t="inlineStr">
         <is>
           <t>level</t>
         </is>
       </c>
-      <c r="L270" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="N270" t="inlineStr">
+      <c r="L270" s="0" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="N270" s="0" t="inlineStr">
         <is>
           <t>等级</t>
         </is>
       </c>
     </row>
     <row r="271">
-      <c r="J271" t="inlineStr">
+      <c r="J271" s="0" t="inlineStr">
         <is>
           <t>expToNext</t>
         </is>
       </c>
-      <c r="L271" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="N271" t="inlineStr">
+      <c r="L271" s="0" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="N271" s="0" t="inlineStr">
         <is>
           <t>升到下一级所需经验</t>
         </is>
       </c>
     </row>
     <row r="272">
-      <c r="B272" t="inlineStr">
+      <c r="B272" s="0" t="inlineStr">
         <is>
           <t>cfg.Unlock</t>
         </is>
       </c>
-      <c r="G272" t="inlineStr">
+      <c r="G272" s="0" t="inlineStr">
         <is>
           <t>内容解锁表</t>
         </is>
       </c>
-      <c r="I272" t="inlineStr">
+      <c r="I272" s="0" t="inlineStr">
         <is>
           <t>c</t>
         </is>
       </c>
     </row>
     <row r="273">
-      <c r="J273" t="inlineStr">
+      <c r="J273" s="0" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="L273" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="N273" t="inlineStr">
+      <c r="L273" s="0" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="N273" s="0" t="inlineStr">
         <is>
           <t>解锁ID</t>
         </is>
       </c>
     </row>
     <row r="274">
-      <c r="J274" t="inlineStr">
+      <c r="J274" s="0" t="inlineStr">
         <is>
           <t>contentType</t>
         </is>
       </c>
-      <c r="L274" t="inlineStr">
+      <c r="L274" s="0" t="inlineStr">
         <is>
           <t>cfg.UnlockContentType</t>
         </is>
       </c>
-      <c r="N274" t="inlineStr">
+      <c r="N274" s="0" t="inlineStr">
         <is>
           <t>内容类型</t>
         </is>
       </c>
     </row>
     <row r="275">
-      <c r="J275" t="inlineStr">
+      <c r="J275" s="0" t="inlineStr">
         <is>
           <t>targetId</t>
         </is>
       </c>
-      <c r="L275" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="N275" t="inlineStr">
+      <c r="L275" s="0" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="N275" s="0" t="inlineStr">
         <is>
           <t>目标ID（关卡/武器）</t>
         </is>
       </c>
     </row>
     <row r="276">
-      <c r="J276" t="inlineStr">
+      <c r="J276" s="0" t="inlineStr">
         <is>
           <t>requirePlayerLevel</t>
         </is>
       </c>
-      <c r="L276" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="N276" t="inlineStr">
+      <c r="L276" s="0" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="N276" s="0" t="inlineStr">
         <is>
           <t>要求玩家等级(0=无)</t>
         </is>
       </c>
     </row>
     <row r="277">
-      <c r="J277" t="inlineStr">
+      <c r="J277" s="0" t="inlineStr">
         <is>
           <t>requireCompleteLevelId</t>
         </is>
       </c>
-      <c r="L277" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="N277" t="inlineStr">
+      <c r="L277" s="0" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="N277" s="0" t="inlineStr">
         <is>
           <t>要求通关关卡ID(0=无)</t>
         </is>
       </c>
     </row>
     <row r="278">
-      <c r="J278" t="inlineStr">
+      <c r="J278" s="0" t="inlineStr">
         <is>
           <t>costGold</t>
         </is>
       </c>
-      <c r="L278" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="N278" t="inlineStr">
+      <c r="L278" s="0" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="N278" s="0" t="inlineStr">
         <is>
           <t>解锁花费金币(0=免费)</t>
         </is>
       </c>
     </row>
     <row r="279">
-      <c r="J279" t="inlineStr">
+      <c r="J279" s="0" t="inlineStr">
         <is>
           <t>comment</t>
         </is>
       </c>
-      <c r="L279" t="inlineStr">
+      <c r="L279" s="0" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="N279" t="inlineStr">
+      <c r="N279" s="0" t="inlineStr">
         <is>
           <t>备注</t>
+        </is>
+      </c>
+    </row>
+    <row r="280">
+      <c r="B280" t="inlineStr">
+        <is>
+          <t>cfg.Npc</t>
+        </is>
+      </c>
+      <c r="G280" t="inlineStr">
+        <is>
+          <t>NPC记录</t>
+        </is>
+      </c>
+      <c r="I280" t="inlineStr">
+        <is>
+          <t>c</t>
+        </is>
+      </c>
+    </row>
+    <row r="281">
+      <c r="J281" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="L281" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="N281" t="inlineStr">
+        <is>
+          <t>NPC ID</t>
+        </is>
+      </c>
+    </row>
+    <row r="282">
+      <c r="J282" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="L282" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="N282" t="inlineStr">
+        <is>
+          <t>显示名</t>
+        </is>
+      </c>
+    </row>
+    <row r="283">
+      <c r="J283" t="inlineStr">
+        <is>
+          <t>role</t>
+        </is>
+      </c>
+      <c r="L283" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="N283" t="inlineStr">
+        <is>
+          <t>身份/职业</t>
+        </is>
+      </c>
+    </row>
+    <row r="284">
+      <c r="J284" t="inlineStr">
+        <is>
+          <t>dialogueId</t>
+        </is>
+      </c>
+      <c r="L284" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="N284" t="inlineStr">
+        <is>
+          <t>对话ID(预留,0=无)</t>
         </is>
       </c>
     </row>

--- a/AfterToken/Configs/GameConfig/Datas/__beans__.xlsx
+++ b/AfterToken/Configs/GameConfig/Datas/__beans__.xlsx
@@ -1025,7 +1025,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P284"/>
+  <dimension ref="A1:P302"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col width="20.625" customWidth="1" style="1" min="2" max="4"/>
@@ -5465,6 +5465,7 @@
         </is>
       </c>
     </row>
+    <row r="256"/>
     <row r="257">
       <c r="B257" s="0" t="inlineStr">
         <is>
@@ -5554,6 +5555,7 @@
         </is>
       </c>
     </row>
+    <row r="264"/>
     <row r="265">
       <c r="B265" s="0" t="inlineStr">
         <is>
@@ -5811,68 +5813,68 @@
       </c>
     </row>
     <row r="280">
-      <c r="B280" t="inlineStr">
+      <c r="B280" s="0" t="inlineStr">
         <is>
           <t>cfg.Npc</t>
         </is>
       </c>
-      <c r="G280" t="inlineStr">
+      <c r="G280" s="0" t="inlineStr">
         <is>
           <t>NPC记录</t>
         </is>
       </c>
-      <c r="I280" t="inlineStr">
+      <c r="I280" s="0" t="inlineStr">
         <is>
           <t>c</t>
         </is>
       </c>
     </row>
     <row r="281">
-      <c r="J281" t="inlineStr">
+      <c r="J281" s="0" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="L281" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="N281" t="inlineStr">
+      <c r="L281" s="0" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="N281" s="0" t="inlineStr">
         <is>
           <t>NPC ID</t>
         </is>
       </c>
     </row>
     <row r="282">
-      <c r="J282" t="inlineStr">
+      <c r="J282" s="0" t="inlineStr">
         <is>
           <t>name</t>
         </is>
       </c>
-      <c r="L282" t="inlineStr">
+      <c r="L282" s="0" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="N282" t="inlineStr">
+      <c r="N282" s="0" t="inlineStr">
         <is>
           <t>显示名</t>
         </is>
       </c>
     </row>
     <row r="283">
-      <c r="J283" t="inlineStr">
+      <c r="J283" s="0" t="inlineStr">
         <is>
           <t>role</t>
         </is>
       </c>
-      <c r="L283" t="inlineStr">
+      <c r="L283" s="0" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="N283" t="inlineStr">
+      <c r="N283" s="0" t="inlineStr">
         <is>
           <t>身份/职业</t>
         </is>
@@ -5881,17 +5883,323 @@
     <row r="284">
       <c r="J284" t="inlineStr">
         <is>
+          <t>moveSpeed</t>
+        </is>
+      </c>
+      <c r="L284" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="N284" t="inlineStr">
+        <is>
+          <t>移动速度(0=站桩)</t>
+        </is>
+      </c>
+    </row>
+    <row r="285">
+      <c r="J285" t="inlineStr">
+        <is>
+          <t>patrolPath</t>
+        </is>
+      </c>
+      <c r="L285" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="N285" t="inlineStr">
+        <is>
+          <t>巡逻路径(x,z|x,z 空=不巡逻)</t>
+        </is>
+      </c>
+    </row>
+    <row r="286">
+      <c r="J286" s="0" t="inlineStr">
+        <is>
           <t>dialogueId</t>
         </is>
       </c>
-      <c r="L284" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="N284" t="inlineStr">
+      <c r="L286" s="0" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="N286" s="0" t="inlineStr">
         <is>
           <t>对话ID(预留,0=无)</t>
+        </is>
+      </c>
+    </row>
+    <row r="287">
+      <c r="B287" s="0" t="inlineStr">
+        <is>
+          <t>cfg.Dialogue</t>
+        </is>
+      </c>
+      <c r="G287" s="0" t="inlineStr">
+        <is>
+          <t>对话头</t>
+        </is>
+      </c>
+      <c r="I287" s="0" t="inlineStr">
+        <is>
+          <t>c</t>
+        </is>
+      </c>
+    </row>
+    <row r="288">
+      <c r="J288" s="0" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="L288" s="0" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="N288" s="0" t="inlineStr">
+        <is>
+          <t>对话ID</t>
+        </is>
+      </c>
+    </row>
+    <row r="289">
+      <c r="J289" s="0" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="L289" s="0" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="N289" s="0" t="inlineStr">
+        <is>
+          <t>注释名(不显示)</t>
+        </is>
+      </c>
+    </row>
+    <row r="290">
+      <c r="J290" s="0" t="inlineStr">
+        <is>
+          <t>startNode</t>
+        </is>
+      </c>
+      <c r="L290" s="0" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="N290" s="0" t="inlineStr">
+        <is>
+          <t>起始节点ID</t>
+        </is>
+      </c>
+    </row>
+    <row r="291">
+      <c r="J291" s="0" t="inlineStr">
+        <is>
+          <t>onceOnly</t>
+        </is>
+      </c>
+      <c r="L291" s="0" t="inlineStr">
+        <is>
+          <t>bool</t>
+        </is>
+      </c>
+      <c r="N291" s="0" t="inlineStr">
+        <is>
+          <t>只触发一次</t>
+        </is>
+      </c>
+    </row>
+    <row r="292">
+      <c r="J292" s="0" t="inlineStr">
+        <is>
+          <t>priority</t>
+        </is>
+      </c>
+      <c r="L292" s="0" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="N292" s="0" t="inlineStr">
+        <is>
+          <t>优先级(大优先)</t>
+        </is>
+      </c>
+    </row>
+    <row r="293">
+      <c r="B293" s="0" t="inlineStr">
+        <is>
+          <t>cfg.DialogueNode</t>
+        </is>
+      </c>
+      <c r="G293" s="0" t="inlineStr">
+        <is>
+          <t>对话节点</t>
+        </is>
+      </c>
+      <c r="I293" s="0" t="inlineStr">
+        <is>
+          <t>c</t>
+        </is>
+      </c>
+    </row>
+    <row r="294">
+      <c r="J294" s="0" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="L294" s="0" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="N294" s="0" t="inlineStr">
+        <is>
+          <t>节点ID</t>
+        </is>
+      </c>
+    </row>
+    <row r="295">
+      <c r="J295" s="0" t="inlineStr">
+        <is>
+          <t>dialogueId</t>
+        </is>
+      </c>
+      <c r="L295" s="0" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="N295" s="0" t="inlineStr">
+        <is>
+          <t>所属对话</t>
+        </is>
+      </c>
+    </row>
+    <row r="296">
+      <c r="J296" s="0" t="inlineStr">
+        <is>
+          <t>type</t>
+        </is>
+      </c>
+      <c r="L296" s="0" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="N296" s="0" t="inlineStr">
+        <is>
+          <t>类型(line/choice/setflag/end)</t>
+        </is>
+      </c>
+    </row>
+    <row r="297">
+      <c r="J297" s="0" t="inlineStr">
+        <is>
+          <t>speaker</t>
+        </is>
+      </c>
+      <c r="L297" s="0" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="N297" s="0" t="inlineStr">
+        <is>
+          <t>说话人</t>
+        </is>
+      </c>
+    </row>
+    <row r="298">
+      <c r="J298" s="0" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="L298" s="0" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="N298" s="0" t="inlineStr">
+        <is>
+          <t>正文</t>
+        </is>
+      </c>
+    </row>
+    <row r="299">
+      <c r="J299" s="0" t="inlineStr">
+        <is>
+          <t>choices</t>
+        </is>
+      </c>
+      <c r="L299" s="0" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="N299" s="0" t="inlineStr">
+        <is>
+          <t>选项(文本-&gt;节点|...)</t>
+        </is>
+      </c>
+    </row>
+    <row r="300">
+      <c r="J300" s="0" t="inlineStr">
+        <is>
+          <t>condition</t>
+        </is>
+      </c>
+      <c r="L300" s="0" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="N300" s="0" t="inlineStr">
+        <is>
+          <t>进入条件</t>
+        </is>
+      </c>
+    </row>
+    <row r="301">
+      <c r="J301" s="0" t="inlineStr">
+        <is>
+          <t>action</t>
+        </is>
+      </c>
+      <c r="L301" s="0" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="N301" s="0" t="inlineStr">
+        <is>
+          <t>到达动作</t>
+        </is>
+      </c>
+    </row>
+    <row r="302">
+      <c r="J302" s="0" t="inlineStr">
+        <is>
+          <t>next</t>
+        </is>
+      </c>
+      <c r="L302" s="0" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="N302" s="0" t="inlineStr">
+        <is>
+          <t>下一节点(0=结束)</t>
         </is>
       </c>
     </row>

--- a/AfterToken/Configs/GameConfig/Datas/__beans__.xlsx
+++ b/AfterToken/Configs/GameConfig/Datas/__beans__.xlsx
@@ -1025,7 +1025,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P302"/>
+  <dimension ref="A1:P318"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col width="20.625" customWidth="1" style="1" min="2" max="4"/>
@@ -2355,60 +2355,60 @@
       </c>
     </row>
     <row r="73">
-      <c r="B73" s="0" t="inlineStr">
+      <c r="J73" s="0" t="inlineStr">
+        <is>
+          <t>extractionTime</t>
+        </is>
+      </c>
+      <c r="L73" s="0" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="N73" s="0" t="inlineStr">
+        <is>
+          <t>撤离倒计时秒数</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="B74" s="0" t="inlineStr">
         <is>
           <t>cfg.Item</t>
         </is>
       </c>
-      <c r="G73" s="0" t="inlineStr">
+      <c r="G74" s="0" t="inlineStr">
         <is>
           <t>道具配置</t>
         </is>
       </c>
-      <c r="I73" s="0" t="inlineStr">
+      <c r="I74" s="0" t="inlineStr">
         <is>
           <t>c</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="J74" s="0" t="inlineStr">
-        <is>
-          <t>id</t>
-        </is>
-      </c>
-      <c r="L74" s="0" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="N74" s="0" t="inlineStr">
-        <is>
-          <t>道具ID</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="J75" s="0" t="inlineStr">
         <is>
-          <t>name</t>
+          <t>id</t>
         </is>
       </c>
       <c r="L75" s="0" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>int</t>
         </is>
       </c>
       <c r="N75" s="0" t="inlineStr">
         <is>
-          <t>名称</t>
+          <t>道具ID</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="J76" s="0" t="inlineStr">
         <is>
-          <t>desc</t>
+          <t>name</t>
         </is>
       </c>
       <c r="L76" s="0" t="inlineStr">
@@ -2418,201 +2418,201 @@
       </c>
       <c r="N76" s="0" t="inlineStr">
         <is>
-          <t>描述</t>
+          <t>名称</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="J77" s="0" t="inlineStr">
         <is>
-          <t>price</t>
+          <t>desc</t>
         </is>
       </c>
       <c r="L77" s="0" t="inlineStr">
         <is>
-          <t>int</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N77" s="0" t="inlineStr">
         <is>
-          <t>价格</t>
+          <t>描述</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="J78" s="0" t="inlineStr">
         <is>
-          <t>quality</t>
+          <t>price</t>
         </is>
       </c>
       <c r="L78" s="0" t="inlineStr">
         <is>
-          <t>cfg.EQuality</t>
+          <t>int</t>
         </is>
       </c>
       <c r="N78" s="0" t="inlineStr">
         <is>
-          <t>品质</t>
+          <t>价格</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="J79" s="0" t="inlineStr">
         <is>
-          <t>upgradeToItemId</t>
+          <t>quality</t>
         </is>
       </c>
       <c r="L79" s="0" t="inlineStr">
         <is>
-          <t>int</t>
+          <t>cfg.EQuality</t>
         </is>
       </c>
       <c r="N79" s="0" t="inlineStr">
         <is>
-          <t>升级目标道具ID</t>
+          <t>品质</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="J80" s="0" t="inlineStr">
         <is>
-          <t>expireTime</t>
+          <t>upgradeToItemId</t>
         </is>
       </c>
       <c r="L80" s="0" t="inlineStr">
         <is>
-          <t>datetime?</t>
+          <t>int</t>
         </is>
       </c>
       <c r="N80" s="0" t="inlineStr">
         <is>
-          <t>过期时间</t>
+          <t>升级目标道具ID</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="J81" s="0" t="inlineStr">
         <is>
-          <t>batchUseable</t>
+          <t>expireTime</t>
         </is>
       </c>
       <c r="L81" s="0" t="inlineStr">
         <is>
-          <t>bool</t>
+          <t>datetime?</t>
         </is>
       </c>
       <c r="N81" s="0" t="inlineStr">
         <is>
-          <t>是否可批量使用</t>
+          <t>过期时间</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="J82" s="0" t="inlineStr">
         <is>
-          <t>exchangeList</t>
+          <t>batchUseable</t>
         </is>
       </c>
       <c r="L82" s="0" t="inlineStr">
         <is>
-          <t>(list#sep=;),cfg.ItemExchange#sep=,</t>
+          <t>bool</t>
         </is>
       </c>
       <c r="N82" s="0" t="inlineStr">
         <is>
-          <t>兑换列表</t>
+          <t>是否可批量使用</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="J83" s="0" t="inlineStr">
         <is>
-          <t>itemType</t>
+          <t>exchangeList</t>
         </is>
       </c>
       <c r="L83" s="0" t="inlineStr">
         <is>
-          <t>cfg.EItemType</t>
+          <t>(list#sep=;),cfg.ItemExchange#sep=,</t>
         </is>
       </c>
       <c r="N83" s="0" t="inlineStr">
         <is>
-          <t>道具类型</t>
+          <t>兑换列表</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="J84" s="0" t="inlineStr">
         <is>
-          <t>icon</t>
+          <t>itemType</t>
         </is>
       </c>
       <c r="L84" s="0" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>cfg.EItemType</t>
         </is>
       </c>
       <c r="N84" s="0" t="inlineStr">
         <is>
-          <t>图标资源地址</t>
+          <t>道具类型</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="J85" s="0" t="inlineStr">
         <is>
+          <t>icon</t>
+        </is>
+      </c>
+      <c r="L85" s="0" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="N85" s="0" t="inlineStr">
+        <is>
+          <t>图标资源地址</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="J86" s="0" t="inlineStr">
+        <is>
           <t>stackLimit</t>
         </is>
       </c>
-      <c r="L85" s="0" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="N85" s="0" t="inlineStr">
+      <c r="L86" s="0" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="N86" s="0" t="inlineStr">
         <is>
           <t>堆叠上限</t>
         </is>
       </c>
     </row>
-    <row r="86">
-      <c r="B86" s="0" t="inlineStr">
+    <row r="87">
+      <c r="B87" s="0" t="inlineStr">
         <is>
           <t>cfg.Player</t>
         </is>
       </c>
-      <c r="G86" s="0" t="inlineStr">
+      <c r="G87" s="0" t="inlineStr">
         <is>
           <t>玩家属性</t>
         </is>
       </c>
-      <c r="I86" s="0" t="inlineStr">
+      <c r="I87" s="0" t="inlineStr">
         <is>
           <t>c</t>
-        </is>
-      </c>
-    </row>
-    <row r="87">
-      <c r="J87" s="0" t="inlineStr">
-        <is>
-          <t>id</t>
-        </is>
-      </c>
-      <c r="L87" s="0" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="N87" s="0" t="inlineStr">
-        <is>
-          <t>配置ID</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="J88" s="0" t="inlineStr">
         <is>
-          <t>maxHp</t>
+          <t>id</t>
         </is>
       </c>
       <c r="L88" s="0" t="inlineStr">
@@ -2622,31 +2622,31 @@
       </c>
       <c r="N88" s="0" t="inlineStr">
         <is>
-          <t>最大血量</t>
+          <t>配置ID</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="J89" s="0" t="inlineStr">
         <is>
-          <t>moveSpeed</t>
+          <t>maxHp</t>
         </is>
       </c>
       <c r="L89" s="0" t="inlineStr">
         <is>
-          <t>float</t>
+          <t>int</t>
         </is>
       </c>
       <c r="N89" s="0" t="inlineStr">
         <is>
-          <t>移动速度</t>
+          <t>最大血量</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="J90" s="0" t="inlineStr">
         <is>
-          <t>rotationSpeed</t>
+          <t>moveSpeed</t>
         </is>
       </c>
       <c r="L90" s="0" t="inlineStr">
@@ -2656,14 +2656,14 @@
       </c>
       <c r="N90" s="0" t="inlineStr">
         <is>
-          <t>旋转速度</t>
+          <t>移动速度</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="J91" s="0" t="inlineStr">
         <is>
-          <t>colliderRadius</t>
+          <t>rotationSpeed</t>
         </is>
       </c>
       <c r="L91" s="0" t="inlineStr">
@@ -2673,82 +2673,82 @@
       </c>
       <c r="N91" s="0" t="inlineStr">
         <is>
-          <t>碰撞体半径</t>
+          <t>旋转速度</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="J92" s="0" t="inlineStr">
         <is>
-          <t>maxStamina</t>
+          <t>colliderRadius</t>
         </is>
       </c>
       <c r="L92" s="0" t="inlineStr">
         <is>
-          <t>int</t>
+          <t>float</t>
         </is>
       </c>
       <c r="N92" s="0" t="inlineStr">
         <is>
-          <t>最大体力</t>
+          <t>碰撞体半径</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="J93" s="0" t="inlineStr">
         <is>
-          <t>staminaRecoveryRate</t>
+          <t>maxStamina</t>
         </is>
       </c>
       <c r="L93" s="0" t="inlineStr">
         <is>
-          <t>float</t>
+          <t>int</t>
         </is>
       </c>
       <c r="N93" s="0" t="inlineStr">
         <is>
-          <t>体力恢复速率</t>
+          <t>最大体力</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="J94" s="0" t="inlineStr">
         <is>
-          <t>dodgeStaminaCost</t>
+          <t>staminaRecoveryRate</t>
         </is>
       </c>
       <c r="L94" s="0" t="inlineStr">
         <is>
-          <t>int</t>
+          <t>float</t>
         </is>
       </c>
       <c r="N94" s="0" t="inlineStr">
         <is>
-          <t>闪避消耗体力</t>
+          <t>体力恢复速率</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="J95" s="0" t="inlineStr">
         <is>
-          <t>dodgeSpeed</t>
+          <t>dodgeStaminaCost</t>
         </is>
       </c>
       <c r="L95" s="0" t="inlineStr">
         <is>
-          <t>float</t>
+          <t>int</t>
         </is>
       </c>
       <c r="N95" s="0" t="inlineStr">
         <is>
-          <t>闪避速度</t>
+          <t>闪避消耗体力</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="J96" s="0" t="inlineStr">
         <is>
-          <t>dodgeDuration</t>
+          <t>dodgeSpeed</t>
         </is>
       </c>
       <c r="L96" s="0" t="inlineStr">
@@ -2758,31 +2758,31 @@
       </c>
       <c r="N96" s="0" t="inlineStr">
         <is>
-          <t>闪避持续时间</t>
+          <t>闪避速度</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="J97" s="0" t="inlineStr">
         <is>
-          <t>prefab</t>
+          <t>dodgeDuration</t>
         </is>
       </c>
       <c r="L97" s="0" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>float</t>
         </is>
       </c>
       <c r="N97" s="0" t="inlineStr">
         <is>
-          <t>预制体</t>
+          <t>闪避持续时间</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="J98" s="0" t="inlineStr">
         <is>
-          <t>idleAnim</t>
+          <t>prefab</t>
         </is>
       </c>
       <c r="L98" s="0" t="inlineStr">
@@ -2792,14 +2792,14 @@
       </c>
       <c r="N98" s="0" t="inlineStr">
         <is>
-          <t>待机动画名</t>
+          <t>预制体</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="J99" s="0" t="inlineStr">
         <is>
-          <t>moveAnim</t>
+          <t>idleAnim</t>
         </is>
       </c>
       <c r="L99" s="0" t="inlineStr">
@@ -2809,14 +2809,14 @@
       </c>
       <c r="N99" s="0" t="inlineStr">
         <is>
-          <t>移动动画名</t>
+          <t>待机动画名</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="J100" s="0" t="inlineStr">
         <is>
-          <t>dodgeAnim</t>
+          <t>moveAnim</t>
         </is>
       </c>
       <c r="L100" s="0" t="inlineStr">
@@ -2826,14 +2826,14 @@
       </c>
       <c r="N100" s="0" t="inlineStr">
         <is>
-          <t>闪避动画名</t>
+          <t>移动动画名</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="J101" s="0" t="inlineStr">
         <is>
-          <t>reloadAnim</t>
+          <t>dodgeAnim</t>
         </is>
       </c>
       <c r="L101" s="0" t="inlineStr">
@@ -2843,133 +2843,133 @@
       </c>
       <c r="N101" s="0" t="inlineStr">
         <is>
-          <t>换弹动画名</t>
+          <t>闪避动画名</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="J102" s="0" t="inlineStr">
         <is>
-          <t>weaponSwitchCooldown</t>
+          <t>reloadAnim</t>
         </is>
       </c>
       <c r="L102" s="0" t="inlineStr">
         <is>
-          <t>float</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N102" s="0" t="inlineStr">
         <is>
-          <t>武器切换冷却</t>
+          <t>换弹动画名</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="J103" s="0" t="inlineStr">
         <is>
+          <t>weaponSwitchCooldown</t>
+        </is>
+      </c>
+      <c r="L103" s="0" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="N103" s="0" t="inlineStr">
+        <is>
+          <t>武器切换冷却</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="J104" s="0" t="inlineStr">
+        <is>
           <t>deadAnim</t>
         </is>
       </c>
-      <c r="L103" s="0" t="inlineStr">
+      <c r="L104" s="0" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="N103" s="0" t="inlineStr">
+      <c r="N104" s="0" t="inlineStr">
         <is>
           <t>死亡动画名</t>
         </is>
       </c>
     </row>
-    <row r="104">
-      <c r="B104" s="0" t="inlineStr">
+    <row r="105">
+      <c r="B105" s="0" t="inlineStr">
         <is>
           <t>cfg.Enemy</t>
         </is>
       </c>
-      <c r="G104" s="0" t="inlineStr">
+      <c r="G105" s="0" t="inlineStr">
         <is>
           <t>敌人属性</t>
         </is>
       </c>
-      <c r="I104" s="0" t="inlineStr">
+      <c r="I105" s="0" t="inlineStr">
         <is>
           <t>c</t>
-        </is>
-      </c>
-    </row>
-    <row r="105">
-      <c r="J105" s="0" t="inlineStr">
-        <is>
-          <t>id</t>
-        </is>
-      </c>
-      <c r="L105" s="0" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="N105" s="0" t="inlineStr">
-        <is>
-          <t>敌人ID</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="J106" s="0" t="inlineStr">
         <is>
-          <t>name</t>
+          <t>id</t>
         </is>
       </c>
       <c r="L106" s="0" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>int</t>
         </is>
       </c>
       <c r="N106" s="0" t="inlineStr">
         <is>
-          <t>名称</t>
+          <t>敌人ID</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="J107" s="0" t="inlineStr">
         <is>
-          <t>maxHp</t>
+          <t>name</t>
         </is>
       </c>
       <c r="L107" s="0" t="inlineStr">
         <is>
-          <t>int</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N107" s="0" t="inlineStr">
         <is>
-          <t>最大血量</t>
+          <t>名称</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="J108" s="0" t="inlineStr">
         <is>
-          <t>moveSpeed</t>
+          <t>maxHp</t>
         </is>
       </c>
       <c r="L108" s="0" t="inlineStr">
         <is>
-          <t>float</t>
+          <t>int</t>
         </is>
       </c>
       <c r="N108" s="0" t="inlineStr">
         <is>
-          <t>移动速度</t>
+          <t>最大血量</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="J109" s="0" t="inlineStr">
         <is>
-          <t>rotationSpeed</t>
+          <t>moveSpeed</t>
         </is>
       </c>
       <c r="L109" s="0" t="inlineStr">
@@ -2979,48 +2979,48 @@
       </c>
       <c r="N109" s="0" t="inlineStr">
         <is>
-          <t>旋转速度</t>
+          <t>移动速度</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="J110" s="0" t="inlineStr">
         <is>
-          <t>attackDamage</t>
+          <t>rotationSpeed</t>
         </is>
       </c>
       <c r="L110" s="0" t="inlineStr">
         <is>
-          <t>int</t>
+          <t>float</t>
         </is>
       </c>
       <c r="N110" s="0" t="inlineStr">
         <is>
-          <t>攻击伤害</t>
+          <t>旋转速度</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="J111" s="0" t="inlineStr">
         <is>
-          <t>attackRange</t>
+          <t>attackDamage</t>
         </is>
       </c>
       <c r="L111" s="0" t="inlineStr">
         <is>
-          <t>float</t>
+          <t>int</t>
         </is>
       </c>
       <c r="N111" s="0" t="inlineStr">
         <is>
-          <t>攻击范围</t>
+          <t>攻击伤害</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="J112" s="0" t="inlineStr">
         <is>
-          <t>attackInterval</t>
+          <t>attackRange</t>
         </is>
       </c>
       <c r="L112" s="0" t="inlineStr">
@@ -3030,14 +3030,14 @@
       </c>
       <c r="N112" s="0" t="inlineStr">
         <is>
-          <t>攻击间隔</t>
+          <t>攻击范围</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="J113" s="0" t="inlineStr">
         <is>
-          <t>pathRefreshInterval</t>
+          <t>attackInterval</t>
         </is>
       </c>
       <c r="L113" s="0" t="inlineStr">
@@ -3047,82 +3047,82 @@
       </c>
       <c r="N113" s="0" t="inlineStr">
         <is>
-          <t>路径刷新间隔</t>
+          <t>攻击间隔</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="J114" s="0" t="inlineStr">
         <is>
-          <t>prefab</t>
+          <t>pathRefreshInterval</t>
         </is>
       </c>
       <c r="L114" s="0" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>float</t>
         </is>
       </c>
       <c r="N114" s="0" t="inlineStr">
         <is>
-          <t>预制体</t>
+          <t>路径刷新间隔</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="J115" s="0" t="inlineStr">
         <is>
+          <t>prefab</t>
+        </is>
+      </c>
+      <c r="L115" s="0" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="N115" s="0" t="inlineStr">
+        <is>
+          <t>预制体</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="J116" s="0" t="inlineStr">
+        <is>
           <t>chaseRange</t>
         </is>
       </c>
-      <c r="L115" s="0" t="inlineStr">
-        <is>
-          <t>float</t>
-        </is>
-      </c>
-      <c r="N115" s="0" t="inlineStr">
+      <c r="L116" s="0" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="N116" s="0" t="inlineStr">
         <is>
           <t>仇恨范围（追击触发距离）</t>
         </is>
       </c>
     </row>
-    <row r="116">
-      <c r="B116" s="0" t="inlineStr">
+    <row r="117">
+      <c r="B117" s="0" t="inlineStr">
         <is>
           <t>cfg.Wave</t>
         </is>
       </c>
-      <c r="G116" s="0" t="inlineStr">
+      <c r="G117" s="0" t="inlineStr">
         <is>
           <t>波次配置</t>
         </is>
       </c>
-      <c r="I116" s="0" t="inlineStr">
+      <c r="I117" s="0" t="inlineStr">
         <is>
           <t>c</t>
-        </is>
-      </c>
-    </row>
-    <row r="117">
-      <c r="J117" s="0" t="inlineStr">
-        <is>
-          <t>id</t>
-        </is>
-      </c>
-      <c r="L117" s="0" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="N117" s="0" t="inlineStr">
-        <is>
-          <t>波次ID</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="J118" s="0" t="inlineStr">
         <is>
-          <t>levelId</t>
+          <t>id</t>
         </is>
       </c>
       <c r="L118" s="0" t="inlineStr">
@@ -3132,14 +3132,14 @@
       </c>
       <c r="N118" s="0" t="inlineStr">
         <is>
-          <t>关卡ID</t>
+          <t>波次ID</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="J119" s="0" t="inlineStr">
         <is>
-          <t>waveIndex</t>
+          <t>levelId</t>
         </is>
       </c>
       <c r="L119" s="0" t="inlineStr">
@@ -3149,14 +3149,14 @@
       </c>
       <c r="N119" s="0" t="inlineStr">
         <is>
-          <t>波次索引</t>
+          <t>关卡ID</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="J120" s="0" t="inlineStr">
         <is>
-          <t>enemyId</t>
+          <t>waveIndex</t>
         </is>
       </c>
       <c r="L120" s="0" t="inlineStr">
@@ -3166,14 +3166,14 @@
       </c>
       <c r="N120" s="0" t="inlineStr">
         <is>
-          <t>敌人ID</t>
+          <t>波次索引</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="J121" s="0" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>enemyId</t>
         </is>
       </c>
       <c r="L121" s="0" t="inlineStr">
@@ -3183,82 +3183,82 @@
       </c>
       <c r="N121" s="0" t="inlineStr">
         <is>
-          <t>数量</t>
+          <t>敌人ID</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="J122" s="0" t="inlineStr">
         <is>
-          <t>spawnInterval</t>
+          <t>count</t>
         </is>
       </c>
       <c r="L122" s="0" t="inlineStr">
         <is>
-          <t>float</t>
+          <t>int</t>
         </is>
       </c>
       <c r="N122" s="0" t="inlineStr">
         <is>
-          <t>刷新间隔</t>
+          <t>数量</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="J123" s="0" t="inlineStr">
         <is>
+          <t>spawnInterval</t>
+        </is>
+      </c>
+      <c r="L123" s="0" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="N123" s="0" t="inlineStr">
+        <is>
+          <t>刷新间隔</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="J124" s="0" t="inlineStr">
+        <is>
           <t>spawnRadius</t>
         </is>
       </c>
-      <c r="L123" s="0" t="inlineStr">
-        <is>
-          <t>float</t>
-        </is>
-      </c>
-      <c r="N123" s="0" t="inlineStr">
+      <c r="L124" s="0" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="N124" s="0" t="inlineStr">
         <is>
           <t>刷新半径</t>
         </is>
       </c>
     </row>
-    <row r="124">
-      <c r="B124" s="0" t="inlineStr">
+    <row r="125">
+      <c r="B125" s="0" t="inlineStr">
         <is>
           <t>cfg.Drop</t>
         </is>
       </c>
-      <c r="G124" s="0" t="inlineStr">
+      <c r="G125" s="0" t="inlineStr">
         <is>
           <t>掉落配置</t>
         </is>
       </c>
-      <c r="I124" s="0" t="inlineStr">
+      <c r="I125" s="0" t="inlineStr">
         <is>
           <t>c</t>
-        </is>
-      </c>
-    </row>
-    <row r="125">
-      <c r="J125" s="0" t="inlineStr">
-        <is>
-          <t>id</t>
-        </is>
-      </c>
-      <c r="L125" s="0" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="N125" s="0" t="inlineStr">
-        <is>
-          <t>掉落ID</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="J126" s="0" t="inlineStr">
         <is>
-          <t>enemyId</t>
+          <t>id</t>
         </is>
       </c>
       <c r="L126" s="0" t="inlineStr">
@@ -3268,14 +3268,14 @@
       </c>
       <c r="N126" s="0" t="inlineStr">
         <is>
-          <t>敌人ID</t>
+          <t>掉落ID</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="J127" s="0" t="inlineStr">
         <is>
-          <t>itemId</t>
+          <t>enemyId</t>
         </is>
       </c>
       <c r="L127" s="0" t="inlineStr">
@@ -3285,14 +3285,14 @@
       </c>
       <c r="N127" s="0" t="inlineStr">
         <is>
-          <t>道具ID</t>
+          <t>敌人ID</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="J128" s="0" t="inlineStr">
         <is>
-          <t>dropRate</t>
+          <t>itemId</t>
         </is>
       </c>
       <c r="L128" s="0" t="inlineStr">
@@ -3302,14 +3302,14 @@
       </c>
       <c r="N128" s="0" t="inlineStr">
         <is>
-          <t>掉落概率(万分之一)</t>
+          <t>道具ID</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="J129" s="0" t="inlineStr">
         <is>
-          <t>minCount</t>
+          <t>dropRate</t>
         </is>
       </c>
       <c r="L129" s="0" t="inlineStr">
@@ -3319,235 +3319,235 @@
       </c>
       <c r="N129" s="0" t="inlineStr">
         <is>
-          <t>最小数量</t>
+          <t>掉落概率(万分之一)</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="J130" s="0" t="inlineStr">
         <is>
+          <t>minCount</t>
+        </is>
+      </c>
+      <c r="L130" s="0" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="N130" s="0" t="inlineStr">
+        <is>
+          <t>最小数量</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="J131" s="0" t="inlineStr">
+        <is>
           <t>maxCount</t>
         </is>
       </c>
-      <c r="L130" s="0" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="N130" s="0" t="inlineStr">
+      <c r="L131" s="0" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="N131" s="0" t="inlineStr">
         <is>
           <t>最大数量</t>
         </is>
       </c>
     </row>
-    <row r="131">
-      <c r="B131" s="0" t="inlineStr">
+    <row r="132">
+      <c r="B132" s="0" t="inlineStr">
         <is>
           <t>cfg.Buff</t>
         </is>
       </c>
-      <c r="G131" s="0" t="inlineStr">
+      <c r="G132" s="0" t="inlineStr">
         <is>
           <t>Buff配置</t>
         </is>
       </c>
-      <c r="I131" s="0" t="inlineStr">
+      <c r="I132" s="0" t="inlineStr">
         <is>
           <t>c</t>
-        </is>
-      </c>
-    </row>
-    <row r="132">
-      <c r="J132" s="0" t="inlineStr">
-        <is>
-          <t>id</t>
-        </is>
-      </c>
-      <c r="L132" s="0" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="N132" s="0" t="inlineStr">
-        <is>
-          <t>BuffID</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="J133" s="0" t="inlineStr">
         <is>
-          <t>name</t>
+          <t>id</t>
         </is>
       </c>
       <c r="L133" s="0" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>int</t>
         </is>
       </c>
       <c r="N133" s="0" t="inlineStr">
         <is>
-          <t>名称</t>
+          <t>BuffID</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="J134" s="0" t="inlineStr">
         <is>
-          <t>duration</t>
+          <t>name</t>
         </is>
       </c>
       <c r="L134" s="0" t="inlineStr">
         <is>
-          <t>float</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N134" s="0" t="inlineStr">
         <is>
-          <t>持续时间</t>
+          <t>名称</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="J135" s="0" t="inlineStr">
         <is>
-          <t>effectType</t>
+          <t>duration</t>
         </is>
       </c>
       <c r="L135" s="0" t="inlineStr">
         <is>
-          <t>int</t>
+          <t>float</t>
         </is>
       </c>
       <c r="N135" s="0" t="inlineStr">
         <is>
-          <t>效果类型</t>
+          <t>持续时间</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="J136" s="0" t="inlineStr">
         <is>
-          <t>value</t>
+          <t>effectType</t>
         </is>
       </c>
       <c r="L136" s="0" t="inlineStr">
         <is>
-          <t>float</t>
+          <t>int</t>
         </is>
       </c>
       <c r="N136" s="0" t="inlineStr">
         <is>
-          <t>数值</t>
+          <t>效果类型</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="J137" s="0" t="inlineStr">
         <is>
+          <t>value</t>
+        </is>
+      </c>
+      <c r="L137" s="0" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="N137" s="0" t="inlineStr">
+        <is>
+          <t>数值</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="J138" s="0" t="inlineStr">
+        <is>
           <t>icon</t>
         </is>
       </c>
-      <c r="L137" s="0" t="inlineStr">
+      <c r="L138" s="0" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="N137" s="0" t="inlineStr">
+      <c r="N138" s="0" t="inlineStr">
         <is>
           <t>图标</t>
         </is>
       </c>
     </row>
-    <row r="138">
-      <c r="B138" s="0" t="inlineStr">
+    <row r="139">
+      <c r="B139" s="0" t="inlineStr">
         <is>
           <t>cfg.Portal</t>
         </is>
       </c>
-      <c r="G138" s="0" t="inlineStr">
+      <c r="G139" s="0" t="inlineStr">
         <is>
           <t>传送门配置</t>
         </is>
       </c>
-      <c r="I138" s="0" t="inlineStr">
+      <c r="I139" s="0" t="inlineStr">
         <is>
           <t>c</t>
-        </is>
-      </c>
-    </row>
-    <row r="139">
-      <c r="J139" s="0" t="inlineStr">
-        <is>
-          <t>id</t>
-        </is>
-      </c>
-      <c r="L139" s="0" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="N139" s="0" t="inlineStr">
-        <is>
-          <t>传送门ID</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="J140" s="0" t="inlineStr">
         <is>
-          <t>portalType</t>
+          <t>id</t>
         </is>
       </c>
       <c r="L140" s="0" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>int</t>
         </is>
       </c>
       <c r="N140" s="0" t="inlineStr">
         <is>
-          <t>传送门类型</t>
+          <t>传送门ID</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="J141" s="0" t="inlineStr">
         <is>
-          <t>targetLevelId</t>
+          <t>portalType</t>
         </is>
       </c>
       <c r="L141" s="0" t="inlineStr">
         <is>
-          <t>int</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N141" s="0" t="inlineStr">
         <is>
-          <t>目标关卡ID</t>
+          <t>传送门类型</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="J142" s="0" t="inlineStr">
         <is>
-          <t>targetSceneName</t>
+          <t>targetLevelId</t>
         </is>
       </c>
       <c r="L142" s="0" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>int</t>
         </is>
       </c>
       <c r="N142" s="0" t="inlineStr">
         <is>
-          <t>目标场景名</t>
+          <t>目标关卡ID</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="J143" s="0" t="inlineStr">
         <is>
-          <t>spawnCondition</t>
+          <t>targetSceneName</t>
         </is>
       </c>
       <c r="L143" s="0" t="inlineStr">
@@ -3557,14 +3557,14 @@
       </c>
       <c r="N143" s="0" t="inlineStr">
         <is>
-          <t>出现条件</t>
+          <t>目标场景名</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="J144" s="0" t="inlineStr">
         <is>
-          <t>conditionParam</t>
+          <t>spawnCondition</t>
         </is>
       </c>
       <c r="L144" s="0" t="inlineStr">
@@ -3574,48 +3574,48 @@
       </c>
       <c r="N144" s="0" t="inlineStr">
         <is>
-          <t>条件参数</t>
+          <t>出现条件</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="J145" s="0" t="inlineStr">
         <is>
-          <t>keepPlayerState</t>
+          <t>conditionParam</t>
         </is>
       </c>
       <c r="L145" s="0" t="inlineStr">
         <is>
-          <t>bool</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N145" s="0" t="inlineStr">
         <is>
-          <t>保留玩家状态</t>
+          <t>条件参数</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="J146" s="0" t="inlineStr">
         <is>
-          <t>promptText</t>
+          <t>keepPlayerState</t>
         </is>
       </c>
       <c r="L146" s="0" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>bool</t>
         </is>
       </c>
       <c r="N146" s="0" t="inlineStr">
         <is>
-          <t>提示文本</t>
+          <t>保留玩家状态</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="J147" s="0" t="inlineStr">
         <is>
-          <t>transitionType</t>
+          <t>promptText</t>
         </is>
       </c>
       <c r="L147" s="0" t="inlineStr">
@@ -3625,65 +3625,65 @@
       </c>
       <c r="N147" s="0" t="inlineStr">
         <is>
-          <t>转场类型</t>
+          <t>提示文本</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="J148" s="0" t="inlineStr">
         <is>
+          <t>transitionType</t>
+        </is>
+      </c>
+      <c r="L148" s="0" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="N148" s="0" t="inlineStr">
+        <is>
+          <t>转场类型</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="J149" s="0" t="inlineStr">
+        <is>
           <t>transitionDuration</t>
         </is>
       </c>
-      <c r="L148" s="0" t="inlineStr">
-        <is>
-          <t>float</t>
-        </is>
-      </c>
-      <c r="N148" s="0" t="inlineStr">
+      <c r="L149" s="0" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="N149" s="0" t="inlineStr">
         <is>
           <t>转场时长</t>
         </is>
       </c>
     </row>
-    <row r="149">
-      <c r="B149" s="0" t="inlineStr">
+    <row r="150">
+      <c r="B150" s="0" t="inlineStr">
         <is>
           <t>cfg.InventoryConfig</t>
         </is>
       </c>
-      <c r="G149" s="0" t="inlineStr">
+      <c r="G150" s="0" t="inlineStr">
         <is>
           <t>背包容量配置</t>
         </is>
       </c>
-      <c r="I149" s="0" t="inlineStr">
+      <c r="I150" s="0" t="inlineStr">
         <is>
           <t>c</t>
-        </is>
-      </c>
-    </row>
-    <row r="150">
-      <c r="J150" s="0" t="inlineStr">
-        <is>
-          <t>id</t>
-        </is>
-      </c>
-      <c r="L150" s="0" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="N150" s="0" t="inlineStr">
-        <is>
-          <t>ID</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="J151" s="0" t="inlineStr">
         <is>
-          <t>tempBagCapacity</t>
+          <t>id</t>
         </is>
       </c>
       <c r="L151" s="0" t="inlineStr">
@@ -3693,82 +3693,82 @@
       </c>
       <c r="N151" s="0" t="inlineStr">
         <is>
-          <t>临时背包槽位</t>
+          <t>ID</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="J152" s="0" t="inlineStr">
         <is>
+          <t>tempBagCapacity</t>
+        </is>
+      </c>
+      <c r="L152" s="0" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="N152" s="0" t="inlineStr">
+        <is>
+          <t>临时背包槽位</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="J153" s="0" t="inlineStr">
+        <is>
           <t>warehouseCapacity</t>
         </is>
       </c>
-      <c r="L152" s="0" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="N152" s="0" t="inlineStr">
+      <c r="L153" s="0" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="N153" s="0" t="inlineStr">
         <is>
           <t>仓库槽位</t>
         </is>
       </c>
     </row>
-    <row r="153">
-      <c r="B153" s="0" t="inlineStr">
+    <row r="154">
+      <c r="B154" s="0" t="inlineStr">
         <is>
           <t>cfg.Camera</t>
         </is>
       </c>
-      <c r="G153" s="0" t="inlineStr">
+      <c r="G154" s="0" t="inlineStr">
         <is>
           <t>相机配置</t>
         </is>
       </c>
-      <c r="H153" s="0" t="inlineStr">
+      <c r="H154" s="0" t="inlineStr">
         <is>
           <t>c</t>
-        </is>
-      </c>
-    </row>
-    <row r="154">
-      <c r="J154" s="0" t="inlineStr">
-        <is>
-          <t>id</t>
-        </is>
-      </c>
-      <c r="L154" s="0" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="N154" s="0" t="inlineStr">
-        <is>
-          <t>配置ID</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="J155" s="0" t="inlineStr">
         <is>
-          <t>smoothTime</t>
+          <t>id</t>
         </is>
       </c>
       <c r="L155" s="0" t="inlineStr">
         <is>
-          <t>float</t>
+          <t>int</t>
         </is>
       </c>
       <c r="N155" s="0" t="inlineStr">
         <is>
-          <t>相机平滑时间</t>
+          <t>配置ID</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="J156" s="0" t="inlineStr">
         <is>
-          <t>defaultFov</t>
+          <t>smoothTime</t>
         </is>
       </c>
       <c r="L156" s="0" t="inlineStr">
@@ -3778,14 +3778,14 @@
       </c>
       <c r="N156" s="0" t="inlineStr">
         <is>
-          <t>默认FOV</t>
+          <t>相机平滑时间</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="J157" s="0" t="inlineStr">
         <is>
-          <t>fovSmoothTime</t>
+          <t>defaultFov</t>
         </is>
       </c>
       <c r="L157" s="0" t="inlineStr">
@@ -3795,14 +3795,14 @@
       </c>
       <c r="N157" s="0" t="inlineStr">
         <is>
-          <t>FOV平滑时间</t>
+          <t>默认FOV</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="J158" s="0" t="inlineStr">
         <is>
-          <t>shakeDamping</t>
+          <t>fovSmoothTime</t>
         </is>
       </c>
       <c r="L158" s="0" t="inlineStr">
@@ -3812,116 +3812,116 @@
       </c>
       <c r="N158" s="0" t="inlineStr">
         <is>
-          <t>震动衰减速度</t>
+          <t>FOV平滑时间</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="J159" s="0" t="inlineStr">
         <is>
-          <t>scopeRenderSize</t>
+          <t>shakeDamping</t>
         </is>
       </c>
       <c r="L159" s="0" t="inlineStr">
         <is>
-          <t>int</t>
+          <t>float</t>
         </is>
       </c>
       <c r="N159" s="0" t="inlineStr">
         <is>
-          <t>狙击镜渲染纹理尺寸</t>
+          <t>震动衰减速度</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="J160" s="0" t="inlineStr">
         <is>
-          <t>scopeCameraFov</t>
+          <t>scopeRenderSize</t>
         </is>
       </c>
       <c r="L160" s="0" t="inlineStr">
         <is>
-          <t>float</t>
+          <t>int</t>
         </is>
       </c>
       <c r="N160" s="0" t="inlineStr">
         <is>
-          <t>狙击镜相机FOV</t>
+          <t>狙击镜渲染纹理尺寸</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="J161" s="0" t="inlineStr">
         <is>
+          <t>scopeCameraFov</t>
+        </is>
+      </c>
+      <c r="L161" s="0" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="N161" s="0" t="inlineStr">
+        <is>
+          <t>狙击镜相机FOV</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="J162" s="0" t="inlineStr">
+        <is>
           <t>defaultOrthographicSize</t>
         </is>
       </c>
-      <c r="L161" s="0" t="inlineStr">
-        <is>
-          <t>float</t>
-        </is>
-      </c>
-      <c r="N161" s="0" t="inlineStr">
+      <c r="L162" s="0" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="N162" s="0" t="inlineStr">
         <is>
           <t>默认正交尺寸</t>
         </is>
       </c>
     </row>
-    <row r="162">
-      <c r="B162" s="0" t="inlineStr">
+    <row r="163">
+      <c r="B163" s="0" t="inlineStr">
         <is>
           <t>cfg.Ballistic</t>
         </is>
       </c>
-      <c r="G162" s="0" t="inlineStr">
+      <c r="G163" s="0" t="inlineStr">
         <is>
           <t>弹道全局配置</t>
         </is>
       </c>
-      <c r="H162" s="0" t="inlineStr">
+      <c r="H163" s="0" t="inlineStr">
         <is>
           <t>c</t>
-        </is>
-      </c>
-    </row>
-    <row r="163">
-      <c r="J163" s="0" t="inlineStr">
-        <is>
-          <t>id</t>
-        </is>
-      </c>
-      <c r="L163" s="0" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="N163" s="0" t="inlineStr">
-        <is>
-          <t>配置ID</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="J164" s="0" t="inlineStr">
         <is>
-          <t>tracerRadius</t>
+          <t>id</t>
         </is>
       </c>
       <c r="L164" s="0" t="inlineStr">
         <is>
-          <t>float</t>
+          <t>int</t>
         </is>
       </c>
       <c r="N164" s="0" t="inlineStr">
         <is>
-          <t>Tracer射线检测半径</t>
+          <t>配置ID</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="J165" s="0" t="inlineStr">
         <is>
-          <t>tracerStartWidth</t>
+          <t>tracerRadius</t>
         </is>
       </c>
       <c r="L165" s="0" t="inlineStr">
@@ -3931,14 +3931,14 @@
       </c>
       <c r="N165" s="0" t="inlineStr">
         <is>
-          <t>Tracer起始宽度</t>
+          <t>Tracer射线检测半径</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="J166" s="0" t="inlineStr">
         <is>
-          <t>tracerEndWidth</t>
+          <t>tracerStartWidth</t>
         </is>
       </c>
       <c r="L166" s="0" t="inlineStr">
@@ -3948,14 +3948,14 @@
       </c>
       <c r="N166" s="0" t="inlineStr">
         <is>
-          <t>Tracer结束宽度</t>
+          <t>Tracer起始宽度</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="J167" s="0" t="inlineStr">
         <is>
-          <t>tracerTailLength</t>
+          <t>tracerEndWidth</t>
         </is>
       </c>
       <c r="L167" s="0" t="inlineStr">
@@ -3965,116 +3965,116 @@
       </c>
       <c r="N167" s="0" t="inlineStr">
         <is>
-          <t>Tracer尾迹长度</t>
+          <t>Tracer结束宽度</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="J168" s="0" t="inlineStr">
         <is>
-          <t>maxActiveTracers</t>
+          <t>tracerTailLength</t>
         </is>
       </c>
       <c r="L168" s="0" t="inlineStr">
         <is>
-          <t>int</t>
+          <t>float</t>
         </is>
       </c>
       <c r="N168" s="0" t="inlineStr">
         <is>
-          <t>最大同时存在Tracer数量</t>
+          <t>Tracer尾迹长度</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="J169" s="0" t="inlineStr">
         <is>
-          <t>hitLayers</t>
+          <t>maxActiveTracers</t>
         </is>
       </c>
       <c r="L169" s="0" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>int</t>
         </is>
       </c>
       <c r="N169" s="0" t="inlineStr">
         <is>
-          <t>默认命中层级</t>
+          <t>最大同时存在Tracer数量</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="J170" s="0" t="inlineStr">
         <is>
-          <t>tracerStartColor</t>
+          <t>hitLayers</t>
         </is>
       </c>
       <c r="L170" s="0" t="inlineStr">
         <is>
-          <t>cfg.Color#sep=,</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N170" s="0" t="inlineStr">
         <is>
-          <t>Tracer起始颜色</t>
+          <t>默认命中层级</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="J171" s="0" t="inlineStr">
         <is>
+          <t>tracerStartColor</t>
+        </is>
+      </c>
+      <c r="L171" s="0" t="inlineStr">
+        <is>
+          <t>cfg.Color#sep=,</t>
+        </is>
+      </c>
+      <c r="N171" s="0" t="inlineStr">
+        <is>
+          <t>Tracer起始颜色</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="J172" s="0" t="inlineStr">
+        <is>
           <t>tracerEndColor</t>
         </is>
       </c>
-      <c r="L171" s="0" t="inlineStr">
+      <c r="L172" s="0" t="inlineStr">
         <is>
           <t>cfg.Color#sep=,</t>
         </is>
       </c>
-      <c r="N171" s="0" t="inlineStr">
+      <c r="N172" s="0" t="inlineStr">
         <is>
           <t>Tracer结束颜色</t>
         </is>
       </c>
     </row>
-    <row r="172">
-      <c r="B172" s="0" t="inlineStr">
+    <row r="173">
+      <c r="B173" s="0" t="inlineStr">
         <is>
           <t>cfg.UiConfig</t>
         </is>
       </c>
-      <c r="G172" s="0" t="inlineStr">
+      <c r="G173" s="0" t="inlineStr">
         <is>
           <t>UI全局配置</t>
         </is>
       </c>
-      <c r="H172" s="0" t="inlineStr">
+      <c r="H173" s="0" t="inlineStr">
         <is>
           <t>c</t>
-        </is>
-      </c>
-    </row>
-    <row r="173">
-      <c r="J173" s="0" t="inlineStr">
-        <is>
-          <t>id</t>
-        </is>
-      </c>
-      <c r="L173" s="0" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="N173" s="0" t="inlineStr">
-        <is>
-          <t>配置ID</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="J174" s="0" t="inlineStr">
         <is>
-          <t>damageNumberPoolSize</t>
+          <t>id</t>
         </is>
       </c>
       <c r="L174" s="0" t="inlineStr">
@@ -4084,31 +4084,31 @@
       </c>
       <c r="N174" s="0" t="inlineStr">
         <is>
-          <t>伤害数字对象池大小</t>
+          <t>配置ID</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="J175" s="0" t="inlineStr">
         <is>
-          <t>damageNumberFadeDuration</t>
+          <t>damageNumberPoolSize</t>
         </is>
       </c>
       <c r="L175" s="0" t="inlineStr">
         <is>
-          <t>float</t>
+          <t>int</t>
         </is>
       </c>
       <c r="N175" s="0" t="inlineStr">
         <is>
-          <t>伤害数字渐隐时间</t>
+          <t>伤害数字对象池大小</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="J176" s="0" t="inlineStr">
         <is>
-          <t>damageNumberMoveOffset</t>
+          <t>damageNumberFadeDuration</t>
         </is>
       </c>
       <c r="L176" s="0" t="inlineStr">
@@ -4118,31 +4118,31 @@
       </c>
       <c r="N176" s="0" t="inlineStr">
         <is>
-          <t>伤害数字上浮偏移</t>
+          <t>伤害数字渐隐时间</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="J177" s="0" t="inlineStr">
         <is>
-          <t>damageNumberNormalColor</t>
+          <t>damageNumberMoveOffset</t>
         </is>
       </c>
       <c r="L177" s="0" t="inlineStr">
         <is>
-          <t>cfg.Color#sep=,</t>
+          <t>float</t>
         </is>
       </c>
       <c r="N177" s="0" t="inlineStr">
         <is>
-          <t>普通伤害数字颜色</t>
+          <t>伤害数字上浮偏移</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="J178" s="0" t="inlineStr">
         <is>
-          <t>damageNumberCriticalColor</t>
+          <t>damageNumberNormalColor</t>
         </is>
       </c>
       <c r="L178" s="0" t="inlineStr">
@@ -4152,31 +4152,31 @@
       </c>
       <c r="N178" s="0" t="inlineStr">
         <is>
-          <t>暴击伤害数字颜色</t>
+          <t>普通伤害数字颜色</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="J179" s="0" t="inlineStr">
         <is>
-          <t>damageNumberNormalFontSize</t>
+          <t>damageNumberCriticalColor</t>
         </is>
       </c>
       <c r="L179" s="0" t="inlineStr">
         <is>
-          <t>int</t>
+          <t>cfg.Color#sep=,</t>
         </is>
       </c>
       <c r="N179" s="0" t="inlineStr">
         <is>
-          <t>普通伤害数字字体大小</t>
+          <t>暴击伤害数字颜色</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="J180" s="0" t="inlineStr">
         <is>
-          <t>damageNumberCriticalFontSize</t>
+          <t>damageNumberNormalFontSize</t>
         </is>
       </c>
       <c r="L180" s="0" t="inlineStr">
@@ -4186,14 +4186,14 @@
       </c>
       <c r="N180" s="0" t="inlineStr">
         <is>
-          <t>暴击伤害数字字体大小</t>
+          <t>普通伤害数字字体大小</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="J181" s="0" t="inlineStr">
         <is>
-          <t>hitMarkerPoolSize</t>
+          <t>damageNumberCriticalFontSize</t>
         </is>
       </c>
       <c r="L181" s="0" t="inlineStr">
@@ -4203,31 +4203,31 @@
       </c>
       <c r="N181" s="0" t="inlineStr">
         <is>
-          <t>命中标记对象池大小</t>
+          <t>暴击伤害数字字体大小</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="J182" s="0" t="inlineStr">
         <is>
-          <t>hitMarkerDuration</t>
+          <t>hitMarkerPoolSize</t>
         </is>
       </c>
       <c r="L182" s="0" t="inlineStr">
         <is>
-          <t>float</t>
+          <t>int</t>
         </is>
       </c>
       <c r="N182" s="0" t="inlineStr">
         <is>
-          <t>命中标记显示时间</t>
+          <t>命中标记对象池大小</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="J183" s="0" t="inlineStr">
         <is>
-          <t>hitMarkerSize</t>
+          <t>hitMarkerDuration</t>
         </is>
       </c>
       <c r="L183" s="0" t="inlineStr">
@@ -4237,31 +4237,31 @@
       </c>
       <c r="N183" s="0" t="inlineStr">
         <is>
-          <t>命中标记大小</t>
+          <t>命中标记显示时间</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="J184" s="0" t="inlineStr">
         <is>
-          <t>hitMarkerNormalColor</t>
+          <t>hitMarkerSize</t>
         </is>
       </c>
       <c r="L184" s="0" t="inlineStr">
         <is>
-          <t>cfg.Color#sep=,</t>
+          <t>float</t>
         </is>
       </c>
       <c r="N184" s="0" t="inlineStr">
         <is>
-          <t>普通命中标记颜色</t>
+          <t>命中标记大小</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="J185" s="0" t="inlineStr">
         <is>
-          <t>hitMarkerCriticalColor</t>
+          <t>hitMarkerNormalColor</t>
         </is>
       </c>
       <c r="L185" s="0" t="inlineStr">
@@ -4271,116 +4271,116 @@
       </c>
       <c r="N185" s="0" t="inlineStr">
         <is>
-          <t>暴击命中标记颜色</t>
+          <t>普通命中标记颜色</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="J186" s="0" t="inlineStr">
         <is>
-          <t>indicatorFadeSpeed</t>
+          <t>hitMarkerCriticalColor</t>
         </is>
       </c>
       <c r="L186" s="0" t="inlineStr">
         <is>
-          <t>float</t>
+          <t>cfg.Color#sep=,</t>
         </is>
       </c>
       <c r="N186" s="0" t="inlineStr">
         <is>
-          <t>受击指示器淡出速度</t>
+          <t>暴击命中标记颜色</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="J187" s="0" t="inlineStr">
         <is>
-          <t>indicatorColor</t>
+          <t>indicatorFadeSpeed</t>
         </is>
       </c>
       <c r="L187" s="0" t="inlineStr">
         <is>
-          <t>cfg.Color#sep=,</t>
+          <t>float</t>
         </is>
       </c>
       <c r="N187" s="0" t="inlineStr">
         <is>
-          <t>受击指示器颜色</t>
+          <t>受击指示器淡出速度</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="J188" s="0" t="inlineStr">
         <is>
+          <t>indicatorColor</t>
+        </is>
+      </c>
+      <c r="L188" s="0" t="inlineStr">
+        <is>
+          <t>cfg.Color#sep=,</t>
+        </is>
+      </c>
+      <c r="N188" s="0" t="inlineStr">
+        <is>
+          <t>受击指示器颜色</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="J189" s="0" t="inlineStr">
+        <is>
           <t>loadingTextFormat</t>
         </is>
       </c>
-      <c r="L188" s="0" t="inlineStr">
+      <c r="L189" s="0" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="N188" s="0" t="inlineStr">
+      <c r="N189" s="0" t="inlineStr">
         <is>
           <t>加载进度文本格式</t>
         </is>
       </c>
     </row>
-    <row r="189">
-      <c r="B189" s="0" t="inlineStr">
+    <row r="190">
+      <c r="B190" s="0" t="inlineStr">
         <is>
           <t>cfg.Pickup</t>
         </is>
       </c>
-      <c r="G189" s="0" t="inlineStr">
+      <c r="G190" s="0" t="inlineStr">
         <is>
           <t>拾取物配置</t>
         </is>
       </c>
-      <c r="H189" s="0" t="inlineStr">
+      <c r="H190" s="0" t="inlineStr">
         <is>
           <t>c</t>
-        </is>
-      </c>
-    </row>
-    <row r="190">
-      <c r="J190" s="0" t="inlineStr">
-        <is>
-          <t>id</t>
-        </is>
-      </c>
-      <c r="L190" s="0" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="N190" s="0" t="inlineStr">
-        <is>
-          <t>配置ID</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="J191" s="0" t="inlineStr">
         <is>
-          <t>colliderRadius</t>
+          <t>id</t>
         </is>
       </c>
       <c r="L191" s="0" t="inlineStr">
         <is>
-          <t>float</t>
+          <t>int</t>
         </is>
       </c>
       <c r="N191" s="0" t="inlineStr">
         <is>
-          <t>拾取物碰撞体半径</t>
+          <t>配置ID</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="J192" s="0" t="inlineStr">
         <is>
-          <t>visualScale</t>
+          <t>colliderRadius</t>
         </is>
       </c>
       <c r="L192" s="0" t="inlineStr">
@@ -4390,82 +4390,82 @@
       </c>
       <c r="N192" s="0" t="inlineStr">
         <is>
-          <t>拾取物视觉缩放</t>
+          <t>拾取物碰撞体半径</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="J193" s="0" t="inlineStr">
         <is>
+          <t>visualScale</t>
+        </is>
+      </c>
+      <c r="L193" s="0" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="N193" s="0" t="inlineStr">
+        <is>
+          <t>拾取物视觉缩放</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="J194" s="0" t="inlineStr">
+        <is>
           <t>sortingOrder</t>
         </is>
       </c>
-      <c r="L193" s="0" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="N193" s="0" t="inlineStr">
+      <c r="L194" s="0" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="N194" s="0" t="inlineStr">
         <is>
           <t>拾取物渲染排序</t>
         </is>
       </c>
     </row>
-    <row r="194">
-      <c r="B194" s="0" t="inlineStr">
+    <row r="195">
+      <c r="B195" s="0" t="inlineStr">
         <is>
           <t>cfg.Building</t>
         </is>
       </c>
-      <c r="G194" s="0" t="inlineStr">
+      <c r="G195" s="0" t="inlineStr">
         <is>
           <t>建筑配置</t>
         </is>
       </c>
-      <c r="I194" s="0" t="inlineStr">
+      <c r="I195" s="0" t="inlineStr">
         <is>
           <t>c</t>
-        </is>
-      </c>
-    </row>
-    <row r="195">
-      <c r="J195" s="0" t="inlineStr">
-        <is>
-          <t>id</t>
-        </is>
-      </c>
-      <c r="L195" s="0" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="N195" s="0" t="inlineStr">
-        <is>
-          <t>建筑ID</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="J196" s="0" t="inlineStr">
         <is>
-          <t>name</t>
+          <t>id</t>
         </is>
       </c>
       <c r="L196" s="0" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>int</t>
         </is>
       </c>
       <c r="N196" s="0" t="inlineStr">
         <is>
-          <t>名称</t>
+          <t>建筑ID</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="J197" s="0" t="inlineStr">
         <is>
-          <t>desc</t>
+          <t>name</t>
         </is>
       </c>
       <c r="L197" s="0" t="inlineStr">
@@ -4475,65 +4475,65 @@
       </c>
       <c r="N197" s="0" t="inlineStr">
         <is>
-          <t>描述</t>
+          <t>名称</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="J198" s="0" t="inlineStr">
         <is>
-          <t>buildingType</t>
+          <t>desc</t>
         </is>
       </c>
       <c r="L198" s="0" t="inlineStr">
         <is>
-          <t>cfg.EBuildingType</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N198" s="0" t="inlineStr">
         <is>
-          <t>建筑类型</t>
+          <t>描述</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="J199" s="0" t="inlineStr">
         <is>
-          <t>icon</t>
+          <t>buildingType</t>
         </is>
       </c>
       <c r="L199" s="0" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>cfg.EBuildingType</t>
         </is>
       </c>
       <c r="N199" s="0" t="inlineStr">
         <is>
-          <t>图标</t>
+          <t>建筑类型</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="J200" s="0" t="inlineStr">
         <is>
-          <t>maxLevel</t>
+          <t>icon</t>
         </is>
       </c>
       <c r="L200" s="0" t="inlineStr">
         <is>
-          <t>int</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N200" s="0" t="inlineStr">
         <is>
-          <t>最大等级</t>
+          <t>图标</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="J201" s="0" t="inlineStr">
         <is>
-          <t>buildCostGold</t>
+          <t>maxLevel</t>
         </is>
       </c>
       <c r="L201" s="0" t="inlineStr">
@@ -4543,116 +4543,116 @@
       </c>
       <c r="N201" s="0" t="inlineStr">
         <is>
-          <t>建造金币</t>
+          <t>最大等级</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="J202" s="0" t="inlineStr">
         <is>
-          <t>buildCostItems</t>
+          <t>buildCostGold</t>
         </is>
       </c>
       <c r="L202" s="0" t="inlineStr">
         <is>
-          <t>(list#sep=;),cfg.ItemExchange#sep=,</t>
+          <t>int</t>
         </is>
       </c>
       <c r="N202" s="0" t="inlineStr">
         <is>
-          <t>建造材料</t>
+          <t>建造金币</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="J203" s="0" t="inlineStr">
         <is>
-          <t>buildTime</t>
+          <t>buildCostItems</t>
         </is>
       </c>
       <c r="L203" s="0" t="inlineStr">
         <is>
-          <t>float</t>
+          <t>(list#sep=;),cfg.ItemExchange#sep=,</t>
         </is>
       </c>
       <c r="N203" s="0" t="inlineStr">
         <is>
-          <t>建造耗时</t>
+          <t>建造材料</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="J204" s="0" t="inlineStr">
         <is>
-          <t>upgradeCostGold</t>
+          <t>buildTime</t>
         </is>
       </c>
       <c r="L204" s="0" t="inlineStr">
         <is>
-          <t>int</t>
+          <t>float</t>
         </is>
       </c>
       <c r="N204" s="0" t="inlineStr">
         <is>
-          <t>升级金币</t>
+          <t>建造耗时</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="J205" s="0" t="inlineStr">
         <is>
-          <t>upgradeCostItems</t>
+          <t>upgradeCostGold</t>
         </is>
       </c>
       <c r="L205" s="0" t="inlineStr">
         <is>
-          <t>(list#sep=;),cfg.ItemExchange#sep=,</t>
+          <t>int</t>
         </is>
       </c>
       <c r="N205" s="0" t="inlineStr">
         <is>
-          <t>升级材料</t>
+          <t>升级金币</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="J206" s="0" t="inlineStr">
         <is>
-          <t>upgradeTime</t>
+          <t>upgradeCostItems</t>
         </is>
       </c>
       <c r="L206" s="0" t="inlineStr">
         <is>
-          <t>float</t>
+          <t>(list#sep=;),cfg.ItemExchange#sep=,</t>
         </is>
       </c>
       <c r="N206" s="0" t="inlineStr">
         <is>
-          <t>升级耗时</t>
+          <t>升级材料</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="J207" s="0" t="inlineStr">
         <is>
-          <t>productionSlotCount</t>
+          <t>upgradeTime</t>
         </is>
       </c>
       <c r="L207" s="0" t="inlineStr">
         <is>
-          <t>int</t>
+          <t>float</t>
         </is>
       </c>
       <c r="N207" s="0" t="inlineStr">
         <is>
-          <t>生产槽位</t>
+          <t>升级耗时</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="J208" s="0" t="inlineStr">
         <is>
-          <t>unlockLevel</t>
+          <t>productionSlotCount</t>
         </is>
       </c>
       <c r="L208" s="0" t="inlineStr">
@@ -4662,14 +4662,14 @@
       </c>
       <c r="N208" s="0" t="inlineStr">
         <is>
-          <t>解锁等级</t>
+          <t>生产槽位</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="J209" s="0" t="inlineStr">
         <is>
-          <t>footprintX</t>
+          <t>unlockLevel</t>
         </is>
       </c>
       <c r="L209" s="0" t="inlineStr">
@@ -4679,14 +4679,14 @@
       </c>
       <c r="N209" s="0" t="inlineStr">
         <is>
-          <t>占地格数X(1m格)</t>
+          <t>解锁等级</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="J210" s="0" t="inlineStr">
         <is>
-          <t>maxCount</t>
+          <t>footprintX</t>
         </is>
       </c>
       <c r="L210" s="0" t="inlineStr">
@@ -4696,14 +4696,14 @@
       </c>
       <c r="N210" s="0" t="inlineStr">
         <is>
-          <t>数量上限-基础值(默认1)</t>
+          <t>占地格数X(1m格)</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="J211" s="0" t="inlineStr">
         <is>
-          <t>maxCountPerPlayerLevel</t>
+          <t>maxCount</t>
         </is>
       </c>
       <c r="L211" s="0" t="inlineStr">
@@ -4713,14 +4713,14 @@
       </c>
       <c r="N211" s="0" t="inlineStr">
         <is>
-          <t>数量上限-玩家等级解锁:玩家每升1级上限+N(默认0)</t>
+          <t>数量上限-基础值(默认1)</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="J212" s="0" t="inlineStr">
         <is>
-          <t>maxCountUpgradeLevel</t>
+          <t>maxCountPerPlayerLevel</t>
         </is>
       </c>
       <c r="L212" s="0" t="inlineStr">
@@ -4730,14 +4730,14 @@
       </c>
       <c r="N212" s="0" t="inlineStr">
         <is>
-          <t>数量上限-升级解锁(默认方式):同类建筑每有1座达到该等级上限+1,0=不启用</t>
+          <t>数量上限-玩家等级解锁:玩家每升1级上限+N(默认0)</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="J213" s="0" t="inlineStr">
         <is>
-          <t>maxCountSlotBaseCost</t>
+          <t>maxCountUpgradeLevel</t>
         </is>
       </c>
       <c r="L213" s="0" t="inlineStr">
@@ -4747,14 +4747,14 @@
       </c>
       <c r="N213" s="0" t="inlineStr">
         <is>
-          <t>数量上限-购买解锁:购买1个栏位的金币基础价,0=不可购买</t>
+          <t>数量上限-升级解锁(默认方式):同类建筑每有1座达到该等级上限+1,0=不启用</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="J214" s="0" t="inlineStr">
         <is>
-          <t>maxCountSlotCostGrow</t>
+          <t>maxCountSlotBaseCost</t>
         </is>
       </c>
       <c r="L214" s="0" t="inlineStr">
@@ -4764,82 +4764,82 @@
       </c>
       <c r="N214" s="0" t="inlineStr">
         <is>
-          <t>数量上限-购买解锁:每已购1个栏位价格+N(线性涨价)</t>
+          <t>数量上限-购买解锁:购买1个栏位的金币基础价,0=不可购买</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="J215" s="0" t="inlineStr">
         <is>
+          <t>maxCountSlotCostGrow</t>
+        </is>
+      </c>
+      <c r="L215" s="0" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="N215" s="0" t="inlineStr">
+        <is>
+          <t>数量上限-购买解锁:每已购1个栏位价格+N(线性涨价)</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="J216" s="0" t="inlineStr">
+        <is>
           <t>footprintZ</t>
         </is>
       </c>
-      <c r="L215" s="0" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="N215" s="0" t="inlineStr">
+      <c r="L216" s="0" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="N216" s="0" t="inlineStr">
         <is>
           <t>占地格数Z(1m格)</t>
         </is>
       </c>
     </row>
-    <row r="216">
-      <c r="B216" s="0" t="inlineStr">
+    <row r="217">
+      <c r="B217" s="0" t="inlineStr">
         <is>
           <t>cfg.Production</t>
         </is>
       </c>
-      <c r="G216" s="0" t="inlineStr">
+      <c r="G217" s="0" t="inlineStr">
         <is>
           <t>生产配方</t>
         </is>
       </c>
-      <c r="I216" s="0" t="inlineStr">
+      <c r="I217" s="0" t="inlineStr">
         <is>
           <t>c</t>
-        </is>
-      </c>
-    </row>
-    <row r="217">
-      <c r="J217" s="0" t="inlineStr">
-        <is>
-          <t>id</t>
-        </is>
-      </c>
-      <c r="L217" s="0" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="N217" s="0" t="inlineStr">
-        <is>
-          <t>配方ID</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="J218" s="0" t="inlineStr">
         <is>
-          <t>name</t>
+          <t>id</t>
         </is>
       </c>
       <c r="L218" s="0" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>int</t>
         </is>
       </c>
       <c r="N218" s="0" t="inlineStr">
         <is>
-          <t>名称</t>
+          <t>配方ID</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="J219" s="0" t="inlineStr">
         <is>
-          <t>desc</t>
+          <t>name</t>
         </is>
       </c>
       <c r="L219" s="0" t="inlineStr">
@@ -4849,31 +4849,31 @@
       </c>
       <c r="N219" s="0" t="inlineStr">
         <is>
-          <t>描述</t>
+          <t>名称</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="J220" s="0" t="inlineStr">
         <is>
-          <t>buildingId</t>
+          <t>desc</t>
         </is>
       </c>
       <c r="L220" s="0" t="inlineStr">
         <is>
-          <t>int</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N220" s="0" t="inlineStr">
         <is>
-          <t>建筑ID</t>
+          <t>描述</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="J221" s="0" t="inlineStr">
         <is>
-          <t>levelRequired</t>
+          <t>buildingId</t>
         </is>
       </c>
       <c r="L221" s="0" t="inlineStr">
@@ -4883,48 +4883,48 @@
       </c>
       <c r="N221" s="0" t="inlineStr">
         <is>
-          <t>等级要求</t>
+          <t>建筑ID</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="J222" s="0" t="inlineStr">
         <is>
-          <t>inputItems</t>
+          <t>levelRequired</t>
         </is>
       </c>
       <c r="L222" s="0" t="inlineStr">
         <is>
-          <t>(list#sep=;),cfg.ItemExchange#sep=,</t>
+          <t>int</t>
         </is>
       </c>
       <c r="N222" s="0" t="inlineStr">
         <is>
-          <t>输入材料</t>
+          <t>等级要求</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="J223" s="0" t="inlineStr">
         <is>
-          <t>outputItemId</t>
+          <t>inputItems</t>
         </is>
       </c>
       <c r="L223" s="0" t="inlineStr">
         <is>
-          <t>int</t>
+          <t>(list#sep=;),cfg.ItemExchange#sep=,</t>
         </is>
       </c>
       <c r="N223" s="0" t="inlineStr">
         <is>
-          <t>产出物品</t>
+          <t>输入材料</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="J224" s="0" t="inlineStr">
         <is>
-          <t>outputCount</t>
+          <t>outputItemId</t>
         </is>
       </c>
       <c r="L224" s="0" t="inlineStr">
@@ -4934,252 +4934,252 @@
       </c>
       <c r="N224" s="0" t="inlineStr">
         <is>
-          <t>产出数量</t>
+          <t>产出物品</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="J225" s="0" t="inlineStr">
         <is>
-          <t>productionTime</t>
+          <t>outputCount</t>
         </is>
       </c>
       <c r="L225" s="0" t="inlineStr">
         <is>
-          <t>float</t>
+          <t>int</t>
         </is>
       </c>
       <c r="N225" s="0" t="inlineStr">
         <is>
-          <t>生产耗时</t>
+          <t>产出数量</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="J226" s="0" t="inlineStr">
         <is>
+          <t>productionTime</t>
+        </is>
+      </c>
+      <c r="L226" s="0" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="N226" s="0" t="inlineStr">
+        <is>
+          <t>生产耗时</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="J227" s="0" t="inlineStr">
+        <is>
           <t>icon</t>
         </is>
       </c>
-      <c r="L226" s="0" t="inlineStr">
+      <c r="L227" s="0" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="N226" s="0" t="inlineStr">
+      <c r="N227" s="0" t="inlineStr">
         <is>
           <t>图标</t>
         </is>
       </c>
     </row>
-    <row r="227">
-      <c r="B227" s="0" t="inlineStr">
+    <row r="228">
+      <c r="B228" s="0" t="inlineStr">
         <is>
           <t>cfg.Order</t>
         </is>
       </c>
-      <c r="G227" s="0" t="inlineStr">
+      <c r="G228" s="0" t="inlineStr">
         <is>
           <t>订单配置</t>
         </is>
       </c>
-      <c r="I227" s="0" t="inlineStr">
+      <c r="I228" s="0" t="inlineStr">
         <is>
           <t>c</t>
-        </is>
-      </c>
-    </row>
-    <row r="228">
-      <c r="J228" s="0" t="inlineStr">
-        <is>
-          <t>id</t>
-        </is>
-      </c>
-      <c r="L228" s="0" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="N228" s="0" t="inlineStr">
-        <is>
-          <t>订单ID</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="J229" s="0" t="inlineStr">
         <is>
-          <t>requiredItems</t>
+          <t>id</t>
         </is>
       </c>
       <c r="L229" s="0" t="inlineStr">
         <is>
-          <t>(list#sep=;),cfg.ItemExchange#sep=,</t>
+          <t>int</t>
         </is>
       </c>
       <c r="N229" s="0" t="inlineStr">
         <is>
-          <t>需求物品</t>
+          <t>订单ID</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="J230" s="0" t="inlineStr">
         <is>
-          <t>rewardGold</t>
+          <t>requiredItems</t>
         </is>
       </c>
       <c r="L230" s="0" t="inlineStr">
         <is>
-          <t>int</t>
+          <t>(list#sep=;),cfg.ItemExchange#sep=,</t>
         </is>
       </c>
       <c r="N230" s="0" t="inlineStr">
         <is>
-          <t>奖励金币</t>
+          <t>需求物品</t>
         </is>
       </c>
     </row>
     <row r="231">
       <c r="J231" s="0" t="inlineStr">
         <is>
-          <t>rewardItems</t>
+          <t>rewardGold</t>
         </is>
       </c>
       <c r="L231" s="0" t="inlineStr">
         <is>
-          <t>(list#sep=;),cfg.ItemExchange#sep=,</t>
+          <t>int</t>
         </is>
       </c>
       <c r="N231" s="0" t="inlineStr">
         <is>
-          <t>奖励物品</t>
+          <t>奖励金币</t>
         </is>
       </c>
     </row>
     <row r="232">
       <c r="J232" s="0" t="inlineStr">
         <is>
-          <t>rewardExp</t>
+          <t>rewardItems</t>
         </is>
       </c>
       <c r="L232" s="0" t="inlineStr">
         <is>
-          <t>int</t>
+          <t>(list#sep=;),cfg.ItemExchange#sep=,</t>
         </is>
       </c>
       <c r="N232" s="0" t="inlineStr">
         <is>
-          <t>奖励经验</t>
+          <t>奖励物品</t>
         </is>
       </c>
     </row>
     <row r="233">
       <c r="J233" s="0" t="inlineStr">
         <is>
-          <t>timeLimit</t>
+          <t>rewardExp</t>
         </is>
       </c>
       <c r="L233" s="0" t="inlineStr">
         <is>
-          <t>float</t>
+          <t>int</t>
         </is>
       </c>
       <c r="N233" s="0" t="inlineStr">
         <is>
-          <t>时限</t>
+          <t>奖励经验</t>
         </is>
       </c>
     </row>
     <row r="234">
       <c r="J234" s="0" t="inlineStr">
         <is>
-          <t>weight</t>
+          <t>timeLimit</t>
         </is>
       </c>
       <c r="L234" s="0" t="inlineStr">
         <is>
-          <t>int</t>
+          <t>float</t>
         </is>
       </c>
       <c r="N234" s="0" t="inlineStr">
         <is>
-          <t>权重</t>
+          <t>时限</t>
         </is>
       </c>
     </row>
     <row r="235">
       <c r="J235" s="0" t="inlineStr">
         <is>
+          <t>weight</t>
+        </is>
+      </c>
+      <c r="L235" s="0" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="N235" s="0" t="inlineStr">
+        <is>
+          <t>权重</t>
+        </is>
+      </c>
+    </row>
+    <row r="236">
+      <c r="J236" s="0" t="inlineStr">
+        <is>
           <t>minPlayerLevel</t>
         </is>
       </c>
-      <c r="L235" s="0" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="N235" s="0" t="inlineStr">
+      <c r="L236" s="0" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="N236" s="0" t="inlineStr">
         <is>
           <t>最低等级</t>
         </is>
       </c>
     </row>
-    <row r="236">
-      <c r="B236" s="0" t="inlineStr">
+    <row r="237">
+      <c r="B237" s="0" t="inlineStr">
         <is>
           <t>cfg.SimTimeConfig</t>
         </is>
       </c>
-      <c r="G236" s="0" t="inlineStr">
+      <c r="G237" s="0" t="inlineStr">
         <is>
           <t>经营时间配置</t>
         </is>
       </c>
-      <c r="I236" s="0" t="inlineStr">
+      <c r="I237" s="0" t="inlineStr">
         <is>
           <t>c</t>
-        </is>
-      </c>
-    </row>
-    <row r="237">
-      <c r="J237" s="0" t="inlineStr">
-        <is>
-          <t>id</t>
-        </is>
-      </c>
-      <c r="L237" s="0" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="N237" s="0" t="inlineStr">
-        <is>
-          <t>ID</t>
         </is>
       </c>
     </row>
     <row r="238">
       <c r="J238" s="0" t="inlineStr">
         <is>
-          <t>baseSpeed</t>
+          <t>id</t>
         </is>
       </c>
       <c r="L238" s="0" t="inlineStr">
         <is>
-          <t>float</t>
+          <t>int</t>
         </is>
       </c>
       <c r="N238" s="0" t="inlineStr">
         <is>
-          <t>基础速度</t>
+          <t>ID</t>
         </is>
       </c>
     </row>
     <row r="239">
       <c r="J239" s="0" t="inlineStr">
         <is>
-          <t>fastSpeed</t>
+          <t>baseSpeed</t>
         </is>
       </c>
       <c r="L239" s="0" t="inlineStr">
@@ -5189,14 +5189,14 @@
       </c>
       <c r="N239" s="0" t="inlineStr">
         <is>
-          <t>加速速度</t>
+          <t>基础速度</t>
         </is>
       </c>
     </row>
     <row r="240">
       <c r="J240" s="0" t="inlineStr">
         <is>
-          <t>maxSpeed</t>
+          <t>fastSpeed</t>
         </is>
       </c>
       <c r="L240" s="0" t="inlineStr">
@@ -5206,14 +5206,14 @@
       </c>
       <c r="N240" s="0" t="inlineStr">
         <is>
-          <t>最大速度</t>
+          <t>加速速度</t>
         </is>
       </c>
     </row>
     <row r="241">
       <c r="J241" s="0" t="inlineStr">
         <is>
-          <t>orderRefreshInterval</t>
+          <t>maxSpeed</t>
         </is>
       </c>
       <c r="L241" s="0" t="inlineStr">
@@ -5223,82 +5223,82 @@
       </c>
       <c r="N241" s="0" t="inlineStr">
         <is>
-          <t>订单刷新间隔</t>
+          <t>最大速度</t>
         </is>
       </c>
     </row>
     <row r="242">
       <c r="J242" s="0" t="inlineStr">
         <is>
+          <t>orderRefreshInterval</t>
+        </is>
+      </c>
+      <c r="L242" s="0" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="N242" s="0" t="inlineStr">
+        <is>
+          <t>订单刷新间隔</t>
+        </is>
+      </c>
+    </row>
+    <row r="243">
+      <c r="J243" s="0" t="inlineStr">
+        <is>
           <t>maxOrderCount</t>
         </is>
       </c>
-      <c r="L242" s="0" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="N242" s="0" t="inlineStr">
+      <c r="L243" s="0" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="N243" s="0" t="inlineStr">
         <is>
           <t>最大订单数</t>
         </is>
       </c>
     </row>
-    <row r="243">
-      <c r="B243" s="0" t="inlineStr">
+    <row r="244">
+      <c r="B244" s="0" t="inlineStr">
         <is>
           <t>cfg.Camera3D</t>
         </is>
       </c>
-      <c r="G243" s="0" t="inlineStr">
+      <c r="G244" s="0" t="inlineStr">
         <is>
           <t>3D摄像机配置</t>
         </is>
       </c>
-      <c r="I243" s="0" t="inlineStr">
+      <c r="I244" s="0" t="inlineStr">
         <is>
           <t>c</t>
-        </is>
-      </c>
-    </row>
-    <row r="244">
-      <c r="J244" s="0" t="inlineStr">
-        <is>
-          <t>id</t>
-        </is>
-      </c>
-      <c r="L244" s="0" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="N244" s="0" t="inlineStr">
-        <is>
-          <t>配置ID</t>
         </is>
       </c>
     </row>
     <row r="245">
       <c r="J245" s="0" t="inlineStr">
         <is>
-          <t>pitchAngle</t>
+          <t>id</t>
         </is>
       </c>
       <c r="L245" s="0" t="inlineStr">
         <is>
-          <t>float</t>
+          <t>int</t>
         </is>
       </c>
       <c r="N245" s="0" t="inlineStr">
         <is>
-          <t>俯视角度</t>
+          <t>配置ID</t>
         </is>
       </c>
     </row>
     <row r="246">
       <c r="J246" s="0" t="inlineStr">
         <is>
-          <t>initialHeight</t>
+          <t>pitchAngle</t>
         </is>
       </c>
       <c r="L246" s="0" t="inlineStr">
@@ -5308,14 +5308,14 @@
       </c>
       <c r="N246" s="0" t="inlineStr">
         <is>
-          <t>初始高度</t>
+          <t>俯视角度</t>
         </is>
       </c>
     </row>
     <row r="247">
       <c r="J247" s="0" t="inlineStr">
         <is>
-          <t>initialDistance</t>
+          <t>initialHeight</t>
         </is>
       </c>
       <c r="L247" s="0" t="inlineStr">
@@ -5325,14 +5325,14 @@
       </c>
       <c r="N247" s="0" t="inlineStr">
         <is>
-          <t>初始距离</t>
+          <t>初始高度</t>
         </is>
       </c>
     </row>
     <row r="248">
       <c r="J248" s="0" t="inlineStr">
         <is>
-          <t>fov</t>
+          <t>initialDistance</t>
         </is>
       </c>
       <c r="L248" s="0" t="inlineStr">
@@ -5342,14 +5342,14 @@
       </c>
       <c r="N248" s="0" t="inlineStr">
         <is>
-          <t>视场角</t>
+          <t>初始距离</t>
         </is>
       </c>
     </row>
     <row r="249">
       <c r="J249" s="0" t="inlineStr">
         <is>
-          <t>minZoom</t>
+          <t>fov</t>
         </is>
       </c>
       <c r="L249" s="0" t="inlineStr">
@@ -5359,14 +5359,14 @@
       </c>
       <c r="N249" s="0" t="inlineStr">
         <is>
-          <t>最小缩放</t>
+          <t>视场角</t>
         </is>
       </c>
     </row>
     <row r="250">
       <c r="J250" s="0" t="inlineStr">
         <is>
-          <t>maxZoom</t>
+          <t>minZoom</t>
         </is>
       </c>
       <c r="L250" s="0" t="inlineStr">
@@ -5376,14 +5376,14 @@
       </c>
       <c r="N250" s="0" t="inlineStr">
         <is>
-          <t>最大缩放</t>
+          <t>最小缩放</t>
         </is>
       </c>
     </row>
     <row r="251">
       <c r="J251" s="0" t="inlineStr">
         <is>
-          <t>moveSpeed</t>
+          <t>maxZoom</t>
         </is>
       </c>
       <c r="L251" s="0" t="inlineStr">
@@ -5393,14 +5393,14 @@
       </c>
       <c r="N251" s="0" t="inlineStr">
         <is>
-          <t>移动速度</t>
+          <t>最大缩放</t>
         </is>
       </c>
     </row>
     <row r="252">
       <c r="J252" s="0" t="inlineStr">
         <is>
-          <t>zoomSpeed</t>
+          <t>moveSpeed</t>
         </is>
       </c>
       <c r="L252" s="0" t="inlineStr">
@@ -5410,14 +5410,14 @@
       </c>
       <c r="N252" s="0" t="inlineStr">
         <is>
-          <t>缩放速度</t>
+          <t>移动速度</t>
         </is>
       </c>
     </row>
     <row r="253">
       <c r="J253" s="0" t="inlineStr">
         <is>
-          <t>maxRotationAngle</t>
+          <t>zoomSpeed</t>
         </is>
       </c>
       <c r="L253" s="0" t="inlineStr">
@@ -5427,14 +5427,14 @@
       </c>
       <c r="N253" s="0" t="inlineStr">
         <is>
-          <t>最大旋转角度</t>
+          <t>缩放速度</t>
         </is>
       </c>
     </row>
     <row r="254">
       <c r="J254" s="0" t="inlineStr">
         <is>
-          <t>rotationSpeed</t>
+          <t>maxRotationAngle</t>
         </is>
       </c>
       <c r="L254" s="0" t="inlineStr">
@@ -5444,61 +5444,65 @@
       </c>
       <c r="N254" s="0" t="inlineStr">
         <is>
-          <t>旋转速度</t>
+          <t>最大旋转角度</t>
         </is>
       </c>
     </row>
     <row r="255">
       <c r="J255" s="0" t="inlineStr">
         <is>
+          <t>rotationSpeed</t>
+        </is>
+      </c>
+      <c r="L255" s="0" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="N255" s="0" t="inlineStr">
+        <is>
+          <t>旋转速度</t>
+        </is>
+      </c>
+    </row>
+    <row r="256">
+      <c r="J256" s="0" t="inlineStr">
+        <is>
           <t>followSmoothTime</t>
         </is>
       </c>
-      <c r="L255" s="0" t="inlineStr">
-        <is>
-          <t>float</t>
-        </is>
-      </c>
-      <c r="N255" s="0" t="inlineStr">
+      <c r="L256" s="0" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="N256" s="0" t="inlineStr">
         <is>
           <t>跟随平滑时间</t>
         </is>
       </c>
     </row>
-    <row r="256"/>
-    <row r="257">
-      <c r="B257" s="0" t="inlineStr">
+    <row r="258">
+      <c r="B258" s="0" t="inlineStr">
         <is>
           <t>cfg.LootContainer</t>
         </is>
       </c>
-      <c r="G257" s="0" t="inlineStr">
+      <c r="G258" s="0" t="inlineStr">
         <is>
           <t>容器掉落记录</t>
         </is>
       </c>
-      <c r="I257" s="0" t="inlineStr">
+      <c r="I258" s="0" t="inlineStr">
         <is>
           <t>c</t>
-        </is>
-      </c>
-    </row>
-    <row r="258">
-      <c r="J258" s="0" t="inlineStr">
-        <is>
-          <t>id</t>
-        </is>
-      </c>
-      <c r="L258" s="0" t="inlineStr">
-        <is>
-          <t>int</t>
         </is>
       </c>
     </row>
     <row r="259">
       <c r="J259" s="0" t="inlineStr">
         <is>
-          <t>containerId</t>
+          <t>id</t>
         </is>
       </c>
       <c r="L259" s="0" t="inlineStr">
@@ -5510,7 +5514,7 @@
     <row r="260">
       <c r="J260" s="0" t="inlineStr">
         <is>
-          <t>itemId</t>
+          <t>containerId</t>
         </is>
       </c>
       <c r="L260" s="0" t="inlineStr">
@@ -5522,7 +5526,7 @@
     <row r="261">
       <c r="J261" s="0" t="inlineStr">
         <is>
-          <t>weight</t>
+          <t>itemId</t>
         </is>
       </c>
       <c r="L261" s="0" t="inlineStr">
@@ -5534,7 +5538,7 @@
     <row r="262">
       <c r="J262" s="0" t="inlineStr">
         <is>
-          <t>minCount</t>
+          <t>weight</t>
         </is>
       </c>
       <c r="L262" s="0" t="inlineStr">
@@ -5546,208 +5550,202 @@
     <row r="263">
       <c r="J263" s="0" t="inlineStr">
         <is>
+          <t>minCount</t>
+        </is>
+      </c>
+      <c r="L263" s="0" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+    </row>
+    <row r="264">
+      <c r="J264" s="0" t="inlineStr">
+        <is>
           <t>maxCount</t>
         </is>
       </c>
-      <c r="L263" s="0" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-    </row>
-    <row r="264"/>
-    <row r="265">
-      <c r="B265" s="0" t="inlineStr">
+      <c r="L264" s="0" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+    </row>
+    <row r="266">
+      <c r="B266" s="0" t="inlineStr">
         <is>
           <t>cfg.Note</t>
         </is>
       </c>
-      <c r="G265" s="0" t="inlineStr">
+      <c r="G266" s="0" t="inlineStr">
         <is>
           <t>小纸条记录</t>
         </is>
       </c>
-      <c r="I265" s="0" t="inlineStr">
+      <c r="I266" s="0" t="inlineStr">
         <is>
           <t>c</t>
-        </is>
-      </c>
-    </row>
-    <row r="266">
-      <c r="J266" s="0" t="inlineStr">
-        <is>
-          <t>id</t>
-        </is>
-      </c>
-      <c r="L266" s="0" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="N266" s="0" t="inlineStr">
-        <is>
-          <t>纸条ID</t>
         </is>
       </c>
     </row>
     <row r="267">
       <c r="J267" s="0" t="inlineStr">
         <is>
-          <t>title</t>
+          <t>id</t>
         </is>
       </c>
       <c r="L267" s="0" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>int</t>
         </is>
       </c>
       <c r="N267" s="0" t="inlineStr">
         <is>
-          <t>标题</t>
+          <t>纸条ID</t>
         </is>
       </c>
     </row>
     <row r="268">
       <c r="J268" s="0" t="inlineStr">
         <is>
+          <t>title</t>
+        </is>
+      </c>
+      <c r="L268" s="0" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="N268" s="0" t="inlineStr">
+        <is>
+          <t>标题</t>
+        </is>
+      </c>
+    </row>
+    <row r="269">
+      <c r="J269" s="0" t="inlineStr">
+        <is>
           <t>content</t>
         </is>
       </c>
-      <c r="L268" s="0" t="inlineStr">
+      <c r="L269" s="0" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="N268" s="0" t="inlineStr">
+      <c r="N269" s="0" t="inlineStr">
         <is>
           <t>正文(支持
 换行)</t>
         </is>
       </c>
     </row>
-    <row r="269">
-      <c r="B269" s="0" t="inlineStr">
+    <row r="270">
+      <c r="B270" s="0" t="inlineStr">
         <is>
           <t>cfg.PlayerLevel</t>
         </is>
       </c>
-      <c r="G269" s="0" t="inlineStr">
+      <c r="G270" s="0" t="inlineStr">
         <is>
           <t>玩家等级经验表</t>
         </is>
       </c>
-      <c r="I269" s="0" t="inlineStr">
+      <c r="I270" s="0" t="inlineStr">
         <is>
           <t>c</t>
-        </is>
-      </c>
-    </row>
-    <row r="270">
-      <c r="J270" s="0" t="inlineStr">
-        <is>
-          <t>level</t>
-        </is>
-      </c>
-      <c r="L270" s="0" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="N270" s="0" t="inlineStr">
-        <is>
-          <t>等级</t>
         </is>
       </c>
     </row>
     <row r="271">
       <c r="J271" s="0" t="inlineStr">
         <is>
+          <t>level</t>
+        </is>
+      </c>
+      <c r="L271" s="0" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="N271" s="0" t="inlineStr">
+        <is>
+          <t>等级</t>
+        </is>
+      </c>
+    </row>
+    <row r="272">
+      <c r="J272" s="0" t="inlineStr">
+        <is>
           <t>expToNext</t>
         </is>
       </c>
-      <c r="L271" s="0" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="N271" s="0" t="inlineStr">
+      <c r="L272" s="0" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="N272" s="0" t="inlineStr">
         <is>
           <t>升到下一级所需经验</t>
         </is>
       </c>
     </row>
-    <row r="272">
-      <c r="B272" s="0" t="inlineStr">
+    <row r="273">
+      <c r="B273" s="0" t="inlineStr">
         <is>
           <t>cfg.Unlock</t>
         </is>
       </c>
-      <c r="G272" s="0" t="inlineStr">
+      <c r="G273" s="0" t="inlineStr">
         <is>
           <t>内容解锁表</t>
         </is>
       </c>
-      <c r="I272" s="0" t="inlineStr">
+      <c r="I273" s="0" t="inlineStr">
         <is>
           <t>c</t>
-        </is>
-      </c>
-    </row>
-    <row r="273">
-      <c r="J273" s="0" t="inlineStr">
-        <is>
-          <t>id</t>
-        </is>
-      </c>
-      <c r="L273" s="0" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="N273" s="0" t="inlineStr">
-        <is>
-          <t>解锁ID</t>
         </is>
       </c>
     </row>
     <row r="274">
       <c r="J274" s="0" t="inlineStr">
         <is>
-          <t>contentType</t>
+          <t>id</t>
         </is>
       </c>
       <c r="L274" s="0" t="inlineStr">
         <is>
-          <t>cfg.UnlockContentType</t>
+          <t>int</t>
         </is>
       </c>
       <c r="N274" s="0" t="inlineStr">
         <is>
-          <t>内容类型</t>
+          <t>解锁ID</t>
         </is>
       </c>
     </row>
     <row r="275">
       <c r="J275" s="0" t="inlineStr">
         <is>
-          <t>targetId</t>
+          <t>contentType</t>
         </is>
       </c>
       <c r="L275" s="0" t="inlineStr">
         <is>
-          <t>int</t>
+          <t>cfg.UnlockContentType</t>
         </is>
       </c>
       <c r="N275" s="0" t="inlineStr">
         <is>
-          <t>目标ID（关卡/武器）</t>
+          <t>内容类型</t>
         </is>
       </c>
     </row>
     <row r="276">
       <c r="J276" s="0" t="inlineStr">
         <is>
-          <t>requirePlayerLevel</t>
+          <t>targetId</t>
         </is>
       </c>
       <c r="L276" s="0" t="inlineStr">
@@ -5757,14 +5755,14 @@
       </c>
       <c r="N276" s="0" t="inlineStr">
         <is>
-          <t>要求玩家等级(0=无)</t>
+          <t>目标ID（关卡/武器）</t>
         </is>
       </c>
     </row>
     <row r="277">
       <c r="J277" s="0" t="inlineStr">
         <is>
-          <t>requireCompleteLevelId</t>
+          <t>requirePlayerLevel</t>
         </is>
       </c>
       <c r="L277" s="0" t="inlineStr">
@@ -5774,14 +5772,14 @@
       </c>
       <c r="N277" s="0" t="inlineStr">
         <is>
-          <t>要求通关关卡ID(0=无)</t>
+          <t>要求玩家等级(0=无)</t>
         </is>
       </c>
     </row>
     <row r="278">
       <c r="J278" s="0" t="inlineStr">
         <is>
-          <t>costGold</t>
+          <t>requireCompleteLevelId</t>
         </is>
       </c>
       <c r="L278" s="0" t="inlineStr">
@@ -5791,286 +5789,286 @@
       </c>
       <c r="N278" s="0" t="inlineStr">
         <is>
-          <t>解锁花费金币(0=免费)</t>
+          <t>要求通关关卡ID(0=无)</t>
         </is>
       </c>
     </row>
     <row r="279">
       <c r="J279" s="0" t="inlineStr">
         <is>
+          <t>costGold</t>
+        </is>
+      </c>
+      <c r="L279" s="0" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="N279" s="0" t="inlineStr">
+        <is>
+          <t>解锁花费金币(0=免费)</t>
+        </is>
+      </c>
+    </row>
+    <row r="280">
+      <c r="J280" s="0" t="inlineStr">
+        <is>
           <t>comment</t>
         </is>
       </c>
-      <c r="L279" s="0" t="inlineStr">
+      <c r="L280" s="0" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="N279" s="0" t="inlineStr">
+      <c r="N280" s="0" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="280">
-      <c r="B280" s="0" t="inlineStr">
+    <row r="281">
+      <c r="B281" s="0" t="inlineStr">
         <is>
           <t>cfg.Npc</t>
         </is>
       </c>
-      <c r="G280" s="0" t="inlineStr">
+      <c r="G281" s="0" t="inlineStr">
         <is>
           <t>NPC记录</t>
         </is>
       </c>
-      <c r="I280" s="0" t="inlineStr">
+      <c r="I281" s="0" t="inlineStr">
         <is>
           <t>c</t>
-        </is>
-      </c>
-    </row>
-    <row r="281">
-      <c r="J281" s="0" t="inlineStr">
-        <is>
-          <t>id</t>
-        </is>
-      </c>
-      <c r="L281" s="0" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="N281" s="0" t="inlineStr">
-        <is>
-          <t>NPC ID</t>
         </is>
       </c>
     </row>
     <row r="282">
       <c r="J282" s="0" t="inlineStr">
         <is>
-          <t>name</t>
+          <t>id</t>
         </is>
       </c>
       <c r="L282" s="0" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>int</t>
         </is>
       </c>
       <c r="N282" s="0" t="inlineStr">
         <is>
-          <t>显示名</t>
+          <t>NPC ID</t>
         </is>
       </c>
     </row>
     <row r="283">
       <c r="J283" s="0" t="inlineStr">
         <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="L283" s="0" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="N283" s="0" t="inlineStr">
+        <is>
+          <t>显示名</t>
+        </is>
+      </c>
+    </row>
+    <row r="284">
+      <c r="J284" s="0" t="inlineStr">
+        <is>
           <t>role</t>
         </is>
       </c>
-      <c r="L283" s="0" t="inlineStr">
+      <c r="L284" s="0" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="N283" s="0" t="inlineStr">
+      <c r="N284" s="0" t="inlineStr">
         <is>
           <t>身份/职业</t>
         </is>
       </c>
     </row>
-    <row r="284">
-      <c r="J284" t="inlineStr">
+    <row r="285">
+      <c r="J285" s="0" t="inlineStr">
         <is>
           <t>moveSpeed</t>
         </is>
       </c>
-      <c r="L284" t="inlineStr">
-        <is>
-          <t>float</t>
-        </is>
-      </c>
-      <c r="N284" t="inlineStr">
+      <c r="L285" s="0" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="N285" s="0" t="inlineStr">
         <is>
           <t>移动速度(0=站桩)</t>
-        </is>
-      </c>
-    </row>
-    <row r="285">
-      <c r="J285" t="inlineStr">
-        <is>
-          <t>patrolPath</t>
-        </is>
-      </c>
-      <c r="L285" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="N285" t="inlineStr">
-        <is>
-          <t>巡逻路径(x,z|x,z 空=不巡逻)</t>
         </is>
       </c>
     </row>
     <row r="286">
       <c r="J286" s="0" t="inlineStr">
         <is>
+          <t>patrolPath</t>
+        </is>
+      </c>
+      <c r="L286" s="0" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="N286" s="0" t="inlineStr">
+        <is>
+          <t>巡逻路径(x,z|x,z 空=不巡逻)</t>
+        </is>
+      </c>
+    </row>
+    <row r="287">
+      <c r="J287" s="0" t="inlineStr">
+        <is>
           <t>dialogueId</t>
         </is>
       </c>
-      <c r="L286" s="0" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="N286" s="0" t="inlineStr">
+      <c r="L287" s="0" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="N287" s="0" t="inlineStr">
         <is>
           <t>对话ID(预留,0=无)</t>
         </is>
       </c>
     </row>
-    <row r="287">
-      <c r="B287" s="0" t="inlineStr">
+    <row r="288">
+      <c r="B288" s="0" t="inlineStr">
         <is>
           <t>cfg.Dialogue</t>
         </is>
       </c>
-      <c r="G287" s="0" t="inlineStr">
+      <c r="G288" s="0" t="inlineStr">
         <is>
           <t>对话头</t>
         </is>
       </c>
-      <c r="I287" s="0" t="inlineStr">
+      <c r="I288" s="0" t="inlineStr">
         <is>
           <t>c</t>
-        </is>
-      </c>
-    </row>
-    <row r="288">
-      <c r="J288" s="0" t="inlineStr">
-        <is>
-          <t>id</t>
-        </is>
-      </c>
-      <c r="L288" s="0" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="N288" s="0" t="inlineStr">
-        <is>
-          <t>对话ID</t>
         </is>
       </c>
     </row>
     <row r="289">
       <c r="J289" s="0" t="inlineStr">
         <is>
-          <t>name</t>
+          <t>id</t>
         </is>
       </c>
       <c r="L289" s="0" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>int</t>
         </is>
       </c>
       <c r="N289" s="0" t="inlineStr">
         <is>
-          <t>注释名(不显示)</t>
+          <t>对话ID</t>
         </is>
       </c>
     </row>
     <row r="290">
       <c r="J290" s="0" t="inlineStr">
         <is>
-          <t>startNode</t>
+          <t>name</t>
         </is>
       </c>
       <c r="L290" s="0" t="inlineStr">
         <is>
-          <t>int</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N290" s="0" t="inlineStr">
         <is>
-          <t>起始节点ID</t>
+          <t>注释名(不显示)</t>
         </is>
       </c>
     </row>
     <row r="291">
       <c r="J291" s="0" t="inlineStr">
         <is>
-          <t>onceOnly</t>
+          <t>startNode</t>
         </is>
       </c>
       <c r="L291" s="0" t="inlineStr">
         <is>
-          <t>bool</t>
+          <t>int</t>
         </is>
       </c>
       <c r="N291" s="0" t="inlineStr">
         <is>
-          <t>只触发一次</t>
+          <t>起始节点ID</t>
         </is>
       </c>
     </row>
     <row r="292">
       <c r="J292" s="0" t="inlineStr">
         <is>
+          <t>onceOnly</t>
+        </is>
+      </c>
+      <c r="L292" s="0" t="inlineStr">
+        <is>
+          <t>bool</t>
+        </is>
+      </c>
+      <c r="N292" s="0" t="inlineStr">
+        <is>
+          <t>只触发一次</t>
+        </is>
+      </c>
+    </row>
+    <row r="293">
+      <c r="J293" s="0" t="inlineStr">
+        <is>
           <t>priority</t>
         </is>
       </c>
-      <c r="L292" s="0" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="N292" s="0" t="inlineStr">
+      <c r="L293" s="0" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="N293" s="0" t="inlineStr">
         <is>
           <t>优先级(大优先)</t>
         </is>
       </c>
     </row>
-    <row r="293">
-      <c r="B293" s="0" t="inlineStr">
+    <row r="294">
+      <c r="B294" s="0" t="inlineStr">
         <is>
           <t>cfg.DialogueNode</t>
         </is>
       </c>
-      <c r="G293" s="0" t="inlineStr">
+      <c r="G294" s="0" t="inlineStr">
         <is>
           <t>对话节点</t>
         </is>
       </c>
-      <c r="I293" s="0" t="inlineStr">
+      <c r="I294" s="0" t="inlineStr">
         <is>
           <t>c</t>
-        </is>
-      </c>
-    </row>
-    <row r="294">
-      <c r="J294" s="0" t="inlineStr">
-        <is>
-          <t>id</t>
-        </is>
-      </c>
-      <c r="L294" s="0" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="N294" s="0" t="inlineStr">
-        <is>
-          <t>节点ID</t>
         </is>
       </c>
     </row>
     <row r="295">
       <c r="J295" s="0" t="inlineStr">
         <is>
-          <t>dialogueId</t>
+          <t>id</t>
         </is>
       </c>
       <c r="L295" s="0" t="inlineStr">
@@ -6080,31 +6078,31 @@
       </c>
       <c r="N295" s="0" t="inlineStr">
         <is>
-          <t>所属对话</t>
+          <t>节点ID</t>
         </is>
       </c>
     </row>
     <row r="296">
       <c r="J296" s="0" t="inlineStr">
         <is>
-          <t>type</t>
+          <t>dialogueId</t>
         </is>
       </c>
       <c r="L296" s="0" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>int</t>
         </is>
       </c>
       <c r="N296" s="0" t="inlineStr">
         <is>
-          <t>类型(line/choice/setflag/end)</t>
+          <t>所属对话</t>
         </is>
       </c>
     </row>
     <row r="297">
       <c r="J297" s="0" t="inlineStr">
         <is>
-          <t>speaker</t>
+          <t>type</t>
         </is>
       </c>
       <c r="L297" s="0" t="inlineStr">
@@ -6114,14 +6112,14 @@
       </c>
       <c r="N297" s="0" t="inlineStr">
         <is>
-          <t>说话人</t>
+          <t>类型(line/choice/setflag/end)</t>
         </is>
       </c>
     </row>
     <row r="298">
       <c r="J298" s="0" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>speaker</t>
         </is>
       </c>
       <c r="L298" s="0" t="inlineStr">
@@ -6131,14 +6129,14 @@
       </c>
       <c r="N298" s="0" t="inlineStr">
         <is>
-          <t>正文</t>
+          <t>说话人</t>
         </is>
       </c>
     </row>
     <row r="299">
       <c r="J299" s="0" t="inlineStr">
         <is>
-          <t>choices</t>
+          <t>text</t>
         </is>
       </c>
       <c r="L299" s="0" t="inlineStr">
@@ -6148,14 +6146,14 @@
       </c>
       <c r="N299" s="0" t="inlineStr">
         <is>
-          <t>选项(文本-&gt;节点|...)</t>
+          <t>正文</t>
         </is>
       </c>
     </row>
     <row r="300">
       <c r="J300" s="0" t="inlineStr">
         <is>
-          <t>condition</t>
+          <t>choices</t>
         </is>
       </c>
       <c r="L300" s="0" t="inlineStr">
@@ -6165,14 +6163,14 @@
       </c>
       <c r="N300" s="0" t="inlineStr">
         <is>
-          <t>进入条件</t>
+          <t>选项(文本-&gt;节点|...)</t>
         </is>
       </c>
     </row>
     <row r="301">
       <c r="J301" s="0" t="inlineStr">
         <is>
-          <t>action</t>
+          <t>condition</t>
         </is>
       </c>
       <c r="L301" s="0" t="inlineStr">
@@ -6182,24 +6180,296 @@
       </c>
       <c r="N301" s="0" t="inlineStr">
         <is>
-          <t>到达动作</t>
+          <t>进入条件</t>
         </is>
       </c>
     </row>
     <row r="302">
       <c r="J302" s="0" t="inlineStr">
         <is>
+          <t>action</t>
+        </is>
+      </c>
+      <c r="L302" s="0" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="N302" s="0" t="inlineStr">
+        <is>
+          <t>到达动作</t>
+        </is>
+      </c>
+    </row>
+    <row r="303">
+      <c r="J303" s="0" t="inlineStr">
+        <is>
           <t>next</t>
         </is>
       </c>
-      <c r="L302" s="0" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="N302" s="0" t="inlineStr">
+      <c r="L303" s="0" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="N303" s="0" t="inlineStr">
         <is>
           <t>下一节点(0=结束)</t>
+        </is>
+      </c>
+    </row>
+    <row r="304">
+      <c r="B304" t="inlineStr">
+        <is>
+          <t>cfg.Quest</t>
+        </is>
+      </c>
+      <c r="G304" t="inlineStr">
+        <is>
+          <t>任务定义</t>
+        </is>
+      </c>
+      <c r="I304" t="inlineStr">
+        <is>
+          <t>c</t>
+        </is>
+      </c>
+    </row>
+    <row r="305">
+      <c r="J305" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="L305" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="N305" t="inlineStr">
+        <is>
+          <t>任务ID</t>
+        </is>
+      </c>
+    </row>
+    <row r="306">
+      <c r="J306" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="L306" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="N306" t="inlineStr">
+        <is>
+          <t>显示名</t>
+        </is>
+      </c>
+    </row>
+    <row r="307">
+      <c r="J307" t="inlineStr">
+        <is>
+          <t>desc</t>
+        </is>
+      </c>
+      <c r="L307" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="N307" t="inlineStr">
+        <is>
+          <t>描述</t>
+        </is>
+      </c>
+    </row>
+    <row r="308">
+      <c r="J308" t="inlineStr">
+        <is>
+          <t>giverNpc</t>
+        </is>
+      </c>
+      <c r="L308" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="N308" t="inlineStr">
+        <is>
+          <t>发布NPC(0=任务板)</t>
+        </is>
+      </c>
+    </row>
+    <row r="309">
+      <c r="J309" t="inlineStr">
+        <is>
+          <t>prereq</t>
+        </is>
+      </c>
+      <c r="L309" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="N309" t="inlineStr">
+        <is>
+          <t>接取条件表达式(空=无)</t>
+        </is>
+      </c>
+    </row>
+    <row r="310">
+      <c r="J310" t="inlineStr">
+        <is>
+          <t>rewards</t>
+        </is>
+      </c>
+      <c r="L310" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="N310" t="inlineStr">
+        <is>
+          <t>奖励(gold:200|exp:50|item:3001:2)</t>
+        </is>
+      </c>
+    </row>
+    <row r="311">
+      <c r="J311" t="inlineStr">
+        <is>
+          <t>nextQuest</t>
+        </is>
+      </c>
+      <c r="L311" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="N311" t="inlineStr">
+        <is>
+          <t>后继任务(0=无)</t>
+        </is>
+      </c>
+    </row>
+    <row r="312">
+      <c r="B312" t="inlineStr">
+        <is>
+          <t>cfg.QuestObjective</t>
+        </is>
+      </c>
+      <c r="G312" t="inlineStr">
+        <is>
+          <t>任务目标</t>
+        </is>
+      </c>
+      <c r="I312" t="inlineStr">
+        <is>
+          <t>c</t>
+        </is>
+      </c>
+    </row>
+    <row r="313">
+      <c r="J313" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="L313" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="N313" t="inlineStr">
+        <is>
+          <t>目标ID</t>
+        </is>
+      </c>
+    </row>
+    <row r="314">
+      <c r="J314" t="inlineStr">
+        <is>
+          <t>questId</t>
+        </is>
+      </c>
+      <c r="L314" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="N314" t="inlineStr">
+        <is>
+          <t>所属任务</t>
+        </is>
+      </c>
+    </row>
+    <row r="315">
+      <c r="J315" t="inlineStr">
+        <is>
+          <t>type</t>
+        </is>
+      </c>
+      <c r="L315" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="N315" t="inlineStr">
+        <is>
+          <t>类型(kill/collect/extract/flag)</t>
+        </is>
+      </c>
+    </row>
+    <row r="316">
+      <c r="J316" t="inlineStr">
+        <is>
+          <t>targetId</t>
+        </is>
+      </c>
+      <c r="L316" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="N316" t="inlineStr">
+        <is>
+          <t>目标ID/标志键</t>
+        </is>
+      </c>
+    </row>
+    <row r="317">
+      <c r="J317" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="L317" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="N317" t="inlineStr">
+        <is>
+          <t>需求数(extract恒1)</t>
+        </is>
+      </c>
+    </row>
+    <row r="318">
+      <c r="J318" t="inlineStr">
+        <is>
+          <t>desc</t>
+        </is>
+      </c>
+      <c r="L318" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="N318" t="inlineStr">
+        <is>
+          <t>目标一行描述</t>
         </is>
       </c>
     </row>

--- a/AfterToken/Configs/GameConfig/Datas/__beans__.xlsx
+++ b/AfterToken/Configs/GameConfig/Datas/__beans__.xlsx
@@ -1025,7 +1025,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P318"/>
+  <dimension ref="A1:P325"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col width="20.625" customWidth="1" style="1" min="2" max="4"/>
@@ -6219,257 +6219,376 @@
       </c>
     </row>
     <row r="304">
-      <c r="B304" t="inlineStr">
+      <c r="B304" s="0" t="inlineStr">
         <is>
           <t>cfg.Quest</t>
         </is>
       </c>
-      <c r="G304" t="inlineStr">
+      <c r="G304" s="0" t="inlineStr">
         <is>
           <t>任务定义</t>
         </is>
       </c>
-      <c r="I304" t="inlineStr">
+      <c r="I304" s="0" t="inlineStr">
         <is>
           <t>c</t>
         </is>
       </c>
     </row>
     <row r="305">
-      <c r="J305" t="inlineStr">
+      <c r="J305" s="0" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="L305" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="N305" t="inlineStr">
+      <c r="L305" s="0" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="N305" s="0" t="inlineStr">
         <is>
           <t>任务ID</t>
         </is>
       </c>
     </row>
     <row r="306">
-      <c r="J306" t="inlineStr">
+      <c r="J306" s="0" t="inlineStr">
         <is>
           <t>name</t>
         </is>
       </c>
-      <c r="L306" t="inlineStr">
+      <c r="L306" s="0" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="N306" t="inlineStr">
+      <c r="N306" s="0" t="inlineStr">
         <is>
           <t>显示名</t>
         </is>
       </c>
     </row>
     <row r="307">
-      <c r="J307" t="inlineStr">
+      <c r="J307" s="0" t="inlineStr">
         <is>
           <t>desc</t>
         </is>
       </c>
-      <c r="L307" t="inlineStr">
+      <c r="L307" s="0" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="N307" t="inlineStr">
+      <c r="N307" s="0" t="inlineStr">
         <is>
           <t>描述</t>
         </is>
       </c>
     </row>
     <row r="308">
-      <c r="J308" t="inlineStr">
+      <c r="J308" s="0" t="inlineStr">
         <is>
           <t>giverNpc</t>
         </is>
       </c>
-      <c r="L308" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="N308" t="inlineStr">
+      <c r="L308" s="0" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="N308" s="0" t="inlineStr">
         <is>
           <t>发布NPC(0=任务板)</t>
         </is>
       </c>
     </row>
     <row r="309">
-      <c r="J309" t="inlineStr">
+      <c r="J309" s="0" t="inlineStr">
         <is>
           <t>prereq</t>
         </is>
       </c>
-      <c r="L309" t="inlineStr">
+      <c r="L309" s="0" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="N309" t="inlineStr">
+      <c r="N309" s="0" t="inlineStr">
         <is>
           <t>接取条件表达式(空=无)</t>
         </is>
       </c>
     </row>
     <row r="310">
-      <c r="J310" t="inlineStr">
+      <c r="J310" s="0" t="inlineStr">
         <is>
           <t>rewards</t>
         </is>
       </c>
-      <c r="L310" t="inlineStr">
+      <c r="L310" s="0" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="N310" t="inlineStr">
+      <c r="N310" s="0" t="inlineStr">
         <is>
           <t>奖励(gold:200|exp:50|item:3001:2)</t>
         </is>
       </c>
     </row>
     <row r="311">
-      <c r="J311" t="inlineStr">
+      <c r="J311" s="0" t="inlineStr">
         <is>
           <t>nextQuest</t>
         </is>
       </c>
-      <c r="L311" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="N311" t="inlineStr">
+      <c r="L311" s="0" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="N311" s="0" t="inlineStr">
         <is>
           <t>后继任务(0=无)</t>
         </is>
       </c>
     </row>
     <row r="312">
-      <c r="B312" t="inlineStr">
+      <c r="B312" s="0" t="inlineStr">
         <is>
           <t>cfg.QuestObjective</t>
         </is>
       </c>
-      <c r="G312" t="inlineStr">
+      <c r="G312" s="0" t="inlineStr">
         <is>
           <t>任务目标</t>
         </is>
       </c>
-      <c r="I312" t="inlineStr">
+      <c r="I312" s="0" t="inlineStr">
         <is>
           <t>c</t>
         </is>
       </c>
     </row>
     <row r="313">
-      <c r="J313" t="inlineStr">
+      <c r="J313" s="0" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="L313" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="N313" t="inlineStr">
+      <c r="L313" s="0" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="N313" s="0" t="inlineStr">
         <is>
           <t>目标ID</t>
         </is>
       </c>
     </row>
     <row r="314">
-      <c r="J314" t="inlineStr">
+      <c r="J314" s="0" t="inlineStr">
         <is>
           <t>questId</t>
         </is>
       </c>
-      <c r="L314" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="N314" t="inlineStr">
+      <c r="L314" s="0" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="N314" s="0" t="inlineStr">
         <is>
           <t>所属任务</t>
         </is>
       </c>
     </row>
     <row r="315">
-      <c r="J315" t="inlineStr">
+      <c r="J315" s="0" t="inlineStr">
         <is>
           <t>type</t>
         </is>
       </c>
-      <c r="L315" t="inlineStr">
+      <c r="L315" s="0" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="N315" t="inlineStr">
+      <c r="N315" s="0" t="inlineStr">
         <is>
           <t>类型(kill/collect/extract/flag)</t>
         </is>
       </c>
     </row>
     <row r="316">
-      <c r="J316" t="inlineStr">
+      <c r="J316" s="0" t="inlineStr">
         <is>
           <t>targetId</t>
         </is>
       </c>
-      <c r="L316" t="inlineStr">
+      <c r="L316" s="0" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="N316" t="inlineStr">
+      <c r="N316" s="0" t="inlineStr">
         <is>
           <t>目标ID/标志键</t>
         </is>
       </c>
     </row>
     <row r="317">
-      <c r="J317" t="inlineStr">
+      <c r="J317" s="0" t="inlineStr">
         <is>
           <t>count</t>
         </is>
       </c>
-      <c r="L317" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="N317" t="inlineStr">
+      <c r="L317" s="0" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="N317" s="0" t="inlineStr">
         <is>
           <t>需求数(extract恒1)</t>
         </is>
       </c>
     </row>
     <row r="318">
-      <c r="J318" t="inlineStr">
+      <c r="J318" s="0" t="inlineStr">
         <is>
           <t>desc</t>
         </is>
       </c>
-      <c r="L318" t="inlineStr">
+      <c r="L318" s="0" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="N318" t="inlineStr">
+      <c r="N318" s="0" t="inlineStr">
         <is>
           <t>目标一行描述</t>
+        </is>
+      </c>
+    </row>
+    <row r="319">
+      <c r="B319" t="inlineStr">
+        <is>
+          <t>cfg.Localization</t>
+        </is>
+      </c>
+      <c r="G319" t="inlineStr">
+        <is>
+          <t>本地化词条</t>
+        </is>
+      </c>
+      <c r="I319" t="inlineStr">
+        <is>
+          <t>c</t>
+        </is>
+      </c>
+    </row>
+    <row r="320">
+      <c r="J320" t="inlineStr">
+        <is>
+          <t>key</t>
+        </is>
+      </c>
+      <c r="L320" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="N320" t="inlineStr">
+        <is>
+          <t>词条Key</t>
+        </is>
+      </c>
+    </row>
+    <row r="321">
+      <c r="J321" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="L321" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="N321" t="inlineStr">
+        <is>
+          <t>英文(必填/兜底)</t>
+        </is>
+      </c>
+    </row>
+    <row r="322">
+      <c r="J322" t="inlineStr">
+        <is>
+          <t>zh_cn</t>
+        </is>
+      </c>
+      <c r="L322" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="N322" t="inlineStr">
+        <is>
+          <t>简体中文</t>
+        </is>
+      </c>
+    </row>
+    <row r="323">
+      <c r="J323" t="inlineStr">
+        <is>
+          <t>zh_tw</t>
+        </is>
+      </c>
+      <c r="L323" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="N323" t="inlineStr">
+        <is>
+          <t>繁体中文</t>
+        </is>
+      </c>
+    </row>
+    <row r="324">
+      <c r="J324" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="L324" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="N324" t="inlineStr">
+        <is>
+          <t>日文</t>
+        </is>
+      </c>
+    </row>
+    <row r="325">
+      <c r="J325" t="inlineStr">
+        <is>
+          <t>ko</t>
+        </is>
+      </c>
+      <c r="L325" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="N325" t="inlineStr">
+        <is>
+          <t>韩文</t>
         </is>
       </c>
     </row>

--- a/AfterToken/Configs/GameConfig/Datas/__beans__.xlsx
+++ b/AfterToken/Configs/GameConfig/Datas/__beans__.xlsx
@@ -1025,7 +1025,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P325"/>
+  <dimension ref="A1:P326"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col width="20.625" customWidth="1" style="1" min="2" max="4"/>
@@ -3103,43 +3103,43 @@
       </c>
     </row>
     <row r="117">
-      <c r="B117" s="0" t="inlineStr">
+      <c r="J117" t="inlineStr">
+        <is>
+          <t>radius</t>
+        </is>
+      </c>
+      <c r="L117" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="N117" t="inlineStr">
+        <is>
+          <t>碰撞/寻路膨胀半径（米）</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="B118" s="0" t="inlineStr">
         <is>
           <t>cfg.Wave</t>
         </is>
       </c>
-      <c r="G117" s="0" t="inlineStr">
+      <c r="G118" s="0" t="inlineStr">
         <is>
           <t>波次配置</t>
         </is>
       </c>
-      <c r="I117" s="0" t="inlineStr">
+      <c r="I118" s="0" t="inlineStr">
         <is>
           <t>c</t>
-        </is>
-      </c>
-    </row>
-    <row r="118">
-      <c r="J118" s="0" t="inlineStr">
-        <is>
-          <t>id</t>
-        </is>
-      </c>
-      <c r="L118" s="0" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="N118" s="0" t="inlineStr">
-        <is>
-          <t>波次ID</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="J119" s="0" t="inlineStr">
         <is>
-          <t>levelId</t>
+          <t>id</t>
         </is>
       </c>
       <c r="L119" s="0" t="inlineStr">
@@ -3149,14 +3149,14 @@
       </c>
       <c r="N119" s="0" t="inlineStr">
         <is>
-          <t>关卡ID</t>
+          <t>波次ID</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="J120" s="0" t="inlineStr">
         <is>
-          <t>waveIndex</t>
+          <t>levelId</t>
         </is>
       </c>
       <c r="L120" s="0" t="inlineStr">
@@ -3166,14 +3166,14 @@
       </c>
       <c r="N120" s="0" t="inlineStr">
         <is>
-          <t>波次索引</t>
+          <t>关卡ID</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="J121" s="0" t="inlineStr">
         <is>
-          <t>enemyId</t>
+          <t>waveIndex</t>
         </is>
       </c>
       <c r="L121" s="0" t="inlineStr">
@@ -3183,14 +3183,14 @@
       </c>
       <c r="N121" s="0" t="inlineStr">
         <is>
-          <t>敌人ID</t>
+          <t>波次索引</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="J122" s="0" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>enemyId</t>
         </is>
       </c>
       <c r="L122" s="0" t="inlineStr">
@@ -3200,82 +3200,82 @@
       </c>
       <c r="N122" s="0" t="inlineStr">
         <is>
-          <t>数量</t>
+          <t>敌人ID</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="J123" s="0" t="inlineStr">
         <is>
-          <t>spawnInterval</t>
+          <t>count</t>
         </is>
       </c>
       <c r="L123" s="0" t="inlineStr">
         <is>
-          <t>float</t>
+          <t>int</t>
         </is>
       </c>
       <c r="N123" s="0" t="inlineStr">
         <is>
-          <t>刷新间隔</t>
+          <t>数量</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="J124" s="0" t="inlineStr">
         <is>
+          <t>spawnInterval</t>
+        </is>
+      </c>
+      <c r="L124" s="0" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="N124" s="0" t="inlineStr">
+        <is>
+          <t>刷新间隔</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="J125" s="0" t="inlineStr">
+        <is>
           <t>spawnRadius</t>
         </is>
       </c>
-      <c r="L124" s="0" t="inlineStr">
-        <is>
-          <t>float</t>
-        </is>
-      </c>
-      <c r="N124" s="0" t="inlineStr">
+      <c r="L125" s="0" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="N125" s="0" t="inlineStr">
         <is>
           <t>刷新半径</t>
         </is>
       </c>
     </row>
-    <row r="125">
-      <c r="B125" s="0" t="inlineStr">
+    <row r="126">
+      <c r="B126" s="0" t="inlineStr">
         <is>
           <t>cfg.Drop</t>
         </is>
       </c>
-      <c r="G125" s="0" t="inlineStr">
+      <c r="G126" s="0" t="inlineStr">
         <is>
           <t>掉落配置</t>
         </is>
       </c>
-      <c r="I125" s="0" t="inlineStr">
+      <c r="I126" s="0" t="inlineStr">
         <is>
           <t>c</t>
-        </is>
-      </c>
-    </row>
-    <row r="126">
-      <c r="J126" s="0" t="inlineStr">
-        <is>
-          <t>id</t>
-        </is>
-      </c>
-      <c r="L126" s="0" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="N126" s="0" t="inlineStr">
-        <is>
-          <t>掉落ID</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="J127" s="0" t="inlineStr">
         <is>
-          <t>enemyId</t>
+          <t>id</t>
         </is>
       </c>
       <c r="L127" s="0" t="inlineStr">
@@ -3285,14 +3285,14 @@
       </c>
       <c r="N127" s="0" t="inlineStr">
         <is>
-          <t>敌人ID</t>
+          <t>掉落ID</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="J128" s="0" t="inlineStr">
         <is>
-          <t>itemId</t>
+          <t>enemyId</t>
         </is>
       </c>
       <c r="L128" s="0" t="inlineStr">
@@ -3302,14 +3302,14 @@
       </c>
       <c r="N128" s="0" t="inlineStr">
         <is>
-          <t>道具ID</t>
+          <t>敌人ID</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="J129" s="0" t="inlineStr">
         <is>
-          <t>dropRate</t>
+          <t>itemId</t>
         </is>
       </c>
       <c r="L129" s="0" t="inlineStr">
@@ -3319,14 +3319,14 @@
       </c>
       <c r="N129" s="0" t="inlineStr">
         <is>
-          <t>掉落概率(万分之一)</t>
+          <t>道具ID</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="J130" s="0" t="inlineStr">
         <is>
-          <t>minCount</t>
+          <t>dropRate</t>
         </is>
       </c>
       <c r="L130" s="0" t="inlineStr">
@@ -3336,235 +3336,235 @@
       </c>
       <c r="N130" s="0" t="inlineStr">
         <is>
-          <t>最小数量</t>
+          <t>掉落概率(万分之一)</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="J131" s="0" t="inlineStr">
         <is>
+          <t>minCount</t>
+        </is>
+      </c>
+      <c r="L131" s="0" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="N131" s="0" t="inlineStr">
+        <is>
+          <t>最小数量</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="J132" s="0" t="inlineStr">
+        <is>
           <t>maxCount</t>
         </is>
       </c>
-      <c r="L131" s="0" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="N131" s="0" t="inlineStr">
+      <c r="L132" s="0" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="N132" s="0" t="inlineStr">
         <is>
           <t>最大数量</t>
         </is>
       </c>
     </row>
-    <row r="132">
-      <c r="B132" s="0" t="inlineStr">
+    <row r="133">
+      <c r="B133" s="0" t="inlineStr">
         <is>
           <t>cfg.Buff</t>
         </is>
       </c>
-      <c r="G132" s="0" t="inlineStr">
+      <c r="G133" s="0" t="inlineStr">
         <is>
           <t>Buff配置</t>
         </is>
       </c>
-      <c r="I132" s="0" t="inlineStr">
+      <c r="I133" s="0" t="inlineStr">
         <is>
           <t>c</t>
-        </is>
-      </c>
-    </row>
-    <row r="133">
-      <c r="J133" s="0" t="inlineStr">
-        <is>
-          <t>id</t>
-        </is>
-      </c>
-      <c r="L133" s="0" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="N133" s="0" t="inlineStr">
-        <is>
-          <t>BuffID</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="J134" s="0" t="inlineStr">
         <is>
-          <t>name</t>
+          <t>id</t>
         </is>
       </c>
       <c r="L134" s="0" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>int</t>
         </is>
       </c>
       <c r="N134" s="0" t="inlineStr">
         <is>
-          <t>名称</t>
+          <t>BuffID</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="J135" s="0" t="inlineStr">
         <is>
-          <t>duration</t>
+          <t>name</t>
         </is>
       </c>
       <c r="L135" s="0" t="inlineStr">
         <is>
-          <t>float</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N135" s="0" t="inlineStr">
         <is>
-          <t>持续时间</t>
+          <t>名称</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="J136" s="0" t="inlineStr">
         <is>
-          <t>effectType</t>
+          <t>duration</t>
         </is>
       </c>
       <c r="L136" s="0" t="inlineStr">
         <is>
-          <t>int</t>
+          <t>float</t>
         </is>
       </c>
       <c r="N136" s="0" t="inlineStr">
         <is>
-          <t>效果类型</t>
+          <t>持续时间</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="J137" s="0" t="inlineStr">
         <is>
-          <t>value</t>
+          <t>effectType</t>
         </is>
       </c>
       <c r="L137" s="0" t="inlineStr">
         <is>
-          <t>float</t>
+          <t>int</t>
         </is>
       </c>
       <c r="N137" s="0" t="inlineStr">
         <is>
-          <t>数值</t>
+          <t>效果类型</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="J138" s="0" t="inlineStr">
         <is>
+          <t>value</t>
+        </is>
+      </c>
+      <c r="L138" s="0" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="N138" s="0" t="inlineStr">
+        <is>
+          <t>数值</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="J139" s="0" t="inlineStr">
+        <is>
           <t>icon</t>
         </is>
       </c>
-      <c r="L138" s="0" t="inlineStr">
+      <c r="L139" s="0" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="N138" s="0" t="inlineStr">
+      <c r="N139" s="0" t="inlineStr">
         <is>
           <t>图标</t>
         </is>
       </c>
     </row>
-    <row r="139">
-      <c r="B139" s="0" t="inlineStr">
+    <row r="140">
+      <c r="B140" s="0" t="inlineStr">
         <is>
           <t>cfg.Portal</t>
         </is>
       </c>
-      <c r="G139" s="0" t="inlineStr">
+      <c r="G140" s="0" t="inlineStr">
         <is>
           <t>传送门配置</t>
         </is>
       </c>
-      <c r="I139" s="0" t="inlineStr">
+      <c r="I140" s="0" t="inlineStr">
         <is>
           <t>c</t>
-        </is>
-      </c>
-    </row>
-    <row r="140">
-      <c r="J140" s="0" t="inlineStr">
-        <is>
-          <t>id</t>
-        </is>
-      </c>
-      <c r="L140" s="0" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="N140" s="0" t="inlineStr">
-        <is>
-          <t>传送门ID</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="J141" s="0" t="inlineStr">
         <is>
-          <t>portalType</t>
+          <t>id</t>
         </is>
       </c>
       <c r="L141" s="0" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>int</t>
         </is>
       </c>
       <c r="N141" s="0" t="inlineStr">
         <is>
-          <t>传送门类型</t>
+          <t>传送门ID</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="J142" s="0" t="inlineStr">
         <is>
-          <t>targetLevelId</t>
+          <t>portalType</t>
         </is>
       </c>
       <c r="L142" s="0" t="inlineStr">
         <is>
-          <t>int</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N142" s="0" t="inlineStr">
         <is>
-          <t>目标关卡ID</t>
+          <t>传送门类型</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="J143" s="0" t="inlineStr">
         <is>
-          <t>targetSceneName</t>
+          <t>targetLevelId</t>
         </is>
       </c>
       <c r="L143" s="0" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>int</t>
         </is>
       </c>
       <c r="N143" s="0" t="inlineStr">
         <is>
-          <t>目标场景名</t>
+          <t>目标关卡ID</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="J144" s="0" t="inlineStr">
         <is>
-          <t>spawnCondition</t>
+          <t>targetSceneName</t>
         </is>
       </c>
       <c r="L144" s="0" t="inlineStr">
@@ -3574,14 +3574,14 @@
       </c>
       <c r="N144" s="0" t="inlineStr">
         <is>
-          <t>出现条件</t>
+          <t>目标场景名</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="J145" s="0" t="inlineStr">
         <is>
-          <t>conditionParam</t>
+          <t>spawnCondition</t>
         </is>
       </c>
       <c r="L145" s="0" t="inlineStr">
@@ -3591,48 +3591,48 @@
       </c>
       <c r="N145" s="0" t="inlineStr">
         <is>
-          <t>条件参数</t>
+          <t>出现条件</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="J146" s="0" t="inlineStr">
         <is>
-          <t>keepPlayerState</t>
+          <t>conditionParam</t>
         </is>
       </c>
       <c r="L146" s="0" t="inlineStr">
         <is>
-          <t>bool</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N146" s="0" t="inlineStr">
         <is>
-          <t>保留玩家状态</t>
+          <t>条件参数</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="J147" s="0" t="inlineStr">
         <is>
-          <t>promptText</t>
+          <t>keepPlayerState</t>
         </is>
       </c>
       <c r="L147" s="0" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>bool</t>
         </is>
       </c>
       <c r="N147" s="0" t="inlineStr">
         <is>
-          <t>提示文本</t>
+          <t>保留玩家状态</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="J148" s="0" t="inlineStr">
         <is>
-          <t>transitionType</t>
+          <t>promptText</t>
         </is>
       </c>
       <c r="L148" s="0" t="inlineStr">
@@ -3642,65 +3642,65 @@
       </c>
       <c r="N148" s="0" t="inlineStr">
         <is>
-          <t>转场类型</t>
+          <t>提示文本</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="J149" s="0" t="inlineStr">
         <is>
+          <t>transitionType</t>
+        </is>
+      </c>
+      <c r="L149" s="0" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="N149" s="0" t="inlineStr">
+        <is>
+          <t>转场类型</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="J150" s="0" t="inlineStr">
+        <is>
           <t>transitionDuration</t>
         </is>
       </c>
-      <c r="L149" s="0" t="inlineStr">
-        <is>
-          <t>float</t>
-        </is>
-      </c>
-      <c r="N149" s="0" t="inlineStr">
+      <c r="L150" s="0" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="N150" s="0" t="inlineStr">
         <is>
           <t>转场时长</t>
         </is>
       </c>
     </row>
-    <row r="150">
-      <c r="B150" s="0" t="inlineStr">
+    <row r="151">
+      <c r="B151" s="0" t="inlineStr">
         <is>
           <t>cfg.InventoryConfig</t>
         </is>
       </c>
-      <c r="G150" s="0" t="inlineStr">
+      <c r="G151" s="0" t="inlineStr">
         <is>
           <t>背包容量配置</t>
         </is>
       </c>
-      <c r="I150" s="0" t="inlineStr">
+      <c r="I151" s="0" t="inlineStr">
         <is>
           <t>c</t>
-        </is>
-      </c>
-    </row>
-    <row r="151">
-      <c r="J151" s="0" t="inlineStr">
-        <is>
-          <t>id</t>
-        </is>
-      </c>
-      <c r="L151" s="0" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="N151" s="0" t="inlineStr">
-        <is>
-          <t>ID</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="J152" s="0" t="inlineStr">
         <is>
-          <t>tempBagCapacity</t>
+          <t>id</t>
         </is>
       </c>
       <c r="L152" s="0" t="inlineStr">
@@ -3710,82 +3710,82 @@
       </c>
       <c r="N152" s="0" t="inlineStr">
         <is>
-          <t>临时背包槽位</t>
+          <t>ID</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="J153" s="0" t="inlineStr">
         <is>
+          <t>tempBagCapacity</t>
+        </is>
+      </c>
+      <c r="L153" s="0" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="N153" s="0" t="inlineStr">
+        <is>
+          <t>临时背包槽位</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="J154" s="0" t="inlineStr">
+        <is>
           <t>warehouseCapacity</t>
         </is>
       </c>
-      <c r="L153" s="0" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="N153" s="0" t="inlineStr">
+      <c r="L154" s="0" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="N154" s="0" t="inlineStr">
         <is>
           <t>仓库槽位</t>
         </is>
       </c>
     </row>
-    <row r="154">
-      <c r="B154" s="0" t="inlineStr">
+    <row r="155">
+      <c r="B155" s="0" t="inlineStr">
         <is>
           <t>cfg.Camera</t>
         </is>
       </c>
-      <c r="G154" s="0" t="inlineStr">
+      <c r="G155" s="0" t="inlineStr">
         <is>
           <t>相机配置</t>
         </is>
       </c>
-      <c r="H154" s="0" t="inlineStr">
+      <c r="H155" s="0" t="inlineStr">
         <is>
           <t>c</t>
-        </is>
-      </c>
-    </row>
-    <row r="155">
-      <c r="J155" s="0" t="inlineStr">
-        <is>
-          <t>id</t>
-        </is>
-      </c>
-      <c r="L155" s="0" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="N155" s="0" t="inlineStr">
-        <is>
-          <t>配置ID</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="J156" s="0" t="inlineStr">
         <is>
-          <t>smoothTime</t>
+          <t>id</t>
         </is>
       </c>
       <c r="L156" s="0" t="inlineStr">
         <is>
-          <t>float</t>
+          <t>int</t>
         </is>
       </c>
       <c r="N156" s="0" t="inlineStr">
         <is>
-          <t>相机平滑时间</t>
+          <t>配置ID</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="J157" s="0" t="inlineStr">
         <is>
-          <t>defaultFov</t>
+          <t>smoothTime</t>
         </is>
       </c>
       <c r="L157" s="0" t="inlineStr">
@@ -3795,14 +3795,14 @@
       </c>
       <c r="N157" s="0" t="inlineStr">
         <is>
-          <t>默认FOV</t>
+          <t>相机平滑时间</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="J158" s="0" t="inlineStr">
         <is>
-          <t>fovSmoothTime</t>
+          <t>defaultFov</t>
         </is>
       </c>
       <c r="L158" s="0" t="inlineStr">
@@ -3812,14 +3812,14 @@
       </c>
       <c r="N158" s="0" t="inlineStr">
         <is>
-          <t>FOV平滑时间</t>
+          <t>默认FOV</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="J159" s="0" t="inlineStr">
         <is>
-          <t>shakeDamping</t>
+          <t>fovSmoothTime</t>
         </is>
       </c>
       <c r="L159" s="0" t="inlineStr">
@@ -3829,116 +3829,116 @@
       </c>
       <c r="N159" s="0" t="inlineStr">
         <is>
-          <t>震动衰减速度</t>
+          <t>FOV平滑时间</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="J160" s="0" t="inlineStr">
         <is>
-          <t>scopeRenderSize</t>
+          <t>shakeDamping</t>
         </is>
       </c>
       <c r="L160" s="0" t="inlineStr">
         <is>
-          <t>int</t>
+          <t>float</t>
         </is>
       </c>
       <c r="N160" s="0" t="inlineStr">
         <is>
-          <t>狙击镜渲染纹理尺寸</t>
+          <t>震动衰减速度</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="J161" s="0" t="inlineStr">
         <is>
-          <t>scopeCameraFov</t>
+          <t>scopeRenderSize</t>
         </is>
       </c>
       <c r="L161" s="0" t="inlineStr">
         <is>
-          <t>float</t>
+          <t>int</t>
         </is>
       </c>
       <c r="N161" s="0" t="inlineStr">
         <is>
-          <t>狙击镜相机FOV</t>
+          <t>狙击镜渲染纹理尺寸</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="J162" s="0" t="inlineStr">
         <is>
+          <t>scopeCameraFov</t>
+        </is>
+      </c>
+      <c r="L162" s="0" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="N162" s="0" t="inlineStr">
+        <is>
+          <t>狙击镜相机FOV</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="J163" s="0" t="inlineStr">
+        <is>
           <t>defaultOrthographicSize</t>
         </is>
       </c>
-      <c r="L162" s="0" t="inlineStr">
-        <is>
-          <t>float</t>
-        </is>
-      </c>
-      <c r="N162" s="0" t="inlineStr">
+      <c r="L163" s="0" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="N163" s="0" t="inlineStr">
         <is>
           <t>默认正交尺寸</t>
         </is>
       </c>
     </row>
-    <row r="163">
-      <c r="B163" s="0" t="inlineStr">
+    <row r="164">
+      <c r="B164" s="0" t="inlineStr">
         <is>
           <t>cfg.Ballistic</t>
         </is>
       </c>
-      <c r="G163" s="0" t="inlineStr">
+      <c r="G164" s="0" t="inlineStr">
         <is>
           <t>弹道全局配置</t>
         </is>
       </c>
-      <c r="H163" s="0" t="inlineStr">
+      <c r="H164" s="0" t="inlineStr">
         <is>
           <t>c</t>
-        </is>
-      </c>
-    </row>
-    <row r="164">
-      <c r="J164" s="0" t="inlineStr">
-        <is>
-          <t>id</t>
-        </is>
-      </c>
-      <c r="L164" s="0" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="N164" s="0" t="inlineStr">
-        <is>
-          <t>配置ID</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="J165" s="0" t="inlineStr">
         <is>
-          <t>tracerRadius</t>
+          <t>id</t>
         </is>
       </c>
       <c r="L165" s="0" t="inlineStr">
         <is>
-          <t>float</t>
+          <t>int</t>
         </is>
       </c>
       <c r="N165" s="0" t="inlineStr">
         <is>
-          <t>Tracer射线检测半径</t>
+          <t>配置ID</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="J166" s="0" t="inlineStr">
         <is>
-          <t>tracerStartWidth</t>
+          <t>tracerRadius</t>
         </is>
       </c>
       <c r="L166" s="0" t="inlineStr">
@@ -3948,14 +3948,14 @@
       </c>
       <c r="N166" s="0" t="inlineStr">
         <is>
-          <t>Tracer起始宽度</t>
+          <t>Tracer射线检测半径</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="J167" s="0" t="inlineStr">
         <is>
-          <t>tracerEndWidth</t>
+          <t>tracerStartWidth</t>
         </is>
       </c>
       <c r="L167" s="0" t="inlineStr">
@@ -3965,14 +3965,14 @@
       </c>
       <c r="N167" s="0" t="inlineStr">
         <is>
-          <t>Tracer结束宽度</t>
+          <t>Tracer起始宽度</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="J168" s="0" t="inlineStr">
         <is>
-          <t>tracerTailLength</t>
+          <t>tracerEndWidth</t>
         </is>
       </c>
       <c r="L168" s="0" t="inlineStr">
@@ -3982,116 +3982,116 @@
       </c>
       <c r="N168" s="0" t="inlineStr">
         <is>
-          <t>Tracer尾迹长度</t>
+          <t>Tracer结束宽度</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="J169" s="0" t="inlineStr">
         <is>
-          <t>maxActiveTracers</t>
+          <t>tracerTailLength</t>
         </is>
       </c>
       <c r="L169" s="0" t="inlineStr">
         <is>
-          <t>int</t>
+          <t>float</t>
         </is>
       </c>
       <c r="N169" s="0" t="inlineStr">
         <is>
-          <t>最大同时存在Tracer数量</t>
+          <t>Tracer尾迹长度</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="J170" s="0" t="inlineStr">
         <is>
-          <t>hitLayers</t>
+          <t>maxActiveTracers</t>
         </is>
       </c>
       <c r="L170" s="0" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>int</t>
         </is>
       </c>
       <c r="N170" s="0" t="inlineStr">
         <is>
-          <t>默认命中层级</t>
+          <t>最大同时存在Tracer数量</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="J171" s="0" t="inlineStr">
         <is>
-          <t>tracerStartColor</t>
+          <t>hitLayers</t>
         </is>
       </c>
       <c r="L171" s="0" t="inlineStr">
         <is>
-          <t>cfg.Color#sep=,</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N171" s="0" t="inlineStr">
         <is>
-          <t>Tracer起始颜色</t>
+          <t>默认命中层级</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="J172" s="0" t="inlineStr">
         <is>
+          <t>tracerStartColor</t>
+        </is>
+      </c>
+      <c r="L172" s="0" t="inlineStr">
+        <is>
+          <t>cfg.Color#sep=,</t>
+        </is>
+      </c>
+      <c r="N172" s="0" t="inlineStr">
+        <is>
+          <t>Tracer起始颜色</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="J173" s="0" t="inlineStr">
+        <is>
           <t>tracerEndColor</t>
         </is>
       </c>
-      <c r="L172" s="0" t="inlineStr">
+      <c r="L173" s="0" t="inlineStr">
         <is>
           <t>cfg.Color#sep=,</t>
         </is>
       </c>
-      <c r="N172" s="0" t="inlineStr">
+      <c r="N173" s="0" t="inlineStr">
         <is>
           <t>Tracer结束颜色</t>
         </is>
       </c>
     </row>
-    <row r="173">
-      <c r="B173" s="0" t="inlineStr">
+    <row r="174">
+      <c r="B174" s="0" t="inlineStr">
         <is>
           <t>cfg.UiConfig</t>
         </is>
       </c>
-      <c r="G173" s="0" t="inlineStr">
+      <c r="G174" s="0" t="inlineStr">
         <is>
           <t>UI全局配置</t>
         </is>
       </c>
-      <c r="H173" s="0" t="inlineStr">
+      <c r="H174" s="0" t="inlineStr">
         <is>
           <t>c</t>
-        </is>
-      </c>
-    </row>
-    <row r="174">
-      <c r="J174" s="0" t="inlineStr">
-        <is>
-          <t>id</t>
-        </is>
-      </c>
-      <c r="L174" s="0" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="N174" s="0" t="inlineStr">
-        <is>
-          <t>配置ID</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="J175" s="0" t="inlineStr">
         <is>
-          <t>damageNumberPoolSize</t>
+          <t>id</t>
         </is>
       </c>
       <c r="L175" s="0" t="inlineStr">
@@ -4101,31 +4101,31 @@
       </c>
       <c r="N175" s="0" t="inlineStr">
         <is>
-          <t>伤害数字对象池大小</t>
+          <t>配置ID</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="J176" s="0" t="inlineStr">
         <is>
-          <t>damageNumberFadeDuration</t>
+          <t>damageNumberPoolSize</t>
         </is>
       </c>
       <c r="L176" s="0" t="inlineStr">
         <is>
-          <t>float</t>
+          <t>int</t>
         </is>
       </c>
       <c r="N176" s="0" t="inlineStr">
         <is>
-          <t>伤害数字渐隐时间</t>
+          <t>伤害数字对象池大小</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="J177" s="0" t="inlineStr">
         <is>
-          <t>damageNumberMoveOffset</t>
+          <t>damageNumberFadeDuration</t>
         </is>
       </c>
       <c r="L177" s="0" t="inlineStr">
@@ -4135,31 +4135,31 @@
       </c>
       <c r="N177" s="0" t="inlineStr">
         <is>
-          <t>伤害数字上浮偏移</t>
+          <t>伤害数字渐隐时间</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="J178" s="0" t="inlineStr">
         <is>
-          <t>damageNumberNormalColor</t>
+          <t>damageNumberMoveOffset</t>
         </is>
       </c>
       <c r="L178" s="0" t="inlineStr">
         <is>
-          <t>cfg.Color#sep=,</t>
+          <t>float</t>
         </is>
       </c>
       <c r="N178" s="0" t="inlineStr">
         <is>
-          <t>普通伤害数字颜色</t>
+          <t>伤害数字上浮偏移</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="J179" s="0" t="inlineStr">
         <is>
-          <t>damageNumberCriticalColor</t>
+          <t>damageNumberNormalColor</t>
         </is>
       </c>
       <c r="L179" s="0" t="inlineStr">
@@ -4169,31 +4169,31 @@
       </c>
       <c r="N179" s="0" t="inlineStr">
         <is>
-          <t>暴击伤害数字颜色</t>
+          <t>普通伤害数字颜色</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="J180" s="0" t="inlineStr">
         <is>
-          <t>damageNumberNormalFontSize</t>
+          <t>damageNumberCriticalColor</t>
         </is>
       </c>
       <c r="L180" s="0" t="inlineStr">
         <is>
-          <t>int</t>
+          <t>cfg.Color#sep=,</t>
         </is>
       </c>
       <c r="N180" s="0" t="inlineStr">
         <is>
-          <t>普通伤害数字字体大小</t>
+          <t>暴击伤害数字颜色</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="J181" s="0" t="inlineStr">
         <is>
-          <t>damageNumberCriticalFontSize</t>
+          <t>damageNumberNormalFontSize</t>
         </is>
       </c>
       <c r="L181" s="0" t="inlineStr">
@@ -4203,14 +4203,14 @@
       </c>
       <c r="N181" s="0" t="inlineStr">
         <is>
-          <t>暴击伤害数字字体大小</t>
+          <t>普通伤害数字字体大小</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="J182" s="0" t="inlineStr">
         <is>
-          <t>hitMarkerPoolSize</t>
+          <t>damageNumberCriticalFontSize</t>
         </is>
       </c>
       <c r="L182" s="0" t="inlineStr">
@@ -4220,31 +4220,31 @@
       </c>
       <c r="N182" s="0" t="inlineStr">
         <is>
-          <t>命中标记对象池大小</t>
+          <t>暴击伤害数字字体大小</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="J183" s="0" t="inlineStr">
         <is>
-          <t>hitMarkerDuration</t>
+          <t>hitMarkerPoolSize</t>
         </is>
       </c>
       <c r="L183" s="0" t="inlineStr">
         <is>
-          <t>float</t>
+          <t>int</t>
         </is>
       </c>
       <c r="N183" s="0" t="inlineStr">
         <is>
-          <t>命中标记显示时间</t>
+          <t>命中标记对象池大小</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="J184" s="0" t="inlineStr">
         <is>
-          <t>hitMarkerSize</t>
+          <t>hitMarkerDuration</t>
         </is>
       </c>
       <c r="L184" s="0" t="inlineStr">
@@ -4254,31 +4254,31 @@
       </c>
       <c r="N184" s="0" t="inlineStr">
         <is>
-          <t>命中标记大小</t>
+          <t>命中标记显示时间</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="J185" s="0" t="inlineStr">
         <is>
-          <t>hitMarkerNormalColor</t>
+          <t>hitMarkerSize</t>
         </is>
       </c>
       <c r="L185" s="0" t="inlineStr">
         <is>
-          <t>cfg.Color#sep=,</t>
+          <t>float</t>
         </is>
       </c>
       <c r="N185" s="0" t="inlineStr">
         <is>
-          <t>普通命中标记颜色</t>
+          <t>命中标记大小</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="J186" s="0" t="inlineStr">
         <is>
-          <t>hitMarkerCriticalColor</t>
+          <t>hitMarkerNormalColor</t>
         </is>
       </c>
       <c r="L186" s="0" t="inlineStr">
@@ -4288,116 +4288,116 @@
       </c>
       <c r="N186" s="0" t="inlineStr">
         <is>
-          <t>暴击命中标记颜色</t>
+          <t>普通命中标记颜色</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="J187" s="0" t="inlineStr">
         <is>
-          <t>indicatorFadeSpeed</t>
+          <t>hitMarkerCriticalColor</t>
         </is>
       </c>
       <c r="L187" s="0" t="inlineStr">
         <is>
-          <t>float</t>
+          <t>cfg.Color#sep=,</t>
         </is>
       </c>
       <c r="N187" s="0" t="inlineStr">
         <is>
-          <t>受击指示器淡出速度</t>
+          <t>暴击命中标记颜色</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="J188" s="0" t="inlineStr">
         <is>
-          <t>indicatorColor</t>
+          <t>indicatorFadeSpeed</t>
         </is>
       </c>
       <c r="L188" s="0" t="inlineStr">
         <is>
-          <t>cfg.Color#sep=,</t>
+          <t>float</t>
         </is>
       </c>
       <c r="N188" s="0" t="inlineStr">
         <is>
-          <t>受击指示器颜色</t>
+          <t>受击指示器淡出速度</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="J189" s="0" t="inlineStr">
         <is>
+          <t>indicatorColor</t>
+        </is>
+      </c>
+      <c r="L189" s="0" t="inlineStr">
+        <is>
+          <t>cfg.Color#sep=,</t>
+        </is>
+      </c>
+      <c r="N189" s="0" t="inlineStr">
+        <is>
+          <t>受击指示器颜色</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="J190" s="0" t="inlineStr">
+        <is>
           <t>loadingTextFormat</t>
         </is>
       </c>
-      <c r="L189" s="0" t="inlineStr">
+      <c r="L190" s="0" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="N189" s="0" t="inlineStr">
+      <c r="N190" s="0" t="inlineStr">
         <is>
           <t>加载进度文本格式</t>
         </is>
       </c>
     </row>
-    <row r="190">
-      <c r="B190" s="0" t="inlineStr">
+    <row r="191">
+      <c r="B191" s="0" t="inlineStr">
         <is>
           <t>cfg.Pickup</t>
         </is>
       </c>
-      <c r="G190" s="0" t="inlineStr">
+      <c r="G191" s="0" t="inlineStr">
         <is>
           <t>拾取物配置</t>
         </is>
       </c>
-      <c r="H190" s="0" t="inlineStr">
+      <c r="H191" s="0" t="inlineStr">
         <is>
           <t>c</t>
-        </is>
-      </c>
-    </row>
-    <row r="191">
-      <c r="J191" s="0" t="inlineStr">
-        <is>
-          <t>id</t>
-        </is>
-      </c>
-      <c r="L191" s="0" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="N191" s="0" t="inlineStr">
-        <is>
-          <t>配置ID</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="J192" s="0" t="inlineStr">
         <is>
-          <t>colliderRadius</t>
+          <t>id</t>
         </is>
       </c>
       <c r="L192" s="0" t="inlineStr">
         <is>
-          <t>float</t>
+          <t>int</t>
         </is>
       </c>
       <c r="N192" s="0" t="inlineStr">
         <is>
-          <t>拾取物碰撞体半径</t>
+          <t>配置ID</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="J193" s="0" t="inlineStr">
         <is>
-          <t>visualScale</t>
+          <t>colliderRadius</t>
         </is>
       </c>
       <c r="L193" s="0" t="inlineStr">
@@ -4407,82 +4407,82 @@
       </c>
       <c r="N193" s="0" t="inlineStr">
         <is>
-          <t>拾取物视觉缩放</t>
+          <t>拾取物碰撞体半径</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="J194" s="0" t="inlineStr">
         <is>
+          <t>visualScale</t>
+        </is>
+      </c>
+      <c r="L194" s="0" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="N194" s="0" t="inlineStr">
+        <is>
+          <t>拾取物视觉缩放</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="J195" s="0" t="inlineStr">
+        <is>
           <t>sortingOrder</t>
         </is>
       </c>
-      <c r="L194" s="0" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="N194" s="0" t="inlineStr">
+      <c r="L195" s="0" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="N195" s="0" t="inlineStr">
         <is>
           <t>拾取物渲染排序</t>
         </is>
       </c>
     </row>
-    <row r="195">
-      <c r="B195" s="0" t="inlineStr">
+    <row r="196">
+      <c r="B196" s="0" t="inlineStr">
         <is>
           <t>cfg.Building</t>
         </is>
       </c>
-      <c r="G195" s="0" t="inlineStr">
+      <c r="G196" s="0" t="inlineStr">
         <is>
           <t>建筑配置</t>
         </is>
       </c>
-      <c r="I195" s="0" t="inlineStr">
+      <c r="I196" s="0" t="inlineStr">
         <is>
           <t>c</t>
-        </is>
-      </c>
-    </row>
-    <row r="196">
-      <c r="J196" s="0" t="inlineStr">
-        <is>
-          <t>id</t>
-        </is>
-      </c>
-      <c r="L196" s="0" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="N196" s="0" t="inlineStr">
-        <is>
-          <t>建筑ID</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="J197" s="0" t="inlineStr">
         <is>
-          <t>name</t>
+          <t>id</t>
         </is>
       </c>
       <c r="L197" s="0" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>int</t>
         </is>
       </c>
       <c r="N197" s="0" t="inlineStr">
         <is>
-          <t>名称</t>
+          <t>建筑ID</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="J198" s="0" t="inlineStr">
         <is>
-          <t>desc</t>
+          <t>name</t>
         </is>
       </c>
       <c r="L198" s="0" t="inlineStr">
@@ -4492,65 +4492,65 @@
       </c>
       <c r="N198" s="0" t="inlineStr">
         <is>
-          <t>描述</t>
+          <t>名称</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="J199" s="0" t="inlineStr">
         <is>
-          <t>buildingType</t>
+          <t>desc</t>
         </is>
       </c>
       <c r="L199" s="0" t="inlineStr">
         <is>
-          <t>cfg.EBuildingType</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N199" s="0" t="inlineStr">
         <is>
-          <t>建筑类型</t>
+          <t>描述</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="J200" s="0" t="inlineStr">
         <is>
-          <t>icon</t>
+          <t>buildingType</t>
         </is>
       </c>
       <c r="L200" s="0" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>cfg.EBuildingType</t>
         </is>
       </c>
       <c r="N200" s="0" t="inlineStr">
         <is>
-          <t>图标</t>
+          <t>建筑类型</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="J201" s="0" t="inlineStr">
         <is>
-          <t>maxLevel</t>
+          <t>icon</t>
         </is>
       </c>
       <c r="L201" s="0" t="inlineStr">
         <is>
-          <t>int</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N201" s="0" t="inlineStr">
         <is>
-          <t>最大等级</t>
+          <t>图标</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="J202" s="0" t="inlineStr">
         <is>
-          <t>buildCostGold</t>
+          <t>maxLevel</t>
         </is>
       </c>
       <c r="L202" s="0" t="inlineStr">
@@ -4560,116 +4560,116 @@
       </c>
       <c r="N202" s="0" t="inlineStr">
         <is>
-          <t>建造金币</t>
+          <t>最大等级</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="J203" s="0" t="inlineStr">
         <is>
-          <t>buildCostItems</t>
+          <t>buildCostGold</t>
         </is>
       </c>
       <c r="L203" s="0" t="inlineStr">
         <is>
-          <t>(list#sep=;),cfg.ItemExchange#sep=,</t>
+          <t>int</t>
         </is>
       </c>
       <c r="N203" s="0" t="inlineStr">
         <is>
-          <t>建造材料</t>
+          <t>建造金币</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="J204" s="0" t="inlineStr">
         <is>
-          <t>buildTime</t>
+          <t>buildCostItems</t>
         </is>
       </c>
       <c r="L204" s="0" t="inlineStr">
         <is>
-          <t>float</t>
+          <t>(list#sep=;),cfg.ItemExchange#sep=,</t>
         </is>
       </c>
       <c r="N204" s="0" t="inlineStr">
         <is>
-          <t>建造耗时</t>
+          <t>建造材料</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="J205" s="0" t="inlineStr">
         <is>
-          <t>upgradeCostGold</t>
+          <t>buildTime</t>
         </is>
       </c>
       <c r="L205" s="0" t="inlineStr">
         <is>
-          <t>int</t>
+          <t>float</t>
         </is>
       </c>
       <c r="N205" s="0" t="inlineStr">
         <is>
-          <t>升级金币</t>
+          <t>建造耗时</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="J206" s="0" t="inlineStr">
         <is>
-          <t>upgradeCostItems</t>
+          <t>upgradeCostGold</t>
         </is>
       </c>
       <c r="L206" s="0" t="inlineStr">
         <is>
-          <t>(list#sep=;),cfg.ItemExchange#sep=,</t>
+          <t>int</t>
         </is>
       </c>
       <c r="N206" s="0" t="inlineStr">
         <is>
-          <t>升级材料</t>
+          <t>升级金币</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="J207" s="0" t="inlineStr">
         <is>
-          <t>upgradeTime</t>
+          <t>upgradeCostItems</t>
         </is>
       </c>
       <c r="L207" s="0" t="inlineStr">
         <is>
-          <t>float</t>
+          <t>(list#sep=;),cfg.ItemExchange#sep=,</t>
         </is>
       </c>
       <c r="N207" s="0" t="inlineStr">
         <is>
-          <t>升级耗时</t>
+          <t>升级材料</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="J208" s="0" t="inlineStr">
         <is>
-          <t>productionSlotCount</t>
+          <t>upgradeTime</t>
         </is>
       </c>
       <c r="L208" s="0" t="inlineStr">
         <is>
-          <t>int</t>
+          <t>float</t>
         </is>
       </c>
       <c r="N208" s="0" t="inlineStr">
         <is>
-          <t>生产槽位</t>
+          <t>升级耗时</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="J209" s="0" t="inlineStr">
         <is>
-          <t>unlockLevel</t>
+          <t>productionSlotCount</t>
         </is>
       </c>
       <c r="L209" s="0" t="inlineStr">
@@ -4679,14 +4679,14 @@
       </c>
       <c r="N209" s="0" t="inlineStr">
         <is>
-          <t>解锁等级</t>
+          <t>生产槽位</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="J210" s="0" t="inlineStr">
         <is>
-          <t>footprintX</t>
+          <t>unlockLevel</t>
         </is>
       </c>
       <c r="L210" s="0" t="inlineStr">
@@ -4696,14 +4696,14 @@
       </c>
       <c r="N210" s="0" t="inlineStr">
         <is>
-          <t>占地格数X(1m格)</t>
+          <t>解锁等级</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="J211" s="0" t="inlineStr">
         <is>
-          <t>maxCount</t>
+          <t>footprintX</t>
         </is>
       </c>
       <c r="L211" s="0" t="inlineStr">
@@ -4713,14 +4713,14 @@
       </c>
       <c r="N211" s="0" t="inlineStr">
         <is>
-          <t>数量上限-基础值(默认1)</t>
+          <t>占地格数X(1m格)</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="J212" s="0" t="inlineStr">
         <is>
-          <t>maxCountPerPlayerLevel</t>
+          <t>maxCount</t>
         </is>
       </c>
       <c r="L212" s="0" t="inlineStr">
@@ -4730,14 +4730,14 @@
       </c>
       <c r="N212" s="0" t="inlineStr">
         <is>
-          <t>数量上限-玩家等级解锁:玩家每升1级上限+N(默认0)</t>
+          <t>数量上限-基础值(默认1)</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="J213" s="0" t="inlineStr">
         <is>
-          <t>maxCountUpgradeLevel</t>
+          <t>maxCountPerPlayerLevel</t>
         </is>
       </c>
       <c r="L213" s="0" t="inlineStr">
@@ -4747,14 +4747,14 @@
       </c>
       <c r="N213" s="0" t="inlineStr">
         <is>
-          <t>数量上限-升级解锁(默认方式):同类建筑每有1座达到该等级上限+1,0=不启用</t>
+          <t>数量上限-玩家等级解锁:玩家每升1级上限+N(默认0)</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="J214" s="0" t="inlineStr">
         <is>
-          <t>maxCountSlotBaseCost</t>
+          <t>maxCountUpgradeLevel</t>
         </is>
       </c>
       <c r="L214" s="0" t="inlineStr">
@@ -4764,14 +4764,14 @@
       </c>
       <c r="N214" s="0" t="inlineStr">
         <is>
-          <t>数量上限-购买解锁:购买1个栏位的金币基础价,0=不可购买</t>
+          <t>数量上限-升级解锁(默认方式):同类建筑每有1座达到该等级上限+1,0=不启用</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="J215" s="0" t="inlineStr">
         <is>
-          <t>maxCountSlotCostGrow</t>
+          <t>maxCountSlotBaseCost</t>
         </is>
       </c>
       <c r="L215" s="0" t="inlineStr">
@@ -4781,82 +4781,82 @@
       </c>
       <c r="N215" s="0" t="inlineStr">
         <is>
-          <t>数量上限-购买解锁:每已购1个栏位价格+N(线性涨价)</t>
+          <t>数量上限-购买解锁:购买1个栏位的金币基础价,0=不可购买</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="J216" s="0" t="inlineStr">
         <is>
+          <t>maxCountSlotCostGrow</t>
+        </is>
+      </c>
+      <c r="L216" s="0" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="N216" s="0" t="inlineStr">
+        <is>
+          <t>数量上限-购买解锁:每已购1个栏位价格+N(线性涨价)</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="J217" s="0" t="inlineStr">
+        <is>
           <t>footprintZ</t>
         </is>
       </c>
-      <c r="L216" s="0" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="N216" s="0" t="inlineStr">
+      <c r="L217" s="0" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="N217" s="0" t="inlineStr">
         <is>
           <t>占地格数Z(1m格)</t>
         </is>
       </c>
     </row>
-    <row r="217">
-      <c r="B217" s="0" t="inlineStr">
+    <row r="218">
+      <c r="B218" s="0" t="inlineStr">
         <is>
           <t>cfg.Production</t>
         </is>
       </c>
-      <c r="G217" s="0" t="inlineStr">
+      <c r="G218" s="0" t="inlineStr">
         <is>
           <t>生产配方</t>
         </is>
       </c>
-      <c r="I217" s="0" t="inlineStr">
+      <c r="I218" s="0" t="inlineStr">
         <is>
           <t>c</t>
-        </is>
-      </c>
-    </row>
-    <row r="218">
-      <c r="J218" s="0" t="inlineStr">
-        <is>
-          <t>id</t>
-        </is>
-      </c>
-      <c r="L218" s="0" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="N218" s="0" t="inlineStr">
-        <is>
-          <t>配方ID</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="J219" s="0" t="inlineStr">
         <is>
-          <t>name</t>
+          <t>id</t>
         </is>
       </c>
       <c r="L219" s="0" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>int</t>
         </is>
       </c>
       <c r="N219" s="0" t="inlineStr">
         <is>
-          <t>名称</t>
+          <t>配方ID</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="J220" s="0" t="inlineStr">
         <is>
-          <t>desc</t>
+          <t>name</t>
         </is>
       </c>
       <c r="L220" s="0" t="inlineStr">
@@ -4866,31 +4866,31 @@
       </c>
       <c r="N220" s="0" t="inlineStr">
         <is>
-          <t>描述</t>
+          <t>名称</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="J221" s="0" t="inlineStr">
         <is>
-          <t>buildingId</t>
+          <t>desc</t>
         </is>
       </c>
       <c r="L221" s="0" t="inlineStr">
         <is>
-          <t>int</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N221" s="0" t="inlineStr">
         <is>
-          <t>建筑ID</t>
+          <t>描述</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="J222" s="0" t="inlineStr">
         <is>
-          <t>levelRequired</t>
+          <t>buildingId</t>
         </is>
       </c>
       <c r="L222" s="0" t="inlineStr">
@@ -4900,48 +4900,48 @@
       </c>
       <c r="N222" s="0" t="inlineStr">
         <is>
-          <t>等级要求</t>
+          <t>建筑ID</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="J223" s="0" t="inlineStr">
         <is>
-          <t>inputItems</t>
+          <t>levelRequired</t>
         </is>
       </c>
       <c r="L223" s="0" t="inlineStr">
         <is>
-          <t>(list#sep=;),cfg.ItemExchange#sep=,</t>
+          <t>int</t>
         </is>
       </c>
       <c r="N223" s="0" t="inlineStr">
         <is>
-          <t>输入材料</t>
+          <t>等级要求</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="J224" s="0" t="inlineStr">
         <is>
-          <t>outputItemId</t>
+          <t>inputItems</t>
         </is>
       </c>
       <c r="L224" s="0" t="inlineStr">
         <is>
-          <t>int</t>
+          <t>(list#sep=;),cfg.ItemExchange#sep=,</t>
         </is>
       </c>
       <c r="N224" s="0" t="inlineStr">
         <is>
-          <t>产出物品</t>
+          <t>输入材料</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="J225" s="0" t="inlineStr">
         <is>
-          <t>outputCount</t>
+          <t>outputItemId</t>
         </is>
       </c>
       <c r="L225" s="0" t="inlineStr">
@@ -4951,252 +4951,252 @@
       </c>
       <c r="N225" s="0" t="inlineStr">
         <is>
-          <t>产出数量</t>
+          <t>产出物品</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="J226" s="0" t="inlineStr">
         <is>
-          <t>productionTime</t>
+          <t>outputCount</t>
         </is>
       </c>
       <c r="L226" s="0" t="inlineStr">
         <is>
-          <t>float</t>
+          <t>int</t>
         </is>
       </c>
       <c r="N226" s="0" t="inlineStr">
         <is>
-          <t>生产耗时</t>
+          <t>产出数量</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="J227" s="0" t="inlineStr">
         <is>
+          <t>productionTime</t>
+        </is>
+      </c>
+      <c r="L227" s="0" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="N227" s="0" t="inlineStr">
+        <is>
+          <t>生产耗时</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="J228" s="0" t="inlineStr">
+        <is>
           <t>icon</t>
         </is>
       </c>
-      <c r="L227" s="0" t="inlineStr">
+      <c r="L228" s="0" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="N227" s="0" t="inlineStr">
+      <c r="N228" s="0" t="inlineStr">
         <is>
           <t>图标</t>
         </is>
       </c>
     </row>
-    <row r="228">
-      <c r="B228" s="0" t="inlineStr">
+    <row r="229">
+      <c r="B229" s="0" t="inlineStr">
         <is>
           <t>cfg.Order</t>
         </is>
       </c>
-      <c r="G228" s="0" t="inlineStr">
+      <c r="G229" s="0" t="inlineStr">
         <is>
           <t>订单配置</t>
         </is>
       </c>
-      <c r="I228" s="0" t="inlineStr">
+      <c r="I229" s="0" t="inlineStr">
         <is>
           <t>c</t>
-        </is>
-      </c>
-    </row>
-    <row r="229">
-      <c r="J229" s="0" t="inlineStr">
-        <is>
-          <t>id</t>
-        </is>
-      </c>
-      <c r="L229" s="0" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="N229" s="0" t="inlineStr">
-        <is>
-          <t>订单ID</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="J230" s="0" t="inlineStr">
         <is>
-          <t>requiredItems</t>
+          <t>id</t>
         </is>
       </c>
       <c r="L230" s="0" t="inlineStr">
         <is>
-          <t>(list#sep=;),cfg.ItemExchange#sep=,</t>
+          <t>int</t>
         </is>
       </c>
       <c r="N230" s="0" t="inlineStr">
         <is>
-          <t>需求物品</t>
+          <t>订单ID</t>
         </is>
       </c>
     </row>
     <row r="231">
       <c r="J231" s="0" t="inlineStr">
         <is>
-          <t>rewardGold</t>
+          <t>requiredItems</t>
         </is>
       </c>
       <c r="L231" s="0" t="inlineStr">
         <is>
-          <t>int</t>
+          <t>(list#sep=;),cfg.ItemExchange#sep=,</t>
         </is>
       </c>
       <c r="N231" s="0" t="inlineStr">
         <is>
-          <t>奖励金币</t>
+          <t>需求物品</t>
         </is>
       </c>
     </row>
     <row r="232">
       <c r="J232" s="0" t="inlineStr">
         <is>
-          <t>rewardItems</t>
+          <t>rewardGold</t>
         </is>
       </c>
       <c r="L232" s="0" t="inlineStr">
         <is>
-          <t>(list#sep=;),cfg.ItemExchange#sep=,</t>
+          <t>int</t>
         </is>
       </c>
       <c r="N232" s="0" t="inlineStr">
         <is>
-          <t>奖励物品</t>
+          <t>奖励金币</t>
         </is>
       </c>
     </row>
     <row r="233">
       <c r="J233" s="0" t="inlineStr">
         <is>
-          <t>rewardExp</t>
+          <t>rewardItems</t>
         </is>
       </c>
       <c r="L233" s="0" t="inlineStr">
         <is>
-          <t>int</t>
+          <t>(list#sep=;),cfg.ItemExchange#sep=,</t>
         </is>
       </c>
       <c r="N233" s="0" t="inlineStr">
         <is>
-          <t>奖励经验</t>
+          <t>奖励物品</t>
         </is>
       </c>
     </row>
     <row r="234">
       <c r="J234" s="0" t="inlineStr">
         <is>
-          <t>timeLimit</t>
+          <t>rewardExp</t>
         </is>
       </c>
       <c r="L234" s="0" t="inlineStr">
         <is>
-          <t>float</t>
+          <t>int</t>
         </is>
       </c>
       <c r="N234" s="0" t="inlineStr">
         <is>
-          <t>时限</t>
+          <t>奖励经验</t>
         </is>
       </c>
     </row>
     <row r="235">
       <c r="J235" s="0" t="inlineStr">
         <is>
-          <t>weight</t>
+          <t>timeLimit</t>
         </is>
       </c>
       <c r="L235" s="0" t="inlineStr">
         <is>
-          <t>int</t>
+          <t>float</t>
         </is>
       </c>
       <c r="N235" s="0" t="inlineStr">
         <is>
-          <t>权重</t>
+          <t>时限</t>
         </is>
       </c>
     </row>
     <row r="236">
       <c r="J236" s="0" t="inlineStr">
         <is>
+          <t>weight</t>
+        </is>
+      </c>
+      <c r="L236" s="0" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="N236" s="0" t="inlineStr">
+        <is>
+          <t>权重</t>
+        </is>
+      </c>
+    </row>
+    <row r="237">
+      <c r="J237" s="0" t="inlineStr">
+        <is>
           <t>minPlayerLevel</t>
         </is>
       </c>
-      <c r="L236" s="0" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="N236" s="0" t="inlineStr">
+      <c r="L237" s="0" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="N237" s="0" t="inlineStr">
         <is>
           <t>最低等级</t>
         </is>
       </c>
     </row>
-    <row r="237">
-      <c r="B237" s="0" t="inlineStr">
+    <row r="238">
+      <c r="B238" s="0" t="inlineStr">
         <is>
           <t>cfg.SimTimeConfig</t>
         </is>
       </c>
-      <c r="G237" s="0" t="inlineStr">
+      <c r="G238" s="0" t="inlineStr">
         <is>
           <t>经营时间配置</t>
         </is>
       </c>
-      <c r="I237" s="0" t="inlineStr">
+      <c r="I238" s="0" t="inlineStr">
         <is>
           <t>c</t>
-        </is>
-      </c>
-    </row>
-    <row r="238">
-      <c r="J238" s="0" t="inlineStr">
-        <is>
-          <t>id</t>
-        </is>
-      </c>
-      <c r="L238" s="0" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="N238" s="0" t="inlineStr">
-        <is>
-          <t>ID</t>
         </is>
       </c>
     </row>
     <row r="239">
       <c r="J239" s="0" t="inlineStr">
         <is>
-          <t>baseSpeed</t>
+          <t>id</t>
         </is>
       </c>
       <c r="L239" s="0" t="inlineStr">
         <is>
-          <t>float</t>
+          <t>int</t>
         </is>
       </c>
       <c r="N239" s="0" t="inlineStr">
         <is>
-          <t>基础速度</t>
+          <t>ID</t>
         </is>
       </c>
     </row>
     <row r="240">
       <c r="J240" s="0" t="inlineStr">
         <is>
-          <t>fastSpeed</t>
+          <t>baseSpeed</t>
         </is>
       </c>
       <c r="L240" s="0" t="inlineStr">
@@ -5206,14 +5206,14 @@
       </c>
       <c r="N240" s="0" t="inlineStr">
         <is>
-          <t>加速速度</t>
+          <t>基础速度</t>
         </is>
       </c>
     </row>
     <row r="241">
       <c r="J241" s="0" t="inlineStr">
         <is>
-          <t>maxSpeed</t>
+          <t>fastSpeed</t>
         </is>
       </c>
       <c r="L241" s="0" t="inlineStr">
@@ -5223,14 +5223,14 @@
       </c>
       <c r="N241" s="0" t="inlineStr">
         <is>
-          <t>最大速度</t>
+          <t>加速速度</t>
         </is>
       </c>
     </row>
     <row r="242">
       <c r="J242" s="0" t="inlineStr">
         <is>
-          <t>orderRefreshInterval</t>
+          <t>maxSpeed</t>
         </is>
       </c>
       <c r="L242" s="0" t="inlineStr">
@@ -5240,82 +5240,82 @@
       </c>
       <c r="N242" s="0" t="inlineStr">
         <is>
-          <t>订单刷新间隔</t>
+          <t>最大速度</t>
         </is>
       </c>
     </row>
     <row r="243">
       <c r="J243" s="0" t="inlineStr">
         <is>
+          <t>orderRefreshInterval</t>
+        </is>
+      </c>
+      <c r="L243" s="0" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="N243" s="0" t="inlineStr">
+        <is>
+          <t>订单刷新间隔</t>
+        </is>
+      </c>
+    </row>
+    <row r="244">
+      <c r="J244" s="0" t="inlineStr">
+        <is>
           <t>maxOrderCount</t>
         </is>
       </c>
-      <c r="L243" s="0" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="N243" s="0" t="inlineStr">
+      <c r="L244" s="0" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="N244" s="0" t="inlineStr">
         <is>
           <t>最大订单数</t>
         </is>
       </c>
     </row>
-    <row r="244">
-      <c r="B244" s="0" t="inlineStr">
+    <row r="245">
+      <c r="B245" s="0" t="inlineStr">
         <is>
           <t>cfg.Camera3D</t>
         </is>
       </c>
-      <c r="G244" s="0" t="inlineStr">
+      <c r="G245" s="0" t="inlineStr">
         <is>
           <t>3D摄像机配置</t>
         </is>
       </c>
-      <c r="I244" s="0" t="inlineStr">
+      <c r="I245" s="0" t="inlineStr">
         <is>
           <t>c</t>
-        </is>
-      </c>
-    </row>
-    <row r="245">
-      <c r="J245" s="0" t="inlineStr">
-        <is>
-          <t>id</t>
-        </is>
-      </c>
-      <c r="L245" s="0" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="N245" s="0" t="inlineStr">
-        <is>
-          <t>配置ID</t>
         </is>
       </c>
     </row>
     <row r="246">
       <c r="J246" s="0" t="inlineStr">
         <is>
-          <t>pitchAngle</t>
+          <t>id</t>
         </is>
       </c>
       <c r="L246" s="0" t="inlineStr">
         <is>
-          <t>float</t>
+          <t>int</t>
         </is>
       </c>
       <c r="N246" s="0" t="inlineStr">
         <is>
-          <t>俯视角度</t>
+          <t>配置ID</t>
         </is>
       </c>
     </row>
     <row r="247">
       <c r="J247" s="0" t="inlineStr">
         <is>
-          <t>initialHeight</t>
+          <t>pitchAngle</t>
         </is>
       </c>
       <c r="L247" s="0" t="inlineStr">
@@ -5325,14 +5325,14 @@
       </c>
       <c r="N247" s="0" t="inlineStr">
         <is>
-          <t>初始高度</t>
+          <t>俯视角度</t>
         </is>
       </c>
     </row>
     <row r="248">
       <c r="J248" s="0" t="inlineStr">
         <is>
-          <t>initialDistance</t>
+          <t>initialHeight</t>
         </is>
       </c>
       <c r="L248" s="0" t="inlineStr">
@@ -5342,14 +5342,14 @@
       </c>
       <c r="N248" s="0" t="inlineStr">
         <is>
-          <t>初始距离</t>
+          <t>初始高度</t>
         </is>
       </c>
     </row>
     <row r="249">
       <c r="J249" s="0" t="inlineStr">
         <is>
-          <t>fov</t>
+          <t>initialDistance</t>
         </is>
       </c>
       <c r="L249" s="0" t="inlineStr">
@@ -5359,14 +5359,14 @@
       </c>
       <c r="N249" s="0" t="inlineStr">
         <is>
-          <t>视场角</t>
+          <t>初始距离</t>
         </is>
       </c>
     </row>
     <row r="250">
       <c r="J250" s="0" t="inlineStr">
         <is>
-          <t>minZoom</t>
+          <t>fov</t>
         </is>
       </c>
       <c r="L250" s="0" t="inlineStr">
@@ -5376,14 +5376,14 @@
       </c>
       <c r="N250" s="0" t="inlineStr">
         <is>
-          <t>最小缩放</t>
+          <t>视场角</t>
         </is>
       </c>
     </row>
     <row r="251">
       <c r="J251" s="0" t="inlineStr">
         <is>
-          <t>maxZoom</t>
+          <t>minZoom</t>
         </is>
       </c>
       <c r="L251" s="0" t="inlineStr">
@@ -5393,14 +5393,14 @@
       </c>
       <c r="N251" s="0" t="inlineStr">
         <is>
-          <t>最大缩放</t>
+          <t>最小缩放</t>
         </is>
       </c>
     </row>
     <row r="252">
       <c r="J252" s="0" t="inlineStr">
         <is>
-          <t>moveSpeed</t>
+          <t>maxZoom</t>
         </is>
       </c>
       <c r="L252" s="0" t="inlineStr">
@@ -5410,14 +5410,14 @@
       </c>
       <c r="N252" s="0" t="inlineStr">
         <is>
-          <t>移动速度</t>
+          <t>最大缩放</t>
         </is>
       </c>
     </row>
     <row r="253">
       <c r="J253" s="0" t="inlineStr">
         <is>
-          <t>zoomSpeed</t>
+          <t>moveSpeed</t>
         </is>
       </c>
       <c r="L253" s="0" t="inlineStr">
@@ -5427,14 +5427,14 @@
       </c>
       <c r="N253" s="0" t="inlineStr">
         <is>
-          <t>缩放速度</t>
+          <t>移动速度</t>
         </is>
       </c>
     </row>
     <row r="254">
       <c r="J254" s="0" t="inlineStr">
         <is>
-          <t>maxRotationAngle</t>
+          <t>zoomSpeed</t>
         </is>
       </c>
       <c r="L254" s="0" t="inlineStr">
@@ -5444,14 +5444,14 @@
       </c>
       <c r="N254" s="0" t="inlineStr">
         <is>
-          <t>最大旋转角度</t>
+          <t>缩放速度</t>
         </is>
       </c>
     </row>
     <row r="255">
       <c r="J255" s="0" t="inlineStr">
         <is>
-          <t>rotationSpeed</t>
+          <t>maxRotationAngle</t>
         </is>
       </c>
       <c r="L255" s="0" t="inlineStr">
@@ -5461,60 +5461,66 @@
       </c>
       <c r="N255" s="0" t="inlineStr">
         <is>
-          <t>旋转速度</t>
+          <t>最大旋转角度</t>
         </is>
       </c>
     </row>
     <row r="256">
       <c r="J256" s="0" t="inlineStr">
         <is>
+          <t>rotationSpeed</t>
+        </is>
+      </c>
+      <c r="L256" s="0" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="N256" s="0" t="inlineStr">
+        <is>
+          <t>旋转速度</t>
+        </is>
+      </c>
+    </row>
+    <row r="257">
+      <c r="J257" s="0" t="inlineStr">
+        <is>
           <t>followSmoothTime</t>
         </is>
       </c>
-      <c r="L256" s="0" t="inlineStr">
-        <is>
-          <t>float</t>
-        </is>
-      </c>
-      <c r="N256" s="0" t="inlineStr">
+      <c r="L257" s="0" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="N257" s="0" t="inlineStr">
         <is>
           <t>跟随平滑时间</t>
         </is>
       </c>
     </row>
-    <row r="258">
-      <c r="B258" s="0" t="inlineStr">
+    <row r="258"/>
+    <row r="259">
+      <c r="B259" s="0" t="inlineStr">
         <is>
           <t>cfg.LootContainer</t>
         </is>
       </c>
-      <c r="G258" s="0" t="inlineStr">
+      <c r="G259" s="0" t="inlineStr">
         <is>
           <t>容器掉落记录</t>
         </is>
       </c>
-      <c r="I258" s="0" t="inlineStr">
+      <c r="I259" s="0" t="inlineStr">
         <is>
           <t>c</t>
-        </is>
-      </c>
-    </row>
-    <row r="259">
-      <c r="J259" s="0" t="inlineStr">
-        <is>
-          <t>id</t>
-        </is>
-      </c>
-      <c r="L259" s="0" t="inlineStr">
-        <is>
-          <t>int</t>
         </is>
       </c>
     </row>
     <row r="260">
       <c r="J260" s="0" t="inlineStr">
         <is>
-          <t>containerId</t>
+          <t>id</t>
         </is>
       </c>
       <c r="L260" s="0" t="inlineStr">
@@ -5526,7 +5532,7 @@
     <row r="261">
       <c r="J261" s="0" t="inlineStr">
         <is>
-          <t>itemId</t>
+          <t>containerId</t>
         </is>
       </c>
       <c r="L261" s="0" t="inlineStr">
@@ -5538,7 +5544,7 @@
     <row r="262">
       <c r="J262" s="0" t="inlineStr">
         <is>
-          <t>weight</t>
+          <t>itemId</t>
         </is>
       </c>
       <c r="L262" s="0" t="inlineStr">
@@ -5550,7 +5556,7 @@
     <row r="263">
       <c r="J263" s="0" t="inlineStr">
         <is>
-          <t>minCount</t>
+          <t>weight</t>
         </is>
       </c>
       <c r="L263" s="0" t="inlineStr">
@@ -5562,207 +5568,203 @@
     <row r="264">
       <c r="J264" s="0" t="inlineStr">
         <is>
+          <t>minCount</t>
+        </is>
+      </c>
+      <c r="L264" s="0" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+    </row>
+    <row r="265">
+      <c r="J265" s="0" t="inlineStr">
+        <is>
           <t>maxCount</t>
         </is>
       </c>
-      <c r="L264" s="0" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-    </row>
-    <row r="266">
-      <c r="B266" s="0" t="inlineStr">
+      <c r="L265" s="0" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+    </row>
+    <row r="266"/>
+    <row r="267">
+      <c r="B267" s="0" t="inlineStr">
         <is>
           <t>cfg.Note</t>
         </is>
       </c>
-      <c r="G266" s="0" t="inlineStr">
+      <c r="G267" s="0" t="inlineStr">
         <is>
           <t>小纸条记录</t>
         </is>
       </c>
-      <c r="I266" s="0" t="inlineStr">
+      <c r="I267" s="0" t="inlineStr">
         <is>
           <t>c</t>
-        </is>
-      </c>
-    </row>
-    <row r="267">
-      <c r="J267" s="0" t="inlineStr">
-        <is>
-          <t>id</t>
-        </is>
-      </c>
-      <c r="L267" s="0" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="N267" s="0" t="inlineStr">
-        <is>
-          <t>纸条ID</t>
         </is>
       </c>
     </row>
     <row r="268">
       <c r="J268" s="0" t="inlineStr">
         <is>
-          <t>title</t>
+          <t>id</t>
         </is>
       </c>
       <c r="L268" s="0" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>int</t>
         </is>
       </c>
       <c r="N268" s="0" t="inlineStr">
         <is>
-          <t>标题</t>
+          <t>纸条ID</t>
         </is>
       </c>
     </row>
     <row r="269">
       <c r="J269" s="0" t="inlineStr">
         <is>
+          <t>title</t>
+        </is>
+      </c>
+      <c r="L269" s="0" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="N269" s="0" t="inlineStr">
+        <is>
+          <t>标题</t>
+        </is>
+      </c>
+    </row>
+    <row r="270">
+      <c r="J270" s="0" t="inlineStr">
+        <is>
           <t>content</t>
         </is>
       </c>
-      <c r="L269" s="0" t="inlineStr">
+      <c r="L270" s="0" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="N269" s="0" t="inlineStr">
+      <c r="N270" s="0" t="inlineStr">
         <is>
           <t>正文(支持
 换行)</t>
         </is>
       </c>
     </row>
-    <row r="270">
-      <c r="B270" s="0" t="inlineStr">
+    <row r="271">
+      <c r="B271" s="0" t="inlineStr">
         <is>
           <t>cfg.PlayerLevel</t>
         </is>
       </c>
-      <c r="G270" s="0" t="inlineStr">
+      <c r="G271" s="0" t="inlineStr">
         <is>
           <t>玩家等级经验表</t>
         </is>
       </c>
-      <c r="I270" s="0" t="inlineStr">
+      <c r="I271" s="0" t="inlineStr">
         <is>
           <t>c</t>
-        </is>
-      </c>
-    </row>
-    <row r="271">
-      <c r="J271" s="0" t="inlineStr">
-        <is>
-          <t>level</t>
-        </is>
-      </c>
-      <c r="L271" s="0" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="N271" s="0" t="inlineStr">
-        <is>
-          <t>等级</t>
         </is>
       </c>
     </row>
     <row r="272">
       <c r="J272" s="0" t="inlineStr">
         <is>
+          <t>level</t>
+        </is>
+      </c>
+      <c r="L272" s="0" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="N272" s="0" t="inlineStr">
+        <is>
+          <t>等级</t>
+        </is>
+      </c>
+    </row>
+    <row r="273">
+      <c r="J273" s="0" t="inlineStr">
+        <is>
           <t>expToNext</t>
         </is>
       </c>
-      <c r="L272" s="0" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="N272" s="0" t="inlineStr">
+      <c r="L273" s="0" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="N273" s="0" t="inlineStr">
         <is>
           <t>升到下一级所需经验</t>
         </is>
       </c>
     </row>
-    <row r="273">
-      <c r="B273" s="0" t="inlineStr">
+    <row r="274">
+      <c r="B274" s="0" t="inlineStr">
         <is>
           <t>cfg.Unlock</t>
         </is>
       </c>
-      <c r="G273" s="0" t="inlineStr">
+      <c r="G274" s="0" t="inlineStr">
         <is>
           <t>内容解锁表</t>
         </is>
       </c>
-      <c r="I273" s="0" t="inlineStr">
+      <c r="I274" s="0" t="inlineStr">
         <is>
           <t>c</t>
-        </is>
-      </c>
-    </row>
-    <row r="274">
-      <c r="J274" s="0" t="inlineStr">
-        <is>
-          <t>id</t>
-        </is>
-      </c>
-      <c r="L274" s="0" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="N274" s="0" t="inlineStr">
-        <is>
-          <t>解锁ID</t>
         </is>
       </c>
     </row>
     <row r="275">
       <c r="J275" s="0" t="inlineStr">
         <is>
-          <t>contentType</t>
+          <t>id</t>
         </is>
       </c>
       <c r="L275" s="0" t="inlineStr">
         <is>
-          <t>cfg.UnlockContentType</t>
+          <t>int</t>
         </is>
       </c>
       <c r="N275" s="0" t="inlineStr">
         <is>
-          <t>内容类型</t>
+          <t>解锁ID</t>
         </is>
       </c>
     </row>
     <row r="276">
       <c r="J276" s="0" t="inlineStr">
         <is>
-          <t>targetId</t>
+          <t>contentType</t>
         </is>
       </c>
       <c r="L276" s="0" t="inlineStr">
         <is>
-          <t>int</t>
+          <t>cfg.UnlockContentType</t>
         </is>
       </c>
       <c r="N276" s="0" t="inlineStr">
         <is>
-          <t>目标ID（关卡/武器）</t>
+          <t>内容类型</t>
         </is>
       </c>
     </row>
     <row r="277">
       <c r="J277" s="0" t="inlineStr">
         <is>
-          <t>requirePlayerLevel</t>
+          <t>targetId</t>
         </is>
       </c>
       <c r="L277" s="0" t="inlineStr">
@@ -5772,14 +5774,14 @@
       </c>
       <c r="N277" s="0" t="inlineStr">
         <is>
-          <t>要求玩家等级(0=无)</t>
+          <t>目标ID（关卡/武器）</t>
         </is>
       </c>
     </row>
     <row r="278">
       <c r="J278" s="0" t="inlineStr">
         <is>
-          <t>requireCompleteLevelId</t>
+          <t>requirePlayerLevel</t>
         </is>
       </c>
       <c r="L278" s="0" t="inlineStr">
@@ -5789,14 +5791,14 @@
       </c>
       <c r="N278" s="0" t="inlineStr">
         <is>
-          <t>要求通关关卡ID(0=无)</t>
+          <t>要求玩家等级(0=无)</t>
         </is>
       </c>
     </row>
     <row r="279">
       <c r="J279" s="0" t="inlineStr">
         <is>
-          <t>costGold</t>
+          <t>requireCompleteLevelId</t>
         </is>
       </c>
       <c r="L279" s="0" t="inlineStr">
@@ -5806,82 +5808,82 @@
       </c>
       <c r="N279" s="0" t="inlineStr">
         <is>
-          <t>解锁花费金币(0=免费)</t>
+          <t>要求通关关卡ID(0=无)</t>
         </is>
       </c>
     </row>
     <row r="280">
       <c r="J280" s="0" t="inlineStr">
         <is>
+          <t>costGold</t>
+        </is>
+      </c>
+      <c r="L280" s="0" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="N280" s="0" t="inlineStr">
+        <is>
+          <t>解锁花费金币(0=免费)</t>
+        </is>
+      </c>
+    </row>
+    <row r="281">
+      <c r="J281" s="0" t="inlineStr">
+        <is>
           <t>comment</t>
         </is>
       </c>
-      <c r="L280" s="0" t="inlineStr">
+      <c r="L281" s="0" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="N280" s="0" t="inlineStr">
+      <c r="N281" s="0" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="281">
-      <c r="B281" s="0" t="inlineStr">
+    <row r="282">
+      <c r="B282" s="0" t="inlineStr">
         <is>
           <t>cfg.Npc</t>
         </is>
       </c>
-      <c r="G281" s="0" t="inlineStr">
+      <c r="G282" s="0" t="inlineStr">
         <is>
           <t>NPC记录</t>
         </is>
       </c>
-      <c r="I281" s="0" t="inlineStr">
+      <c r="I282" s="0" t="inlineStr">
         <is>
           <t>c</t>
-        </is>
-      </c>
-    </row>
-    <row r="282">
-      <c r="J282" s="0" t="inlineStr">
-        <is>
-          <t>id</t>
-        </is>
-      </c>
-      <c r="L282" s="0" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="N282" s="0" t="inlineStr">
-        <is>
-          <t>NPC ID</t>
         </is>
       </c>
     </row>
     <row r="283">
       <c r="J283" s="0" t="inlineStr">
         <is>
-          <t>name</t>
+          <t>id</t>
         </is>
       </c>
       <c r="L283" s="0" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>int</t>
         </is>
       </c>
       <c r="N283" s="0" t="inlineStr">
         <is>
-          <t>显示名</t>
+          <t>NPC ID</t>
         </is>
       </c>
     </row>
     <row r="284">
       <c r="J284" s="0" t="inlineStr">
         <is>
-          <t>role</t>
+          <t>name</t>
         </is>
       </c>
       <c r="L284" s="0" t="inlineStr">
@@ -5891,201 +5893,201 @@
       </c>
       <c r="N284" s="0" t="inlineStr">
         <is>
-          <t>身份/职业</t>
+          <t>显示名</t>
         </is>
       </c>
     </row>
     <row r="285">
       <c r="J285" s="0" t="inlineStr">
         <is>
-          <t>moveSpeed</t>
+          <t>role</t>
         </is>
       </c>
       <c r="L285" s="0" t="inlineStr">
         <is>
-          <t>float</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N285" s="0" t="inlineStr">
         <is>
-          <t>移动速度(0=站桩)</t>
+          <t>身份/职业</t>
         </is>
       </c>
     </row>
     <row r="286">
       <c r="J286" s="0" t="inlineStr">
         <is>
-          <t>patrolPath</t>
+          <t>moveSpeed</t>
         </is>
       </c>
       <c r="L286" s="0" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>float</t>
         </is>
       </c>
       <c r="N286" s="0" t="inlineStr">
         <is>
-          <t>巡逻路径(x,z|x,z 空=不巡逻)</t>
+          <t>移动速度(0=站桩)</t>
         </is>
       </c>
     </row>
     <row r="287">
       <c r="J287" s="0" t="inlineStr">
         <is>
+          <t>patrolPath</t>
+        </is>
+      </c>
+      <c r="L287" s="0" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="N287" s="0" t="inlineStr">
+        <is>
+          <t>巡逻路径(x,z|x,z 空=不巡逻)</t>
+        </is>
+      </c>
+    </row>
+    <row r="288">
+      <c r="J288" s="0" t="inlineStr">
+        <is>
           <t>dialogueId</t>
         </is>
       </c>
-      <c r="L287" s="0" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="N287" s="0" t="inlineStr">
+      <c r="L288" s="0" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="N288" s="0" t="inlineStr">
         <is>
           <t>对话ID(预留,0=无)</t>
         </is>
       </c>
     </row>
-    <row r="288">
-      <c r="B288" s="0" t="inlineStr">
+    <row r="289">
+      <c r="B289" s="0" t="inlineStr">
         <is>
           <t>cfg.Dialogue</t>
         </is>
       </c>
-      <c r="G288" s="0" t="inlineStr">
+      <c r="G289" s="0" t="inlineStr">
         <is>
           <t>对话头</t>
         </is>
       </c>
-      <c r="I288" s="0" t="inlineStr">
+      <c r="I289" s="0" t="inlineStr">
         <is>
           <t>c</t>
-        </is>
-      </c>
-    </row>
-    <row r="289">
-      <c r="J289" s="0" t="inlineStr">
-        <is>
-          <t>id</t>
-        </is>
-      </c>
-      <c r="L289" s="0" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="N289" s="0" t="inlineStr">
-        <is>
-          <t>对话ID</t>
         </is>
       </c>
     </row>
     <row r="290">
       <c r="J290" s="0" t="inlineStr">
         <is>
-          <t>name</t>
+          <t>id</t>
         </is>
       </c>
       <c r="L290" s="0" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>int</t>
         </is>
       </c>
       <c r="N290" s="0" t="inlineStr">
         <is>
-          <t>注释名(不显示)</t>
+          <t>对话ID</t>
         </is>
       </c>
     </row>
     <row r="291">
       <c r="J291" s="0" t="inlineStr">
         <is>
-          <t>startNode</t>
+          <t>name</t>
         </is>
       </c>
       <c r="L291" s="0" t="inlineStr">
         <is>
-          <t>int</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N291" s="0" t="inlineStr">
         <is>
-          <t>起始节点ID</t>
+          <t>注释名(不显示)</t>
         </is>
       </c>
     </row>
     <row r="292">
       <c r="J292" s="0" t="inlineStr">
         <is>
-          <t>onceOnly</t>
+          <t>startNode</t>
         </is>
       </c>
       <c r="L292" s="0" t="inlineStr">
         <is>
-          <t>bool</t>
+          <t>int</t>
         </is>
       </c>
       <c r="N292" s="0" t="inlineStr">
         <is>
-          <t>只触发一次</t>
+          <t>起始节点ID</t>
         </is>
       </c>
     </row>
     <row r="293">
       <c r="J293" s="0" t="inlineStr">
         <is>
+          <t>onceOnly</t>
+        </is>
+      </c>
+      <c r="L293" s="0" t="inlineStr">
+        <is>
+          <t>bool</t>
+        </is>
+      </c>
+      <c r="N293" s="0" t="inlineStr">
+        <is>
+          <t>只触发一次</t>
+        </is>
+      </c>
+    </row>
+    <row r="294">
+      <c r="J294" s="0" t="inlineStr">
+        <is>
           <t>priority</t>
         </is>
       </c>
-      <c r="L293" s="0" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="N293" s="0" t="inlineStr">
+      <c r="L294" s="0" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="N294" s="0" t="inlineStr">
         <is>
           <t>优先级(大优先)</t>
         </is>
       </c>
     </row>
-    <row r="294">
-      <c r="B294" s="0" t="inlineStr">
+    <row r="295">
+      <c r="B295" s="0" t="inlineStr">
         <is>
           <t>cfg.DialogueNode</t>
         </is>
       </c>
-      <c r="G294" s="0" t="inlineStr">
+      <c r="G295" s="0" t="inlineStr">
         <is>
           <t>对话节点</t>
         </is>
       </c>
-      <c r="I294" s="0" t="inlineStr">
+      <c r="I295" s="0" t="inlineStr">
         <is>
           <t>c</t>
-        </is>
-      </c>
-    </row>
-    <row r="295">
-      <c r="J295" s="0" t="inlineStr">
-        <is>
-          <t>id</t>
-        </is>
-      </c>
-      <c r="L295" s="0" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="N295" s="0" t="inlineStr">
-        <is>
-          <t>节点ID</t>
         </is>
       </c>
     </row>
     <row r="296">
       <c r="J296" s="0" t="inlineStr">
         <is>
-          <t>dialogueId</t>
+          <t>id</t>
         </is>
       </c>
       <c r="L296" s="0" t="inlineStr">
@@ -6095,31 +6097,31 @@
       </c>
       <c r="N296" s="0" t="inlineStr">
         <is>
-          <t>所属对话</t>
+          <t>节点ID</t>
         </is>
       </c>
     </row>
     <row r="297">
       <c r="J297" s="0" t="inlineStr">
         <is>
-          <t>type</t>
+          <t>dialogueId</t>
         </is>
       </c>
       <c r="L297" s="0" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>int</t>
         </is>
       </c>
       <c r="N297" s="0" t="inlineStr">
         <is>
-          <t>类型(line/choice/setflag/end)</t>
+          <t>所属对话</t>
         </is>
       </c>
     </row>
     <row r="298">
       <c r="J298" s="0" t="inlineStr">
         <is>
-          <t>speaker</t>
+          <t>type</t>
         </is>
       </c>
       <c r="L298" s="0" t="inlineStr">
@@ -6129,14 +6131,14 @@
       </c>
       <c r="N298" s="0" t="inlineStr">
         <is>
-          <t>说话人</t>
+          <t>类型(line/choice/setflag/end)</t>
         </is>
       </c>
     </row>
     <row r="299">
       <c r="J299" s="0" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>speaker</t>
         </is>
       </c>
       <c r="L299" s="0" t="inlineStr">
@@ -6146,14 +6148,14 @@
       </c>
       <c r="N299" s="0" t="inlineStr">
         <is>
-          <t>正文</t>
+          <t>说话人</t>
         </is>
       </c>
     </row>
     <row r="300">
       <c r="J300" s="0" t="inlineStr">
         <is>
-          <t>choices</t>
+          <t>text</t>
         </is>
       </c>
       <c r="L300" s="0" t="inlineStr">
@@ -6163,14 +6165,14 @@
       </c>
       <c r="N300" s="0" t="inlineStr">
         <is>
-          <t>选项(文本-&gt;节点|...)</t>
+          <t>正文</t>
         </is>
       </c>
     </row>
     <row r="301">
       <c r="J301" s="0" t="inlineStr">
         <is>
-          <t>condition</t>
+          <t>choices</t>
         </is>
       </c>
       <c r="L301" s="0" t="inlineStr">
@@ -6180,14 +6182,14 @@
       </c>
       <c r="N301" s="0" t="inlineStr">
         <is>
-          <t>进入条件</t>
+          <t>选项(文本-&gt;节点|...)</t>
         </is>
       </c>
     </row>
     <row r="302">
       <c r="J302" s="0" t="inlineStr">
         <is>
-          <t>action</t>
+          <t>condition</t>
         </is>
       </c>
       <c r="L302" s="0" t="inlineStr">
@@ -6197,82 +6199,82 @@
       </c>
       <c r="N302" s="0" t="inlineStr">
         <is>
-          <t>到达动作</t>
+          <t>进入条件</t>
         </is>
       </c>
     </row>
     <row r="303">
       <c r="J303" s="0" t="inlineStr">
         <is>
+          <t>action</t>
+        </is>
+      </c>
+      <c r="L303" s="0" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="N303" s="0" t="inlineStr">
+        <is>
+          <t>到达动作</t>
+        </is>
+      </c>
+    </row>
+    <row r="304">
+      <c r="J304" s="0" t="inlineStr">
+        <is>
           <t>next</t>
         </is>
       </c>
-      <c r="L303" s="0" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="N303" s="0" t="inlineStr">
+      <c r="L304" s="0" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="N304" s="0" t="inlineStr">
         <is>
           <t>下一节点(0=结束)</t>
         </is>
       </c>
     </row>
-    <row r="304">
-      <c r="B304" s="0" t="inlineStr">
+    <row r="305">
+      <c r="B305" s="0" t="inlineStr">
         <is>
           <t>cfg.Quest</t>
         </is>
       </c>
-      <c r="G304" s="0" t="inlineStr">
+      <c r="G305" s="0" t="inlineStr">
         <is>
           <t>任务定义</t>
         </is>
       </c>
-      <c r="I304" s="0" t="inlineStr">
+      <c r="I305" s="0" t="inlineStr">
         <is>
           <t>c</t>
-        </is>
-      </c>
-    </row>
-    <row r="305">
-      <c r="J305" s="0" t="inlineStr">
-        <is>
-          <t>id</t>
-        </is>
-      </c>
-      <c r="L305" s="0" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="N305" s="0" t="inlineStr">
-        <is>
-          <t>任务ID</t>
         </is>
       </c>
     </row>
     <row r="306">
       <c r="J306" s="0" t="inlineStr">
         <is>
-          <t>name</t>
+          <t>id</t>
         </is>
       </c>
       <c r="L306" s="0" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>int</t>
         </is>
       </c>
       <c r="N306" s="0" t="inlineStr">
         <is>
-          <t>显示名</t>
+          <t>任务ID</t>
         </is>
       </c>
     </row>
     <row r="307">
       <c r="J307" s="0" t="inlineStr">
         <is>
-          <t>desc</t>
+          <t>name</t>
         </is>
       </c>
       <c r="L307" s="0" t="inlineStr">
@@ -6282,48 +6284,48 @@
       </c>
       <c r="N307" s="0" t="inlineStr">
         <is>
-          <t>描述</t>
+          <t>显示名</t>
         </is>
       </c>
     </row>
     <row r="308">
       <c r="J308" s="0" t="inlineStr">
         <is>
-          <t>giverNpc</t>
+          <t>desc</t>
         </is>
       </c>
       <c r="L308" s="0" t="inlineStr">
         <is>
-          <t>int</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N308" s="0" t="inlineStr">
         <is>
-          <t>发布NPC(0=任务板)</t>
+          <t>描述</t>
         </is>
       </c>
     </row>
     <row r="309">
       <c r="J309" s="0" t="inlineStr">
         <is>
-          <t>prereq</t>
+          <t>giverNpc</t>
         </is>
       </c>
       <c r="L309" s="0" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>int</t>
         </is>
       </c>
       <c r="N309" s="0" t="inlineStr">
         <is>
-          <t>接取条件表达式(空=无)</t>
+          <t>发布NPC(0=任务板)</t>
         </is>
       </c>
     </row>
     <row r="310">
       <c r="J310" s="0" t="inlineStr">
         <is>
-          <t>rewards</t>
+          <t>prereq</t>
         </is>
       </c>
       <c r="L310" s="0" t="inlineStr">
@@ -6333,65 +6335,65 @@
       </c>
       <c r="N310" s="0" t="inlineStr">
         <is>
-          <t>奖励(gold:200|exp:50|item:3001:2)</t>
+          <t>接取条件表达式(空=无)</t>
         </is>
       </c>
     </row>
     <row r="311">
       <c r="J311" s="0" t="inlineStr">
         <is>
+          <t>rewards</t>
+        </is>
+      </c>
+      <c r="L311" s="0" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="N311" s="0" t="inlineStr">
+        <is>
+          <t>奖励(gold:200|exp:50|item:3001:2)</t>
+        </is>
+      </c>
+    </row>
+    <row r="312">
+      <c r="J312" s="0" t="inlineStr">
+        <is>
           <t>nextQuest</t>
         </is>
       </c>
-      <c r="L311" s="0" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="N311" s="0" t="inlineStr">
+      <c r="L312" s="0" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="N312" s="0" t="inlineStr">
         <is>
           <t>后继任务(0=无)</t>
         </is>
       </c>
     </row>
-    <row r="312">
-      <c r="B312" s="0" t="inlineStr">
+    <row r="313">
+      <c r="B313" s="0" t="inlineStr">
         <is>
           <t>cfg.QuestObjective</t>
         </is>
       </c>
-      <c r="G312" s="0" t="inlineStr">
+      <c r="G313" s="0" t="inlineStr">
         <is>
           <t>任务目标</t>
         </is>
       </c>
-      <c r="I312" s="0" t="inlineStr">
+      <c r="I313" s="0" t="inlineStr">
         <is>
           <t>c</t>
-        </is>
-      </c>
-    </row>
-    <row r="313">
-      <c r="J313" s="0" t="inlineStr">
-        <is>
-          <t>id</t>
-        </is>
-      </c>
-      <c r="L313" s="0" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="N313" s="0" t="inlineStr">
-        <is>
-          <t>目标ID</t>
         </is>
       </c>
     </row>
     <row r="314">
       <c r="J314" s="0" t="inlineStr">
         <is>
-          <t>questId</t>
+          <t>id</t>
         </is>
       </c>
       <c r="L314" s="0" t="inlineStr">
@@ -6401,31 +6403,31 @@
       </c>
       <c r="N314" s="0" t="inlineStr">
         <is>
-          <t>所属任务</t>
+          <t>目标ID</t>
         </is>
       </c>
     </row>
     <row r="315">
       <c r="J315" s="0" t="inlineStr">
         <is>
-          <t>type</t>
+          <t>questId</t>
         </is>
       </c>
       <c r="L315" s="0" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>int</t>
         </is>
       </c>
       <c r="N315" s="0" t="inlineStr">
         <is>
-          <t>类型(kill/collect/extract/flag)</t>
+          <t>所属任务</t>
         </is>
       </c>
     </row>
     <row r="316">
       <c r="J316" s="0" t="inlineStr">
         <is>
-          <t>targetId</t>
+          <t>type</t>
         </is>
       </c>
       <c r="L316" s="0" t="inlineStr">
@@ -6435,158 +6437,175 @@
       </c>
       <c r="N316" s="0" t="inlineStr">
         <is>
-          <t>目标ID/标志键</t>
+          <t>类型(kill/collect/extract/flag)</t>
         </is>
       </c>
     </row>
     <row r="317">
       <c r="J317" s="0" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>targetId</t>
         </is>
       </c>
       <c r="L317" s="0" t="inlineStr">
         <is>
-          <t>int</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N317" s="0" t="inlineStr">
         <is>
-          <t>需求数(extract恒1)</t>
+          <t>目标ID/标志键</t>
         </is>
       </c>
     </row>
     <row r="318">
       <c r="J318" s="0" t="inlineStr">
         <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="L318" s="0" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="N318" s="0" t="inlineStr">
+        <is>
+          <t>需求数(extract恒1)</t>
+        </is>
+      </c>
+    </row>
+    <row r="319">
+      <c r="J319" s="0" t="inlineStr">
+        <is>
           <t>desc</t>
         </is>
       </c>
-      <c r="L318" s="0" t="inlineStr">
+      <c r="L319" s="0" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="N318" s="0" t="inlineStr">
+      <c r="N319" s="0" t="inlineStr">
         <is>
           <t>目标一行描述</t>
         </is>
       </c>
     </row>
-    <row r="319">
-      <c r="B319" t="inlineStr">
+    <row r="320">
+      <c r="B320" s="0" t="inlineStr">
         <is>
           <t>cfg.Localization</t>
         </is>
       </c>
-      <c r="G319" t="inlineStr">
+      <c r="G320" s="0" t="inlineStr">
         <is>
           <t>本地化词条</t>
         </is>
       </c>
-      <c r="I319" t="inlineStr">
+      <c r="I320" s="0" t="inlineStr">
         <is>
           <t>c</t>
         </is>
       </c>
     </row>
-    <row r="320">
-      <c r="J320" t="inlineStr">
+    <row r="321">
+      <c r="J321" s="0" t="inlineStr">
         <is>
           <t>key</t>
         </is>
       </c>
-      <c r="L320" t="inlineStr">
+      <c r="L321" s="0" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="N320" t="inlineStr">
+      <c r="N321" s="0" t="inlineStr">
         <is>
           <t>词条Key</t>
         </is>
       </c>
     </row>
-    <row r="321">
-      <c r="J321" t="inlineStr">
+    <row r="322">
+      <c r="J322" s="0" t="inlineStr">
         <is>
           <t>en</t>
         </is>
       </c>
-      <c r="L321" t="inlineStr">
+      <c r="L322" s="0" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="N321" t="inlineStr">
+      <c r="N322" s="0" t="inlineStr">
         <is>
           <t>英文(必填/兜底)</t>
         </is>
       </c>
     </row>
-    <row r="322">
-      <c r="J322" t="inlineStr">
+    <row r="323">
+      <c r="J323" s="0" t="inlineStr">
         <is>
           <t>zh_cn</t>
         </is>
       </c>
-      <c r="L322" t="inlineStr">
+      <c r="L323" s="0" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="N322" t="inlineStr">
+      <c r="N323" s="0" t="inlineStr">
         <is>
           <t>简体中文</t>
         </is>
       </c>
     </row>
-    <row r="323">
-      <c r="J323" t="inlineStr">
+    <row r="324">
+      <c r="J324" s="0" t="inlineStr">
         <is>
           <t>zh_tw</t>
         </is>
       </c>
-      <c r="L323" t="inlineStr">
+      <c r="L324" s="0" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="N323" t="inlineStr">
+      <c r="N324" s="0" t="inlineStr">
         <is>
           <t>繁体中文</t>
         </is>
       </c>
     </row>
-    <row r="324">
-      <c r="J324" t="inlineStr">
+    <row r="325">
+      <c r="J325" s="0" t="inlineStr">
         <is>
           <t>ja</t>
         </is>
       </c>
-      <c r="L324" t="inlineStr">
+      <c r="L325" s="0" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="N324" t="inlineStr">
+      <c r="N325" s="0" t="inlineStr">
         <is>
           <t>日文</t>
         </is>
       </c>
     </row>
-    <row r="325">
-      <c r="J325" t="inlineStr">
+    <row r="326">
+      <c r="J326" s="0" t="inlineStr">
         <is>
           <t>ko</t>
         </is>
       </c>
-      <c r="L325" t="inlineStr">
+      <c r="L326" s="0" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="N325" t="inlineStr">
+      <c r="N326" s="0" t="inlineStr">
         <is>
           <t>韩文</t>
         </is>

--- a/AfterToken/Configs/GameConfig/Datas/__beans__.xlsx
+++ b/AfterToken/Configs/GameConfig/Datas/__beans__.xlsx
@@ -1025,7 +1025,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P326"/>
+  <dimension ref="A1:P327"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col width="20.625" customWidth="1" style="1" min="2" max="4"/>
@@ -3098,65 +3098,65 @@
       </c>
       <c r="N116" s="0" t="inlineStr">
         <is>
-          <t>仇恨范围（追击触发距离）</t>
+          <t>检测距离（米）：玩家进入此距离触发追击</t>
         </is>
       </c>
     </row>
     <row r="117">
-      <c r="J117" t="inlineStr">
+      <c r="J117" s="0" t="inlineStr">
         <is>
           <t>radius</t>
         </is>
       </c>
-      <c r="L117" t="inlineStr">
-        <is>
-          <t>float</t>
-        </is>
-      </c>
-      <c r="N117" t="inlineStr">
+      <c r="L117" s="0" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="N117" s="0" t="inlineStr">
         <is>
           <t>碰撞/寻路膨胀半径（米）</t>
         </is>
       </c>
     </row>
     <row r="118">
-      <c r="B118" s="0" t="inlineStr">
+      <c r="J118" t="inlineStr">
+        <is>
+          <t>pursuitRange</t>
+        </is>
+      </c>
+      <c r="L118" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="N118" t="inlineStr">
+        <is>
+          <t>追踪范围（米）：追击状态下玩家超过此距离则丢失目标</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="B119" s="0" t="inlineStr">
         <is>
           <t>cfg.Wave</t>
         </is>
       </c>
-      <c r="G118" s="0" t="inlineStr">
+      <c r="G119" s="0" t="inlineStr">
         <is>
           <t>波次配置</t>
         </is>
       </c>
-      <c r="I118" s="0" t="inlineStr">
+      <c r="I119" s="0" t="inlineStr">
         <is>
           <t>c</t>
-        </is>
-      </c>
-    </row>
-    <row r="119">
-      <c r="J119" s="0" t="inlineStr">
-        <is>
-          <t>id</t>
-        </is>
-      </c>
-      <c r="L119" s="0" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="N119" s="0" t="inlineStr">
-        <is>
-          <t>波次ID</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="J120" s="0" t="inlineStr">
         <is>
-          <t>levelId</t>
+          <t>id</t>
         </is>
       </c>
       <c r="L120" s="0" t="inlineStr">
@@ -3166,14 +3166,14 @@
       </c>
       <c r="N120" s="0" t="inlineStr">
         <is>
-          <t>关卡ID</t>
+          <t>波次ID</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="J121" s="0" t="inlineStr">
         <is>
-          <t>waveIndex</t>
+          <t>levelId</t>
         </is>
       </c>
       <c r="L121" s="0" t="inlineStr">
@@ -3183,14 +3183,14 @@
       </c>
       <c r="N121" s="0" t="inlineStr">
         <is>
-          <t>波次索引</t>
+          <t>关卡ID</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="J122" s="0" t="inlineStr">
         <is>
-          <t>enemyId</t>
+          <t>waveIndex</t>
         </is>
       </c>
       <c r="L122" s="0" t="inlineStr">
@@ -3200,14 +3200,14 @@
       </c>
       <c r="N122" s="0" t="inlineStr">
         <is>
-          <t>敌人ID</t>
+          <t>波次索引</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="J123" s="0" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>enemyId</t>
         </is>
       </c>
       <c r="L123" s="0" t="inlineStr">
@@ -3217,82 +3217,82 @@
       </c>
       <c r="N123" s="0" t="inlineStr">
         <is>
-          <t>数量</t>
+          <t>敌人ID</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="J124" s="0" t="inlineStr">
         <is>
-          <t>spawnInterval</t>
+          <t>count</t>
         </is>
       </c>
       <c r="L124" s="0" t="inlineStr">
         <is>
-          <t>float</t>
+          <t>int</t>
         </is>
       </c>
       <c r="N124" s="0" t="inlineStr">
         <is>
-          <t>刷新间隔</t>
+          <t>数量</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="J125" s="0" t="inlineStr">
         <is>
+          <t>spawnInterval</t>
+        </is>
+      </c>
+      <c r="L125" s="0" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="N125" s="0" t="inlineStr">
+        <is>
+          <t>刷新间隔</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="J126" s="0" t="inlineStr">
+        <is>
           <t>spawnRadius</t>
         </is>
       </c>
-      <c r="L125" s="0" t="inlineStr">
-        <is>
-          <t>float</t>
-        </is>
-      </c>
-      <c r="N125" s="0" t="inlineStr">
+      <c r="L126" s="0" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="N126" s="0" t="inlineStr">
         <is>
           <t>刷新半径</t>
         </is>
       </c>
     </row>
-    <row r="126">
-      <c r="B126" s="0" t="inlineStr">
+    <row r="127">
+      <c r="B127" s="0" t="inlineStr">
         <is>
           <t>cfg.Drop</t>
         </is>
       </c>
-      <c r="G126" s="0" t="inlineStr">
+      <c r="G127" s="0" t="inlineStr">
         <is>
           <t>掉落配置</t>
         </is>
       </c>
-      <c r="I126" s="0" t="inlineStr">
+      <c r="I127" s="0" t="inlineStr">
         <is>
           <t>c</t>
-        </is>
-      </c>
-    </row>
-    <row r="127">
-      <c r="J127" s="0" t="inlineStr">
-        <is>
-          <t>id</t>
-        </is>
-      </c>
-      <c r="L127" s="0" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="N127" s="0" t="inlineStr">
-        <is>
-          <t>掉落ID</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="J128" s="0" t="inlineStr">
         <is>
-          <t>enemyId</t>
+          <t>id</t>
         </is>
       </c>
       <c r="L128" s="0" t="inlineStr">
@@ -3302,14 +3302,14 @@
       </c>
       <c r="N128" s="0" t="inlineStr">
         <is>
-          <t>敌人ID</t>
+          <t>掉落ID</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="J129" s="0" t="inlineStr">
         <is>
-          <t>itemId</t>
+          <t>enemyId</t>
         </is>
       </c>
       <c r="L129" s="0" t="inlineStr">
@@ -3319,14 +3319,14 @@
       </c>
       <c r="N129" s="0" t="inlineStr">
         <is>
-          <t>道具ID</t>
+          <t>敌人ID</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="J130" s="0" t="inlineStr">
         <is>
-          <t>dropRate</t>
+          <t>itemId</t>
         </is>
       </c>
       <c r="L130" s="0" t="inlineStr">
@@ -3336,14 +3336,14 @@
       </c>
       <c r="N130" s="0" t="inlineStr">
         <is>
-          <t>掉落概率(万分之一)</t>
+          <t>道具ID</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="J131" s="0" t="inlineStr">
         <is>
-          <t>minCount</t>
+          <t>dropRate</t>
         </is>
       </c>
       <c r="L131" s="0" t="inlineStr">
@@ -3353,235 +3353,235 @@
       </c>
       <c r="N131" s="0" t="inlineStr">
         <is>
-          <t>最小数量</t>
+          <t>掉落概率(万分之一)</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="J132" s="0" t="inlineStr">
         <is>
+          <t>minCount</t>
+        </is>
+      </c>
+      <c r="L132" s="0" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="N132" s="0" t="inlineStr">
+        <is>
+          <t>最小数量</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="J133" s="0" t="inlineStr">
+        <is>
           <t>maxCount</t>
         </is>
       </c>
-      <c r="L132" s="0" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="N132" s="0" t="inlineStr">
+      <c r="L133" s="0" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="N133" s="0" t="inlineStr">
         <is>
           <t>最大数量</t>
         </is>
       </c>
     </row>
-    <row r="133">
-      <c r="B133" s="0" t="inlineStr">
+    <row r="134">
+      <c r="B134" s="0" t="inlineStr">
         <is>
           <t>cfg.Buff</t>
         </is>
       </c>
-      <c r="G133" s="0" t="inlineStr">
+      <c r="G134" s="0" t="inlineStr">
         <is>
           <t>Buff配置</t>
         </is>
       </c>
-      <c r="I133" s="0" t="inlineStr">
+      <c r="I134" s="0" t="inlineStr">
         <is>
           <t>c</t>
-        </is>
-      </c>
-    </row>
-    <row r="134">
-      <c r="J134" s="0" t="inlineStr">
-        <is>
-          <t>id</t>
-        </is>
-      </c>
-      <c r="L134" s="0" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="N134" s="0" t="inlineStr">
-        <is>
-          <t>BuffID</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="J135" s="0" t="inlineStr">
         <is>
-          <t>name</t>
+          <t>id</t>
         </is>
       </c>
       <c r="L135" s="0" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>int</t>
         </is>
       </c>
       <c r="N135" s="0" t="inlineStr">
         <is>
-          <t>名称</t>
+          <t>BuffID</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="J136" s="0" t="inlineStr">
         <is>
-          <t>duration</t>
+          <t>name</t>
         </is>
       </c>
       <c r="L136" s="0" t="inlineStr">
         <is>
-          <t>float</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N136" s="0" t="inlineStr">
         <is>
-          <t>持续时间</t>
+          <t>名称</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="J137" s="0" t="inlineStr">
         <is>
-          <t>effectType</t>
+          <t>duration</t>
         </is>
       </c>
       <c r="L137" s="0" t="inlineStr">
         <is>
-          <t>int</t>
+          <t>float</t>
         </is>
       </c>
       <c r="N137" s="0" t="inlineStr">
         <is>
-          <t>效果类型</t>
+          <t>持续时间</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="J138" s="0" t="inlineStr">
         <is>
-          <t>value</t>
+          <t>effectType</t>
         </is>
       </c>
       <c r="L138" s="0" t="inlineStr">
         <is>
-          <t>float</t>
+          <t>int</t>
         </is>
       </c>
       <c r="N138" s="0" t="inlineStr">
         <is>
-          <t>数值</t>
+          <t>效果类型</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="J139" s="0" t="inlineStr">
         <is>
+          <t>value</t>
+        </is>
+      </c>
+      <c r="L139" s="0" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="N139" s="0" t="inlineStr">
+        <is>
+          <t>数值</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="J140" s="0" t="inlineStr">
+        <is>
           <t>icon</t>
         </is>
       </c>
-      <c r="L139" s="0" t="inlineStr">
+      <c r="L140" s="0" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="N139" s="0" t="inlineStr">
+      <c r="N140" s="0" t="inlineStr">
         <is>
           <t>图标</t>
         </is>
       </c>
     </row>
-    <row r="140">
-      <c r="B140" s="0" t="inlineStr">
+    <row r="141">
+      <c r="B141" s="0" t="inlineStr">
         <is>
           <t>cfg.Portal</t>
         </is>
       </c>
-      <c r="G140" s="0" t="inlineStr">
+      <c r="G141" s="0" t="inlineStr">
         <is>
           <t>传送门配置</t>
         </is>
       </c>
-      <c r="I140" s="0" t="inlineStr">
+      <c r="I141" s="0" t="inlineStr">
         <is>
           <t>c</t>
-        </is>
-      </c>
-    </row>
-    <row r="141">
-      <c r="J141" s="0" t="inlineStr">
-        <is>
-          <t>id</t>
-        </is>
-      </c>
-      <c r="L141" s="0" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="N141" s="0" t="inlineStr">
-        <is>
-          <t>传送门ID</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="J142" s="0" t="inlineStr">
         <is>
-          <t>portalType</t>
+          <t>id</t>
         </is>
       </c>
       <c r="L142" s="0" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>int</t>
         </is>
       </c>
       <c r="N142" s="0" t="inlineStr">
         <is>
-          <t>传送门类型</t>
+          <t>传送门ID</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="J143" s="0" t="inlineStr">
         <is>
-          <t>targetLevelId</t>
+          <t>portalType</t>
         </is>
       </c>
       <c r="L143" s="0" t="inlineStr">
         <is>
-          <t>int</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N143" s="0" t="inlineStr">
         <is>
-          <t>目标关卡ID</t>
+          <t>传送门类型</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="J144" s="0" t="inlineStr">
         <is>
-          <t>targetSceneName</t>
+          <t>targetLevelId</t>
         </is>
       </c>
       <c r="L144" s="0" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>int</t>
         </is>
       </c>
       <c r="N144" s="0" t="inlineStr">
         <is>
-          <t>目标场景名</t>
+          <t>目标关卡ID</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="J145" s="0" t="inlineStr">
         <is>
-          <t>spawnCondition</t>
+          <t>targetSceneName</t>
         </is>
       </c>
       <c r="L145" s="0" t="inlineStr">
@@ -3591,14 +3591,14 @@
       </c>
       <c r="N145" s="0" t="inlineStr">
         <is>
-          <t>出现条件</t>
+          <t>目标场景名</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="J146" s="0" t="inlineStr">
         <is>
-          <t>conditionParam</t>
+          <t>spawnCondition</t>
         </is>
       </c>
       <c r="L146" s="0" t="inlineStr">
@@ -3608,48 +3608,48 @@
       </c>
       <c r="N146" s="0" t="inlineStr">
         <is>
-          <t>条件参数</t>
+          <t>出现条件</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="J147" s="0" t="inlineStr">
         <is>
-          <t>keepPlayerState</t>
+          <t>conditionParam</t>
         </is>
       </c>
       <c r="L147" s="0" t="inlineStr">
         <is>
-          <t>bool</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N147" s="0" t="inlineStr">
         <is>
-          <t>保留玩家状态</t>
+          <t>条件参数</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="J148" s="0" t="inlineStr">
         <is>
-          <t>promptText</t>
+          <t>keepPlayerState</t>
         </is>
       </c>
       <c r="L148" s="0" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>bool</t>
         </is>
       </c>
       <c r="N148" s="0" t="inlineStr">
         <is>
-          <t>提示文本</t>
+          <t>保留玩家状态</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="J149" s="0" t="inlineStr">
         <is>
-          <t>transitionType</t>
+          <t>promptText</t>
         </is>
       </c>
       <c r="L149" s="0" t="inlineStr">
@@ -3659,65 +3659,65 @@
       </c>
       <c r="N149" s="0" t="inlineStr">
         <is>
-          <t>转场类型</t>
+          <t>提示文本</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="J150" s="0" t="inlineStr">
         <is>
+          <t>transitionType</t>
+        </is>
+      </c>
+      <c r="L150" s="0" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="N150" s="0" t="inlineStr">
+        <is>
+          <t>转场类型</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="J151" s="0" t="inlineStr">
+        <is>
           <t>transitionDuration</t>
         </is>
       </c>
-      <c r="L150" s="0" t="inlineStr">
-        <is>
-          <t>float</t>
-        </is>
-      </c>
-      <c r="N150" s="0" t="inlineStr">
+      <c r="L151" s="0" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="N151" s="0" t="inlineStr">
         <is>
           <t>转场时长</t>
         </is>
       </c>
     </row>
-    <row r="151">
-      <c r="B151" s="0" t="inlineStr">
+    <row r="152">
+      <c r="B152" s="0" t="inlineStr">
         <is>
           <t>cfg.InventoryConfig</t>
         </is>
       </c>
-      <c r="G151" s="0" t="inlineStr">
+      <c r="G152" s="0" t="inlineStr">
         <is>
           <t>背包容量配置</t>
         </is>
       </c>
-      <c r="I151" s="0" t="inlineStr">
+      <c r="I152" s="0" t="inlineStr">
         <is>
           <t>c</t>
-        </is>
-      </c>
-    </row>
-    <row r="152">
-      <c r="J152" s="0" t="inlineStr">
-        <is>
-          <t>id</t>
-        </is>
-      </c>
-      <c r="L152" s="0" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="N152" s="0" t="inlineStr">
-        <is>
-          <t>ID</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="J153" s="0" t="inlineStr">
         <is>
-          <t>tempBagCapacity</t>
+          <t>id</t>
         </is>
       </c>
       <c r="L153" s="0" t="inlineStr">
@@ -3727,82 +3727,82 @@
       </c>
       <c r="N153" s="0" t="inlineStr">
         <is>
-          <t>临时背包槽位</t>
+          <t>ID</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="J154" s="0" t="inlineStr">
         <is>
+          <t>tempBagCapacity</t>
+        </is>
+      </c>
+      <c r="L154" s="0" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="N154" s="0" t="inlineStr">
+        <is>
+          <t>临时背包槽位</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="J155" s="0" t="inlineStr">
+        <is>
           <t>warehouseCapacity</t>
         </is>
       </c>
-      <c r="L154" s="0" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="N154" s="0" t="inlineStr">
+      <c r="L155" s="0" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="N155" s="0" t="inlineStr">
         <is>
           <t>仓库槽位</t>
         </is>
       </c>
     </row>
-    <row r="155">
-      <c r="B155" s="0" t="inlineStr">
+    <row r="156">
+      <c r="B156" s="0" t="inlineStr">
         <is>
           <t>cfg.Camera</t>
         </is>
       </c>
-      <c r="G155" s="0" t="inlineStr">
+      <c r="G156" s="0" t="inlineStr">
         <is>
           <t>相机配置</t>
         </is>
       </c>
-      <c r="H155" s="0" t="inlineStr">
+      <c r="H156" s="0" t="inlineStr">
         <is>
           <t>c</t>
-        </is>
-      </c>
-    </row>
-    <row r="156">
-      <c r="J156" s="0" t="inlineStr">
-        <is>
-          <t>id</t>
-        </is>
-      </c>
-      <c r="L156" s="0" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="N156" s="0" t="inlineStr">
-        <is>
-          <t>配置ID</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="J157" s="0" t="inlineStr">
         <is>
-          <t>smoothTime</t>
+          <t>id</t>
         </is>
       </c>
       <c r="L157" s="0" t="inlineStr">
         <is>
-          <t>float</t>
+          <t>int</t>
         </is>
       </c>
       <c r="N157" s="0" t="inlineStr">
         <is>
-          <t>相机平滑时间</t>
+          <t>配置ID</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="J158" s="0" t="inlineStr">
         <is>
-          <t>defaultFov</t>
+          <t>smoothTime</t>
         </is>
       </c>
       <c r="L158" s="0" t="inlineStr">
@@ -3812,14 +3812,14 @@
       </c>
       <c r="N158" s="0" t="inlineStr">
         <is>
-          <t>默认FOV</t>
+          <t>相机平滑时间</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="J159" s="0" t="inlineStr">
         <is>
-          <t>fovSmoothTime</t>
+          <t>defaultFov</t>
         </is>
       </c>
       <c r="L159" s="0" t="inlineStr">
@@ -3829,14 +3829,14 @@
       </c>
       <c r="N159" s="0" t="inlineStr">
         <is>
-          <t>FOV平滑时间</t>
+          <t>默认FOV</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="J160" s="0" t="inlineStr">
         <is>
-          <t>shakeDamping</t>
+          <t>fovSmoothTime</t>
         </is>
       </c>
       <c r="L160" s="0" t="inlineStr">
@@ -3846,116 +3846,116 @@
       </c>
       <c r="N160" s="0" t="inlineStr">
         <is>
-          <t>震动衰减速度</t>
+          <t>FOV平滑时间</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="J161" s="0" t="inlineStr">
         <is>
-          <t>scopeRenderSize</t>
+          <t>shakeDamping</t>
         </is>
       </c>
       <c r="L161" s="0" t="inlineStr">
         <is>
-          <t>int</t>
+          <t>float</t>
         </is>
       </c>
       <c r="N161" s="0" t="inlineStr">
         <is>
-          <t>狙击镜渲染纹理尺寸</t>
+          <t>震动衰减速度</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="J162" s="0" t="inlineStr">
         <is>
-          <t>scopeCameraFov</t>
+          <t>scopeRenderSize</t>
         </is>
       </c>
       <c r="L162" s="0" t="inlineStr">
         <is>
-          <t>float</t>
+          <t>int</t>
         </is>
       </c>
       <c r="N162" s="0" t="inlineStr">
         <is>
-          <t>狙击镜相机FOV</t>
+          <t>狙击镜渲染纹理尺寸</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="J163" s="0" t="inlineStr">
         <is>
+          <t>scopeCameraFov</t>
+        </is>
+      </c>
+      <c r="L163" s="0" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="N163" s="0" t="inlineStr">
+        <is>
+          <t>狙击镜相机FOV</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="J164" s="0" t="inlineStr">
+        <is>
           <t>defaultOrthographicSize</t>
         </is>
       </c>
-      <c r="L163" s="0" t="inlineStr">
-        <is>
-          <t>float</t>
-        </is>
-      </c>
-      <c r="N163" s="0" t="inlineStr">
+      <c r="L164" s="0" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="N164" s="0" t="inlineStr">
         <is>
           <t>默认正交尺寸</t>
         </is>
       </c>
     </row>
-    <row r="164">
-      <c r="B164" s="0" t="inlineStr">
+    <row r="165">
+      <c r="B165" s="0" t="inlineStr">
         <is>
           <t>cfg.Ballistic</t>
         </is>
       </c>
-      <c r="G164" s="0" t="inlineStr">
+      <c r="G165" s="0" t="inlineStr">
         <is>
           <t>弹道全局配置</t>
         </is>
       </c>
-      <c r="H164" s="0" t="inlineStr">
+      <c r="H165" s="0" t="inlineStr">
         <is>
           <t>c</t>
-        </is>
-      </c>
-    </row>
-    <row r="165">
-      <c r="J165" s="0" t="inlineStr">
-        <is>
-          <t>id</t>
-        </is>
-      </c>
-      <c r="L165" s="0" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="N165" s="0" t="inlineStr">
-        <is>
-          <t>配置ID</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="J166" s="0" t="inlineStr">
         <is>
-          <t>tracerRadius</t>
+          <t>id</t>
         </is>
       </c>
       <c r="L166" s="0" t="inlineStr">
         <is>
-          <t>float</t>
+          <t>int</t>
         </is>
       </c>
       <c r="N166" s="0" t="inlineStr">
         <is>
-          <t>Tracer射线检测半径</t>
+          <t>配置ID</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="J167" s="0" t="inlineStr">
         <is>
-          <t>tracerStartWidth</t>
+          <t>tracerRadius</t>
         </is>
       </c>
       <c r="L167" s="0" t="inlineStr">
@@ -3965,14 +3965,14 @@
       </c>
       <c r="N167" s="0" t="inlineStr">
         <is>
-          <t>Tracer起始宽度</t>
+          <t>Tracer射线检测半径</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="J168" s="0" t="inlineStr">
         <is>
-          <t>tracerEndWidth</t>
+          <t>tracerStartWidth</t>
         </is>
       </c>
       <c r="L168" s="0" t="inlineStr">
@@ -3982,14 +3982,14 @@
       </c>
       <c r="N168" s="0" t="inlineStr">
         <is>
-          <t>Tracer结束宽度</t>
+          <t>Tracer起始宽度</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="J169" s="0" t="inlineStr">
         <is>
-          <t>tracerTailLength</t>
+          <t>tracerEndWidth</t>
         </is>
       </c>
       <c r="L169" s="0" t="inlineStr">
@@ -3999,116 +3999,116 @@
       </c>
       <c r="N169" s="0" t="inlineStr">
         <is>
-          <t>Tracer尾迹长度</t>
+          <t>Tracer结束宽度</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="J170" s="0" t="inlineStr">
         <is>
-          <t>maxActiveTracers</t>
+          <t>tracerTailLength</t>
         </is>
       </c>
       <c r="L170" s="0" t="inlineStr">
         <is>
-          <t>int</t>
+          <t>float</t>
         </is>
       </c>
       <c r="N170" s="0" t="inlineStr">
         <is>
-          <t>最大同时存在Tracer数量</t>
+          <t>Tracer尾迹长度</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="J171" s="0" t="inlineStr">
         <is>
-          <t>hitLayers</t>
+          <t>maxActiveTracers</t>
         </is>
       </c>
       <c r="L171" s="0" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>int</t>
         </is>
       </c>
       <c r="N171" s="0" t="inlineStr">
         <is>
-          <t>默认命中层级</t>
+          <t>最大同时存在Tracer数量</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="J172" s="0" t="inlineStr">
         <is>
-          <t>tracerStartColor</t>
+          <t>hitLayers</t>
         </is>
       </c>
       <c r="L172" s="0" t="inlineStr">
         <is>
-          <t>cfg.Color#sep=,</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N172" s="0" t="inlineStr">
         <is>
-          <t>Tracer起始颜色</t>
+          <t>默认命中层级</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="J173" s="0" t="inlineStr">
         <is>
+          <t>tracerStartColor</t>
+        </is>
+      </c>
+      <c r="L173" s="0" t="inlineStr">
+        <is>
+          <t>cfg.Color#sep=,</t>
+        </is>
+      </c>
+      <c r="N173" s="0" t="inlineStr">
+        <is>
+          <t>Tracer起始颜色</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="J174" s="0" t="inlineStr">
+        <is>
           <t>tracerEndColor</t>
         </is>
       </c>
-      <c r="L173" s="0" t="inlineStr">
+      <c r="L174" s="0" t="inlineStr">
         <is>
           <t>cfg.Color#sep=,</t>
         </is>
       </c>
-      <c r="N173" s="0" t="inlineStr">
+      <c r="N174" s="0" t="inlineStr">
         <is>
           <t>Tracer结束颜色</t>
         </is>
       </c>
     </row>
-    <row r="174">
-      <c r="B174" s="0" t="inlineStr">
+    <row r="175">
+      <c r="B175" s="0" t="inlineStr">
         <is>
           <t>cfg.UiConfig</t>
         </is>
       </c>
-      <c r="G174" s="0" t="inlineStr">
+      <c r="G175" s="0" t="inlineStr">
         <is>
           <t>UI全局配置</t>
         </is>
       </c>
-      <c r="H174" s="0" t="inlineStr">
+      <c r="H175" s="0" t="inlineStr">
         <is>
           <t>c</t>
-        </is>
-      </c>
-    </row>
-    <row r="175">
-      <c r="J175" s="0" t="inlineStr">
-        <is>
-          <t>id</t>
-        </is>
-      </c>
-      <c r="L175" s="0" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="N175" s="0" t="inlineStr">
-        <is>
-          <t>配置ID</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="J176" s="0" t="inlineStr">
         <is>
-          <t>damageNumberPoolSize</t>
+          <t>id</t>
         </is>
       </c>
       <c r="L176" s="0" t="inlineStr">
@@ -4118,31 +4118,31 @@
       </c>
       <c r="N176" s="0" t="inlineStr">
         <is>
-          <t>伤害数字对象池大小</t>
+          <t>配置ID</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="J177" s="0" t="inlineStr">
         <is>
-          <t>damageNumberFadeDuration</t>
+          <t>damageNumberPoolSize</t>
         </is>
       </c>
       <c r="L177" s="0" t="inlineStr">
         <is>
-          <t>float</t>
+          <t>int</t>
         </is>
       </c>
       <c r="N177" s="0" t="inlineStr">
         <is>
-          <t>伤害数字渐隐时间</t>
+          <t>伤害数字对象池大小</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="J178" s="0" t="inlineStr">
         <is>
-          <t>damageNumberMoveOffset</t>
+          <t>damageNumberFadeDuration</t>
         </is>
       </c>
       <c r="L178" s="0" t="inlineStr">
@@ -4152,31 +4152,31 @@
       </c>
       <c r="N178" s="0" t="inlineStr">
         <is>
-          <t>伤害数字上浮偏移</t>
+          <t>伤害数字渐隐时间</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="J179" s="0" t="inlineStr">
         <is>
-          <t>damageNumberNormalColor</t>
+          <t>damageNumberMoveOffset</t>
         </is>
       </c>
       <c r="L179" s="0" t="inlineStr">
         <is>
-          <t>cfg.Color#sep=,</t>
+          <t>float</t>
         </is>
       </c>
       <c r="N179" s="0" t="inlineStr">
         <is>
-          <t>普通伤害数字颜色</t>
+          <t>伤害数字上浮偏移</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="J180" s="0" t="inlineStr">
         <is>
-          <t>damageNumberCriticalColor</t>
+          <t>damageNumberNormalColor</t>
         </is>
       </c>
       <c r="L180" s="0" t="inlineStr">
@@ -4186,31 +4186,31 @@
       </c>
       <c r="N180" s="0" t="inlineStr">
         <is>
-          <t>暴击伤害数字颜色</t>
+          <t>普通伤害数字颜色</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="J181" s="0" t="inlineStr">
         <is>
-          <t>damageNumberNormalFontSize</t>
+          <t>damageNumberCriticalColor</t>
         </is>
       </c>
       <c r="L181" s="0" t="inlineStr">
         <is>
-          <t>int</t>
+          <t>cfg.Color#sep=,</t>
         </is>
       </c>
       <c r="N181" s="0" t="inlineStr">
         <is>
-          <t>普通伤害数字字体大小</t>
+          <t>暴击伤害数字颜色</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="J182" s="0" t="inlineStr">
         <is>
-          <t>damageNumberCriticalFontSize</t>
+          <t>damageNumberNormalFontSize</t>
         </is>
       </c>
       <c r="L182" s="0" t="inlineStr">
@@ -4220,14 +4220,14 @@
       </c>
       <c r="N182" s="0" t="inlineStr">
         <is>
-          <t>暴击伤害数字字体大小</t>
+          <t>普通伤害数字字体大小</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="J183" s="0" t="inlineStr">
         <is>
-          <t>hitMarkerPoolSize</t>
+          <t>damageNumberCriticalFontSize</t>
         </is>
       </c>
       <c r="L183" s="0" t="inlineStr">
@@ -4237,31 +4237,31 @@
       </c>
       <c r="N183" s="0" t="inlineStr">
         <is>
-          <t>命中标记对象池大小</t>
+          <t>暴击伤害数字字体大小</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="J184" s="0" t="inlineStr">
         <is>
-          <t>hitMarkerDuration</t>
+          <t>hitMarkerPoolSize</t>
         </is>
       </c>
       <c r="L184" s="0" t="inlineStr">
         <is>
-          <t>float</t>
+          <t>int</t>
         </is>
       </c>
       <c r="N184" s="0" t="inlineStr">
         <is>
-          <t>命中标记显示时间</t>
+          <t>命中标记对象池大小</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="J185" s="0" t="inlineStr">
         <is>
-          <t>hitMarkerSize</t>
+          <t>hitMarkerDuration</t>
         </is>
       </c>
       <c r="L185" s="0" t="inlineStr">
@@ -4271,31 +4271,31 @@
       </c>
       <c r="N185" s="0" t="inlineStr">
         <is>
-          <t>命中标记大小</t>
+          <t>命中标记显示时间</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="J186" s="0" t="inlineStr">
         <is>
-          <t>hitMarkerNormalColor</t>
+          <t>hitMarkerSize</t>
         </is>
       </c>
       <c r="L186" s="0" t="inlineStr">
         <is>
-          <t>cfg.Color#sep=,</t>
+          <t>float</t>
         </is>
       </c>
       <c r="N186" s="0" t="inlineStr">
         <is>
-          <t>普通命中标记颜色</t>
+          <t>命中标记大小</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="J187" s="0" t="inlineStr">
         <is>
-          <t>hitMarkerCriticalColor</t>
+          <t>hitMarkerNormalColor</t>
         </is>
       </c>
       <c r="L187" s="0" t="inlineStr">
@@ -4305,116 +4305,116 @@
       </c>
       <c r="N187" s="0" t="inlineStr">
         <is>
-          <t>暴击命中标记颜色</t>
+          <t>普通命中标记颜色</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="J188" s="0" t="inlineStr">
         <is>
-          <t>indicatorFadeSpeed</t>
+          <t>hitMarkerCriticalColor</t>
         </is>
       </c>
       <c r="L188" s="0" t="inlineStr">
         <is>
-          <t>float</t>
+          <t>cfg.Color#sep=,</t>
         </is>
       </c>
       <c r="N188" s="0" t="inlineStr">
         <is>
-          <t>受击指示器淡出速度</t>
+          <t>暴击命中标记颜色</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="J189" s="0" t="inlineStr">
         <is>
-          <t>indicatorColor</t>
+          <t>indicatorFadeSpeed</t>
         </is>
       </c>
       <c r="L189" s="0" t="inlineStr">
         <is>
-          <t>cfg.Color#sep=,</t>
+          <t>float</t>
         </is>
       </c>
       <c r="N189" s="0" t="inlineStr">
         <is>
-          <t>受击指示器颜色</t>
+          <t>受击指示器淡出速度</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="J190" s="0" t="inlineStr">
         <is>
+          <t>indicatorColor</t>
+        </is>
+      </c>
+      <c r="L190" s="0" t="inlineStr">
+        <is>
+          <t>cfg.Color#sep=,</t>
+        </is>
+      </c>
+      <c r="N190" s="0" t="inlineStr">
+        <is>
+          <t>受击指示器颜色</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="J191" s="0" t="inlineStr">
+        <is>
           <t>loadingTextFormat</t>
         </is>
       </c>
-      <c r="L190" s="0" t="inlineStr">
+      <c r="L191" s="0" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="N190" s="0" t="inlineStr">
+      <c r="N191" s="0" t="inlineStr">
         <is>
           <t>加载进度文本格式</t>
         </is>
       </c>
     </row>
-    <row r="191">
-      <c r="B191" s="0" t="inlineStr">
+    <row r="192">
+      <c r="B192" s="0" t="inlineStr">
         <is>
           <t>cfg.Pickup</t>
         </is>
       </c>
-      <c r="G191" s="0" t="inlineStr">
+      <c r="G192" s="0" t="inlineStr">
         <is>
           <t>拾取物配置</t>
         </is>
       </c>
-      <c r="H191" s="0" t="inlineStr">
+      <c r="H192" s="0" t="inlineStr">
         <is>
           <t>c</t>
-        </is>
-      </c>
-    </row>
-    <row r="192">
-      <c r="J192" s="0" t="inlineStr">
-        <is>
-          <t>id</t>
-        </is>
-      </c>
-      <c r="L192" s="0" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="N192" s="0" t="inlineStr">
-        <is>
-          <t>配置ID</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="J193" s="0" t="inlineStr">
         <is>
-          <t>colliderRadius</t>
+          <t>id</t>
         </is>
       </c>
       <c r="L193" s="0" t="inlineStr">
         <is>
-          <t>float</t>
+          <t>int</t>
         </is>
       </c>
       <c r="N193" s="0" t="inlineStr">
         <is>
-          <t>拾取物碰撞体半径</t>
+          <t>配置ID</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="J194" s="0" t="inlineStr">
         <is>
-          <t>visualScale</t>
+          <t>colliderRadius</t>
         </is>
       </c>
       <c r="L194" s="0" t="inlineStr">
@@ -4424,82 +4424,82 @@
       </c>
       <c r="N194" s="0" t="inlineStr">
         <is>
-          <t>拾取物视觉缩放</t>
+          <t>拾取物碰撞体半径</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="J195" s="0" t="inlineStr">
         <is>
+          <t>visualScale</t>
+        </is>
+      </c>
+      <c r="L195" s="0" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="N195" s="0" t="inlineStr">
+        <is>
+          <t>拾取物视觉缩放</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="J196" s="0" t="inlineStr">
+        <is>
           <t>sortingOrder</t>
         </is>
       </c>
-      <c r="L195" s="0" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="N195" s="0" t="inlineStr">
+      <c r="L196" s="0" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="N196" s="0" t="inlineStr">
         <is>
           <t>拾取物渲染排序</t>
         </is>
       </c>
     </row>
-    <row r="196">
-      <c r="B196" s="0" t="inlineStr">
+    <row r="197">
+      <c r="B197" s="0" t="inlineStr">
         <is>
           <t>cfg.Building</t>
         </is>
       </c>
-      <c r="G196" s="0" t="inlineStr">
+      <c r="G197" s="0" t="inlineStr">
         <is>
           <t>建筑配置</t>
         </is>
       </c>
-      <c r="I196" s="0" t="inlineStr">
+      <c r="I197" s="0" t="inlineStr">
         <is>
           <t>c</t>
-        </is>
-      </c>
-    </row>
-    <row r="197">
-      <c r="J197" s="0" t="inlineStr">
-        <is>
-          <t>id</t>
-        </is>
-      </c>
-      <c r="L197" s="0" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="N197" s="0" t="inlineStr">
-        <is>
-          <t>建筑ID</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="J198" s="0" t="inlineStr">
         <is>
-          <t>name</t>
+          <t>id</t>
         </is>
       </c>
       <c r="L198" s="0" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>int</t>
         </is>
       </c>
       <c r="N198" s="0" t="inlineStr">
         <is>
-          <t>名称</t>
+          <t>建筑ID</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="J199" s="0" t="inlineStr">
         <is>
-          <t>desc</t>
+          <t>name</t>
         </is>
       </c>
       <c r="L199" s="0" t="inlineStr">
@@ -4509,65 +4509,65 @@
       </c>
       <c r="N199" s="0" t="inlineStr">
         <is>
-          <t>描述</t>
+          <t>名称</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="J200" s="0" t="inlineStr">
         <is>
-          <t>buildingType</t>
+          <t>desc</t>
         </is>
       </c>
       <c r="L200" s="0" t="inlineStr">
         <is>
-          <t>cfg.EBuildingType</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N200" s="0" t="inlineStr">
         <is>
-          <t>建筑类型</t>
+          <t>描述</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="J201" s="0" t="inlineStr">
         <is>
-          <t>icon</t>
+          <t>buildingType</t>
         </is>
       </c>
       <c r="L201" s="0" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>cfg.EBuildingType</t>
         </is>
       </c>
       <c r="N201" s="0" t="inlineStr">
         <is>
-          <t>图标</t>
+          <t>建筑类型</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="J202" s="0" t="inlineStr">
         <is>
-          <t>maxLevel</t>
+          <t>icon</t>
         </is>
       </c>
       <c r="L202" s="0" t="inlineStr">
         <is>
-          <t>int</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N202" s="0" t="inlineStr">
         <is>
-          <t>最大等级</t>
+          <t>图标</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="J203" s="0" t="inlineStr">
         <is>
-          <t>buildCostGold</t>
+          <t>maxLevel</t>
         </is>
       </c>
       <c r="L203" s="0" t="inlineStr">
@@ -4577,116 +4577,116 @@
       </c>
       <c r="N203" s="0" t="inlineStr">
         <is>
-          <t>建造金币</t>
+          <t>最大等级</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="J204" s="0" t="inlineStr">
         <is>
-          <t>buildCostItems</t>
+          <t>buildCostGold</t>
         </is>
       </c>
       <c r="L204" s="0" t="inlineStr">
         <is>
-          <t>(list#sep=;),cfg.ItemExchange#sep=,</t>
+          <t>int</t>
         </is>
       </c>
       <c r="N204" s="0" t="inlineStr">
         <is>
-          <t>建造材料</t>
+          <t>建造金币</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="J205" s="0" t="inlineStr">
         <is>
-          <t>buildTime</t>
+          <t>buildCostItems</t>
         </is>
       </c>
       <c r="L205" s="0" t="inlineStr">
         <is>
-          <t>float</t>
+          <t>(list#sep=;),cfg.ItemExchange#sep=,</t>
         </is>
       </c>
       <c r="N205" s="0" t="inlineStr">
         <is>
-          <t>建造耗时</t>
+          <t>建造材料</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="J206" s="0" t="inlineStr">
         <is>
-          <t>upgradeCostGold</t>
+          <t>buildTime</t>
         </is>
       </c>
       <c r="L206" s="0" t="inlineStr">
         <is>
-          <t>int</t>
+          <t>float</t>
         </is>
       </c>
       <c r="N206" s="0" t="inlineStr">
         <is>
-          <t>升级金币</t>
+          <t>建造耗时</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="J207" s="0" t="inlineStr">
         <is>
-          <t>upgradeCostItems</t>
+          <t>upgradeCostGold</t>
         </is>
       </c>
       <c r="L207" s="0" t="inlineStr">
         <is>
-          <t>(list#sep=;),cfg.ItemExchange#sep=,</t>
+          <t>int</t>
         </is>
       </c>
       <c r="N207" s="0" t="inlineStr">
         <is>
-          <t>升级材料</t>
+          <t>升级金币</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="J208" s="0" t="inlineStr">
         <is>
-          <t>upgradeTime</t>
+          <t>upgradeCostItems</t>
         </is>
       </c>
       <c r="L208" s="0" t="inlineStr">
         <is>
-          <t>float</t>
+          <t>(list#sep=;),cfg.ItemExchange#sep=,</t>
         </is>
       </c>
       <c r="N208" s="0" t="inlineStr">
         <is>
-          <t>升级耗时</t>
+          <t>升级材料</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="J209" s="0" t="inlineStr">
         <is>
-          <t>productionSlotCount</t>
+          <t>upgradeTime</t>
         </is>
       </c>
       <c r="L209" s="0" t="inlineStr">
         <is>
-          <t>int</t>
+          <t>float</t>
         </is>
       </c>
       <c r="N209" s="0" t="inlineStr">
         <is>
-          <t>生产槽位</t>
+          <t>升级耗时</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="J210" s="0" t="inlineStr">
         <is>
-          <t>unlockLevel</t>
+          <t>productionSlotCount</t>
         </is>
       </c>
       <c r="L210" s="0" t="inlineStr">
@@ -4696,14 +4696,14 @@
       </c>
       <c r="N210" s="0" t="inlineStr">
         <is>
-          <t>解锁等级</t>
+          <t>生产槽位</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="J211" s="0" t="inlineStr">
         <is>
-          <t>footprintX</t>
+          <t>unlockLevel</t>
         </is>
       </c>
       <c r="L211" s="0" t="inlineStr">
@@ -4713,14 +4713,14 @@
       </c>
       <c r="N211" s="0" t="inlineStr">
         <is>
-          <t>占地格数X(1m格)</t>
+          <t>解锁等级</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="J212" s="0" t="inlineStr">
         <is>
-          <t>maxCount</t>
+          <t>footprintX</t>
         </is>
       </c>
       <c r="L212" s="0" t="inlineStr">
@@ -4730,14 +4730,14 @@
       </c>
       <c r="N212" s="0" t="inlineStr">
         <is>
-          <t>数量上限-基础值(默认1)</t>
+          <t>占地格数X(1m格)</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="J213" s="0" t="inlineStr">
         <is>
-          <t>maxCountPerPlayerLevel</t>
+          <t>maxCount</t>
         </is>
       </c>
       <c r="L213" s="0" t="inlineStr">
@@ -4747,14 +4747,14 @@
       </c>
       <c r="N213" s="0" t="inlineStr">
         <is>
-          <t>数量上限-玩家等级解锁:玩家每升1级上限+N(默认0)</t>
+          <t>数量上限-基础值(默认1)</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="J214" s="0" t="inlineStr">
         <is>
-          <t>maxCountUpgradeLevel</t>
+          <t>maxCountPerPlayerLevel</t>
         </is>
       </c>
       <c r="L214" s="0" t="inlineStr">
@@ -4764,14 +4764,14 @@
       </c>
       <c r="N214" s="0" t="inlineStr">
         <is>
-          <t>数量上限-升级解锁(默认方式):同类建筑每有1座达到该等级上限+1,0=不启用</t>
+          <t>数量上限-玩家等级解锁:玩家每升1级上限+N(默认0)</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="J215" s="0" t="inlineStr">
         <is>
-          <t>maxCountSlotBaseCost</t>
+          <t>maxCountUpgradeLevel</t>
         </is>
       </c>
       <c r="L215" s="0" t="inlineStr">
@@ -4781,14 +4781,14 @@
       </c>
       <c r="N215" s="0" t="inlineStr">
         <is>
-          <t>数量上限-购买解锁:购买1个栏位的金币基础价,0=不可购买</t>
+          <t>数量上限-升级解锁(默认方式):同类建筑每有1座达到该等级上限+1,0=不启用</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="J216" s="0" t="inlineStr">
         <is>
-          <t>maxCountSlotCostGrow</t>
+          <t>maxCountSlotBaseCost</t>
         </is>
       </c>
       <c r="L216" s="0" t="inlineStr">
@@ -4798,82 +4798,82 @@
       </c>
       <c r="N216" s="0" t="inlineStr">
         <is>
-          <t>数量上限-购买解锁:每已购1个栏位价格+N(线性涨价)</t>
+          <t>数量上限-购买解锁:购买1个栏位的金币基础价,0=不可购买</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="J217" s="0" t="inlineStr">
         <is>
+          <t>maxCountSlotCostGrow</t>
+        </is>
+      </c>
+      <c r="L217" s="0" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="N217" s="0" t="inlineStr">
+        <is>
+          <t>数量上限-购买解锁:每已购1个栏位价格+N(线性涨价)</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="J218" s="0" t="inlineStr">
+        <is>
           <t>footprintZ</t>
         </is>
       </c>
-      <c r="L217" s="0" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="N217" s="0" t="inlineStr">
+      <c r="L218" s="0" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="N218" s="0" t="inlineStr">
         <is>
           <t>占地格数Z(1m格)</t>
         </is>
       </c>
     </row>
-    <row r="218">
-      <c r="B218" s="0" t="inlineStr">
+    <row r="219">
+      <c r="B219" s="0" t="inlineStr">
         <is>
           <t>cfg.Production</t>
         </is>
       </c>
-      <c r="G218" s="0" t="inlineStr">
+      <c r="G219" s="0" t="inlineStr">
         <is>
           <t>生产配方</t>
         </is>
       </c>
-      <c r="I218" s="0" t="inlineStr">
+      <c r="I219" s="0" t="inlineStr">
         <is>
           <t>c</t>
-        </is>
-      </c>
-    </row>
-    <row r="219">
-      <c r="J219" s="0" t="inlineStr">
-        <is>
-          <t>id</t>
-        </is>
-      </c>
-      <c r="L219" s="0" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="N219" s="0" t="inlineStr">
-        <is>
-          <t>配方ID</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="J220" s="0" t="inlineStr">
         <is>
-          <t>name</t>
+          <t>id</t>
         </is>
       </c>
       <c r="L220" s="0" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>int</t>
         </is>
       </c>
       <c r="N220" s="0" t="inlineStr">
         <is>
-          <t>名称</t>
+          <t>配方ID</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="J221" s="0" t="inlineStr">
         <is>
-          <t>desc</t>
+          <t>name</t>
         </is>
       </c>
       <c r="L221" s="0" t="inlineStr">
@@ -4883,31 +4883,31 @@
       </c>
       <c r="N221" s="0" t="inlineStr">
         <is>
-          <t>描述</t>
+          <t>名称</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="J222" s="0" t="inlineStr">
         <is>
-          <t>buildingId</t>
+          <t>desc</t>
         </is>
       </c>
       <c r="L222" s="0" t="inlineStr">
         <is>
-          <t>int</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N222" s="0" t="inlineStr">
         <is>
-          <t>建筑ID</t>
+          <t>描述</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="J223" s="0" t="inlineStr">
         <is>
-          <t>levelRequired</t>
+          <t>buildingId</t>
         </is>
       </c>
       <c r="L223" s="0" t="inlineStr">
@@ -4917,48 +4917,48 @@
       </c>
       <c r="N223" s="0" t="inlineStr">
         <is>
-          <t>等级要求</t>
+          <t>建筑ID</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="J224" s="0" t="inlineStr">
         <is>
-          <t>inputItems</t>
+          <t>levelRequired</t>
         </is>
       </c>
       <c r="L224" s="0" t="inlineStr">
         <is>
-          <t>(list#sep=;),cfg.ItemExchange#sep=,</t>
+          <t>int</t>
         </is>
       </c>
       <c r="N224" s="0" t="inlineStr">
         <is>
-          <t>输入材料</t>
+          <t>等级要求</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="J225" s="0" t="inlineStr">
         <is>
-          <t>outputItemId</t>
+          <t>inputItems</t>
         </is>
       </c>
       <c r="L225" s="0" t="inlineStr">
         <is>
-          <t>int</t>
+          <t>(list#sep=;),cfg.ItemExchange#sep=,</t>
         </is>
       </c>
       <c r="N225" s="0" t="inlineStr">
         <is>
-          <t>产出物品</t>
+          <t>输入材料</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="J226" s="0" t="inlineStr">
         <is>
-          <t>outputCount</t>
+          <t>outputItemId</t>
         </is>
       </c>
       <c r="L226" s="0" t="inlineStr">
@@ -4968,252 +4968,252 @@
       </c>
       <c r="N226" s="0" t="inlineStr">
         <is>
-          <t>产出数量</t>
+          <t>产出物品</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="J227" s="0" t="inlineStr">
         <is>
-          <t>productionTime</t>
+          <t>outputCount</t>
         </is>
       </c>
       <c r="L227" s="0" t="inlineStr">
         <is>
-          <t>float</t>
+          <t>int</t>
         </is>
       </c>
       <c r="N227" s="0" t="inlineStr">
         <is>
-          <t>生产耗时</t>
+          <t>产出数量</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="J228" s="0" t="inlineStr">
         <is>
+          <t>productionTime</t>
+        </is>
+      </c>
+      <c r="L228" s="0" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="N228" s="0" t="inlineStr">
+        <is>
+          <t>生产耗时</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="J229" s="0" t="inlineStr">
+        <is>
           <t>icon</t>
         </is>
       </c>
-      <c r="L228" s="0" t="inlineStr">
+      <c r="L229" s="0" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="N228" s="0" t="inlineStr">
+      <c r="N229" s="0" t="inlineStr">
         <is>
           <t>图标</t>
         </is>
       </c>
     </row>
-    <row r="229">
-      <c r="B229" s="0" t="inlineStr">
+    <row r="230">
+      <c r="B230" s="0" t="inlineStr">
         <is>
           <t>cfg.Order</t>
         </is>
       </c>
-      <c r="G229" s="0" t="inlineStr">
+      <c r="G230" s="0" t="inlineStr">
         <is>
           <t>订单配置</t>
         </is>
       </c>
-      <c r="I229" s="0" t="inlineStr">
+      <c r="I230" s="0" t="inlineStr">
         <is>
           <t>c</t>
-        </is>
-      </c>
-    </row>
-    <row r="230">
-      <c r="J230" s="0" t="inlineStr">
-        <is>
-          <t>id</t>
-        </is>
-      </c>
-      <c r="L230" s="0" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="N230" s="0" t="inlineStr">
-        <is>
-          <t>订单ID</t>
         </is>
       </c>
     </row>
     <row r="231">
       <c r="J231" s="0" t="inlineStr">
         <is>
-          <t>requiredItems</t>
+          <t>id</t>
         </is>
       </c>
       <c r="L231" s="0" t="inlineStr">
         <is>
-          <t>(list#sep=;),cfg.ItemExchange#sep=,</t>
+          <t>int</t>
         </is>
       </c>
       <c r="N231" s="0" t="inlineStr">
         <is>
-          <t>需求物品</t>
+          <t>订单ID</t>
         </is>
       </c>
     </row>
     <row r="232">
       <c r="J232" s="0" t="inlineStr">
         <is>
-          <t>rewardGold</t>
+          <t>requiredItems</t>
         </is>
       </c>
       <c r="L232" s="0" t="inlineStr">
         <is>
-          <t>int</t>
+          <t>(list#sep=;),cfg.ItemExchange#sep=,</t>
         </is>
       </c>
       <c r="N232" s="0" t="inlineStr">
         <is>
-          <t>奖励金币</t>
+          <t>需求物品</t>
         </is>
       </c>
     </row>
     <row r="233">
       <c r="J233" s="0" t="inlineStr">
         <is>
-          <t>rewardItems</t>
+          <t>rewardGold</t>
         </is>
       </c>
       <c r="L233" s="0" t="inlineStr">
         <is>
-          <t>(list#sep=;),cfg.ItemExchange#sep=,</t>
+          <t>int</t>
         </is>
       </c>
       <c r="N233" s="0" t="inlineStr">
         <is>
-          <t>奖励物品</t>
+          <t>奖励金币</t>
         </is>
       </c>
     </row>
     <row r="234">
       <c r="J234" s="0" t="inlineStr">
         <is>
-          <t>rewardExp</t>
+          <t>rewardItems</t>
         </is>
       </c>
       <c r="L234" s="0" t="inlineStr">
         <is>
-          <t>int</t>
+          <t>(list#sep=;),cfg.ItemExchange#sep=,</t>
         </is>
       </c>
       <c r="N234" s="0" t="inlineStr">
         <is>
-          <t>奖励经验</t>
+          <t>奖励物品</t>
         </is>
       </c>
     </row>
     <row r="235">
       <c r="J235" s="0" t="inlineStr">
         <is>
-          <t>timeLimit</t>
+          <t>rewardExp</t>
         </is>
       </c>
       <c r="L235" s="0" t="inlineStr">
         <is>
-          <t>float</t>
+          <t>int</t>
         </is>
       </c>
       <c r="N235" s="0" t="inlineStr">
         <is>
-          <t>时限</t>
+          <t>奖励经验</t>
         </is>
       </c>
     </row>
     <row r="236">
       <c r="J236" s="0" t="inlineStr">
         <is>
-          <t>weight</t>
+          <t>timeLimit</t>
         </is>
       </c>
       <c r="L236" s="0" t="inlineStr">
         <is>
-          <t>int</t>
+          <t>float</t>
         </is>
       </c>
       <c r="N236" s="0" t="inlineStr">
         <is>
-          <t>权重</t>
+          <t>时限</t>
         </is>
       </c>
     </row>
     <row r="237">
       <c r="J237" s="0" t="inlineStr">
         <is>
+          <t>weight</t>
+        </is>
+      </c>
+      <c r="L237" s="0" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="N237" s="0" t="inlineStr">
+        <is>
+          <t>权重</t>
+        </is>
+      </c>
+    </row>
+    <row r="238">
+      <c r="J238" s="0" t="inlineStr">
+        <is>
           <t>minPlayerLevel</t>
         </is>
       </c>
-      <c r="L237" s="0" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="N237" s="0" t="inlineStr">
+      <c r="L238" s="0" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="N238" s="0" t="inlineStr">
         <is>
           <t>最低等级</t>
         </is>
       </c>
     </row>
-    <row r="238">
-      <c r="B238" s="0" t="inlineStr">
+    <row r="239">
+      <c r="B239" s="0" t="inlineStr">
         <is>
           <t>cfg.SimTimeConfig</t>
         </is>
       </c>
-      <c r="G238" s="0" t="inlineStr">
+      <c r="G239" s="0" t="inlineStr">
         <is>
           <t>经营时间配置</t>
         </is>
       </c>
-      <c r="I238" s="0" t="inlineStr">
+      <c r="I239" s="0" t="inlineStr">
         <is>
           <t>c</t>
-        </is>
-      </c>
-    </row>
-    <row r="239">
-      <c r="J239" s="0" t="inlineStr">
-        <is>
-          <t>id</t>
-        </is>
-      </c>
-      <c r="L239" s="0" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="N239" s="0" t="inlineStr">
-        <is>
-          <t>ID</t>
         </is>
       </c>
     </row>
     <row r="240">
       <c r="J240" s="0" t="inlineStr">
         <is>
-          <t>baseSpeed</t>
+          <t>id</t>
         </is>
       </c>
       <c r="L240" s="0" t="inlineStr">
         <is>
-          <t>float</t>
+          <t>int</t>
         </is>
       </c>
       <c r="N240" s="0" t="inlineStr">
         <is>
-          <t>基础速度</t>
+          <t>ID</t>
         </is>
       </c>
     </row>
     <row r="241">
       <c r="J241" s="0" t="inlineStr">
         <is>
-          <t>fastSpeed</t>
+          <t>baseSpeed</t>
         </is>
       </c>
       <c r="L241" s="0" t="inlineStr">
@@ -5223,14 +5223,14 @@
       </c>
       <c r="N241" s="0" t="inlineStr">
         <is>
-          <t>加速速度</t>
+          <t>基础速度</t>
         </is>
       </c>
     </row>
     <row r="242">
       <c r="J242" s="0" t="inlineStr">
         <is>
-          <t>maxSpeed</t>
+          <t>fastSpeed</t>
         </is>
       </c>
       <c r="L242" s="0" t="inlineStr">
@@ -5240,14 +5240,14 @@
       </c>
       <c r="N242" s="0" t="inlineStr">
         <is>
-          <t>最大速度</t>
+          <t>加速速度</t>
         </is>
       </c>
     </row>
     <row r="243">
       <c r="J243" s="0" t="inlineStr">
         <is>
-          <t>orderRefreshInterval</t>
+          <t>maxSpeed</t>
         </is>
       </c>
       <c r="L243" s="0" t="inlineStr">
@@ -5257,82 +5257,82 @@
       </c>
       <c r="N243" s="0" t="inlineStr">
         <is>
-          <t>订单刷新间隔</t>
+          <t>最大速度</t>
         </is>
       </c>
     </row>
     <row r="244">
       <c r="J244" s="0" t="inlineStr">
         <is>
+          <t>orderRefreshInterval</t>
+        </is>
+      </c>
+      <c r="L244" s="0" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="N244" s="0" t="inlineStr">
+        <is>
+          <t>订单刷新间隔</t>
+        </is>
+      </c>
+    </row>
+    <row r="245">
+      <c r="J245" s="0" t="inlineStr">
+        <is>
           <t>maxOrderCount</t>
         </is>
       </c>
-      <c r="L244" s="0" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="N244" s="0" t="inlineStr">
+      <c r="L245" s="0" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="N245" s="0" t="inlineStr">
         <is>
           <t>最大订单数</t>
         </is>
       </c>
     </row>
-    <row r="245">
-      <c r="B245" s="0" t="inlineStr">
+    <row r="246">
+      <c r="B246" s="0" t="inlineStr">
         <is>
           <t>cfg.Camera3D</t>
         </is>
       </c>
-      <c r="G245" s="0" t="inlineStr">
+      <c r="G246" s="0" t="inlineStr">
         <is>
           <t>3D摄像机配置</t>
         </is>
       </c>
-      <c r="I245" s="0" t="inlineStr">
+      <c r="I246" s="0" t="inlineStr">
         <is>
           <t>c</t>
-        </is>
-      </c>
-    </row>
-    <row r="246">
-      <c r="J246" s="0" t="inlineStr">
-        <is>
-          <t>id</t>
-        </is>
-      </c>
-      <c r="L246" s="0" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="N246" s="0" t="inlineStr">
-        <is>
-          <t>配置ID</t>
         </is>
       </c>
     </row>
     <row r="247">
       <c r="J247" s="0" t="inlineStr">
         <is>
-          <t>pitchAngle</t>
+          <t>id</t>
         </is>
       </c>
       <c r="L247" s="0" t="inlineStr">
         <is>
-          <t>float</t>
+          <t>int</t>
         </is>
       </c>
       <c r="N247" s="0" t="inlineStr">
         <is>
-          <t>俯视角度</t>
+          <t>配置ID</t>
         </is>
       </c>
     </row>
     <row r="248">
       <c r="J248" s="0" t="inlineStr">
         <is>
-          <t>initialHeight</t>
+          <t>pitchAngle</t>
         </is>
       </c>
       <c r="L248" s="0" t="inlineStr">
@@ -5342,14 +5342,14 @@
       </c>
       <c r="N248" s="0" t="inlineStr">
         <is>
-          <t>初始高度</t>
+          <t>俯视角度</t>
         </is>
       </c>
     </row>
     <row r="249">
       <c r="J249" s="0" t="inlineStr">
         <is>
-          <t>initialDistance</t>
+          <t>initialHeight</t>
         </is>
       </c>
       <c r="L249" s="0" t="inlineStr">
@@ -5359,14 +5359,14 @@
       </c>
       <c r="N249" s="0" t="inlineStr">
         <is>
-          <t>初始距离</t>
+          <t>初始高度</t>
         </is>
       </c>
     </row>
     <row r="250">
       <c r="J250" s="0" t="inlineStr">
         <is>
-          <t>fov</t>
+          <t>initialDistance</t>
         </is>
       </c>
       <c r="L250" s="0" t="inlineStr">
@@ -5376,14 +5376,14 @@
       </c>
       <c r="N250" s="0" t="inlineStr">
         <is>
-          <t>视场角</t>
+          <t>初始距离</t>
         </is>
       </c>
     </row>
     <row r="251">
       <c r="J251" s="0" t="inlineStr">
         <is>
-          <t>minZoom</t>
+          <t>fov</t>
         </is>
       </c>
       <c r="L251" s="0" t="inlineStr">
@@ -5393,14 +5393,14 @@
       </c>
       <c r="N251" s="0" t="inlineStr">
         <is>
-          <t>最小缩放</t>
+          <t>视场角</t>
         </is>
       </c>
     </row>
     <row r="252">
       <c r="J252" s="0" t="inlineStr">
         <is>
-          <t>maxZoom</t>
+          <t>minZoom</t>
         </is>
       </c>
       <c r="L252" s="0" t="inlineStr">
@@ -5410,14 +5410,14 @@
       </c>
       <c r="N252" s="0" t="inlineStr">
         <is>
-          <t>最大缩放</t>
+          <t>最小缩放</t>
         </is>
       </c>
     </row>
     <row r="253">
       <c r="J253" s="0" t="inlineStr">
         <is>
-          <t>moveSpeed</t>
+          <t>maxZoom</t>
         </is>
       </c>
       <c r="L253" s="0" t="inlineStr">
@@ -5427,14 +5427,14 @@
       </c>
       <c r="N253" s="0" t="inlineStr">
         <is>
-          <t>移动速度</t>
+          <t>最大缩放</t>
         </is>
       </c>
     </row>
     <row r="254">
       <c r="J254" s="0" t="inlineStr">
         <is>
-          <t>zoomSpeed</t>
+          <t>moveSpeed</t>
         </is>
       </c>
       <c r="L254" s="0" t="inlineStr">
@@ -5444,14 +5444,14 @@
       </c>
       <c r="N254" s="0" t="inlineStr">
         <is>
-          <t>缩放速度</t>
+          <t>移动速度</t>
         </is>
       </c>
     </row>
     <row r="255">
       <c r="J255" s="0" t="inlineStr">
         <is>
-          <t>maxRotationAngle</t>
+          <t>zoomSpeed</t>
         </is>
       </c>
       <c r="L255" s="0" t="inlineStr">
@@ -5461,14 +5461,14 @@
       </c>
       <c r="N255" s="0" t="inlineStr">
         <is>
-          <t>最大旋转角度</t>
+          <t>缩放速度</t>
         </is>
       </c>
     </row>
     <row r="256">
       <c r="J256" s="0" t="inlineStr">
         <is>
-          <t>rotationSpeed</t>
+          <t>maxRotationAngle</t>
         </is>
       </c>
       <c r="L256" s="0" t="inlineStr">
@@ -5478,61 +5478,66 @@
       </c>
       <c r="N256" s="0" t="inlineStr">
         <is>
-          <t>旋转速度</t>
+          <t>最大旋转角度</t>
         </is>
       </c>
     </row>
     <row r="257">
       <c r="J257" s="0" t="inlineStr">
         <is>
+          <t>rotationSpeed</t>
+        </is>
+      </c>
+      <c r="L257" s="0" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="N257" s="0" t="inlineStr">
+        <is>
+          <t>旋转速度</t>
+        </is>
+      </c>
+    </row>
+    <row r="258">
+      <c r="J258" s="0" t="inlineStr">
+        <is>
           <t>followSmoothTime</t>
         </is>
       </c>
-      <c r="L257" s="0" t="inlineStr">
-        <is>
-          <t>float</t>
-        </is>
-      </c>
-      <c r="N257" s="0" t="inlineStr">
+      <c r="L258" s="0" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="N258" s="0" t="inlineStr">
         <is>
           <t>跟随平滑时间</t>
         </is>
       </c>
     </row>
-    <row r="258"/>
-    <row r="259">
-      <c r="B259" s="0" t="inlineStr">
+    <row r="259"/>
+    <row r="260">
+      <c r="B260" s="0" t="inlineStr">
         <is>
           <t>cfg.LootContainer</t>
         </is>
       </c>
-      <c r="G259" s="0" t="inlineStr">
+      <c r="G260" s="0" t="inlineStr">
         <is>
           <t>容器掉落记录</t>
         </is>
       </c>
-      <c r="I259" s="0" t="inlineStr">
+      <c r="I260" s="0" t="inlineStr">
         <is>
           <t>c</t>
-        </is>
-      </c>
-    </row>
-    <row r="260">
-      <c r="J260" s="0" t="inlineStr">
-        <is>
-          <t>id</t>
-        </is>
-      </c>
-      <c r="L260" s="0" t="inlineStr">
-        <is>
-          <t>int</t>
         </is>
       </c>
     </row>
     <row r="261">
       <c r="J261" s="0" t="inlineStr">
         <is>
-          <t>containerId</t>
+          <t>id</t>
         </is>
       </c>
       <c r="L261" s="0" t="inlineStr">
@@ -5544,7 +5549,7 @@
     <row r="262">
       <c r="J262" s="0" t="inlineStr">
         <is>
-          <t>itemId</t>
+          <t>containerId</t>
         </is>
       </c>
       <c r="L262" s="0" t="inlineStr">
@@ -5556,7 +5561,7 @@
     <row r="263">
       <c r="J263" s="0" t="inlineStr">
         <is>
-          <t>weight</t>
+          <t>itemId</t>
         </is>
       </c>
       <c r="L263" s="0" t="inlineStr">
@@ -5568,7 +5573,7 @@
     <row r="264">
       <c r="J264" s="0" t="inlineStr">
         <is>
-          <t>minCount</t>
+          <t>weight</t>
         </is>
       </c>
       <c r="L264" s="0" t="inlineStr">
@@ -5580,208 +5585,203 @@
     <row r="265">
       <c r="J265" s="0" t="inlineStr">
         <is>
+          <t>minCount</t>
+        </is>
+      </c>
+      <c r="L265" s="0" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+    </row>
+    <row r="266">
+      <c r="J266" s="0" t="inlineStr">
+        <is>
           <t>maxCount</t>
         </is>
       </c>
-      <c r="L265" s="0" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-    </row>
-    <row r="266"/>
-    <row r="267">
-      <c r="B267" s="0" t="inlineStr">
+      <c r="L266" s="0" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+    </row>
+    <row r="267"/>
+    <row r="268">
+      <c r="B268" s="0" t="inlineStr">
         <is>
           <t>cfg.Note</t>
         </is>
       </c>
-      <c r="G267" s="0" t="inlineStr">
+      <c r="G268" s="0" t="inlineStr">
         <is>
           <t>小纸条记录</t>
         </is>
       </c>
-      <c r="I267" s="0" t="inlineStr">
+      <c r="I268" s="0" t="inlineStr">
         <is>
           <t>c</t>
-        </is>
-      </c>
-    </row>
-    <row r="268">
-      <c r="J268" s="0" t="inlineStr">
-        <is>
-          <t>id</t>
-        </is>
-      </c>
-      <c r="L268" s="0" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="N268" s="0" t="inlineStr">
-        <is>
-          <t>纸条ID</t>
         </is>
       </c>
     </row>
     <row r="269">
       <c r="J269" s="0" t="inlineStr">
         <is>
-          <t>title</t>
+          <t>id</t>
         </is>
       </c>
       <c r="L269" s="0" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>int</t>
         </is>
       </c>
       <c r="N269" s="0" t="inlineStr">
         <is>
-          <t>标题</t>
+          <t>纸条ID</t>
         </is>
       </c>
     </row>
     <row r="270">
       <c r="J270" s="0" t="inlineStr">
         <is>
+          <t>title</t>
+        </is>
+      </c>
+      <c r="L270" s="0" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="N270" s="0" t="inlineStr">
+        <is>
+          <t>标题</t>
+        </is>
+      </c>
+    </row>
+    <row r="271">
+      <c r="J271" s="0" t="inlineStr">
+        <is>
           <t>content</t>
         </is>
       </c>
-      <c r="L270" s="0" t="inlineStr">
+      <c r="L271" s="0" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="N270" s="0" t="inlineStr">
+      <c r="N271" s="0" t="inlineStr">
         <is>
           <t>正文(支持
 换行)</t>
         </is>
       </c>
     </row>
-    <row r="271">
-      <c r="B271" s="0" t="inlineStr">
+    <row r="272">
+      <c r="B272" s="0" t="inlineStr">
         <is>
           <t>cfg.PlayerLevel</t>
         </is>
       </c>
-      <c r="G271" s="0" t="inlineStr">
+      <c r="G272" s="0" t="inlineStr">
         <is>
           <t>玩家等级经验表</t>
         </is>
       </c>
-      <c r="I271" s="0" t="inlineStr">
+      <c r="I272" s="0" t="inlineStr">
         <is>
           <t>c</t>
-        </is>
-      </c>
-    </row>
-    <row r="272">
-      <c r="J272" s="0" t="inlineStr">
-        <is>
-          <t>level</t>
-        </is>
-      </c>
-      <c r="L272" s="0" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="N272" s="0" t="inlineStr">
-        <is>
-          <t>等级</t>
         </is>
       </c>
     </row>
     <row r="273">
       <c r="J273" s="0" t="inlineStr">
         <is>
+          <t>level</t>
+        </is>
+      </c>
+      <c r="L273" s="0" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="N273" s="0" t="inlineStr">
+        <is>
+          <t>等级</t>
+        </is>
+      </c>
+    </row>
+    <row r="274">
+      <c r="J274" s="0" t="inlineStr">
+        <is>
           <t>expToNext</t>
         </is>
       </c>
-      <c r="L273" s="0" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="N273" s="0" t="inlineStr">
+      <c r="L274" s="0" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="N274" s="0" t="inlineStr">
         <is>
           <t>升到下一级所需经验</t>
         </is>
       </c>
     </row>
-    <row r="274">
-      <c r="B274" s="0" t="inlineStr">
+    <row r="275">
+      <c r="B275" s="0" t="inlineStr">
         <is>
           <t>cfg.Unlock</t>
         </is>
       </c>
-      <c r="G274" s="0" t="inlineStr">
+      <c r="G275" s="0" t="inlineStr">
         <is>
           <t>内容解锁表</t>
         </is>
       </c>
-      <c r="I274" s="0" t="inlineStr">
+      <c r="I275" s="0" t="inlineStr">
         <is>
           <t>c</t>
-        </is>
-      </c>
-    </row>
-    <row r="275">
-      <c r="J275" s="0" t="inlineStr">
-        <is>
-          <t>id</t>
-        </is>
-      </c>
-      <c r="L275" s="0" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="N275" s="0" t="inlineStr">
-        <is>
-          <t>解锁ID</t>
         </is>
       </c>
     </row>
     <row r="276">
       <c r="J276" s="0" t="inlineStr">
         <is>
-          <t>contentType</t>
+          <t>id</t>
         </is>
       </c>
       <c r="L276" s="0" t="inlineStr">
         <is>
-          <t>cfg.UnlockContentType</t>
+          <t>int</t>
         </is>
       </c>
       <c r="N276" s="0" t="inlineStr">
         <is>
-          <t>内容类型</t>
+          <t>解锁ID</t>
         </is>
       </c>
     </row>
     <row r="277">
       <c r="J277" s="0" t="inlineStr">
         <is>
-          <t>targetId</t>
+          <t>contentType</t>
         </is>
       </c>
       <c r="L277" s="0" t="inlineStr">
         <is>
-          <t>int</t>
+          <t>cfg.UnlockContentType</t>
         </is>
       </c>
       <c r="N277" s="0" t="inlineStr">
         <is>
-          <t>目标ID（关卡/武器）</t>
+          <t>内容类型</t>
         </is>
       </c>
     </row>
     <row r="278">
       <c r="J278" s="0" t="inlineStr">
         <is>
-          <t>requirePlayerLevel</t>
+          <t>targetId</t>
         </is>
       </c>
       <c r="L278" s="0" t="inlineStr">
@@ -5791,14 +5791,14 @@
       </c>
       <c r="N278" s="0" t="inlineStr">
         <is>
-          <t>要求玩家等级(0=无)</t>
+          <t>目标ID（关卡/武器）</t>
         </is>
       </c>
     </row>
     <row r="279">
       <c r="J279" s="0" t="inlineStr">
         <is>
-          <t>requireCompleteLevelId</t>
+          <t>requirePlayerLevel</t>
         </is>
       </c>
       <c r="L279" s="0" t="inlineStr">
@@ -5808,14 +5808,14 @@
       </c>
       <c r="N279" s="0" t="inlineStr">
         <is>
-          <t>要求通关关卡ID(0=无)</t>
+          <t>要求玩家等级(0=无)</t>
         </is>
       </c>
     </row>
     <row r="280">
       <c r="J280" s="0" t="inlineStr">
         <is>
-          <t>costGold</t>
+          <t>requireCompleteLevelId</t>
         </is>
       </c>
       <c r="L280" s="0" t="inlineStr">
@@ -5825,82 +5825,82 @@
       </c>
       <c r="N280" s="0" t="inlineStr">
         <is>
-          <t>解锁花费金币(0=免费)</t>
+          <t>要求通关关卡ID(0=无)</t>
         </is>
       </c>
     </row>
     <row r="281">
       <c r="J281" s="0" t="inlineStr">
         <is>
+          <t>costGold</t>
+        </is>
+      </c>
+      <c r="L281" s="0" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="N281" s="0" t="inlineStr">
+        <is>
+          <t>解锁花费金币(0=免费)</t>
+        </is>
+      </c>
+    </row>
+    <row r="282">
+      <c r="J282" s="0" t="inlineStr">
+        <is>
           <t>comment</t>
         </is>
       </c>
-      <c r="L281" s="0" t="inlineStr">
+      <c r="L282" s="0" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="N281" s="0" t="inlineStr">
+      <c r="N282" s="0" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="282">
-      <c r="B282" s="0" t="inlineStr">
+    <row r="283">
+      <c r="B283" s="0" t="inlineStr">
         <is>
           <t>cfg.Npc</t>
         </is>
       </c>
-      <c r="G282" s="0" t="inlineStr">
+      <c r="G283" s="0" t="inlineStr">
         <is>
           <t>NPC记录</t>
         </is>
       </c>
-      <c r="I282" s="0" t="inlineStr">
+      <c r="I283" s="0" t="inlineStr">
         <is>
           <t>c</t>
-        </is>
-      </c>
-    </row>
-    <row r="283">
-      <c r="J283" s="0" t="inlineStr">
-        <is>
-          <t>id</t>
-        </is>
-      </c>
-      <c r="L283" s="0" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="N283" s="0" t="inlineStr">
-        <is>
-          <t>NPC ID</t>
         </is>
       </c>
     </row>
     <row r="284">
       <c r="J284" s="0" t="inlineStr">
         <is>
-          <t>name</t>
+          <t>id</t>
         </is>
       </c>
       <c r="L284" s="0" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>int</t>
         </is>
       </c>
       <c r="N284" s="0" t="inlineStr">
         <is>
-          <t>显示名</t>
+          <t>NPC ID</t>
         </is>
       </c>
     </row>
     <row r="285">
       <c r="J285" s="0" t="inlineStr">
         <is>
-          <t>role</t>
+          <t>name</t>
         </is>
       </c>
       <c r="L285" s="0" t="inlineStr">
@@ -5910,201 +5910,201 @@
       </c>
       <c r="N285" s="0" t="inlineStr">
         <is>
-          <t>身份/职业</t>
+          <t>显示名</t>
         </is>
       </c>
     </row>
     <row r="286">
       <c r="J286" s="0" t="inlineStr">
         <is>
-          <t>moveSpeed</t>
+          <t>role</t>
         </is>
       </c>
       <c r="L286" s="0" t="inlineStr">
         <is>
-          <t>float</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N286" s="0" t="inlineStr">
         <is>
-          <t>移动速度(0=站桩)</t>
+          <t>身份/职业</t>
         </is>
       </c>
     </row>
     <row r="287">
       <c r="J287" s="0" t="inlineStr">
         <is>
-          <t>patrolPath</t>
+          <t>moveSpeed</t>
         </is>
       </c>
       <c r="L287" s="0" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>float</t>
         </is>
       </c>
       <c r="N287" s="0" t="inlineStr">
         <is>
-          <t>巡逻路径(x,z|x,z 空=不巡逻)</t>
+          <t>移动速度(0=站桩)</t>
         </is>
       </c>
     </row>
     <row r="288">
       <c r="J288" s="0" t="inlineStr">
         <is>
+          <t>patrolPath</t>
+        </is>
+      </c>
+      <c r="L288" s="0" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="N288" s="0" t="inlineStr">
+        <is>
+          <t>巡逻路径(x,z|x,z 空=不巡逻)</t>
+        </is>
+      </c>
+    </row>
+    <row r="289">
+      <c r="J289" s="0" t="inlineStr">
+        <is>
           <t>dialogueId</t>
         </is>
       </c>
-      <c r="L288" s="0" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="N288" s="0" t="inlineStr">
+      <c r="L289" s="0" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="N289" s="0" t="inlineStr">
         <is>
           <t>对话ID(预留,0=无)</t>
         </is>
       </c>
     </row>
-    <row r="289">
-      <c r="B289" s="0" t="inlineStr">
+    <row r="290">
+      <c r="B290" s="0" t="inlineStr">
         <is>
           <t>cfg.Dialogue</t>
         </is>
       </c>
-      <c r="G289" s="0" t="inlineStr">
+      <c r="G290" s="0" t="inlineStr">
         <is>
           <t>对话头</t>
         </is>
       </c>
-      <c r="I289" s="0" t="inlineStr">
+      <c r="I290" s="0" t="inlineStr">
         <is>
           <t>c</t>
-        </is>
-      </c>
-    </row>
-    <row r="290">
-      <c r="J290" s="0" t="inlineStr">
-        <is>
-          <t>id</t>
-        </is>
-      </c>
-      <c r="L290" s="0" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="N290" s="0" t="inlineStr">
-        <is>
-          <t>对话ID</t>
         </is>
       </c>
     </row>
     <row r="291">
       <c r="J291" s="0" t="inlineStr">
         <is>
-          <t>name</t>
+          <t>id</t>
         </is>
       </c>
       <c r="L291" s="0" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>int</t>
         </is>
       </c>
       <c r="N291" s="0" t="inlineStr">
         <is>
-          <t>注释名(不显示)</t>
+          <t>对话ID</t>
         </is>
       </c>
     </row>
     <row r="292">
       <c r="J292" s="0" t="inlineStr">
         <is>
-          <t>startNode</t>
+          <t>name</t>
         </is>
       </c>
       <c r="L292" s="0" t="inlineStr">
         <is>
-          <t>int</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N292" s="0" t="inlineStr">
         <is>
-          <t>起始节点ID</t>
+          <t>注释名(不显示)</t>
         </is>
       </c>
     </row>
     <row r="293">
       <c r="J293" s="0" t="inlineStr">
         <is>
-          <t>onceOnly</t>
+          <t>startNode</t>
         </is>
       </c>
       <c r="L293" s="0" t="inlineStr">
         <is>
-          <t>bool</t>
+          <t>int</t>
         </is>
       </c>
       <c r="N293" s="0" t="inlineStr">
         <is>
-          <t>只触发一次</t>
+          <t>起始节点ID</t>
         </is>
       </c>
     </row>
     <row r="294">
       <c r="J294" s="0" t="inlineStr">
         <is>
+          <t>onceOnly</t>
+        </is>
+      </c>
+      <c r="L294" s="0" t="inlineStr">
+        <is>
+          <t>bool</t>
+        </is>
+      </c>
+      <c r="N294" s="0" t="inlineStr">
+        <is>
+          <t>只触发一次</t>
+        </is>
+      </c>
+    </row>
+    <row r="295">
+      <c r="J295" s="0" t="inlineStr">
+        <is>
           <t>priority</t>
         </is>
       </c>
-      <c r="L294" s="0" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="N294" s="0" t="inlineStr">
+      <c r="L295" s="0" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="N295" s="0" t="inlineStr">
         <is>
           <t>优先级(大优先)</t>
         </is>
       </c>
     </row>
-    <row r="295">
-      <c r="B295" s="0" t="inlineStr">
+    <row r="296">
+      <c r="B296" s="0" t="inlineStr">
         <is>
           <t>cfg.DialogueNode</t>
         </is>
       </c>
-      <c r="G295" s="0" t="inlineStr">
+      <c r="G296" s="0" t="inlineStr">
         <is>
           <t>对话节点</t>
         </is>
       </c>
-      <c r="I295" s="0" t="inlineStr">
+      <c r="I296" s="0" t="inlineStr">
         <is>
           <t>c</t>
-        </is>
-      </c>
-    </row>
-    <row r="296">
-      <c r="J296" s="0" t="inlineStr">
-        <is>
-          <t>id</t>
-        </is>
-      </c>
-      <c r="L296" s="0" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="N296" s="0" t="inlineStr">
-        <is>
-          <t>节点ID</t>
         </is>
       </c>
     </row>
     <row r="297">
       <c r="J297" s="0" t="inlineStr">
         <is>
-          <t>dialogueId</t>
+          <t>id</t>
         </is>
       </c>
       <c r="L297" s="0" t="inlineStr">
@@ -6114,31 +6114,31 @@
       </c>
       <c r="N297" s="0" t="inlineStr">
         <is>
-          <t>所属对话</t>
+          <t>节点ID</t>
         </is>
       </c>
     </row>
     <row r="298">
       <c r="J298" s="0" t="inlineStr">
         <is>
-          <t>type</t>
+          <t>dialogueId</t>
         </is>
       </c>
       <c r="L298" s="0" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>int</t>
         </is>
       </c>
       <c r="N298" s="0" t="inlineStr">
         <is>
-          <t>类型(line/choice/setflag/end)</t>
+          <t>所属对话</t>
         </is>
       </c>
     </row>
     <row r="299">
       <c r="J299" s="0" t="inlineStr">
         <is>
-          <t>speaker</t>
+          <t>type</t>
         </is>
       </c>
       <c r="L299" s="0" t="inlineStr">
@@ -6148,14 +6148,14 @@
       </c>
       <c r="N299" s="0" t="inlineStr">
         <is>
-          <t>说话人</t>
+          <t>类型(line/choice/setflag/end)</t>
         </is>
       </c>
     </row>
     <row r="300">
       <c r="J300" s="0" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>speaker</t>
         </is>
       </c>
       <c r="L300" s="0" t="inlineStr">
@@ -6165,14 +6165,14 @@
       </c>
       <c r="N300" s="0" t="inlineStr">
         <is>
-          <t>正文</t>
+          <t>说话人</t>
         </is>
       </c>
     </row>
     <row r="301">
       <c r="J301" s="0" t="inlineStr">
         <is>
-          <t>choices</t>
+          <t>text</t>
         </is>
       </c>
       <c r="L301" s="0" t="inlineStr">
@@ -6182,14 +6182,14 @@
       </c>
       <c r="N301" s="0" t="inlineStr">
         <is>
-          <t>选项(文本-&gt;节点|...)</t>
+          <t>正文</t>
         </is>
       </c>
     </row>
     <row r="302">
       <c r="J302" s="0" t="inlineStr">
         <is>
-          <t>condition</t>
+          <t>choices</t>
         </is>
       </c>
       <c r="L302" s="0" t="inlineStr">
@@ -6199,14 +6199,14 @@
       </c>
       <c r="N302" s="0" t="inlineStr">
         <is>
-          <t>进入条件</t>
+          <t>选项(文本-&gt;节点|...)</t>
         </is>
       </c>
     </row>
     <row r="303">
       <c r="J303" s="0" t="inlineStr">
         <is>
-          <t>action</t>
+          <t>condition</t>
         </is>
       </c>
       <c r="L303" s="0" t="inlineStr">
@@ -6216,82 +6216,82 @@
       </c>
       <c r="N303" s="0" t="inlineStr">
         <is>
-          <t>到达动作</t>
+          <t>进入条件</t>
         </is>
       </c>
     </row>
     <row r="304">
       <c r="J304" s="0" t="inlineStr">
         <is>
+          <t>action</t>
+        </is>
+      </c>
+      <c r="L304" s="0" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="N304" s="0" t="inlineStr">
+        <is>
+          <t>到达动作</t>
+        </is>
+      </c>
+    </row>
+    <row r="305">
+      <c r="J305" s="0" t="inlineStr">
+        <is>
           <t>next</t>
         </is>
       </c>
-      <c r="L304" s="0" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="N304" s="0" t="inlineStr">
+      <c r="L305" s="0" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="N305" s="0" t="inlineStr">
         <is>
           <t>下一节点(0=结束)</t>
         </is>
       </c>
     </row>
-    <row r="305">
-      <c r="B305" s="0" t="inlineStr">
+    <row r="306">
+      <c r="B306" s="0" t="inlineStr">
         <is>
           <t>cfg.Quest</t>
         </is>
       </c>
-      <c r="G305" s="0" t="inlineStr">
+      <c r="G306" s="0" t="inlineStr">
         <is>
           <t>任务定义</t>
         </is>
       </c>
-      <c r="I305" s="0" t="inlineStr">
+      <c r="I306" s="0" t="inlineStr">
         <is>
           <t>c</t>
-        </is>
-      </c>
-    </row>
-    <row r="306">
-      <c r="J306" s="0" t="inlineStr">
-        <is>
-          <t>id</t>
-        </is>
-      </c>
-      <c r="L306" s="0" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="N306" s="0" t="inlineStr">
-        <is>
-          <t>任务ID</t>
         </is>
       </c>
     </row>
     <row r="307">
       <c r="J307" s="0" t="inlineStr">
         <is>
-          <t>name</t>
+          <t>id</t>
         </is>
       </c>
       <c r="L307" s="0" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>int</t>
         </is>
       </c>
       <c r="N307" s="0" t="inlineStr">
         <is>
-          <t>显示名</t>
+          <t>任务ID</t>
         </is>
       </c>
     </row>
     <row r="308">
       <c r="J308" s="0" t="inlineStr">
         <is>
-          <t>desc</t>
+          <t>name</t>
         </is>
       </c>
       <c r="L308" s="0" t="inlineStr">
@@ -6301,48 +6301,48 @@
       </c>
       <c r="N308" s="0" t="inlineStr">
         <is>
-          <t>描述</t>
+          <t>显示名</t>
         </is>
       </c>
     </row>
     <row r="309">
       <c r="J309" s="0" t="inlineStr">
         <is>
-          <t>giverNpc</t>
+          <t>desc</t>
         </is>
       </c>
       <c r="L309" s="0" t="inlineStr">
         <is>
-          <t>int</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N309" s="0" t="inlineStr">
         <is>
-          <t>发布NPC(0=任务板)</t>
+          <t>描述</t>
         </is>
       </c>
     </row>
     <row r="310">
       <c r="J310" s="0" t="inlineStr">
         <is>
-          <t>prereq</t>
+          <t>giverNpc</t>
         </is>
       </c>
       <c r="L310" s="0" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>int</t>
         </is>
       </c>
       <c r="N310" s="0" t="inlineStr">
         <is>
-          <t>接取条件表达式(空=无)</t>
+          <t>发布NPC(0=任务板)</t>
         </is>
       </c>
     </row>
     <row r="311">
       <c r="J311" s="0" t="inlineStr">
         <is>
-          <t>rewards</t>
+          <t>prereq</t>
         </is>
       </c>
       <c r="L311" s="0" t="inlineStr">
@@ -6352,65 +6352,65 @@
       </c>
       <c r="N311" s="0" t="inlineStr">
         <is>
-          <t>奖励(gold:200|exp:50|item:3001:2)</t>
+          <t>接取条件表达式(空=无)</t>
         </is>
       </c>
     </row>
     <row r="312">
       <c r="J312" s="0" t="inlineStr">
         <is>
+          <t>rewards</t>
+        </is>
+      </c>
+      <c r="L312" s="0" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="N312" s="0" t="inlineStr">
+        <is>
+          <t>奖励(gold:200|exp:50|item:3001:2)</t>
+        </is>
+      </c>
+    </row>
+    <row r="313">
+      <c r="J313" s="0" t="inlineStr">
+        <is>
           <t>nextQuest</t>
         </is>
       </c>
-      <c r="L312" s="0" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="N312" s="0" t="inlineStr">
+      <c r="L313" s="0" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="N313" s="0" t="inlineStr">
         <is>
           <t>后继任务(0=无)</t>
         </is>
       </c>
     </row>
-    <row r="313">
-      <c r="B313" s="0" t="inlineStr">
+    <row r="314">
+      <c r="B314" s="0" t="inlineStr">
         <is>
           <t>cfg.QuestObjective</t>
         </is>
       </c>
-      <c r="G313" s="0" t="inlineStr">
+      <c r="G314" s="0" t="inlineStr">
         <is>
           <t>任务目标</t>
         </is>
       </c>
-      <c r="I313" s="0" t="inlineStr">
+      <c r="I314" s="0" t="inlineStr">
         <is>
           <t>c</t>
-        </is>
-      </c>
-    </row>
-    <row r="314">
-      <c r="J314" s="0" t="inlineStr">
-        <is>
-          <t>id</t>
-        </is>
-      </c>
-      <c r="L314" s="0" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="N314" s="0" t="inlineStr">
-        <is>
-          <t>目标ID</t>
         </is>
       </c>
     </row>
     <row r="315">
       <c r="J315" s="0" t="inlineStr">
         <is>
-          <t>questId</t>
+          <t>id</t>
         </is>
       </c>
       <c r="L315" s="0" t="inlineStr">
@@ -6420,31 +6420,31 @@
       </c>
       <c r="N315" s="0" t="inlineStr">
         <is>
-          <t>所属任务</t>
+          <t>目标ID</t>
         </is>
       </c>
     </row>
     <row r="316">
       <c r="J316" s="0" t="inlineStr">
         <is>
-          <t>type</t>
+          <t>questId</t>
         </is>
       </c>
       <c r="L316" s="0" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>int</t>
         </is>
       </c>
       <c r="N316" s="0" t="inlineStr">
         <is>
-          <t>类型(kill/collect/extract/flag)</t>
+          <t>所属任务</t>
         </is>
       </c>
     </row>
     <row r="317">
       <c r="J317" s="0" t="inlineStr">
         <is>
-          <t>targetId</t>
+          <t>type</t>
         </is>
       </c>
       <c r="L317" s="0" t="inlineStr">
@@ -6454,82 +6454,82 @@
       </c>
       <c r="N317" s="0" t="inlineStr">
         <is>
-          <t>目标ID/标志键</t>
+          <t>类型(kill/collect/extract/flag)</t>
         </is>
       </c>
     </row>
     <row r="318">
       <c r="J318" s="0" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>targetId</t>
         </is>
       </c>
       <c r="L318" s="0" t="inlineStr">
         <is>
-          <t>int</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N318" s="0" t="inlineStr">
         <is>
-          <t>需求数(extract恒1)</t>
+          <t>目标ID/标志键</t>
         </is>
       </c>
     </row>
     <row r="319">
       <c r="J319" s="0" t="inlineStr">
         <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="L319" s="0" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="N319" s="0" t="inlineStr">
+        <is>
+          <t>需求数(extract恒1)</t>
+        </is>
+      </c>
+    </row>
+    <row r="320">
+      <c r="J320" s="0" t="inlineStr">
+        <is>
           <t>desc</t>
         </is>
       </c>
-      <c r="L319" s="0" t="inlineStr">
+      <c r="L320" s="0" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="N319" s="0" t="inlineStr">
+      <c r="N320" s="0" t="inlineStr">
         <is>
           <t>目标一行描述</t>
         </is>
       </c>
     </row>
-    <row r="320">
-      <c r="B320" s="0" t="inlineStr">
+    <row r="321">
+      <c r="B321" s="0" t="inlineStr">
         <is>
           <t>cfg.Localization</t>
         </is>
       </c>
-      <c r="G320" s="0" t="inlineStr">
+      <c r="G321" s="0" t="inlineStr">
         <is>
           <t>本地化词条</t>
         </is>
       </c>
-      <c r="I320" s="0" t="inlineStr">
+      <c r="I321" s="0" t="inlineStr">
         <is>
           <t>c</t>
-        </is>
-      </c>
-    </row>
-    <row r="321">
-      <c r="J321" s="0" t="inlineStr">
-        <is>
-          <t>key</t>
-        </is>
-      </c>
-      <c r="L321" s="0" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="N321" s="0" t="inlineStr">
-        <is>
-          <t>词条Key</t>
         </is>
       </c>
     </row>
     <row r="322">
       <c r="J322" s="0" t="inlineStr">
         <is>
-          <t>en</t>
+          <t>key</t>
         </is>
       </c>
       <c r="L322" s="0" t="inlineStr">
@@ -6539,14 +6539,14 @@
       </c>
       <c r="N322" s="0" t="inlineStr">
         <is>
-          <t>英文(必填/兜底)</t>
+          <t>词条Key</t>
         </is>
       </c>
     </row>
     <row r="323">
       <c r="J323" s="0" t="inlineStr">
         <is>
-          <t>zh_cn</t>
+          <t>en</t>
         </is>
       </c>
       <c r="L323" s="0" t="inlineStr">
@@ -6556,14 +6556,14 @@
       </c>
       <c r="N323" s="0" t="inlineStr">
         <is>
-          <t>简体中文</t>
+          <t>英文(必填/兜底)</t>
         </is>
       </c>
     </row>
     <row r="324">
       <c r="J324" s="0" t="inlineStr">
         <is>
-          <t>zh_tw</t>
+          <t>zh_cn</t>
         </is>
       </c>
       <c r="L324" s="0" t="inlineStr">
@@ -6573,14 +6573,14 @@
       </c>
       <c r="N324" s="0" t="inlineStr">
         <is>
-          <t>繁体中文</t>
+          <t>简体中文</t>
         </is>
       </c>
     </row>
     <row r="325">
       <c r="J325" s="0" t="inlineStr">
         <is>
-          <t>ja</t>
+          <t>zh_tw</t>
         </is>
       </c>
       <c r="L325" s="0" t="inlineStr">
@@ -6590,22 +6590,39 @@
       </c>
       <c r="N325" s="0" t="inlineStr">
         <is>
-          <t>日文</t>
+          <t>繁体中文</t>
         </is>
       </c>
     </row>
     <row r="326">
       <c r="J326" s="0" t="inlineStr">
         <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="L326" s="0" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="N326" s="0" t="inlineStr">
+        <is>
+          <t>日文</t>
+        </is>
+      </c>
+    </row>
+    <row r="327">
+      <c r="J327" s="0" t="inlineStr">
+        <is>
           <t>ko</t>
         </is>
       </c>
-      <c r="L326" s="0" t="inlineStr">
+      <c r="L327" s="0" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="N326" s="0" t="inlineStr">
+      <c r="N327" s="0" t="inlineStr">
         <is>
           <t>韩文</t>
         </is>

--- a/AfterToken/Configs/GameConfig/Datas/__beans__.xlsx
+++ b/AfterToken/Configs/GameConfig/Datas/__beans__.xlsx
@@ -1025,7 +1025,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P327"/>
+  <dimension ref="A1:P350"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col width="20.625" customWidth="1" style="1" min="2" max="4"/>
@@ -3120,17 +3120,17 @@
       </c>
     </row>
     <row r="118">
-      <c r="J118" t="inlineStr">
+      <c r="J118" s="0" t="inlineStr">
         <is>
           <t>pursuitRange</t>
         </is>
       </c>
-      <c r="L118" t="inlineStr">
-        <is>
-          <t>float</t>
-        </is>
-      </c>
-      <c r="N118" t="inlineStr">
+      <c r="L118" s="0" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="N118" s="0" t="inlineStr">
         <is>
           <t>追踪范围（米）：追击状态下玩家超过此距离则丢失目标</t>
         </is>
@@ -6625,6 +6625,397 @@
       <c r="N327" s="0" t="inlineStr">
         <is>
           <t>韩文</t>
+        </is>
+      </c>
+    </row>
+    <row r="328">
+      <c r="B328" t="inlineStr">
+        <is>
+          <t>cfg.Companion</t>
+        </is>
+      </c>
+      <c r="G328" t="inlineStr">
+        <is>
+          <t>队友人设卡</t>
+        </is>
+      </c>
+      <c r="H328" t="inlineStr">
+        <is>
+          <t>c</t>
+        </is>
+      </c>
+    </row>
+    <row r="329">
+      <c r="J329" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="L329" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="N329" t="inlineStr">
+        <is>
+          <t>队友ID</t>
+        </is>
+      </c>
+    </row>
+    <row r="330">
+      <c r="J330" t="inlineStr">
+        <is>
+          <t>nameKey</t>
+        </is>
+      </c>
+      <c r="L330" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="N330" t="inlineStr">
+        <is>
+          <t>呼号本地化键</t>
+        </is>
+      </c>
+    </row>
+    <row r="331">
+      <c r="J331" t="inlineStr">
+        <is>
+          <t>personaPrompt</t>
+        </is>
+      </c>
+      <c r="L331" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="N331" t="inlineStr">
+        <is>
+          <t>LLM 人设 system prompt(英文)</t>
+        </is>
+      </c>
+    </row>
+    <row r="332">
+      <c r="J332" t="inlineStr">
+        <is>
+          <t>weaponConfigId</t>
+        </is>
+      </c>
+      <c r="L332" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="N332" t="inlineStr">
+        <is>
+          <t>持有武器</t>
+        </is>
+      </c>
+    </row>
+    <row r="333">
+      <c r="J333" t="inlineStr">
+        <is>
+          <t>maxHp</t>
+        </is>
+      </c>
+      <c r="L333" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="N333" t="inlineStr">
+        <is>
+          <t>最大HP</t>
+        </is>
+      </c>
+    </row>
+    <row r="334">
+      <c r="J334" t="inlineStr">
+        <is>
+          <t>moveSpeed</t>
+        </is>
+      </c>
+      <c r="L334" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="N334" t="inlineStr">
+        <is>
+          <t>移动速度</t>
+        </is>
+      </c>
+    </row>
+    <row r="335">
+      <c r="J335" t="inlineStr">
+        <is>
+          <t>followStopDist</t>
+        </is>
+      </c>
+      <c r="L335" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="N335" t="inlineStr">
+        <is>
+          <t>跟随到位距离</t>
+        </is>
+      </c>
+    </row>
+    <row r="336">
+      <c r="J336" t="inlineStr">
+        <is>
+          <t>engageMinDist</t>
+        </is>
+      </c>
+      <c r="L336" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="N336" t="inlineStr">
+        <is>
+          <t>最小交战距离</t>
+        </is>
+      </c>
+    </row>
+    <row r="337">
+      <c r="J337" t="inlineStr">
+        <is>
+          <t>retreatHpRatio</t>
+        </is>
+      </c>
+      <c r="L337" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="N337" t="inlineStr">
+        <is>
+          <t>撤退血量比例</t>
+        </is>
+      </c>
+    </row>
+    <row r="338">
+      <c r="J338" t="inlineStr">
+        <is>
+          <t>idleChatMinInterval</t>
+        </is>
+      </c>
+      <c r="L338" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="N338" t="inlineStr">
+        <is>
+          <t>安全闲聊最小间隔s</t>
+        </is>
+      </c>
+    </row>
+    <row r="339">
+      <c r="J339" t="inlineStr">
+        <is>
+          <t>idleChatMaxInterval</t>
+        </is>
+      </c>
+      <c r="L339" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="N339" t="inlineStr">
+        <is>
+          <t>安全闲聊最大间隔s</t>
+        </is>
+      </c>
+    </row>
+    <row r="340">
+      <c r="J340" t="inlineStr">
+        <is>
+          <t>llmRequestInterval</t>
+        </is>
+      </c>
+      <c r="L340" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="N340" t="inlineStr">
+        <is>
+          <t>LLM 全局最小请求间隔s</t>
+        </is>
+      </c>
+    </row>
+    <row r="341">
+      <c r="J341" t="inlineStr">
+        <is>
+          <t>llmBudgetPerRun</t>
+        </is>
+      </c>
+      <c r="L341" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="N341" t="inlineStr">
+        <is>
+          <t>单局 LLM 请求限额</t>
+        </is>
+      </c>
+    </row>
+    <row r="342">
+      <c r="J342" t="inlineStr">
+        <is>
+          <t>llmTimeout</t>
+        </is>
+      </c>
+      <c r="L342" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="N342" t="inlineStr">
+        <is>
+          <t>LLM 超时s</t>
+        </is>
+      </c>
+    </row>
+    <row r="343">
+      <c r="J343" t="inlineStr">
+        <is>
+          <t>intentTtl</t>
+        </is>
+      </c>
+      <c r="L343" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="N343" t="inlineStr">
+        <is>
+          <t>意图 TTL s</t>
+        </is>
+      </c>
+    </row>
+    <row r="344">
+      <c r="J344" t="inlineStr">
+        <is>
+          <t>offlineProbeInterval</t>
+        </is>
+      </c>
+      <c r="L344" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="N344" t="inlineStr">
+        <is>
+          <t>离线恢复探测间隔s</t>
+        </is>
+      </c>
+    </row>
+    <row r="345">
+      <c r="B345" t="inlineStr">
+        <is>
+          <t>cfg.CompanionBark</t>
+        </is>
+      </c>
+      <c r="G345" t="inlineStr">
+        <is>
+          <t>队友本地台词</t>
+        </is>
+      </c>
+      <c r="H345" t="inlineStr">
+        <is>
+          <t>c</t>
+        </is>
+      </c>
+    </row>
+    <row r="346">
+      <c r="J346" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="L346" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="N346" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+    </row>
+    <row r="347">
+      <c r="J347" t="inlineStr">
+        <is>
+          <t>trigger</t>
+        </is>
+      </c>
+      <c r="L347" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="N347" t="inlineStr">
+        <is>
+          <t>触发键</t>
+        </is>
+      </c>
+    </row>
+    <row r="348">
+      <c r="J348" t="inlineStr">
+        <is>
+          <t>textKey</t>
+        </is>
+      </c>
+      <c r="L348" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="N348" t="inlineStr">
+        <is>
+          <t>台词本地化键</t>
+        </is>
+      </c>
+    </row>
+    <row r="349">
+      <c r="J349" t="inlineStr">
+        <is>
+          <t>weight</t>
+        </is>
+      </c>
+      <c r="L349" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="N349" t="inlineStr">
+        <is>
+          <t>随机权重</t>
+        </is>
+      </c>
+    </row>
+    <row r="350">
+      <c r="J350" t="inlineStr">
+        <is>
+          <t>cooldown</t>
+        </is>
+      </c>
+      <c r="L350" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="N350" t="inlineStr">
+        <is>
+          <t>单键冷却s(0=不限)</t>
         </is>
       </c>
     </row>

--- a/AfterToken/Configs/GameConfig/Datas/__beans__.xlsx
+++ b/AfterToken/Configs/GameConfig/Datas/__beans__.xlsx
@@ -1025,7 +1025,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P350"/>
+  <dimension ref="A1:P355"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col width="20.625" customWidth="1" style="1" min="2" max="4"/>
@@ -6629,391 +6629,476 @@
       </c>
     </row>
     <row r="328">
-      <c r="B328" t="inlineStr">
+      <c r="B328" s="0" t="inlineStr">
         <is>
           <t>cfg.Companion</t>
         </is>
       </c>
-      <c r="G328" t="inlineStr">
+      <c r="G328" s="0" t="inlineStr">
         <is>
           <t>队友人设卡</t>
         </is>
       </c>
-      <c r="H328" t="inlineStr">
+      <c r="H328" s="0" t="inlineStr">
         <is>
           <t>c</t>
         </is>
       </c>
     </row>
     <row r="329">
-      <c r="J329" t="inlineStr">
+      <c r="J329" s="0" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="L329" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="N329" t="inlineStr">
+      <c r="L329" s="0" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="N329" s="0" t="inlineStr">
         <is>
           <t>队友ID</t>
         </is>
       </c>
     </row>
     <row r="330">
-      <c r="J330" t="inlineStr">
+      <c r="J330" s="0" t="inlineStr">
         <is>
           <t>nameKey</t>
         </is>
       </c>
-      <c r="L330" t="inlineStr">
+      <c r="L330" s="0" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="N330" t="inlineStr">
+      <c r="N330" s="0" t="inlineStr">
         <is>
           <t>呼号本地化键</t>
         </is>
       </c>
     </row>
     <row r="331">
-      <c r="J331" t="inlineStr">
+      <c r="J331" s="0" t="inlineStr">
         <is>
           <t>personaPrompt</t>
         </is>
       </c>
-      <c r="L331" t="inlineStr">
+      <c r="L331" s="0" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="N331" t="inlineStr">
+      <c r="N331" s="0" t="inlineStr">
         <is>
           <t>LLM 人设 system prompt(英文)</t>
         </is>
       </c>
     </row>
     <row r="332">
-      <c r="J332" t="inlineStr">
+      <c r="J332" s="0" t="inlineStr">
         <is>
           <t>weaponConfigId</t>
         </is>
       </c>
-      <c r="L332" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="N332" t="inlineStr">
+      <c r="L332" s="0" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="N332" s="0" t="inlineStr">
         <is>
           <t>持有武器</t>
         </is>
       </c>
     </row>
     <row r="333">
-      <c r="J333" t="inlineStr">
+      <c r="J333" s="0" t="inlineStr">
         <is>
           <t>maxHp</t>
         </is>
       </c>
-      <c r="L333" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="N333" t="inlineStr">
+      <c r="L333" s="0" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="N333" s="0" t="inlineStr">
         <is>
           <t>最大HP</t>
         </is>
       </c>
     </row>
     <row r="334">
-      <c r="J334" t="inlineStr">
+      <c r="J334" s="0" t="inlineStr">
         <is>
           <t>moveSpeed</t>
         </is>
       </c>
-      <c r="L334" t="inlineStr">
-        <is>
-          <t>float</t>
-        </is>
-      </c>
-      <c r="N334" t="inlineStr">
+      <c r="L334" s="0" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="N334" s="0" t="inlineStr">
         <is>
           <t>移动速度</t>
         </is>
       </c>
     </row>
     <row r="335">
-      <c r="J335" t="inlineStr">
+      <c r="J335" s="0" t="inlineStr">
         <is>
           <t>followStopDist</t>
         </is>
       </c>
-      <c r="L335" t="inlineStr">
-        <is>
-          <t>float</t>
-        </is>
-      </c>
-      <c r="N335" t="inlineStr">
+      <c r="L335" s="0" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="N335" s="0" t="inlineStr">
         <is>
           <t>跟随到位距离</t>
         </is>
       </c>
     </row>
     <row r="336">
-      <c r="J336" t="inlineStr">
+      <c r="J336" s="0" t="inlineStr">
         <is>
           <t>engageMinDist</t>
         </is>
       </c>
-      <c r="L336" t="inlineStr">
-        <is>
-          <t>float</t>
-        </is>
-      </c>
-      <c r="N336" t="inlineStr">
+      <c r="L336" s="0" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="N336" s="0" t="inlineStr">
         <is>
           <t>最小交战距离</t>
         </is>
       </c>
     </row>
     <row r="337">
-      <c r="J337" t="inlineStr">
+      <c r="J337" s="0" t="inlineStr">
         <is>
           <t>retreatHpRatio</t>
         </is>
       </c>
-      <c r="L337" t="inlineStr">
-        <is>
-          <t>float</t>
-        </is>
-      </c>
-      <c r="N337" t="inlineStr">
+      <c r="L337" s="0" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="N337" s="0" t="inlineStr">
         <is>
           <t>撤退血量比例</t>
         </is>
       </c>
     </row>
     <row r="338">
-      <c r="J338" t="inlineStr">
+      <c r="J338" s="0" t="inlineStr">
         <is>
           <t>idleChatMinInterval</t>
         </is>
       </c>
-      <c r="L338" t="inlineStr">
-        <is>
-          <t>float</t>
-        </is>
-      </c>
-      <c r="N338" t="inlineStr">
+      <c r="L338" s="0" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="N338" s="0" t="inlineStr">
         <is>
           <t>安全闲聊最小间隔s</t>
         </is>
       </c>
     </row>
     <row r="339">
-      <c r="J339" t="inlineStr">
+      <c r="J339" s="0" t="inlineStr">
         <is>
           <t>idleChatMaxInterval</t>
         </is>
       </c>
-      <c r="L339" t="inlineStr">
-        <is>
-          <t>float</t>
-        </is>
-      </c>
-      <c r="N339" t="inlineStr">
+      <c r="L339" s="0" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="N339" s="0" t="inlineStr">
         <is>
           <t>安全闲聊最大间隔s</t>
         </is>
       </c>
     </row>
     <row r="340">
-      <c r="J340" t="inlineStr">
+      <c r="J340" s="0" t="inlineStr">
         <is>
           <t>llmRequestInterval</t>
         </is>
       </c>
-      <c r="L340" t="inlineStr">
-        <is>
-          <t>float</t>
-        </is>
-      </c>
-      <c r="N340" t="inlineStr">
+      <c r="L340" s="0" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="N340" s="0" t="inlineStr">
         <is>
           <t>LLM 全局最小请求间隔s</t>
         </is>
       </c>
     </row>
     <row r="341">
-      <c r="J341" t="inlineStr">
+      <c r="J341" s="0" t="inlineStr">
         <is>
           <t>llmBudgetPerRun</t>
         </is>
       </c>
-      <c r="L341" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="N341" t="inlineStr">
+      <c r="L341" s="0" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="N341" s="0" t="inlineStr">
         <is>
           <t>单局 LLM 请求限额</t>
         </is>
       </c>
     </row>
     <row r="342">
-      <c r="J342" t="inlineStr">
+      <c r="J342" s="0" t="inlineStr">
         <is>
           <t>llmTimeout</t>
         </is>
       </c>
-      <c r="L342" t="inlineStr">
-        <is>
-          <t>float</t>
-        </is>
-      </c>
-      <c r="N342" t="inlineStr">
+      <c r="L342" s="0" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="N342" s="0" t="inlineStr">
         <is>
           <t>LLM 超时s</t>
         </is>
       </c>
     </row>
     <row r="343">
-      <c r="J343" t="inlineStr">
+      <c r="J343" s="0" t="inlineStr">
         <is>
           <t>intentTtl</t>
         </is>
       </c>
-      <c r="L343" t="inlineStr">
-        <is>
-          <t>float</t>
-        </is>
-      </c>
-      <c r="N343" t="inlineStr">
+      <c r="L343" s="0" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="N343" s="0" t="inlineStr">
         <is>
           <t>意图 TTL s</t>
         </is>
       </c>
     </row>
     <row r="344">
-      <c r="J344" t="inlineStr">
+      <c r="J344" s="0" t="inlineStr">
         <is>
           <t>offlineProbeInterval</t>
         </is>
       </c>
-      <c r="L344" t="inlineStr">
-        <is>
-          <t>float</t>
-        </is>
-      </c>
-      <c r="N344" t="inlineStr">
+      <c r="L344" s="0" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="N344" s="0" t="inlineStr">
         <is>
           <t>离线恢复探测间隔s</t>
         </is>
       </c>
     </row>
     <row r="345">
-      <c r="B345" t="inlineStr">
-        <is>
-          <t>cfg.CompanionBark</t>
-        </is>
-      </c>
-      <c r="G345" t="inlineStr">
-        <is>
-          <t>队友本地台词</t>
-        </is>
-      </c>
-      <c r="H345" t="inlineStr">
-        <is>
-          <t>c</t>
+      <c r="J345" s="0" t="inlineStr">
+        <is>
+          <t>decisionIntervalSafe</t>
+        </is>
+      </c>
+      <c r="L345" s="0" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="N345" s="0" t="inlineStr">
+        <is>
+          <t>安全决策间隔s(M5)</t>
         </is>
       </c>
     </row>
     <row r="346">
-      <c r="J346" t="inlineStr">
-        <is>
-          <t>id</t>
-        </is>
-      </c>
-      <c r="L346" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="N346" t="inlineStr">
-        <is>
-          <t>ID</t>
+      <c r="J346" s="0" t="inlineStr">
+        <is>
+          <t>decisionIntervalCombat</t>
+        </is>
+      </c>
+      <c r="L346" s="0" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="N346" s="0" t="inlineStr">
+        <is>
+          <t>战斗决策间隔s(M5)</t>
         </is>
       </c>
     </row>
     <row r="347">
-      <c r="J347" t="inlineStr">
-        <is>
-          <t>trigger</t>
-        </is>
-      </c>
-      <c r="L347" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="N347" t="inlineStr">
-        <is>
-          <t>触发键</t>
+      <c r="J347" s="0" t="inlineStr">
+        <is>
+          <t>decisionTimeout</t>
+        </is>
+      </c>
+      <c r="L347" s="0" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="N347" s="0" t="inlineStr">
+        <is>
+          <t>决策响应超时s(M5)</t>
         </is>
       </c>
     </row>
     <row r="348">
-      <c r="J348" t="inlineStr">
-        <is>
-          <t>textKey</t>
-        </is>
-      </c>
-      <c r="L348" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="N348" t="inlineStr">
-        <is>
-          <t>台词本地化键</t>
+      <c r="J348" s="0" t="inlineStr">
+        <is>
+          <t>controlBudgetPerRun</t>
+        </is>
+      </c>
+      <c r="L348" s="0" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="N348" s="0" t="inlineStr">
+        <is>
+          <t>单局操控决策限额(M5)</t>
         </is>
       </c>
     </row>
     <row r="349">
       <c r="J349" t="inlineStr">
         <is>
+          <t>proactiveEngageDist</t>
+        </is>
+      </c>
+      <c r="L349" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="N349" t="inlineStr">
+        <is>
+          <t>主动开火警戒半径m</t>
+        </is>
+      </c>
+    </row>
+    <row r="350">
+      <c r="B350" s="0" t="inlineStr">
+        <is>
+          <t>cfg.CompanionBark</t>
+        </is>
+      </c>
+      <c r="G350" s="0" t="inlineStr">
+        <is>
+          <t>队友本地台词</t>
+        </is>
+      </c>
+      <c r="H350" s="0" t="inlineStr">
+        <is>
+          <t>c</t>
+        </is>
+      </c>
+    </row>
+    <row r="351">
+      <c r="J351" s="0" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="L351" s="0" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="N351" s="0" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+    </row>
+    <row r="352">
+      <c r="J352" s="0" t="inlineStr">
+        <is>
+          <t>trigger</t>
+        </is>
+      </c>
+      <c r="L352" s="0" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="N352" s="0" t="inlineStr">
+        <is>
+          <t>触发键</t>
+        </is>
+      </c>
+    </row>
+    <row r="353">
+      <c r="J353" s="0" t="inlineStr">
+        <is>
+          <t>textKey</t>
+        </is>
+      </c>
+      <c r="L353" s="0" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="N353" s="0" t="inlineStr">
+        <is>
+          <t>台词本地化键</t>
+        </is>
+      </c>
+    </row>
+    <row r="354">
+      <c r="J354" s="0" t="inlineStr">
+        <is>
           <t>weight</t>
         </is>
       </c>
-      <c r="L349" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="N349" t="inlineStr">
+      <c r="L354" s="0" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="N354" s="0" t="inlineStr">
         <is>
           <t>随机权重</t>
         </is>
       </c>
     </row>
-    <row r="350">
-      <c r="J350" t="inlineStr">
+    <row r="355">
+      <c r="J355" s="0" t="inlineStr">
         <is>
           <t>cooldown</t>
         </is>
       </c>
-      <c r="L350" t="inlineStr">
-        <is>
-          <t>float</t>
-        </is>
-      </c>
-      <c r="N350" t="inlineStr">
+      <c r="L355" s="0" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="N355" s="0" t="inlineStr">
         <is>
           <t>单键冷却s(0=不限)</t>
         </is>

--- a/AfterToken/Configs/GameConfig/Datas/__beans__.xlsx
+++ b/AfterToken/Configs/GameConfig/Datas/__beans__.xlsx
@@ -1025,7 +1025,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P355"/>
+  <dimension ref="A1:P365"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col width="20.625" customWidth="1" style="1" min="2" max="4"/>
@@ -5516,7 +5516,6 @@
         </is>
       </c>
     </row>
-    <row r="259"/>
     <row r="260">
       <c r="B260" s="0" t="inlineStr">
         <is>
@@ -5606,7 +5605,6 @@
         </is>
       </c>
     </row>
-    <row r="267"/>
     <row r="268">
       <c r="B268" s="0" t="inlineStr">
         <is>
@@ -6986,119 +6984,239 @@
       </c>
     </row>
     <row r="349">
-      <c r="J349" t="inlineStr">
+      <c r="J349" s="0" t="inlineStr">
         <is>
           <t>proactiveEngageDist</t>
         </is>
       </c>
-      <c r="L349" t="inlineStr">
-        <is>
-          <t>float</t>
-        </is>
-      </c>
-      <c r="N349" t="inlineStr">
+      <c r="L349" s="0" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="N349" s="0" t="inlineStr">
         <is>
           <t>主动开火警戒半径m</t>
         </is>
       </c>
     </row>
     <row r="350">
-      <c r="B350" s="0" t="inlineStr">
+      <c r="J350" t="inlineStr">
+        <is>
+          <t>conversationHold</t>
+        </is>
+      </c>
+      <c r="L350" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+    </row>
+    <row r="351">
+      <c r="J351" t="inlineStr">
+        <is>
+          <t>postCombatCalm</t>
+        </is>
+      </c>
+      <c r="L351" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+    </row>
+    <row r="352">
+      <c r="J352" t="inlineStr">
+        <is>
+          <t>dirHintInterval</t>
+        </is>
+      </c>
+      <c r="L352" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+    </row>
+    <row r="353">
+      <c r="J353" t="inlineStr">
+        <is>
+          <t>offlineFailThreshold</t>
+        </is>
+      </c>
+      <c r="L353" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+    </row>
+    <row r="354">
+      <c r="J354" t="inlineStr">
+        <is>
+          <t>decisionSayInterval</t>
+        </is>
+      </c>
+      <c r="L354" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+    </row>
+    <row r="355">
+      <c r="J355" t="inlineStr">
+        <is>
+          <t>maxReportEntries</t>
+        </is>
+      </c>
+      <c r="L355" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+    </row>
+    <row r="356">
+      <c r="J356" t="inlineStr">
+        <is>
+          <t>leashDist</t>
+        </is>
+      </c>
+      <c r="L356" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+    </row>
+    <row r="357">
+      <c r="J357" t="inlineStr">
+        <is>
+          <t>leashStopDist</t>
+        </is>
+      </c>
+      <c r="L357" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+    </row>
+    <row r="358">
+      <c r="J358" t="inlineStr">
+        <is>
+          <t>spawnOffsetX</t>
+        </is>
+      </c>
+      <c r="L358" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+    </row>
+    <row r="359">
+      <c r="J359" t="inlineStr">
+        <is>
+          <t>spawnOffsetZ</t>
+        </is>
+      </c>
+      <c r="L359" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+    </row>
+    <row r="360">
+      <c r="B360" s="0" t="inlineStr">
         <is>
           <t>cfg.CompanionBark</t>
         </is>
       </c>
-      <c r="G350" s="0" t="inlineStr">
+      <c r="G360" s="0" t="inlineStr">
         <is>
           <t>队友本地台词</t>
         </is>
       </c>
-      <c r="H350" s="0" t="inlineStr">
+      <c r="H360" s="0" t="inlineStr">
         <is>
           <t>c</t>
         </is>
       </c>
     </row>
-    <row r="351">
-      <c r="J351" s="0" t="inlineStr">
+    <row r="361">
+      <c r="J361" s="0" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="L351" s="0" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="N351" s="0" t="inlineStr">
+      <c r="L361" s="0" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="N361" s="0" t="inlineStr">
         <is>
           <t>ID</t>
         </is>
       </c>
     </row>
-    <row r="352">
-      <c r="J352" s="0" t="inlineStr">
+    <row r="362">
+      <c r="J362" s="0" t="inlineStr">
         <is>
           <t>trigger</t>
         </is>
       </c>
-      <c r="L352" s="0" t="inlineStr">
+      <c r="L362" s="0" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="N352" s="0" t="inlineStr">
+      <c r="N362" s="0" t="inlineStr">
         <is>
           <t>触发键</t>
         </is>
       </c>
     </row>
-    <row r="353">
-      <c r="J353" s="0" t="inlineStr">
+    <row r="363">
+      <c r="J363" s="0" t="inlineStr">
         <is>
           <t>textKey</t>
         </is>
       </c>
-      <c r="L353" s="0" t="inlineStr">
+      <c r="L363" s="0" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="N353" s="0" t="inlineStr">
+      <c r="N363" s="0" t="inlineStr">
         <is>
           <t>台词本地化键</t>
         </is>
       </c>
     </row>
-    <row r="354">
-      <c r="J354" s="0" t="inlineStr">
+    <row r="364">
+      <c r="J364" s="0" t="inlineStr">
         <is>
           <t>weight</t>
         </is>
       </c>
-      <c r="L354" s="0" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="N354" s="0" t="inlineStr">
+      <c r="L364" s="0" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="N364" s="0" t="inlineStr">
         <is>
           <t>随机权重</t>
         </is>
       </c>
     </row>
-    <row r="355">
-      <c r="J355" s="0" t="inlineStr">
+    <row r="365">
+      <c r="J365" s="0" t="inlineStr">
         <is>
           <t>cooldown</t>
         </is>
       </c>
-      <c r="L355" s="0" t="inlineStr">
-        <is>
-          <t>float</t>
-        </is>
-      </c>
-      <c r="N355" s="0" t="inlineStr">
+      <c r="L365" s="0" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="N365" s="0" t="inlineStr">
         <is>
           <t>单键冷却s(0=不限)</t>
         </is>

--- a/AfterToken/Configs/GameConfig/Datas/__beans__.xlsx
+++ b/AfterToken/Configs/GameConfig/Datas/__beans__.xlsx
@@ -1025,7 +1025,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P365"/>
+  <dimension ref="A1:P376"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col width="20.625" customWidth="1" style="1" min="2" max="4"/>
@@ -5516,6 +5516,7 @@
         </is>
       </c>
     </row>
+    <row r="259"/>
     <row r="260">
       <c r="B260" s="0" t="inlineStr">
         <is>
@@ -5605,6 +5606,7 @@
         </is>
       </c>
     </row>
+    <row r="267"/>
     <row r="268">
       <c r="B268" s="0" t="inlineStr">
         <is>
@@ -6253,60 +6255,55 @@
       </c>
     </row>
     <row r="306">
-      <c r="B306" s="0" t="inlineStr">
+      <c r="J306" s="0" t="inlineStr">
+        <is>
+          <t>voiceClip</t>
+        </is>
+      </c>
+      <c r="L306" s="0" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+    </row>
+    <row r="307">
+      <c r="B307" s="0" t="inlineStr">
         <is>
           <t>cfg.Quest</t>
         </is>
       </c>
-      <c r="G306" s="0" t="inlineStr">
+      <c r="G307" s="0" t="inlineStr">
         <is>
           <t>任务定义</t>
         </is>
       </c>
-      <c r="I306" s="0" t="inlineStr">
+      <c r="I307" s="0" t="inlineStr">
         <is>
           <t>c</t>
-        </is>
-      </c>
-    </row>
-    <row r="307">
-      <c r="J307" s="0" t="inlineStr">
-        <is>
-          <t>id</t>
-        </is>
-      </c>
-      <c r="L307" s="0" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="N307" s="0" t="inlineStr">
-        <is>
-          <t>任务ID</t>
         </is>
       </c>
     </row>
     <row r="308">
       <c r="J308" s="0" t="inlineStr">
         <is>
-          <t>name</t>
+          <t>id</t>
         </is>
       </c>
       <c r="L308" s="0" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>int</t>
         </is>
       </c>
       <c r="N308" s="0" t="inlineStr">
         <is>
-          <t>显示名</t>
+          <t>任务ID</t>
         </is>
       </c>
     </row>
     <row r="309">
       <c r="J309" s="0" t="inlineStr">
         <is>
-          <t>desc</t>
+          <t>name</t>
         </is>
       </c>
       <c r="L309" s="0" t="inlineStr">
@@ -6316,48 +6313,48 @@
       </c>
       <c r="N309" s="0" t="inlineStr">
         <is>
-          <t>描述</t>
+          <t>显示名</t>
         </is>
       </c>
     </row>
     <row r="310">
       <c r="J310" s="0" t="inlineStr">
         <is>
-          <t>giverNpc</t>
+          <t>desc</t>
         </is>
       </c>
       <c r="L310" s="0" t="inlineStr">
         <is>
-          <t>int</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N310" s="0" t="inlineStr">
         <is>
-          <t>发布NPC(0=任务板)</t>
+          <t>描述</t>
         </is>
       </c>
     </row>
     <row r="311">
       <c r="J311" s="0" t="inlineStr">
         <is>
-          <t>prereq</t>
+          <t>giverNpc</t>
         </is>
       </c>
       <c r="L311" s="0" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>int</t>
         </is>
       </c>
       <c r="N311" s="0" t="inlineStr">
         <is>
-          <t>接取条件表达式(空=无)</t>
+          <t>发布NPC(0=任务板)</t>
         </is>
       </c>
     </row>
     <row r="312">
       <c r="J312" s="0" t="inlineStr">
         <is>
-          <t>rewards</t>
+          <t>prereq</t>
         </is>
       </c>
       <c r="L312" s="0" t="inlineStr">
@@ -6367,65 +6364,65 @@
       </c>
       <c r="N312" s="0" t="inlineStr">
         <is>
-          <t>奖励(gold:200|exp:50|item:3001:2)</t>
+          <t>接取条件表达式(空=无)</t>
         </is>
       </c>
     </row>
     <row r="313">
       <c r="J313" s="0" t="inlineStr">
         <is>
+          <t>rewards</t>
+        </is>
+      </c>
+      <c r="L313" s="0" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="N313" s="0" t="inlineStr">
+        <is>
+          <t>奖励(gold:200|exp:50|item:3001:2)</t>
+        </is>
+      </c>
+    </row>
+    <row r="314">
+      <c r="J314" s="0" t="inlineStr">
+        <is>
           <t>nextQuest</t>
         </is>
       </c>
-      <c r="L313" s="0" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="N313" s="0" t="inlineStr">
+      <c r="L314" s="0" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="N314" s="0" t="inlineStr">
         <is>
           <t>后继任务(0=无)</t>
         </is>
       </c>
     </row>
-    <row r="314">
-      <c r="B314" s="0" t="inlineStr">
+    <row r="315">
+      <c r="B315" s="0" t="inlineStr">
         <is>
           <t>cfg.QuestObjective</t>
         </is>
       </c>
-      <c r="G314" s="0" t="inlineStr">
+      <c r="G315" s="0" t="inlineStr">
         <is>
           <t>任务目标</t>
         </is>
       </c>
-      <c r="I314" s="0" t="inlineStr">
+      <c r="I315" s="0" t="inlineStr">
         <is>
           <t>c</t>
-        </is>
-      </c>
-    </row>
-    <row r="315">
-      <c r="J315" s="0" t="inlineStr">
-        <is>
-          <t>id</t>
-        </is>
-      </c>
-      <c r="L315" s="0" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="N315" s="0" t="inlineStr">
-        <is>
-          <t>目标ID</t>
         </is>
       </c>
     </row>
     <row r="316">
       <c r="J316" s="0" t="inlineStr">
         <is>
-          <t>questId</t>
+          <t>id</t>
         </is>
       </c>
       <c r="L316" s="0" t="inlineStr">
@@ -6435,31 +6432,31 @@
       </c>
       <c r="N316" s="0" t="inlineStr">
         <is>
-          <t>所属任务</t>
+          <t>目标ID</t>
         </is>
       </c>
     </row>
     <row r="317">
       <c r="J317" s="0" t="inlineStr">
         <is>
-          <t>type</t>
+          <t>questId</t>
         </is>
       </c>
       <c r="L317" s="0" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>int</t>
         </is>
       </c>
       <c r="N317" s="0" t="inlineStr">
         <is>
-          <t>类型(kill/collect/extract/flag)</t>
+          <t>所属任务</t>
         </is>
       </c>
     </row>
     <row r="318">
       <c r="J318" s="0" t="inlineStr">
         <is>
-          <t>targetId</t>
+          <t>type</t>
         </is>
       </c>
       <c r="L318" s="0" t="inlineStr">
@@ -6469,82 +6466,82 @@
       </c>
       <c r="N318" s="0" t="inlineStr">
         <is>
-          <t>目标ID/标志键</t>
+          <t>类型(kill/collect/extract/flag)</t>
         </is>
       </c>
     </row>
     <row r="319">
       <c r="J319" s="0" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>targetId</t>
         </is>
       </c>
       <c r="L319" s="0" t="inlineStr">
         <is>
-          <t>int</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N319" s="0" t="inlineStr">
         <is>
-          <t>需求数(extract恒1)</t>
+          <t>目标ID/标志键</t>
         </is>
       </c>
     </row>
     <row r="320">
       <c r="J320" s="0" t="inlineStr">
         <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="L320" s="0" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="N320" s="0" t="inlineStr">
+        <is>
+          <t>需求数(extract恒1)</t>
+        </is>
+      </c>
+    </row>
+    <row r="321">
+      <c r="J321" s="0" t="inlineStr">
+        <is>
           <t>desc</t>
         </is>
       </c>
-      <c r="L320" s="0" t="inlineStr">
+      <c r="L321" s="0" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="N320" s="0" t="inlineStr">
+      <c r="N321" s="0" t="inlineStr">
         <is>
           <t>目标一行描述</t>
         </is>
       </c>
     </row>
-    <row r="321">
-      <c r="B321" s="0" t="inlineStr">
+    <row r="322">
+      <c r="B322" s="0" t="inlineStr">
         <is>
           <t>cfg.Localization</t>
         </is>
       </c>
-      <c r="G321" s="0" t="inlineStr">
+      <c r="G322" s="0" t="inlineStr">
         <is>
           <t>本地化词条</t>
         </is>
       </c>
-      <c r="I321" s="0" t="inlineStr">
+      <c r="I322" s="0" t="inlineStr">
         <is>
           <t>c</t>
-        </is>
-      </c>
-    </row>
-    <row r="322">
-      <c r="J322" s="0" t="inlineStr">
-        <is>
-          <t>key</t>
-        </is>
-      </c>
-      <c r="L322" s="0" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="N322" s="0" t="inlineStr">
-        <is>
-          <t>词条Key</t>
         </is>
       </c>
     </row>
     <row r="323">
       <c r="J323" s="0" t="inlineStr">
         <is>
-          <t>en</t>
+          <t>key</t>
         </is>
       </c>
       <c r="L323" s="0" t="inlineStr">
@@ -6554,14 +6551,14 @@
       </c>
       <c r="N323" s="0" t="inlineStr">
         <is>
-          <t>英文(必填/兜底)</t>
+          <t>词条Key</t>
         </is>
       </c>
     </row>
     <row r="324">
       <c r="J324" s="0" t="inlineStr">
         <is>
-          <t>zh_cn</t>
+          <t>en</t>
         </is>
       </c>
       <c r="L324" s="0" t="inlineStr">
@@ -6571,14 +6568,14 @@
       </c>
       <c r="N324" s="0" t="inlineStr">
         <is>
-          <t>简体中文</t>
+          <t>英文(必填/兜底)</t>
         </is>
       </c>
     </row>
     <row r="325">
       <c r="J325" s="0" t="inlineStr">
         <is>
-          <t>zh_tw</t>
+          <t>zh_cn</t>
         </is>
       </c>
       <c r="L325" s="0" t="inlineStr">
@@ -6588,14 +6585,14 @@
       </c>
       <c r="N325" s="0" t="inlineStr">
         <is>
-          <t>繁体中文</t>
+          <t>简体中文</t>
         </is>
       </c>
     </row>
     <row r="326">
       <c r="J326" s="0" t="inlineStr">
         <is>
-          <t>ja</t>
+          <t>zh_tw</t>
         </is>
       </c>
       <c r="L326" s="0" t="inlineStr">
@@ -6605,82 +6602,82 @@
       </c>
       <c r="N326" s="0" t="inlineStr">
         <is>
-          <t>日文</t>
+          <t>繁体中文</t>
         </is>
       </c>
     </row>
     <row r="327">
       <c r="J327" s="0" t="inlineStr">
         <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="L327" s="0" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="N327" s="0" t="inlineStr">
+        <is>
+          <t>日文</t>
+        </is>
+      </c>
+    </row>
+    <row r="328">
+      <c r="J328" s="0" t="inlineStr">
+        <is>
           <t>ko</t>
         </is>
       </c>
-      <c r="L327" s="0" t="inlineStr">
+      <c r="L328" s="0" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="N327" s="0" t="inlineStr">
+      <c r="N328" s="0" t="inlineStr">
         <is>
           <t>韩文</t>
         </is>
       </c>
     </row>
-    <row r="328">
-      <c r="B328" s="0" t="inlineStr">
+    <row r="329">
+      <c r="B329" s="0" t="inlineStr">
         <is>
           <t>cfg.Companion</t>
         </is>
       </c>
-      <c r="G328" s="0" t="inlineStr">
+      <c r="G329" s="0" t="inlineStr">
         <is>
           <t>队友人设卡</t>
         </is>
       </c>
-      <c r="H328" s="0" t="inlineStr">
+      <c r="H329" s="0" t="inlineStr">
         <is>
           <t>c</t>
-        </is>
-      </c>
-    </row>
-    <row r="329">
-      <c r="J329" s="0" t="inlineStr">
-        <is>
-          <t>id</t>
-        </is>
-      </c>
-      <c r="L329" s="0" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="N329" s="0" t="inlineStr">
-        <is>
-          <t>队友ID</t>
         </is>
       </c>
     </row>
     <row r="330">
       <c r="J330" s="0" t="inlineStr">
         <is>
-          <t>nameKey</t>
+          <t>id</t>
         </is>
       </c>
       <c r="L330" s="0" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>int</t>
         </is>
       </c>
       <c r="N330" s="0" t="inlineStr">
         <is>
-          <t>呼号本地化键</t>
+          <t>队友ID</t>
         </is>
       </c>
     </row>
     <row r="331">
       <c r="J331" s="0" t="inlineStr">
         <is>
-          <t>personaPrompt</t>
+          <t>nameKey</t>
         </is>
       </c>
       <c r="L331" s="0" t="inlineStr">
@@ -6690,31 +6687,31 @@
       </c>
       <c r="N331" s="0" t="inlineStr">
         <is>
-          <t>LLM 人设 system prompt(英文)</t>
+          <t>呼号本地化键</t>
         </is>
       </c>
     </row>
     <row r="332">
       <c r="J332" s="0" t="inlineStr">
         <is>
-          <t>weaponConfigId</t>
+          <t>personaPrompt</t>
         </is>
       </c>
       <c r="L332" s="0" t="inlineStr">
         <is>
-          <t>int</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N332" s="0" t="inlineStr">
         <is>
-          <t>持有武器</t>
+          <t>LLM 人设 system prompt(英文)</t>
         </is>
       </c>
     </row>
     <row r="333">
       <c r="J333" s="0" t="inlineStr">
         <is>
-          <t>maxHp</t>
+          <t>weaponConfigId</t>
         </is>
       </c>
       <c r="L333" s="0" t="inlineStr">
@@ -6724,31 +6721,31 @@
       </c>
       <c r="N333" s="0" t="inlineStr">
         <is>
-          <t>最大HP</t>
+          <t>持有武器</t>
         </is>
       </c>
     </row>
     <row r="334">
       <c r="J334" s="0" t="inlineStr">
         <is>
-          <t>moveSpeed</t>
+          <t>maxHp</t>
         </is>
       </c>
       <c r="L334" s="0" t="inlineStr">
         <is>
-          <t>float</t>
+          <t>int</t>
         </is>
       </c>
       <c r="N334" s="0" t="inlineStr">
         <is>
-          <t>移动速度</t>
+          <t>最大HP</t>
         </is>
       </c>
     </row>
     <row r="335">
       <c r="J335" s="0" t="inlineStr">
         <is>
-          <t>followStopDist</t>
+          <t>moveSpeed</t>
         </is>
       </c>
       <c r="L335" s="0" t="inlineStr">
@@ -6758,14 +6755,14 @@
       </c>
       <c r="N335" s="0" t="inlineStr">
         <is>
-          <t>跟随到位距离</t>
+          <t>移动速度</t>
         </is>
       </c>
     </row>
     <row r="336">
       <c r="J336" s="0" t="inlineStr">
         <is>
-          <t>engageMinDist</t>
+          <t>followStopDist</t>
         </is>
       </c>
       <c r="L336" s="0" t="inlineStr">
@@ -6775,14 +6772,14 @@
       </c>
       <c r="N336" s="0" t="inlineStr">
         <is>
-          <t>最小交战距离</t>
+          <t>跟随到位距离</t>
         </is>
       </c>
     </row>
     <row r="337">
       <c r="J337" s="0" t="inlineStr">
         <is>
-          <t>retreatHpRatio</t>
+          <t>engageMinDist</t>
         </is>
       </c>
       <c r="L337" s="0" t="inlineStr">
@@ -6792,14 +6789,14 @@
       </c>
       <c r="N337" s="0" t="inlineStr">
         <is>
-          <t>撤退血量比例</t>
+          <t>最小交战距离</t>
         </is>
       </c>
     </row>
     <row r="338">
       <c r="J338" s="0" t="inlineStr">
         <is>
-          <t>idleChatMinInterval</t>
+          <t>retreatHpRatio</t>
         </is>
       </c>
       <c r="L338" s="0" t="inlineStr">
@@ -6809,14 +6806,14 @@
       </c>
       <c r="N338" s="0" t="inlineStr">
         <is>
-          <t>安全闲聊最小间隔s</t>
+          <t>撤退血量比例</t>
         </is>
       </c>
     </row>
     <row r="339">
       <c r="J339" s="0" t="inlineStr">
         <is>
-          <t>idleChatMaxInterval</t>
+          <t>idleChatMinInterval</t>
         </is>
       </c>
       <c r="L339" s="0" t="inlineStr">
@@ -6826,14 +6823,14 @@
       </c>
       <c r="N339" s="0" t="inlineStr">
         <is>
-          <t>安全闲聊最大间隔s</t>
+          <t>安全闲聊最小间隔s</t>
         </is>
       </c>
     </row>
     <row r="340">
       <c r="J340" s="0" t="inlineStr">
         <is>
-          <t>llmRequestInterval</t>
+          <t>idleChatMaxInterval</t>
         </is>
       </c>
       <c r="L340" s="0" t="inlineStr">
@@ -6843,48 +6840,48 @@
       </c>
       <c r="N340" s="0" t="inlineStr">
         <is>
-          <t>LLM 全局最小请求间隔s</t>
+          <t>安全闲聊最大间隔s</t>
         </is>
       </c>
     </row>
     <row r="341">
       <c r="J341" s="0" t="inlineStr">
         <is>
-          <t>llmBudgetPerRun</t>
+          <t>llmRequestInterval</t>
         </is>
       </c>
       <c r="L341" s="0" t="inlineStr">
         <is>
-          <t>int</t>
+          <t>float</t>
         </is>
       </c>
       <c r="N341" s="0" t="inlineStr">
         <is>
-          <t>单局 LLM 请求限额</t>
+          <t>LLM 全局最小请求间隔s</t>
         </is>
       </c>
     </row>
     <row r="342">
       <c r="J342" s="0" t="inlineStr">
         <is>
-          <t>llmTimeout</t>
+          <t>llmBudgetPerRun</t>
         </is>
       </c>
       <c r="L342" s="0" t="inlineStr">
         <is>
-          <t>float</t>
+          <t>int</t>
         </is>
       </c>
       <c r="N342" s="0" t="inlineStr">
         <is>
-          <t>LLM 超时s</t>
+          <t>单局 LLM 请求限额</t>
         </is>
       </c>
     </row>
     <row r="343">
       <c r="J343" s="0" t="inlineStr">
         <is>
-          <t>intentTtl</t>
+          <t>llmTimeout</t>
         </is>
       </c>
       <c r="L343" s="0" t="inlineStr">
@@ -6894,14 +6891,14 @@
       </c>
       <c r="N343" s="0" t="inlineStr">
         <is>
-          <t>意图 TTL s</t>
+          <t>LLM 超时s</t>
         </is>
       </c>
     </row>
     <row r="344">
       <c r="J344" s="0" t="inlineStr">
         <is>
-          <t>offlineProbeInterval</t>
+          <t>intentTtl</t>
         </is>
       </c>
       <c r="L344" s="0" t="inlineStr">
@@ -6911,14 +6908,14 @@
       </c>
       <c r="N344" s="0" t="inlineStr">
         <is>
-          <t>离线恢复探测间隔s</t>
+          <t>意图 TTL s</t>
         </is>
       </c>
     </row>
     <row r="345">
       <c r="J345" s="0" t="inlineStr">
         <is>
-          <t>decisionIntervalSafe</t>
+          <t>offlineProbeInterval</t>
         </is>
       </c>
       <c r="L345" s="0" t="inlineStr">
@@ -6928,14 +6925,14 @@
       </c>
       <c r="N345" s="0" t="inlineStr">
         <is>
-          <t>安全决策间隔s(M5)</t>
+          <t>离线恢复探测间隔s</t>
         </is>
       </c>
     </row>
     <row r="346">
       <c r="J346" s="0" t="inlineStr">
         <is>
-          <t>decisionIntervalCombat</t>
+          <t>decisionIntervalSafe</t>
         </is>
       </c>
       <c r="L346" s="0" t="inlineStr">
@@ -6945,14 +6942,14 @@
       </c>
       <c r="N346" s="0" t="inlineStr">
         <is>
-          <t>战斗决策间隔s(M5)</t>
+          <t>安全决策间隔s(M5)</t>
         </is>
       </c>
     </row>
     <row r="347">
       <c r="J347" s="0" t="inlineStr">
         <is>
-          <t>decisionTimeout</t>
+          <t>decisionIntervalCombat</t>
         </is>
       </c>
       <c r="L347" s="0" t="inlineStr">
@@ -6962,219 +6959,219 @@
       </c>
       <c r="N347" s="0" t="inlineStr">
         <is>
-          <t>决策响应超时s(M5)</t>
+          <t>战斗决策间隔s(M5)</t>
         </is>
       </c>
     </row>
     <row r="348">
       <c r="J348" s="0" t="inlineStr">
         <is>
-          <t>controlBudgetPerRun</t>
+          <t>decisionTimeout</t>
         </is>
       </c>
       <c r="L348" s="0" t="inlineStr">
         <is>
-          <t>int</t>
+          <t>float</t>
         </is>
       </c>
       <c r="N348" s="0" t="inlineStr">
         <is>
-          <t>单局操控决策限额(M5)</t>
+          <t>决策响应超时s(M5)</t>
         </is>
       </c>
     </row>
     <row r="349">
       <c r="J349" s="0" t="inlineStr">
         <is>
+          <t>controlBudgetPerRun</t>
+        </is>
+      </c>
+      <c r="L349" s="0" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="N349" s="0" t="inlineStr">
+        <is>
+          <t>单局操控决策限额(M5)</t>
+        </is>
+      </c>
+    </row>
+    <row r="350">
+      <c r="J350" s="0" t="inlineStr">
+        <is>
           <t>proactiveEngageDist</t>
         </is>
       </c>
-      <c r="L349" s="0" t="inlineStr">
-        <is>
-          <t>float</t>
-        </is>
-      </c>
-      <c r="N349" s="0" t="inlineStr">
+      <c r="L350" s="0" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="N350" s="0" t="inlineStr">
         <is>
           <t>主动开火警戒半径m</t>
         </is>
       </c>
     </row>
-    <row r="350">
-      <c r="J350" t="inlineStr">
+    <row r="351">
+      <c r="J351" s="0" t="inlineStr">
         <is>
           <t>conversationHold</t>
         </is>
       </c>
-      <c r="L350" t="inlineStr">
-        <is>
-          <t>float</t>
-        </is>
-      </c>
-    </row>
-    <row r="351">
-      <c r="J351" t="inlineStr">
+      <c r="L351" s="0" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+    </row>
+    <row r="352">
+      <c r="J352" s="0" t="inlineStr">
         <is>
           <t>postCombatCalm</t>
         </is>
       </c>
-      <c r="L351" t="inlineStr">
-        <is>
-          <t>float</t>
-        </is>
-      </c>
-    </row>
-    <row r="352">
-      <c r="J352" t="inlineStr">
+      <c r="L352" s="0" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+    </row>
+    <row r="353">
+      <c r="J353" s="0" t="inlineStr">
         <is>
           <t>dirHintInterval</t>
         </is>
       </c>
-      <c r="L352" t="inlineStr">
-        <is>
-          <t>float</t>
-        </is>
-      </c>
-    </row>
-    <row r="353">
-      <c r="J353" t="inlineStr">
+      <c r="L353" s="0" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+    </row>
+    <row r="354">
+      <c r="J354" s="0" t="inlineStr">
         <is>
           <t>offlineFailThreshold</t>
         </is>
       </c>
-      <c r="L353" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-    </row>
-    <row r="354">
-      <c r="J354" t="inlineStr">
+      <c r="L354" s="0" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+    </row>
+    <row r="355">
+      <c r="J355" s="0" t="inlineStr">
         <is>
           <t>decisionSayInterval</t>
         </is>
       </c>
-      <c r="L354" t="inlineStr">
-        <is>
-          <t>float</t>
-        </is>
-      </c>
-    </row>
-    <row r="355">
-      <c r="J355" t="inlineStr">
+      <c r="L355" s="0" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+    </row>
+    <row r="356">
+      <c r="J356" s="0" t="inlineStr">
         <is>
           <t>maxReportEntries</t>
         </is>
       </c>
-      <c r="L355" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-    </row>
-    <row r="356">
-      <c r="J356" t="inlineStr">
+      <c r="L356" s="0" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+    </row>
+    <row r="357">
+      <c r="J357" s="0" t="inlineStr">
         <is>
           <t>leashDist</t>
         </is>
       </c>
-      <c r="L356" t="inlineStr">
-        <is>
-          <t>float</t>
-        </is>
-      </c>
-    </row>
-    <row r="357">
-      <c r="J357" t="inlineStr">
+      <c r="L357" s="0" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+    </row>
+    <row r="358">
+      <c r="J358" s="0" t="inlineStr">
         <is>
           <t>leashStopDist</t>
         </is>
       </c>
-      <c r="L357" t="inlineStr">
-        <is>
-          <t>float</t>
-        </is>
-      </c>
-    </row>
-    <row r="358">
-      <c r="J358" t="inlineStr">
+      <c r="L358" s="0" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+    </row>
+    <row r="359">
+      <c r="J359" s="0" t="inlineStr">
         <is>
           <t>spawnOffsetX</t>
         </is>
       </c>
-      <c r="L358" t="inlineStr">
-        <is>
-          <t>float</t>
-        </is>
-      </c>
-    </row>
-    <row r="359">
-      <c r="J359" t="inlineStr">
+      <c r="L359" s="0" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+    </row>
+    <row r="360">
+      <c r="J360" s="0" t="inlineStr">
         <is>
           <t>spawnOffsetZ</t>
         </is>
       </c>
-      <c r="L359" t="inlineStr">
-        <is>
-          <t>float</t>
-        </is>
-      </c>
-    </row>
-    <row r="360">
-      <c r="B360" s="0" t="inlineStr">
+      <c r="L360" s="0" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+    </row>
+    <row r="361">
+      <c r="B361" s="0" t="inlineStr">
         <is>
           <t>cfg.CompanionBark</t>
         </is>
       </c>
-      <c r="G360" s="0" t="inlineStr">
+      <c r="G361" s="0" t="inlineStr">
         <is>
           <t>队友本地台词</t>
         </is>
       </c>
-      <c r="H360" s="0" t="inlineStr">
+      <c r="H361" s="0" t="inlineStr">
         <is>
           <t>c</t>
-        </is>
-      </c>
-    </row>
-    <row r="361">
-      <c r="J361" s="0" t="inlineStr">
-        <is>
-          <t>id</t>
-        </is>
-      </c>
-      <c r="L361" s="0" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="N361" s="0" t="inlineStr">
-        <is>
-          <t>ID</t>
         </is>
       </c>
     </row>
     <row r="362">
       <c r="J362" s="0" t="inlineStr">
         <is>
-          <t>trigger</t>
+          <t>id</t>
         </is>
       </c>
       <c r="L362" s="0" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>int</t>
         </is>
       </c>
       <c r="N362" s="0" t="inlineStr">
         <is>
-          <t>触发键</t>
+          <t>ID</t>
         </is>
       </c>
     </row>
     <row r="363">
       <c r="J363" s="0" t="inlineStr">
         <is>
-          <t>textKey</t>
+          <t>trigger</t>
         </is>
       </c>
       <c r="L363" s="0" t="inlineStr">
@@ -7184,41 +7181,183 @@
       </c>
       <c r="N363" s="0" t="inlineStr">
         <is>
-          <t>台词本地化键</t>
+          <t>触发键</t>
         </is>
       </c>
     </row>
     <row r="364">
       <c r="J364" s="0" t="inlineStr">
         <is>
-          <t>weight</t>
+          <t>textKey</t>
         </is>
       </c>
       <c r="L364" s="0" t="inlineStr">
         <is>
-          <t>int</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N364" s="0" t="inlineStr">
         <is>
-          <t>随机权重</t>
+          <t>台词本地化键</t>
         </is>
       </c>
     </row>
     <row r="365">
       <c r="J365" s="0" t="inlineStr">
         <is>
+          <t>weight</t>
+        </is>
+      </c>
+      <c r="L365" s="0" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="N365" s="0" t="inlineStr">
+        <is>
+          <t>随机权重</t>
+        </is>
+      </c>
+    </row>
+    <row r="366">
+      <c r="J366" s="0" t="inlineStr">
+        <is>
           <t>cooldown</t>
         </is>
       </c>
-      <c r="L365" s="0" t="inlineStr">
-        <is>
-          <t>float</t>
-        </is>
-      </c>
-      <c r="N365" s="0" t="inlineStr">
+      <c r="L366" s="0" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="N366" s="0" t="inlineStr">
         <is>
           <t>单键冷却s(0=不限)</t>
+        </is>
+      </c>
+    </row>
+    <row r="367">
+      <c r="B367" s="0" t="inlineStr">
+        <is>
+          <t>cfg.Audio</t>
+        </is>
+      </c>
+      <c r="G367" s="0" t="inlineStr">
+        <is>
+          <t>音频条目</t>
+        </is>
+      </c>
+      <c r="H367" s="0" t="inlineStr">
+        <is>
+          <t>c</t>
+        </is>
+      </c>
+    </row>
+    <row r="368">
+      <c r="J368" s="0" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="L368" s="0" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+    </row>
+    <row r="369">
+      <c r="J369" s="0" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="L369" s="0" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+    </row>
+    <row r="370">
+      <c r="J370" s="0" t="inlineStr">
+        <is>
+          <t>audioType</t>
+        </is>
+      </c>
+      <c r="L370" s="0" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+    </row>
+    <row r="371">
+      <c r="J371" s="0" t="inlineStr">
+        <is>
+          <t>volume</t>
+        </is>
+      </c>
+      <c r="L371" s="0" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+    </row>
+    <row r="372">
+      <c r="J372" s="0" t="inlineStr">
+        <is>
+          <t>loop</t>
+        </is>
+      </c>
+      <c r="L372" s="0" t="inlineStr">
+        <is>
+          <t>bool</t>
+        </is>
+      </c>
+    </row>
+    <row r="373">
+      <c r="J373" s="0" t="inlineStr">
+        <is>
+          <t>spatial</t>
+        </is>
+      </c>
+      <c r="L373" s="0" t="inlineStr">
+        <is>
+          <t>bool</t>
+        </is>
+      </c>
+    </row>
+    <row r="374">
+      <c r="J374" s="0" t="inlineStr">
+        <is>
+          <t>minDist</t>
+        </is>
+      </c>
+      <c r="L374" s="0" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+    </row>
+    <row r="375">
+      <c r="J375" s="0" t="inlineStr">
+        <is>
+          <t>maxDist</t>
+        </is>
+      </c>
+      <c r="L375" s="0" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+    </row>
+    <row r="376">
+      <c r="J376" s="0" t="inlineStr">
+        <is>
+          <t>sceneKey</t>
+        </is>
+      </c>
+      <c r="L376" s="0" t="inlineStr">
+        <is>
+          <t>string</t>
         </is>
       </c>
     </row>

--- a/AfterToken/Configs/GameConfig/Datas/__beans__.xlsx
+++ b/AfterToken/Configs/GameConfig/Datas/__beans__.xlsx
@@ -1025,7 +1025,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P376"/>
+  <dimension ref="A1:P391"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col width="20.625" customWidth="1" style="1" min="2" max="4"/>
@@ -5516,7 +5516,6 @@
         </is>
       </c>
     </row>
-    <row r="259"/>
     <row r="260">
       <c r="B260" s="0" t="inlineStr">
         <is>
@@ -5606,7 +5605,6 @@
         </is>
       </c>
     </row>
-    <row r="267"/>
     <row r="268">
       <c r="B268" s="0" t="inlineStr">
         <is>
@@ -5983,145 +5981,145 @@
       </c>
     </row>
     <row r="290">
-      <c r="B290" s="0" t="inlineStr">
+      <c r="J290" t="inlineStr">
+        <is>
+          <t>consoleType</t>
+        </is>
+      </c>
+      <c r="L290" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="N290" t="inlineStr">
+        <is>
+          <t>操作台类型(0=无 1=技能树)</t>
+        </is>
+      </c>
+    </row>
+    <row r="291">
+      <c r="B291" s="0" t="inlineStr">
         <is>
           <t>cfg.Dialogue</t>
         </is>
       </c>
-      <c r="G290" s="0" t="inlineStr">
+      <c r="G291" s="0" t="inlineStr">
         <is>
           <t>对话头</t>
         </is>
       </c>
-      <c r="I290" s="0" t="inlineStr">
+      <c r="I291" s="0" t="inlineStr">
         <is>
           <t>c</t>
-        </is>
-      </c>
-    </row>
-    <row r="291">
-      <c r="J291" s="0" t="inlineStr">
-        <is>
-          <t>id</t>
-        </is>
-      </c>
-      <c r="L291" s="0" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="N291" s="0" t="inlineStr">
-        <is>
-          <t>对话ID</t>
         </is>
       </c>
     </row>
     <row r="292">
       <c r="J292" s="0" t="inlineStr">
         <is>
-          <t>name</t>
+          <t>id</t>
         </is>
       </c>
       <c r="L292" s="0" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>int</t>
         </is>
       </c>
       <c r="N292" s="0" t="inlineStr">
         <is>
-          <t>注释名(不显示)</t>
+          <t>对话ID</t>
         </is>
       </c>
     </row>
     <row r="293">
       <c r="J293" s="0" t="inlineStr">
         <is>
-          <t>startNode</t>
+          <t>name</t>
         </is>
       </c>
       <c r="L293" s="0" t="inlineStr">
         <is>
-          <t>int</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N293" s="0" t="inlineStr">
         <is>
-          <t>起始节点ID</t>
+          <t>注释名(不显示)</t>
         </is>
       </c>
     </row>
     <row r="294">
       <c r="J294" s="0" t="inlineStr">
         <is>
-          <t>onceOnly</t>
+          <t>startNode</t>
         </is>
       </c>
       <c r="L294" s="0" t="inlineStr">
         <is>
-          <t>bool</t>
+          <t>int</t>
         </is>
       </c>
       <c r="N294" s="0" t="inlineStr">
         <is>
-          <t>只触发一次</t>
+          <t>起始节点ID</t>
         </is>
       </c>
     </row>
     <row r="295">
       <c r="J295" s="0" t="inlineStr">
         <is>
+          <t>onceOnly</t>
+        </is>
+      </c>
+      <c r="L295" s="0" t="inlineStr">
+        <is>
+          <t>bool</t>
+        </is>
+      </c>
+      <c r="N295" s="0" t="inlineStr">
+        <is>
+          <t>只触发一次</t>
+        </is>
+      </c>
+    </row>
+    <row r="296">
+      <c r="J296" s="0" t="inlineStr">
+        <is>
           <t>priority</t>
         </is>
       </c>
-      <c r="L295" s="0" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="N295" s="0" t="inlineStr">
+      <c r="L296" s="0" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="N296" s="0" t="inlineStr">
         <is>
           <t>优先级(大优先)</t>
         </is>
       </c>
     </row>
-    <row r="296">
-      <c r="B296" s="0" t="inlineStr">
+    <row r="297">
+      <c r="B297" s="0" t="inlineStr">
         <is>
           <t>cfg.DialogueNode</t>
         </is>
       </c>
-      <c r="G296" s="0" t="inlineStr">
+      <c r="G297" s="0" t="inlineStr">
         <is>
           <t>对话节点</t>
         </is>
       </c>
-      <c r="I296" s="0" t="inlineStr">
+      <c r="I297" s="0" t="inlineStr">
         <is>
           <t>c</t>
-        </is>
-      </c>
-    </row>
-    <row r="297">
-      <c r="J297" s="0" t="inlineStr">
-        <is>
-          <t>id</t>
-        </is>
-      </c>
-      <c r="L297" s="0" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="N297" s="0" t="inlineStr">
-        <is>
-          <t>节点ID</t>
         </is>
       </c>
     </row>
     <row r="298">
       <c r="J298" s="0" t="inlineStr">
         <is>
-          <t>dialogueId</t>
+          <t>id</t>
         </is>
       </c>
       <c r="L298" s="0" t="inlineStr">
@@ -6131,31 +6129,31 @@
       </c>
       <c r="N298" s="0" t="inlineStr">
         <is>
-          <t>所属对话</t>
+          <t>节点ID</t>
         </is>
       </c>
     </row>
     <row r="299">
       <c r="J299" s="0" t="inlineStr">
         <is>
-          <t>type</t>
+          <t>dialogueId</t>
         </is>
       </c>
       <c r="L299" s="0" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>int</t>
         </is>
       </c>
       <c r="N299" s="0" t="inlineStr">
         <is>
-          <t>类型(line/choice/setflag/end)</t>
+          <t>所属对话</t>
         </is>
       </c>
     </row>
     <row r="300">
       <c r="J300" s="0" t="inlineStr">
         <is>
-          <t>speaker</t>
+          <t>type</t>
         </is>
       </c>
       <c r="L300" s="0" t="inlineStr">
@@ -6165,14 +6163,14 @@
       </c>
       <c r="N300" s="0" t="inlineStr">
         <is>
-          <t>说话人</t>
+          <t>类型(line/choice/setflag/end)</t>
         </is>
       </c>
     </row>
     <row r="301">
       <c r="J301" s="0" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>speaker</t>
         </is>
       </c>
       <c r="L301" s="0" t="inlineStr">
@@ -6182,14 +6180,14 @@
       </c>
       <c r="N301" s="0" t="inlineStr">
         <is>
-          <t>正文</t>
+          <t>说话人</t>
         </is>
       </c>
     </row>
     <row r="302">
       <c r="J302" s="0" t="inlineStr">
         <is>
-          <t>choices</t>
+          <t>text</t>
         </is>
       </c>
       <c r="L302" s="0" t="inlineStr">
@@ -6199,14 +6197,14 @@
       </c>
       <c r="N302" s="0" t="inlineStr">
         <is>
-          <t>选项(文本-&gt;节点|...)</t>
+          <t>正文</t>
         </is>
       </c>
     </row>
     <row r="303">
       <c r="J303" s="0" t="inlineStr">
         <is>
-          <t>condition</t>
+          <t>choices</t>
         </is>
       </c>
       <c r="L303" s="0" t="inlineStr">
@@ -6216,14 +6214,14 @@
       </c>
       <c r="N303" s="0" t="inlineStr">
         <is>
-          <t>进入条件</t>
+          <t>选项(文本-&gt;节点|...)</t>
         </is>
       </c>
     </row>
     <row r="304">
       <c r="J304" s="0" t="inlineStr">
         <is>
-          <t>action</t>
+          <t>condition</t>
         </is>
       </c>
       <c r="L304" s="0" t="inlineStr">
@@ -6233,94 +6231,94 @@
       </c>
       <c r="N304" s="0" t="inlineStr">
         <is>
-          <t>到达动作</t>
+          <t>进入条件</t>
         </is>
       </c>
     </row>
     <row r="305">
       <c r="J305" s="0" t="inlineStr">
         <is>
-          <t>next</t>
+          <t>action</t>
         </is>
       </c>
       <c r="L305" s="0" t="inlineStr">
         <is>
-          <t>int</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N305" s="0" t="inlineStr">
         <is>
-          <t>下一节点(0=结束)</t>
+          <t>到达动作</t>
         </is>
       </c>
     </row>
     <row r="306">
       <c r="J306" s="0" t="inlineStr">
         <is>
+          <t>next</t>
+        </is>
+      </c>
+      <c r="L306" s="0" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="N306" s="0" t="inlineStr">
+        <is>
+          <t>下一节点(0=结束)</t>
+        </is>
+      </c>
+    </row>
+    <row r="307">
+      <c r="J307" s="0" t="inlineStr">
+        <is>
           <t>voiceClip</t>
         </is>
       </c>
-      <c r="L306" s="0" t="inlineStr">
+      <c r="L307" s="0" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
     </row>
-    <row r="307">
-      <c r="B307" s="0" t="inlineStr">
+    <row r="308">
+      <c r="B308" s="0" t="inlineStr">
         <is>
           <t>cfg.Quest</t>
         </is>
       </c>
-      <c r="G307" s="0" t="inlineStr">
+      <c r="G308" s="0" t="inlineStr">
         <is>
           <t>任务定义</t>
         </is>
       </c>
-      <c r="I307" s="0" t="inlineStr">
+      <c r="I308" s="0" t="inlineStr">
         <is>
           <t>c</t>
-        </is>
-      </c>
-    </row>
-    <row r="308">
-      <c r="J308" s="0" t="inlineStr">
-        <is>
-          <t>id</t>
-        </is>
-      </c>
-      <c r="L308" s="0" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="N308" s="0" t="inlineStr">
-        <is>
-          <t>任务ID</t>
         </is>
       </c>
     </row>
     <row r="309">
       <c r="J309" s="0" t="inlineStr">
         <is>
-          <t>name</t>
+          <t>id</t>
         </is>
       </c>
       <c r="L309" s="0" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>int</t>
         </is>
       </c>
       <c r="N309" s="0" t="inlineStr">
         <is>
-          <t>显示名</t>
+          <t>任务ID</t>
         </is>
       </c>
     </row>
     <row r="310">
       <c r="J310" s="0" t="inlineStr">
         <is>
-          <t>desc</t>
+          <t>name</t>
         </is>
       </c>
       <c r="L310" s="0" t="inlineStr">
@@ -6330,48 +6328,48 @@
       </c>
       <c r="N310" s="0" t="inlineStr">
         <is>
-          <t>描述</t>
+          <t>显示名</t>
         </is>
       </c>
     </row>
     <row r="311">
       <c r="J311" s="0" t="inlineStr">
         <is>
-          <t>giverNpc</t>
+          <t>desc</t>
         </is>
       </c>
       <c r="L311" s="0" t="inlineStr">
         <is>
-          <t>int</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N311" s="0" t="inlineStr">
         <is>
-          <t>发布NPC(0=任务板)</t>
+          <t>描述</t>
         </is>
       </c>
     </row>
     <row r="312">
       <c r="J312" s="0" t="inlineStr">
         <is>
-          <t>prereq</t>
+          <t>giverNpc</t>
         </is>
       </c>
       <c r="L312" s="0" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>int</t>
         </is>
       </c>
       <c r="N312" s="0" t="inlineStr">
         <is>
-          <t>接取条件表达式(空=无)</t>
+          <t>发布NPC(0=任务板)</t>
         </is>
       </c>
     </row>
     <row r="313">
       <c r="J313" s="0" t="inlineStr">
         <is>
-          <t>rewards</t>
+          <t>prereq</t>
         </is>
       </c>
       <c r="L313" s="0" t="inlineStr">
@@ -6381,65 +6379,65 @@
       </c>
       <c r="N313" s="0" t="inlineStr">
         <is>
-          <t>奖励(gold:200|exp:50|item:3001:2)</t>
+          <t>接取条件表达式(空=无)</t>
         </is>
       </c>
     </row>
     <row r="314">
       <c r="J314" s="0" t="inlineStr">
         <is>
+          <t>rewards</t>
+        </is>
+      </c>
+      <c r="L314" s="0" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="N314" s="0" t="inlineStr">
+        <is>
+          <t>奖励(gold:200|exp:50|item:3001:2)</t>
+        </is>
+      </c>
+    </row>
+    <row r="315">
+      <c r="J315" s="0" t="inlineStr">
+        <is>
           <t>nextQuest</t>
         </is>
       </c>
-      <c r="L314" s="0" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="N314" s="0" t="inlineStr">
+      <c r="L315" s="0" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="N315" s="0" t="inlineStr">
         <is>
           <t>后继任务(0=无)</t>
         </is>
       </c>
     </row>
-    <row r="315">
-      <c r="B315" s="0" t="inlineStr">
+    <row r="316">
+      <c r="B316" s="0" t="inlineStr">
         <is>
           <t>cfg.QuestObjective</t>
         </is>
       </c>
-      <c r="G315" s="0" t="inlineStr">
+      <c r="G316" s="0" t="inlineStr">
         <is>
           <t>任务目标</t>
         </is>
       </c>
-      <c r="I315" s="0" t="inlineStr">
+      <c r="I316" s="0" t="inlineStr">
         <is>
           <t>c</t>
-        </is>
-      </c>
-    </row>
-    <row r="316">
-      <c r="J316" s="0" t="inlineStr">
-        <is>
-          <t>id</t>
-        </is>
-      </c>
-      <c r="L316" s="0" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="N316" s="0" t="inlineStr">
-        <is>
-          <t>目标ID</t>
         </is>
       </c>
     </row>
     <row r="317">
       <c r="J317" s="0" t="inlineStr">
         <is>
-          <t>questId</t>
+          <t>id</t>
         </is>
       </c>
       <c r="L317" s="0" t="inlineStr">
@@ -6449,31 +6447,31 @@
       </c>
       <c r="N317" s="0" t="inlineStr">
         <is>
-          <t>所属任务</t>
+          <t>目标ID</t>
         </is>
       </c>
     </row>
     <row r="318">
       <c r="J318" s="0" t="inlineStr">
         <is>
-          <t>type</t>
+          <t>questId</t>
         </is>
       </c>
       <c r="L318" s="0" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>int</t>
         </is>
       </c>
       <c r="N318" s="0" t="inlineStr">
         <is>
-          <t>类型(kill/collect/extract/flag)</t>
+          <t>所属任务</t>
         </is>
       </c>
     </row>
     <row r="319">
       <c r="J319" s="0" t="inlineStr">
         <is>
-          <t>targetId</t>
+          <t>type</t>
         </is>
       </c>
       <c r="L319" s="0" t="inlineStr">
@@ -6483,82 +6481,82 @@
       </c>
       <c r="N319" s="0" t="inlineStr">
         <is>
-          <t>目标ID/标志键</t>
+          <t>类型(kill/collect/extract/flag)</t>
         </is>
       </c>
     </row>
     <row r="320">
       <c r="J320" s="0" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>targetId</t>
         </is>
       </c>
       <c r="L320" s="0" t="inlineStr">
         <is>
-          <t>int</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N320" s="0" t="inlineStr">
         <is>
-          <t>需求数(extract恒1)</t>
+          <t>目标ID/标志键</t>
         </is>
       </c>
     </row>
     <row r="321">
       <c r="J321" s="0" t="inlineStr">
         <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="L321" s="0" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="N321" s="0" t="inlineStr">
+        <is>
+          <t>需求数(extract恒1)</t>
+        </is>
+      </c>
+    </row>
+    <row r="322">
+      <c r="J322" s="0" t="inlineStr">
+        <is>
           <t>desc</t>
         </is>
       </c>
-      <c r="L321" s="0" t="inlineStr">
+      <c r="L322" s="0" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="N321" s="0" t="inlineStr">
+      <c r="N322" s="0" t="inlineStr">
         <is>
           <t>目标一行描述</t>
         </is>
       </c>
     </row>
-    <row r="322">
-      <c r="B322" s="0" t="inlineStr">
+    <row r="323">
+      <c r="B323" s="0" t="inlineStr">
         <is>
           <t>cfg.Localization</t>
         </is>
       </c>
-      <c r="G322" s="0" t="inlineStr">
+      <c r="G323" s="0" t="inlineStr">
         <is>
           <t>本地化词条</t>
         </is>
       </c>
-      <c r="I322" s="0" t="inlineStr">
+      <c r="I323" s="0" t="inlineStr">
         <is>
           <t>c</t>
-        </is>
-      </c>
-    </row>
-    <row r="323">
-      <c r="J323" s="0" t="inlineStr">
-        <is>
-          <t>key</t>
-        </is>
-      </c>
-      <c r="L323" s="0" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="N323" s="0" t="inlineStr">
-        <is>
-          <t>词条Key</t>
         </is>
       </c>
     </row>
     <row r="324">
       <c r="J324" s="0" t="inlineStr">
         <is>
-          <t>en</t>
+          <t>key</t>
         </is>
       </c>
       <c r="L324" s="0" t="inlineStr">
@@ -6568,14 +6566,14 @@
       </c>
       <c r="N324" s="0" t="inlineStr">
         <is>
-          <t>英文(必填/兜底)</t>
+          <t>词条Key</t>
         </is>
       </c>
     </row>
     <row r="325">
       <c r="J325" s="0" t="inlineStr">
         <is>
-          <t>zh_cn</t>
+          <t>en</t>
         </is>
       </c>
       <c r="L325" s="0" t="inlineStr">
@@ -6585,14 +6583,14 @@
       </c>
       <c r="N325" s="0" t="inlineStr">
         <is>
-          <t>简体中文</t>
+          <t>英文(必填/兜底)</t>
         </is>
       </c>
     </row>
     <row r="326">
       <c r="J326" s="0" t="inlineStr">
         <is>
-          <t>zh_tw</t>
+          <t>zh_cn</t>
         </is>
       </c>
       <c r="L326" s="0" t="inlineStr">
@@ -6602,14 +6600,14 @@
       </c>
       <c r="N326" s="0" t="inlineStr">
         <is>
-          <t>繁体中文</t>
+          <t>简体中文</t>
         </is>
       </c>
     </row>
     <row r="327">
       <c r="J327" s="0" t="inlineStr">
         <is>
-          <t>ja</t>
+          <t>zh_tw</t>
         </is>
       </c>
       <c r="L327" s="0" t="inlineStr">
@@ -6619,82 +6617,82 @@
       </c>
       <c r="N327" s="0" t="inlineStr">
         <is>
-          <t>日文</t>
+          <t>繁体中文</t>
         </is>
       </c>
     </row>
     <row r="328">
       <c r="J328" s="0" t="inlineStr">
         <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="L328" s="0" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="N328" s="0" t="inlineStr">
+        <is>
+          <t>日文</t>
+        </is>
+      </c>
+    </row>
+    <row r="329">
+      <c r="J329" s="0" t="inlineStr">
+        <is>
           <t>ko</t>
         </is>
       </c>
-      <c r="L328" s="0" t="inlineStr">
+      <c r="L329" s="0" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="N328" s="0" t="inlineStr">
+      <c r="N329" s="0" t="inlineStr">
         <is>
           <t>韩文</t>
         </is>
       </c>
     </row>
-    <row r="329">
-      <c r="B329" s="0" t="inlineStr">
+    <row r="330">
+      <c r="B330" s="0" t="inlineStr">
         <is>
           <t>cfg.Companion</t>
         </is>
       </c>
-      <c r="G329" s="0" t="inlineStr">
+      <c r="G330" s="0" t="inlineStr">
         <is>
           <t>队友人设卡</t>
         </is>
       </c>
-      <c r="H329" s="0" t="inlineStr">
+      <c r="H330" s="0" t="inlineStr">
         <is>
           <t>c</t>
-        </is>
-      </c>
-    </row>
-    <row r="330">
-      <c r="J330" s="0" t="inlineStr">
-        <is>
-          <t>id</t>
-        </is>
-      </c>
-      <c r="L330" s="0" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="N330" s="0" t="inlineStr">
-        <is>
-          <t>队友ID</t>
         </is>
       </c>
     </row>
     <row r="331">
       <c r="J331" s="0" t="inlineStr">
         <is>
-          <t>nameKey</t>
+          <t>id</t>
         </is>
       </c>
       <c r="L331" s="0" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>int</t>
         </is>
       </c>
       <c r="N331" s="0" t="inlineStr">
         <is>
-          <t>呼号本地化键</t>
+          <t>队友ID</t>
         </is>
       </c>
     </row>
     <row r="332">
       <c r="J332" s="0" t="inlineStr">
         <is>
-          <t>personaPrompt</t>
+          <t>nameKey</t>
         </is>
       </c>
       <c r="L332" s="0" t="inlineStr">
@@ -6704,31 +6702,31 @@
       </c>
       <c r="N332" s="0" t="inlineStr">
         <is>
-          <t>LLM 人设 system prompt(英文)</t>
+          <t>呼号本地化键</t>
         </is>
       </c>
     </row>
     <row r="333">
       <c r="J333" s="0" t="inlineStr">
         <is>
-          <t>weaponConfigId</t>
+          <t>personaPrompt</t>
         </is>
       </c>
       <c r="L333" s="0" t="inlineStr">
         <is>
-          <t>int</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N333" s="0" t="inlineStr">
         <is>
-          <t>持有武器</t>
+          <t>LLM 人设 system prompt(英文)</t>
         </is>
       </c>
     </row>
     <row r="334">
       <c r="J334" s="0" t="inlineStr">
         <is>
-          <t>maxHp</t>
+          <t>weaponConfigId</t>
         </is>
       </c>
       <c r="L334" s="0" t="inlineStr">
@@ -6738,31 +6736,31 @@
       </c>
       <c r="N334" s="0" t="inlineStr">
         <is>
-          <t>最大HP</t>
+          <t>持有武器</t>
         </is>
       </c>
     </row>
     <row r="335">
       <c r="J335" s="0" t="inlineStr">
         <is>
-          <t>moveSpeed</t>
+          <t>maxHp</t>
         </is>
       </c>
       <c r="L335" s="0" t="inlineStr">
         <is>
-          <t>float</t>
+          <t>int</t>
         </is>
       </c>
       <c r="N335" s="0" t="inlineStr">
         <is>
-          <t>移动速度</t>
+          <t>最大HP</t>
         </is>
       </c>
     </row>
     <row r="336">
       <c r="J336" s="0" t="inlineStr">
         <is>
-          <t>followStopDist</t>
+          <t>moveSpeed</t>
         </is>
       </c>
       <c r="L336" s="0" t="inlineStr">
@@ -6772,14 +6770,14 @@
       </c>
       <c r="N336" s="0" t="inlineStr">
         <is>
-          <t>跟随到位距离</t>
+          <t>移动速度</t>
         </is>
       </c>
     </row>
     <row r="337">
       <c r="J337" s="0" t="inlineStr">
         <is>
-          <t>engageMinDist</t>
+          <t>followStopDist</t>
         </is>
       </c>
       <c r="L337" s="0" t="inlineStr">
@@ -6789,14 +6787,14 @@
       </c>
       <c r="N337" s="0" t="inlineStr">
         <is>
-          <t>最小交战距离</t>
+          <t>跟随到位距离</t>
         </is>
       </c>
     </row>
     <row r="338">
       <c r="J338" s="0" t="inlineStr">
         <is>
-          <t>retreatHpRatio</t>
+          <t>engageMinDist</t>
         </is>
       </c>
       <c r="L338" s="0" t="inlineStr">
@@ -6806,14 +6804,14 @@
       </c>
       <c r="N338" s="0" t="inlineStr">
         <is>
-          <t>撤退血量比例</t>
+          <t>最小交战距离</t>
         </is>
       </c>
     </row>
     <row r="339">
       <c r="J339" s="0" t="inlineStr">
         <is>
-          <t>idleChatMinInterval</t>
+          <t>retreatHpRatio</t>
         </is>
       </c>
       <c r="L339" s="0" t="inlineStr">
@@ -6823,14 +6821,14 @@
       </c>
       <c r="N339" s="0" t="inlineStr">
         <is>
-          <t>安全闲聊最小间隔s</t>
+          <t>撤退血量比例</t>
         </is>
       </c>
     </row>
     <row r="340">
       <c r="J340" s="0" t="inlineStr">
         <is>
-          <t>idleChatMaxInterval</t>
+          <t>idleChatMinInterval</t>
         </is>
       </c>
       <c r="L340" s="0" t="inlineStr">
@@ -6840,14 +6838,14 @@
       </c>
       <c r="N340" s="0" t="inlineStr">
         <is>
-          <t>安全闲聊最大间隔s</t>
+          <t>安全闲聊最小间隔s</t>
         </is>
       </c>
     </row>
     <row r="341">
       <c r="J341" s="0" t="inlineStr">
         <is>
-          <t>llmRequestInterval</t>
+          <t>idleChatMaxInterval</t>
         </is>
       </c>
       <c r="L341" s="0" t="inlineStr">
@@ -6857,48 +6855,48 @@
       </c>
       <c r="N341" s="0" t="inlineStr">
         <is>
-          <t>LLM 全局最小请求间隔s</t>
+          <t>安全闲聊最大间隔s</t>
         </is>
       </c>
     </row>
     <row r="342">
       <c r="J342" s="0" t="inlineStr">
         <is>
-          <t>llmBudgetPerRun</t>
+          <t>llmRequestInterval</t>
         </is>
       </c>
       <c r="L342" s="0" t="inlineStr">
         <is>
-          <t>int</t>
+          <t>float</t>
         </is>
       </c>
       <c r="N342" s="0" t="inlineStr">
         <is>
-          <t>单局 LLM 请求限额</t>
+          <t>LLM 全局最小请求间隔s</t>
         </is>
       </c>
     </row>
     <row r="343">
       <c r="J343" s="0" t="inlineStr">
         <is>
-          <t>llmTimeout</t>
+          <t>llmBudgetPerRun</t>
         </is>
       </c>
       <c r="L343" s="0" t="inlineStr">
         <is>
-          <t>float</t>
+          <t>int</t>
         </is>
       </c>
       <c r="N343" s="0" t="inlineStr">
         <is>
-          <t>LLM 超时s</t>
+          <t>单局 LLM 请求限额</t>
         </is>
       </c>
     </row>
     <row r="344">
       <c r="J344" s="0" t="inlineStr">
         <is>
-          <t>intentTtl</t>
+          <t>llmTimeout</t>
         </is>
       </c>
       <c r="L344" s="0" t="inlineStr">
@@ -6908,14 +6906,14 @@
       </c>
       <c r="N344" s="0" t="inlineStr">
         <is>
-          <t>意图 TTL s</t>
+          <t>LLM 超时s</t>
         </is>
       </c>
     </row>
     <row r="345">
       <c r="J345" s="0" t="inlineStr">
         <is>
-          <t>offlineProbeInterval</t>
+          <t>intentTtl</t>
         </is>
       </c>
       <c r="L345" s="0" t="inlineStr">
@@ -6925,14 +6923,14 @@
       </c>
       <c r="N345" s="0" t="inlineStr">
         <is>
-          <t>离线恢复探测间隔s</t>
+          <t>意图 TTL s</t>
         </is>
       </c>
     </row>
     <row r="346">
       <c r="J346" s="0" t="inlineStr">
         <is>
-          <t>decisionIntervalSafe</t>
+          <t>offlineProbeInterval</t>
         </is>
       </c>
       <c r="L346" s="0" t="inlineStr">
@@ -6942,14 +6940,14 @@
       </c>
       <c r="N346" s="0" t="inlineStr">
         <is>
-          <t>安全决策间隔s(M5)</t>
+          <t>离线恢复探测间隔s</t>
         </is>
       </c>
     </row>
     <row r="347">
       <c r="J347" s="0" t="inlineStr">
         <is>
-          <t>decisionIntervalCombat</t>
+          <t>decisionIntervalSafe</t>
         </is>
       </c>
       <c r="L347" s="0" t="inlineStr">
@@ -6959,14 +6957,14 @@
       </c>
       <c r="N347" s="0" t="inlineStr">
         <is>
-          <t>战斗决策间隔s(M5)</t>
+          <t>安全决策间隔s(M5)</t>
         </is>
       </c>
     </row>
     <row r="348">
       <c r="J348" s="0" t="inlineStr">
         <is>
-          <t>decisionTimeout</t>
+          <t>decisionIntervalCombat</t>
         </is>
       </c>
       <c r="L348" s="0" t="inlineStr">
@@ -6976,60 +6974,65 @@
       </c>
       <c r="N348" s="0" t="inlineStr">
         <is>
-          <t>决策响应超时s(M5)</t>
+          <t>战斗决策间隔s(M5)</t>
         </is>
       </c>
     </row>
     <row r="349">
       <c r="J349" s="0" t="inlineStr">
         <is>
-          <t>controlBudgetPerRun</t>
+          <t>decisionTimeout</t>
         </is>
       </c>
       <c r="L349" s="0" t="inlineStr">
         <is>
-          <t>int</t>
+          <t>float</t>
         </is>
       </c>
       <c r="N349" s="0" t="inlineStr">
         <is>
-          <t>单局操控决策限额(M5)</t>
+          <t>决策响应超时s(M5)</t>
         </is>
       </c>
     </row>
     <row r="350">
       <c r="J350" s="0" t="inlineStr">
         <is>
-          <t>proactiveEngageDist</t>
+          <t>controlBudgetPerRun</t>
         </is>
       </c>
       <c r="L350" s="0" t="inlineStr">
         <is>
-          <t>float</t>
+          <t>int</t>
         </is>
       </c>
       <c r="N350" s="0" t="inlineStr">
         <is>
-          <t>主动开火警戒半径m</t>
+          <t>单局操控决策限额(M5)</t>
         </is>
       </c>
     </row>
     <row r="351">
       <c r="J351" s="0" t="inlineStr">
         <is>
-          <t>conversationHold</t>
+          <t>proactiveEngageDist</t>
         </is>
       </c>
       <c r="L351" s="0" t="inlineStr">
         <is>
           <t>float</t>
+        </is>
+      </c>
+      <c r="N351" s="0" t="inlineStr">
+        <is>
+          <t>主动开火警戒半径m</t>
         </is>
       </c>
     </row>
     <row r="352">
       <c r="J352" s="0" t="inlineStr">
         <is>
-          <t>postCombatCalm</t>
+          <t>conversationHold</t>
         </is>
       </c>
       <c r="L352" s="0" t="inlineStr">
@@ -7041,7 +7044,7 @@
     <row r="353">
       <c r="J353" s="0" t="inlineStr">
         <is>
-          <t>dirHintInterval</t>
+          <t>postCombatCalm</t>
         </is>
       </c>
       <c r="L353" s="0" t="inlineStr">
@@ -7053,55 +7056,55 @@
     <row r="354">
       <c r="J354" s="0" t="inlineStr">
         <is>
-          <t>offlineFailThreshold</t>
+          <t>dirHintInterval</t>
         </is>
       </c>
       <c r="L354" s="0" t="inlineStr">
         <is>
-          <t>int</t>
+          <t>float</t>
         </is>
       </c>
     </row>
     <row r="355">
       <c r="J355" s="0" t="inlineStr">
         <is>
-          <t>decisionSayInterval</t>
+          <t>offlineFailThreshold</t>
         </is>
       </c>
       <c r="L355" s="0" t="inlineStr">
         <is>
-          <t>float</t>
+          <t>int</t>
         </is>
       </c>
     </row>
     <row r="356">
       <c r="J356" s="0" t="inlineStr">
         <is>
-          <t>maxReportEntries</t>
+          <t>decisionSayInterval</t>
         </is>
       </c>
       <c r="L356" s="0" t="inlineStr">
         <is>
-          <t>int</t>
+          <t>float</t>
         </is>
       </c>
     </row>
     <row r="357">
       <c r="J357" s="0" t="inlineStr">
         <is>
-          <t>leashDist</t>
+          <t>maxReportEntries</t>
         </is>
       </c>
       <c r="L357" s="0" t="inlineStr">
         <is>
-          <t>float</t>
+          <t>int</t>
         </is>
       </c>
     </row>
     <row r="358">
       <c r="J358" s="0" t="inlineStr">
         <is>
-          <t>leashStopDist</t>
+          <t>leashDist</t>
         </is>
       </c>
       <c r="L358" s="0" t="inlineStr">
@@ -7113,7 +7116,7 @@
     <row r="359">
       <c r="J359" s="0" t="inlineStr">
         <is>
-          <t>spawnOffsetX</t>
+          <t>leashStopDist</t>
         </is>
       </c>
       <c r="L359" s="0" t="inlineStr">
@@ -7125,70 +7128,65 @@
     <row r="360">
       <c r="J360" s="0" t="inlineStr">
         <is>
+          <t>spawnOffsetX</t>
+        </is>
+      </c>
+      <c r="L360" s="0" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+    </row>
+    <row r="361">
+      <c r="J361" s="0" t="inlineStr">
+        <is>
           <t>spawnOffsetZ</t>
         </is>
       </c>
-      <c r="L360" s="0" t="inlineStr">
-        <is>
-          <t>float</t>
-        </is>
-      </c>
-    </row>
-    <row r="361">
-      <c r="B361" s="0" t="inlineStr">
+      <c r="L361" s="0" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+    </row>
+    <row r="362">
+      <c r="B362" s="0" t="inlineStr">
         <is>
           <t>cfg.CompanionBark</t>
         </is>
       </c>
-      <c r="G361" s="0" t="inlineStr">
+      <c r="G362" s="0" t="inlineStr">
         <is>
           <t>队友本地台词</t>
         </is>
       </c>
-      <c r="H361" s="0" t="inlineStr">
+      <c r="H362" s="0" t="inlineStr">
         <is>
           <t>c</t>
-        </is>
-      </c>
-    </row>
-    <row r="362">
-      <c r="J362" s="0" t="inlineStr">
-        <is>
-          <t>id</t>
-        </is>
-      </c>
-      <c r="L362" s="0" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="N362" s="0" t="inlineStr">
-        <is>
-          <t>ID</t>
         </is>
       </c>
     </row>
     <row r="363">
       <c r="J363" s="0" t="inlineStr">
         <is>
-          <t>trigger</t>
+          <t>id</t>
         </is>
       </c>
       <c r="L363" s="0" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>int</t>
         </is>
       </c>
       <c r="N363" s="0" t="inlineStr">
         <is>
-          <t>触发键</t>
+          <t>ID</t>
         </is>
       </c>
     </row>
     <row r="364">
       <c r="J364" s="0" t="inlineStr">
         <is>
-          <t>textKey</t>
+          <t>trigger</t>
         </is>
       </c>
       <c r="L364" s="0" t="inlineStr">
@@ -7198,89 +7196,94 @@
       </c>
       <c r="N364" s="0" t="inlineStr">
         <is>
-          <t>台词本地化键</t>
+          <t>触发键</t>
         </is>
       </c>
     </row>
     <row r="365">
       <c r="J365" s="0" t="inlineStr">
         <is>
-          <t>weight</t>
+          <t>textKey</t>
         </is>
       </c>
       <c r="L365" s="0" t="inlineStr">
         <is>
-          <t>int</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N365" s="0" t="inlineStr">
         <is>
-          <t>随机权重</t>
+          <t>台词本地化键</t>
         </is>
       </c>
     </row>
     <row r="366">
       <c r="J366" s="0" t="inlineStr">
         <is>
+          <t>weight</t>
+        </is>
+      </c>
+      <c r="L366" s="0" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="N366" s="0" t="inlineStr">
+        <is>
+          <t>随机权重</t>
+        </is>
+      </c>
+    </row>
+    <row r="367">
+      <c r="J367" s="0" t="inlineStr">
+        <is>
           <t>cooldown</t>
         </is>
       </c>
-      <c r="L366" s="0" t="inlineStr">
-        <is>
-          <t>float</t>
-        </is>
-      </c>
-      <c r="N366" s="0" t="inlineStr">
+      <c r="L367" s="0" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="N367" s="0" t="inlineStr">
         <is>
           <t>单键冷却s(0=不限)</t>
         </is>
       </c>
     </row>
-    <row r="367">
-      <c r="B367" s="0" t="inlineStr">
+    <row r="368">
+      <c r="B368" s="0" t="inlineStr">
         <is>
           <t>cfg.Audio</t>
         </is>
       </c>
-      <c r="G367" s="0" t="inlineStr">
+      <c r="G368" s="0" t="inlineStr">
         <is>
           <t>音频条目</t>
         </is>
       </c>
-      <c r="H367" s="0" t="inlineStr">
+      <c r="H368" s="0" t="inlineStr">
         <is>
           <t>c</t>
-        </is>
-      </c>
-    </row>
-    <row r="368">
-      <c r="J368" s="0" t="inlineStr">
-        <is>
-          <t>id</t>
-        </is>
-      </c>
-      <c r="L368" s="0" t="inlineStr">
-        <is>
-          <t>int</t>
         </is>
       </c>
     </row>
     <row r="369">
       <c r="J369" s="0" t="inlineStr">
         <is>
-          <t>name</t>
+          <t>id</t>
         </is>
       </c>
       <c r="L369" s="0" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>int</t>
         </is>
       </c>
     </row>
     <row r="370">
       <c r="J370" s="0" t="inlineStr">
         <is>
-          <t>audioType</t>
+          <t>name</t>
         </is>
       </c>
       <c r="L370" s="0" t="inlineStr">
@@ -7292,31 +7295,31 @@
     <row r="371">
       <c r="J371" s="0" t="inlineStr">
         <is>
-          <t>volume</t>
+          <t>audioType</t>
         </is>
       </c>
       <c r="L371" s="0" t="inlineStr">
         <is>
-          <t>float</t>
+          <t>string</t>
         </is>
       </c>
     </row>
     <row r="372">
       <c r="J372" s="0" t="inlineStr">
         <is>
-          <t>loop</t>
+          <t>volume</t>
         </is>
       </c>
       <c r="L372" s="0" t="inlineStr">
         <is>
-          <t>bool</t>
+          <t>float</t>
         </is>
       </c>
     </row>
     <row r="373">
       <c r="J373" s="0" t="inlineStr">
         <is>
-          <t>spatial</t>
+          <t>loop</t>
         </is>
       </c>
       <c r="L373" s="0" t="inlineStr">
@@ -7328,19 +7331,19 @@
     <row r="374">
       <c r="J374" s="0" t="inlineStr">
         <is>
-          <t>minDist</t>
+          <t>spatial</t>
         </is>
       </c>
       <c r="L374" s="0" t="inlineStr">
         <is>
-          <t>float</t>
+          <t>bool</t>
         </is>
       </c>
     </row>
     <row r="375">
       <c r="J375" s="0" t="inlineStr">
         <is>
-          <t>maxDist</t>
+          <t>minDist</t>
         </is>
       </c>
       <c r="L375" s="0" t="inlineStr">
@@ -7352,12 +7355,262 @@
     <row r="376">
       <c r="J376" s="0" t="inlineStr">
         <is>
+          <t>maxDist</t>
+        </is>
+      </c>
+      <c r="L376" s="0" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+    </row>
+    <row r="377">
+      <c r="J377" s="0" t="inlineStr">
+        <is>
           <t>sceneKey</t>
         </is>
       </c>
-      <c r="L376" s="0" t="inlineStr">
+      <c r="L377" s="0" t="inlineStr">
         <is>
           <t>string</t>
+        </is>
+      </c>
+    </row>
+    <row r="378">
+      <c r="B378" s="0" t="inlineStr">
+        <is>
+          <t>cfg.Skill</t>
+        </is>
+      </c>
+      <c r="G378" s="0" t="inlineStr">
+        <is>
+          <t>技能节点</t>
+        </is>
+      </c>
+      <c r="I378" s="0" t="inlineStr">
+        <is>
+          <t>c</t>
+        </is>
+      </c>
+    </row>
+    <row r="379">
+      <c r="J379" s="0" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="L379" s="0" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="N379" s="0" t="inlineStr">
+        <is>
+          <t>技能ID</t>
+        </is>
+      </c>
+    </row>
+    <row r="380">
+      <c r="J380" s="0" t="inlineStr">
+        <is>
+          <t>nameKey</t>
+        </is>
+      </c>
+      <c r="L380" s="0" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="N380" s="0" t="inlineStr">
+        <is>
+          <t>名称词条键</t>
+        </is>
+      </c>
+    </row>
+    <row r="381">
+      <c r="J381" s="0" t="inlineStr">
+        <is>
+          <t>descKey</t>
+        </is>
+      </c>
+      <c r="L381" s="0" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="N381" s="0" t="inlineStr">
+        <is>
+          <t>描述词条键</t>
+        </is>
+      </c>
+    </row>
+    <row r="382">
+      <c r="J382" s="0" t="inlineStr">
+        <is>
+          <t>branch</t>
+        </is>
+      </c>
+      <c r="L382" s="0" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="N382" s="0" t="inlineStr">
+        <is>
+          <t>分支(1战斗2生存3经营)</t>
+        </is>
+      </c>
+    </row>
+    <row r="383">
+      <c r="J383" s="0" t="inlineStr">
+        <is>
+          <t>maxLevel</t>
+        </is>
+      </c>
+      <c r="L383" s="0" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="N383" s="0" t="inlineStr">
+        <is>
+          <t>最大等级</t>
+        </is>
+      </c>
+    </row>
+    <row r="384">
+      <c r="J384" s="0" t="inlineStr">
+        <is>
+          <t>effectType</t>
+        </is>
+      </c>
+      <c r="L384" s="0" t="inlineStr">
+        <is>
+          <t>cfg.ESkillEffect</t>
+        </is>
+      </c>
+      <c r="N384" s="0" t="inlineStr">
+        <is>
+          <t>效果类型</t>
+        </is>
+      </c>
+    </row>
+    <row r="385">
+      <c r="J385" s="0" t="inlineStr">
+        <is>
+          <t>effectValue</t>
+        </is>
+      </c>
+      <c r="L385" s="0" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="N385" s="0" t="inlineStr">
+        <is>
+          <t>每级效果值</t>
+        </is>
+      </c>
+    </row>
+    <row r="386">
+      <c r="J386" s="0" t="inlineStr">
+        <is>
+          <t>costItems</t>
+        </is>
+      </c>
+      <c r="L386" s="0" t="inlineStr">
+        <is>
+          <t>(list#sep=;),cfg.ItemExchange#sep=,</t>
+        </is>
+      </c>
+      <c r="N386" s="0" t="inlineStr">
+        <is>
+          <t>每级材料消耗</t>
+        </is>
+      </c>
+    </row>
+    <row r="387">
+      <c r="J387" s="0" t="inlineStr">
+        <is>
+          <t>costGold</t>
+        </is>
+      </c>
+      <c r="L387" s="0" t="inlineStr">
+        <is>
+          <t>long</t>
+        </is>
+      </c>
+      <c r="N387" s="0" t="inlineStr">
+        <is>
+          <t>每级金币消耗</t>
+        </is>
+      </c>
+    </row>
+    <row r="388">
+      <c r="J388" s="0" t="inlineStr">
+        <is>
+          <t>prereqSkillId</t>
+        </is>
+      </c>
+      <c r="L388" s="0" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="N388" s="0" t="inlineStr">
+        <is>
+          <t>前置技能(需满级,0=无)</t>
+        </is>
+      </c>
+    </row>
+    <row r="389">
+      <c r="J389" s="0" t="inlineStr">
+        <is>
+          <t>row</t>
+        </is>
+      </c>
+      <c r="L389" s="0" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="N389" s="0" t="inlineStr">
+        <is>
+          <t>树UI行</t>
+        </is>
+      </c>
+    </row>
+    <row r="390">
+      <c r="J390" s="0" t="inlineStr">
+        <is>
+          <t>col</t>
+        </is>
+      </c>
+      <c r="L390" s="0" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="N390" s="0" t="inlineStr">
+        <is>
+          <t>树UI列</t>
+        </is>
+      </c>
+    </row>
+    <row r="391">
+      <c r="J391" s="0" t="inlineStr">
+        <is>
+          <t>icon</t>
+        </is>
+      </c>
+      <c r="L391" s="0" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="N391" s="0" t="inlineStr">
+        <is>
+          <t>图标资源地址</t>
         </is>
       </c>
     </row>

--- a/AfterToken/Configs/GameConfig/Datas/__beans__.xlsx
+++ b/AfterToken/Configs/GameConfig/Datas/__beans__.xlsx
@@ -1025,7 +1025,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P391"/>
+  <dimension ref="A1:P416"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col width="20.625" customWidth="1" style="1" min="2" max="4"/>
@@ -2593,94 +2593,94 @@
       </c>
     </row>
     <row r="87">
-      <c r="B87" s="0" t="inlineStr">
+      <c r="J87" t="inlineStr">
+        <is>
+          <t>affinityValue</t>
+        </is>
+      </c>
+      <c r="L87" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="N87" t="inlineStr">
+        <is>
+          <t>好感值(0=不可赠送)</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="J88" t="inlineStr">
+        <is>
+          <t>companionAccept</t>
+        </is>
+      </c>
+      <c r="L88" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="N88" t="inlineStr">
+        <is>
+          <t>1=NPC接受赠送 0=拒收</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="B89" s="0" t="inlineStr">
         <is>
           <t>cfg.Player</t>
         </is>
       </c>
-      <c r="G87" s="0" t="inlineStr">
+      <c r="G89" s="0" t="inlineStr">
         <is>
           <t>玩家属性</t>
         </is>
       </c>
-      <c r="I87" s="0" t="inlineStr">
+      <c r="I89" s="0" t="inlineStr">
         <is>
           <t>c</t>
-        </is>
-      </c>
-    </row>
-    <row r="88">
-      <c r="J88" s="0" t="inlineStr">
-        <is>
-          <t>id</t>
-        </is>
-      </c>
-      <c r="L88" s="0" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="N88" s="0" t="inlineStr">
-        <is>
-          <t>配置ID</t>
-        </is>
-      </c>
-    </row>
-    <row r="89">
-      <c r="J89" s="0" t="inlineStr">
-        <is>
-          <t>maxHp</t>
-        </is>
-      </c>
-      <c r="L89" s="0" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="N89" s="0" t="inlineStr">
-        <is>
-          <t>最大血量</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="J90" s="0" t="inlineStr">
         <is>
-          <t>moveSpeed</t>
+          <t>id</t>
         </is>
       </c>
       <c r="L90" s="0" t="inlineStr">
         <is>
-          <t>float</t>
+          <t>int</t>
         </is>
       </c>
       <c r="N90" s="0" t="inlineStr">
         <is>
-          <t>移动速度</t>
+          <t>配置ID</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="J91" s="0" t="inlineStr">
         <is>
-          <t>rotationSpeed</t>
+          <t>maxHp</t>
         </is>
       </c>
       <c r="L91" s="0" t="inlineStr">
         <is>
-          <t>float</t>
+          <t>int</t>
         </is>
       </c>
       <c r="N91" s="0" t="inlineStr">
         <is>
-          <t>旋转速度</t>
+          <t>最大血量</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="J92" s="0" t="inlineStr">
         <is>
-          <t>colliderRadius</t>
+          <t>moveSpeed</t>
         </is>
       </c>
       <c r="L92" s="0" t="inlineStr">
@@ -2690,31 +2690,31 @@
       </c>
       <c r="N92" s="0" t="inlineStr">
         <is>
-          <t>碰撞体半径</t>
+          <t>移动速度</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="J93" s="0" t="inlineStr">
         <is>
-          <t>maxStamina</t>
+          <t>rotationSpeed</t>
         </is>
       </c>
       <c r="L93" s="0" t="inlineStr">
         <is>
-          <t>int</t>
+          <t>float</t>
         </is>
       </c>
       <c r="N93" s="0" t="inlineStr">
         <is>
-          <t>最大体力</t>
+          <t>旋转速度</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="J94" s="0" t="inlineStr">
         <is>
-          <t>staminaRecoveryRate</t>
+          <t>colliderRadius</t>
         </is>
       </c>
       <c r="L94" s="0" t="inlineStr">
@@ -2724,14 +2724,14 @@
       </c>
       <c r="N94" s="0" t="inlineStr">
         <is>
-          <t>体力恢复速率</t>
+          <t>碰撞体半径</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="J95" s="0" t="inlineStr">
         <is>
-          <t>dodgeStaminaCost</t>
+          <t>maxStamina</t>
         </is>
       </c>
       <c r="L95" s="0" t="inlineStr">
@@ -2741,14 +2741,14 @@
       </c>
       <c r="N95" s="0" t="inlineStr">
         <is>
-          <t>闪避消耗体力</t>
+          <t>最大体力</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="J96" s="0" t="inlineStr">
         <is>
-          <t>dodgeSpeed</t>
+          <t>staminaRecoveryRate</t>
         </is>
       </c>
       <c r="L96" s="0" t="inlineStr">
@@ -2758,65 +2758,65 @@
       </c>
       <c r="N96" s="0" t="inlineStr">
         <is>
-          <t>闪避速度</t>
+          <t>体力恢复速率</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="J97" s="0" t="inlineStr">
         <is>
-          <t>dodgeDuration</t>
+          <t>dodgeStaminaCost</t>
         </is>
       </c>
       <c r="L97" s="0" t="inlineStr">
         <is>
-          <t>float</t>
+          <t>int</t>
         </is>
       </c>
       <c r="N97" s="0" t="inlineStr">
         <is>
-          <t>闪避持续时间</t>
+          <t>闪避消耗体力</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="J98" s="0" t="inlineStr">
         <is>
-          <t>prefab</t>
+          <t>dodgeSpeed</t>
         </is>
       </c>
       <c r="L98" s="0" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>float</t>
         </is>
       </c>
       <c r="N98" s="0" t="inlineStr">
         <is>
-          <t>预制体</t>
+          <t>闪避速度</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="J99" s="0" t="inlineStr">
         <is>
-          <t>idleAnim</t>
+          <t>dodgeDuration</t>
         </is>
       </c>
       <c r="L99" s="0" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>float</t>
         </is>
       </c>
       <c r="N99" s="0" t="inlineStr">
         <is>
-          <t>待机动画名</t>
+          <t>闪避持续时间</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="J100" s="0" t="inlineStr">
         <is>
-          <t>moveAnim</t>
+          <t>prefab</t>
         </is>
       </c>
       <c r="L100" s="0" t="inlineStr">
@@ -2826,14 +2826,14 @@
       </c>
       <c r="N100" s="0" t="inlineStr">
         <is>
-          <t>移动动画名</t>
+          <t>预制体</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="J101" s="0" t="inlineStr">
         <is>
-          <t>dodgeAnim</t>
+          <t>idleAnim</t>
         </is>
       </c>
       <c r="L101" s="0" t="inlineStr">
@@ -2843,14 +2843,14 @@
       </c>
       <c r="N101" s="0" t="inlineStr">
         <is>
-          <t>闪避动画名</t>
+          <t>待机动画名</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="J102" s="0" t="inlineStr">
         <is>
-          <t>reloadAnim</t>
+          <t>moveAnim</t>
         </is>
       </c>
       <c r="L102" s="0" t="inlineStr">
@@ -2860,31 +2860,31 @@
       </c>
       <c r="N102" s="0" t="inlineStr">
         <is>
-          <t>换弹动画名</t>
+          <t>移动动画名</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="J103" s="0" t="inlineStr">
         <is>
-          <t>weaponSwitchCooldown</t>
+          <t>dodgeAnim</t>
         </is>
       </c>
       <c r="L103" s="0" t="inlineStr">
         <is>
-          <t>float</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N103" s="0" t="inlineStr">
         <is>
-          <t>武器切换冷却</t>
+          <t>闪避动画名</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="J104" s="0" t="inlineStr">
         <is>
-          <t>deadAnim</t>
+          <t>reloadAnim</t>
         </is>
       </c>
       <c r="L104" s="0" t="inlineStr">
@@ -2894,65 +2894,65 @@
       </c>
       <c r="N104" s="0" t="inlineStr">
         <is>
-          <t>死亡动画名</t>
+          <t>换弹动画名</t>
         </is>
       </c>
     </row>
     <row r="105">
-      <c r="B105" s="0" t="inlineStr">
-        <is>
-          <t>cfg.Enemy</t>
-        </is>
-      </c>
-      <c r="G105" s="0" t="inlineStr">
-        <is>
-          <t>敌人属性</t>
-        </is>
-      </c>
-      <c r="I105" s="0" t="inlineStr">
-        <is>
-          <t>c</t>
+      <c r="J105" s="0" t="inlineStr">
+        <is>
+          <t>weaponSwitchCooldown</t>
+        </is>
+      </c>
+      <c r="L105" s="0" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="N105" s="0" t="inlineStr">
+        <is>
+          <t>武器切换冷却</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="J106" s="0" t="inlineStr">
         <is>
-          <t>id</t>
+          <t>deadAnim</t>
         </is>
       </c>
       <c r="L106" s="0" t="inlineStr">
         <is>
-          <t>int</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N106" s="0" t="inlineStr">
         <is>
-          <t>敌人ID</t>
+          <t>死亡动画名</t>
         </is>
       </c>
     </row>
     <row r="107">
-      <c r="J107" s="0" t="inlineStr">
-        <is>
-          <t>name</t>
-        </is>
-      </c>
-      <c r="L107" s="0" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="N107" s="0" t="inlineStr">
-        <is>
-          <t>名称</t>
+      <c r="B107" s="0" t="inlineStr">
+        <is>
+          <t>cfg.Enemy</t>
+        </is>
+      </c>
+      <c r="G107" s="0" t="inlineStr">
+        <is>
+          <t>敌人属性</t>
+        </is>
+      </c>
+      <c r="I107" s="0" t="inlineStr">
+        <is>
+          <t>c</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="J108" s="0" t="inlineStr">
         <is>
-          <t>maxHp</t>
+          <t>id</t>
         </is>
       </c>
       <c r="L108" s="0" t="inlineStr">
@@ -2962,65 +2962,65 @@
       </c>
       <c r="N108" s="0" t="inlineStr">
         <is>
-          <t>最大血量</t>
+          <t>敌人ID</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="J109" s="0" t="inlineStr">
         <is>
-          <t>moveSpeed</t>
+          <t>name</t>
         </is>
       </c>
       <c r="L109" s="0" t="inlineStr">
         <is>
-          <t>float</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N109" s="0" t="inlineStr">
         <is>
-          <t>移动速度</t>
+          <t>名称</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="J110" s="0" t="inlineStr">
         <is>
-          <t>rotationSpeed</t>
+          <t>maxHp</t>
         </is>
       </c>
       <c r="L110" s="0" t="inlineStr">
         <is>
-          <t>float</t>
+          <t>int</t>
         </is>
       </c>
       <c r="N110" s="0" t="inlineStr">
         <is>
-          <t>旋转速度</t>
+          <t>最大血量</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="J111" s="0" t="inlineStr">
         <is>
-          <t>attackDamage</t>
+          <t>moveSpeed</t>
         </is>
       </c>
       <c r="L111" s="0" t="inlineStr">
         <is>
-          <t>int</t>
+          <t>float</t>
         </is>
       </c>
       <c r="N111" s="0" t="inlineStr">
         <is>
-          <t>攻击伤害</t>
+          <t>移动速度</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="J112" s="0" t="inlineStr">
         <is>
-          <t>attackRange</t>
+          <t>rotationSpeed</t>
         </is>
       </c>
       <c r="L112" s="0" t="inlineStr">
@@ -3030,31 +3030,31 @@
       </c>
       <c r="N112" s="0" t="inlineStr">
         <is>
-          <t>攻击范围</t>
+          <t>旋转速度</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="J113" s="0" t="inlineStr">
         <is>
-          <t>attackInterval</t>
+          <t>attackDamage</t>
         </is>
       </c>
       <c r="L113" s="0" t="inlineStr">
         <is>
-          <t>float</t>
+          <t>int</t>
         </is>
       </c>
       <c r="N113" s="0" t="inlineStr">
         <is>
-          <t>攻击间隔</t>
+          <t>攻击伤害</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="J114" s="0" t="inlineStr">
         <is>
-          <t>pathRefreshInterval</t>
+          <t>attackRange</t>
         </is>
       </c>
       <c r="L114" s="0" t="inlineStr">
@@ -3064,31 +3064,31 @@
       </c>
       <c r="N114" s="0" t="inlineStr">
         <is>
-          <t>路径刷新间隔</t>
+          <t>攻击范围</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="J115" s="0" t="inlineStr">
         <is>
-          <t>prefab</t>
+          <t>attackInterval</t>
         </is>
       </c>
       <c r="L115" s="0" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>float</t>
         </is>
       </c>
       <c r="N115" s="0" t="inlineStr">
         <is>
-          <t>预制体</t>
+          <t>攻击间隔</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="J116" s="0" t="inlineStr">
         <is>
-          <t>chaseRange</t>
+          <t>pathRefreshInterval</t>
         </is>
       </c>
       <c r="L116" s="0" t="inlineStr">
@@ -3098,31 +3098,31 @@
       </c>
       <c r="N116" s="0" t="inlineStr">
         <is>
-          <t>检测距离（米）：玩家进入此距离触发追击</t>
+          <t>路径刷新间隔</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="J117" s="0" t="inlineStr">
         <is>
-          <t>radius</t>
+          <t>prefab</t>
         </is>
       </c>
       <c r="L117" s="0" t="inlineStr">
         <is>
-          <t>float</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N117" s="0" t="inlineStr">
         <is>
-          <t>碰撞/寻路膨胀半径（米）</t>
+          <t>预制体</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="J118" s="0" t="inlineStr">
         <is>
-          <t>pursuitRange</t>
+          <t>chaseRange</t>
         </is>
       </c>
       <c r="L118" s="0" t="inlineStr">
@@ -3132,65 +3132,65 @@
       </c>
       <c r="N118" s="0" t="inlineStr">
         <is>
-          <t>追踪范围（米）：追击状态下玩家超过此距离则丢失目标</t>
+          <t>检测距离（米）：玩家进入此距离触发追击</t>
         </is>
       </c>
     </row>
     <row r="119">
-      <c r="B119" s="0" t="inlineStr">
-        <is>
-          <t>cfg.Wave</t>
-        </is>
-      </c>
-      <c r="G119" s="0" t="inlineStr">
-        <is>
-          <t>波次配置</t>
-        </is>
-      </c>
-      <c r="I119" s="0" t="inlineStr">
-        <is>
-          <t>c</t>
+      <c r="J119" s="0" t="inlineStr">
+        <is>
+          <t>radius</t>
+        </is>
+      </c>
+      <c r="L119" s="0" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="N119" s="0" t="inlineStr">
+        <is>
+          <t>碰撞/寻路膨胀半径（米）</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="J120" s="0" t="inlineStr">
         <is>
-          <t>id</t>
+          <t>pursuitRange</t>
         </is>
       </c>
       <c r="L120" s="0" t="inlineStr">
         <is>
-          <t>int</t>
+          <t>float</t>
         </is>
       </c>
       <c r="N120" s="0" t="inlineStr">
         <is>
-          <t>波次ID</t>
+          <t>追踪范围（米）：追击状态下玩家超过此距离则丢失目标</t>
         </is>
       </c>
     </row>
     <row r="121">
-      <c r="J121" s="0" t="inlineStr">
-        <is>
-          <t>levelId</t>
-        </is>
-      </c>
-      <c r="L121" s="0" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="N121" s="0" t="inlineStr">
-        <is>
-          <t>关卡ID</t>
+      <c r="B121" s="0" t="inlineStr">
+        <is>
+          <t>cfg.Wave</t>
+        </is>
+      </c>
+      <c r="G121" s="0" t="inlineStr">
+        <is>
+          <t>波次配置</t>
+        </is>
+      </c>
+      <c r="I121" s="0" t="inlineStr">
+        <is>
+          <t>c</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="J122" s="0" t="inlineStr">
         <is>
-          <t>waveIndex</t>
+          <t>id</t>
         </is>
       </c>
       <c r="L122" s="0" t="inlineStr">
@@ -3200,14 +3200,14 @@
       </c>
       <c r="N122" s="0" t="inlineStr">
         <is>
-          <t>波次索引</t>
+          <t>波次ID</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="J123" s="0" t="inlineStr">
         <is>
-          <t>enemyId</t>
+          <t>levelId</t>
         </is>
       </c>
       <c r="L123" s="0" t="inlineStr">
@@ -3217,14 +3217,14 @@
       </c>
       <c r="N123" s="0" t="inlineStr">
         <is>
-          <t>敌人ID</t>
+          <t>关卡ID</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="J124" s="0" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>waveIndex</t>
         </is>
       </c>
       <c r="L124" s="0" t="inlineStr">
@@ -3234,99 +3234,99 @@
       </c>
       <c r="N124" s="0" t="inlineStr">
         <is>
-          <t>数量</t>
+          <t>波次索引</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="J125" s="0" t="inlineStr">
         <is>
-          <t>spawnInterval</t>
+          <t>enemyId</t>
         </is>
       </c>
       <c r="L125" s="0" t="inlineStr">
         <is>
-          <t>float</t>
+          <t>int</t>
         </is>
       </c>
       <c r="N125" s="0" t="inlineStr">
         <is>
-          <t>刷新间隔</t>
+          <t>敌人ID</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="J126" s="0" t="inlineStr">
         <is>
-          <t>spawnRadius</t>
+          <t>count</t>
         </is>
       </c>
       <c r="L126" s="0" t="inlineStr">
         <is>
-          <t>float</t>
+          <t>int</t>
         </is>
       </c>
       <c r="N126" s="0" t="inlineStr">
         <is>
-          <t>刷新半径</t>
+          <t>数量</t>
         </is>
       </c>
     </row>
     <row r="127">
-      <c r="B127" s="0" t="inlineStr">
-        <is>
-          <t>cfg.Drop</t>
-        </is>
-      </c>
-      <c r="G127" s="0" t="inlineStr">
-        <is>
-          <t>掉落配置</t>
-        </is>
-      </c>
-      <c r="I127" s="0" t="inlineStr">
-        <is>
-          <t>c</t>
+      <c r="J127" s="0" t="inlineStr">
+        <is>
+          <t>spawnInterval</t>
+        </is>
+      </c>
+      <c r="L127" s="0" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="N127" s="0" t="inlineStr">
+        <is>
+          <t>刷新间隔</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="J128" s="0" t="inlineStr">
         <is>
-          <t>id</t>
+          <t>spawnRadius</t>
         </is>
       </c>
       <c r="L128" s="0" t="inlineStr">
         <is>
-          <t>int</t>
+          <t>float</t>
         </is>
       </c>
       <c r="N128" s="0" t="inlineStr">
         <is>
-          <t>掉落ID</t>
+          <t>刷新半径</t>
         </is>
       </c>
     </row>
     <row r="129">
-      <c r="J129" s="0" t="inlineStr">
-        <is>
-          <t>enemyId</t>
-        </is>
-      </c>
-      <c r="L129" s="0" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="N129" s="0" t="inlineStr">
-        <is>
-          <t>敌人ID</t>
+      <c r="B129" s="0" t="inlineStr">
+        <is>
+          <t>cfg.Drop</t>
+        </is>
+      </c>
+      <c r="G129" s="0" t="inlineStr">
+        <is>
+          <t>掉落配置</t>
+        </is>
+      </c>
+      <c r="I129" s="0" t="inlineStr">
+        <is>
+          <t>c</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="J130" s="0" t="inlineStr">
         <is>
-          <t>itemId</t>
+          <t>id</t>
         </is>
       </c>
       <c r="L130" s="0" t="inlineStr">
@@ -3336,14 +3336,14 @@
       </c>
       <c r="N130" s="0" t="inlineStr">
         <is>
-          <t>道具ID</t>
+          <t>掉落ID</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="J131" s="0" t="inlineStr">
         <is>
-          <t>dropRate</t>
+          <t>enemyId</t>
         </is>
       </c>
       <c r="L131" s="0" t="inlineStr">
@@ -3353,14 +3353,14 @@
       </c>
       <c r="N131" s="0" t="inlineStr">
         <is>
-          <t>掉落概率(万分之一)</t>
+          <t>敌人ID</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="J132" s="0" t="inlineStr">
         <is>
-          <t>minCount</t>
+          <t>itemId</t>
         </is>
       </c>
       <c r="L132" s="0" t="inlineStr">
@@ -3370,14 +3370,14 @@
       </c>
       <c r="N132" s="0" t="inlineStr">
         <is>
-          <t>最小数量</t>
+          <t>道具ID</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="J133" s="0" t="inlineStr">
         <is>
-          <t>maxCount</t>
+          <t>dropRate</t>
         </is>
       </c>
       <c r="L133" s="0" t="inlineStr">
@@ -3387,31 +3387,31 @@
       </c>
       <c r="N133" s="0" t="inlineStr">
         <is>
-          <t>最大数量</t>
+          <t>掉落概率(万分之一)</t>
         </is>
       </c>
     </row>
     <row r="134">
-      <c r="B134" s="0" t="inlineStr">
-        <is>
-          <t>cfg.Buff</t>
-        </is>
-      </c>
-      <c r="G134" s="0" t="inlineStr">
-        <is>
-          <t>Buff配置</t>
-        </is>
-      </c>
-      <c r="I134" s="0" t="inlineStr">
-        <is>
-          <t>c</t>
+      <c r="J134" s="0" t="inlineStr">
+        <is>
+          <t>minCount</t>
+        </is>
+      </c>
+      <c r="L134" s="0" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="N134" s="0" t="inlineStr">
+        <is>
+          <t>最小数量</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="J135" s="0" t="inlineStr">
         <is>
-          <t>id</t>
+          <t>maxCount</t>
         </is>
       </c>
       <c r="L135" s="0" t="inlineStr">
@@ -3421,65 +3421,65 @@
       </c>
       <c r="N135" s="0" t="inlineStr">
         <is>
-          <t>BuffID</t>
+          <t>最大数量</t>
         </is>
       </c>
     </row>
     <row r="136">
-      <c r="J136" s="0" t="inlineStr">
-        <is>
-          <t>name</t>
-        </is>
-      </c>
-      <c r="L136" s="0" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="N136" s="0" t="inlineStr">
-        <is>
-          <t>名称</t>
+      <c r="B136" s="0" t="inlineStr">
+        <is>
+          <t>cfg.Buff</t>
+        </is>
+      </c>
+      <c r="G136" s="0" t="inlineStr">
+        <is>
+          <t>Buff配置</t>
+        </is>
+      </c>
+      <c r="I136" s="0" t="inlineStr">
+        <is>
+          <t>c</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="J137" s="0" t="inlineStr">
         <is>
-          <t>duration</t>
+          <t>id</t>
         </is>
       </c>
       <c r="L137" s="0" t="inlineStr">
         <is>
-          <t>float</t>
+          <t>int</t>
         </is>
       </c>
       <c r="N137" s="0" t="inlineStr">
         <is>
-          <t>持续时间</t>
+          <t>BuffID</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="J138" s="0" t="inlineStr">
         <is>
-          <t>effectType</t>
+          <t>name</t>
         </is>
       </c>
       <c r="L138" s="0" t="inlineStr">
         <is>
-          <t>int</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N138" s="0" t="inlineStr">
         <is>
-          <t>效果类型</t>
+          <t>名称</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="J139" s="0" t="inlineStr">
         <is>
-          <t>value</t>
+          <t>duration</t>
         </is>
       </c>
       <c r="L139" s="0" t="inlineStr">
@@ -3489,82 +3489,82 @@
       </c>
       <c r="N139" s="0" t="inlineStr">
         <is>
-          <t>数值</t>
+          <t>持续时间</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="J140" s="0" t="inlineStr">
         <is>
-          <t>icon</t>
+          <t>effectType</t>
         </is>
       </c>
       <c r="L140" s="0" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>int</t>
         </is>
       </c>
       <c r="N140" s="0" t="inlineStr">
         <is>
-          <t>图标</t>
+          <t>效果类型</t>
         </is>
       </c>
     </row>
     <row r="141">
-      <c r="B141" s="0" t="inlineStr">
-        <is>
-          <t>cfg.Portal</t>
-        </is>
-      </c>
-      <c r="G141" s="0" t="inlineStr">
-        <is>
-          <t>传送门配置</t>
-        </is>
-      </c>
-      <c r="I141" s="0" t="inlineStr">
-        <is>
-          <t>c</t>
+      <c r="J141" s="0" t="inlineStr">
+        <is>
+          <t>value</t>
+        </is>
+      </c>
+      <c r="L141" s="0" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="N141" s="0" t="inlineStr">
+        <is>
+          <t>数值</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="J142" s="0" t="inlineStr">
         <is>
-          <t>id</t>
+          <t>icon</t>
         </is>
       </c>
       <c r="L142" s="0" t="inlineStr">
         <is>
-          <t>int</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N142" s="0" t="inlineStr">
         <is>
-          <t>传送门ID</t>
+          <t>图标</t>
         </is>
       </c>
     </row>
     <row r="143">
-      <c r="J143" s="0" t="inlineStr">
-        <is>
-          <t>portalType</t>
-        </is>
-      </c>
-      <c r="L143" s="0" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="N143" s="0" t="inlineStr">
-        <is>
-          <t>传送门类型</t>
+      <c r="B143" s="0" t="inlineStr">
+        <is>
+          <t>cfg.Portal</t>
+        </is>
+      </c>
+      <c r="G143" s="0" t="inlineStr">
+        <is>
+          <t>传送门配置</t>
+        </is>
+      </c>
+      <c r="I143" s="0" t="inlineStr">
+        <is>
+          <t>c</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="J144" s="0" t="inlineStr">
         <is>
-          <t>targetLevelId</t>
+          <t>id</t>
         </is>
       </c>
       <c r="L144" s="0" t="inlineStr">
@@ -3574,14 +3574,14 @@
       </c>
       <c r="N144" s="0" t="inlineStr">
         <is>
-          <t>目标关卡ID</t>
+          <t>传送门ID</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="J145" s="0" t="inlineStr">
         <is>
-          <t>targetSceneName</t>
+          <t>portalType</t>
         </is>
       </c>
       <c r="L145" s="0" t="inlineStr">
@@ -3591,31 +3591,31 @@
       </c>
       <c r="N145" s="0" t="inlineStr">
         <is>
-          <t>目标场景名</t>
+          <t>传送门类型</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="J146" s="0" t="inlineStr">
         <is>
-          <t>spawnCondition</t>
+          <t>targetLevelId</t>
         </is>
       </c>
       <c r="L146" s="0" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>int</t>
         </is>
       </c>
       <c r="N146" s="0" t="inlineStr">
         <is>
-          <t>出现条件</t>
+          <t>目标关卡ID</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="J147" s="0" t="inlineStr">
         <is>
-          <t>conditionParam</t>
+          <t>targetSceneName</t>
         </is>
       </c>
       <c r="L147" s="0" t="inlineStr">
@@ -3625,31 +3625,31 @@
       </c>
       <c r="N147" s="0" t="inlineStr">
         <is>
-          <t>条件参数</t>
+          <t>目标场景名</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="J148" s="0" t="inlineStr">
         <is>
-          <t>keepPlayerState</t>
+          <t>spawnCondition</t>
         </is>
       </c>
       <c r="L148" s="0" t="inlineStr">
         <is>
-          <t>bool</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N148" s="0" t="inlineStr">
         <is>
-          <t>保留玩家状态</t>
+          <t>出现条件</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="J149" s="0" t="inlineStr">
         <is>
-          <t>promptText</t>
+          <t>conditionParam</t>
         </is>
       </c>
       <c r="L149" s="0" t="inlineStr">
@@ -3659,99 +3659,99 @@
       </c>
       <c r="N149" s="0" t="inlineStr">
         <is>
-          <t>提示文本</t>
+          <t>条件参数</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="J150" s="0" t="inlineStr">
         <is>
-          <t>transitionType</t>
+          <t>keepPlayerState</t>
         </is>
       </c>
       <c r="L150" s="0" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>bool</t>
         </is>
       </c>
       <c r="N150" s="0" t="inlineStr">
         <is>
-          <t>转场类型</t>
+          <t>保留玩家状态</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="J151" s="0" t="inlineStr">
         <is>
-          <t>transitionDuration</t>
+          <t>promptText</t>
         </is>
       </c>
       <c r="L151" s="0" t="inlineStr">
         <is>
-          <t>float</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N151" s="0" t="inlineStr">
         <is>
-          <t>转场时长</t>
+          <t>提示文本</t>
         </is>
       </c>
     </row>
     <row r="152">
-      <c r="B152" s="0" t="inlineStr">
-        <is>
-          <t>cfg.InventoryConfig</t>
-        </is>
-      </c>
-      <c r="G152" s="0" t="inlineStr">
-        <is>
-          <t>背包容量配置</t>
-        </is>
-      </c>
-      <c r="I152" s="0" t="inlineStr">
-        <is>
-          <t>c</t>
+      <c r="J152" s="0" t="inlineStr">
+        <is>
+          <t>transitionType</t>
+        </is>
+      </c>
+      <c r="L152" s="0" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="N152" s="0" t="inlineStr">
+        <is>
+          <t>转场类型</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="J153" s="0" t="inlineStr">
         <is>
-          <t>id</t>
+          <t>transitionDuration</t>
         </is>
       </c>
       <c r="L153" s="0" t="inlineStr">
         <is>
-          <t>int</t>
+          <t>float</t>
         </is>
       </c>
       <c r="N153" s="0" t="inlineStr">
         <is>
-          <t>ID</t>
+          <t>转场时长</t>
         </is>
       </c>
     </row>
     <row r="154">
-      <c r="J154" s="0" t="inlineStr">
-        <is>
-          <t>tempBagCapacity</t>
-        </is>
-      </c>
-      <c r="L154" s="0" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="N154" s="0" t="inlineStr">
-        <is>
-          <t>临时背包槽位</t>
+      <c r="B154" s="0" t="inlineStr">
+        <is>
+          <t>cfg.InventoryConfig</t>
+        </is>
+      </c>
+      <c r="G154" s="0" t="inlineStr">
+        <is>
+          <t>背包容量配置</t>
+        </is>
+      </c>
+      <c r="I154" s="0" t="inlineStr">
+        <is>
+          <t>c</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="J155" s="0" t="inlineStr">
         <is>
-          <t>warehouseCapacity</t>
+          <t>id</t>
         </is>
       </c>
       <c r="L155" s="0" t="inlineStr">
@@ -3761,31 +3761,31 @@
       </c>
       <c r="N155" s="0" t="inlineStr">
         <is>
-          <t>仓库槽位</t>
+          <t>ID</t>
         </is>
       </c>
     </row>
     <row r="156">
-      <c r="B156" s="0" t="inlineStr">
-        <is>
-          <t>cfg.Camera</t>
-        </is>
-      </c>
-      <c r="G156" s="0" t="inlineStr">
-        <is>
-          <t>相机配置</t>
-        </is>
-      </c>
-      <c r="H156" s="0" t="inlineStr">
-        <is>
-          <t>c</t>
+      <c r="J156" s="0" t="inlineStr">
+        <is>
+          <t>tempBagCapacity</t>
+        </is>
+      </c>
+      <c r="L156" s="0" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="N156" s="0" t="inlineStr">
+        <is>
+          <t>临时背包槽位</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="J157" s="0" t="inlineStr">
         <is>
-          <t>id</t>
+          <t>warehouseCapacity</t>
         </is>
       </c>
       <c r="L157" s="0" t="inlineStr">
@@ -3795,48 +3795,48 @@
       </c>
       <c r="N157" s="0" t="inlineStr">
         <is>
-          <t>配置ID</t>
+          <t>仓库槽位</t>
         </is>
       </c>
     </row>
     <row r="158">
-      <c r="J158" s="0" t="inlineStr">
-        <is>
-          <t>smoothTime</t>
-        </is>
-      </c>
-      <c r="L158" s="0" t="inlineStr">
-        <is>
-          <t>float</t>
-        </is>
-      </c>
-      <c r="N158" s="0" t="inlineStr">
-        <is>
-          <t>相机平滑时间</t>
+      <c r="B158" s="0" t="inlineStr">
+        <is>
+          <t>cfg.Camera</t>
+        </is>
+      </c>
+      <c r="G158" s="0" t="inlineStr">
+        <is>
+          <t>相机配置</t>
+        </is>
+      </c>
+      <c r="H158" s="0" t="inlineStr">
+        <is>
+          <t>c</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="J159" s="0" t="inlineStr">
         <is>
-          <t>defaultFov</t>
+          <t>id</t>
         </is>
       </c>
       <c r="L159" s="0" t="inlineStr">
         <is>
-          <t>float</t>
+          <t>int</t>
         </is>
       </c>
       <c r="N159" s="0" t="inlineStr">
         <is>
-          <t>默认FOV</t>
+          <t>配置ID</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="J160" s="0" t="inlineStr">
         <is>
-          <t>fovSmoothTime</t>
+          <t>smoothTime</t>
         </is>
       </c>
       <c r="L160" s="0" t="inlineStr">
@@ -3846,14 +3846,14 @@
       </c>
       <c r="N160" s="0" t="inlineStr">
         <is>
-          <t>FOV平滑时间</t>
+          <t>相机平滑时间</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="J161" s="0" t="inlineStr">
         <is>
-          <t>shakeDamping</t>
+          <t>defaultFov</t>
         </is>
       </c>
       <c r="L161" s="0" t="inlineStr">
@@ -3863,31 +3863,31 @@
       </c>
       <c r="N161" s="0" t="inlineStr">
         <is>
-          <t>震动衰减速度</t>
+          <t>默认FOV</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="J162" s="0" t="inlineStr">
         <is>
-          <t>scopeRenderSize</t>
+          <t>fovSmoothTime</t>
         </is>
       </c>
       <c r="L162" s="0" t="inlineStr">
         <is>
-          <t>int</t>
+          <t>float</t>
         </is>
       </c>
       <c r="N162" s="0" t="inlineStr">
         <is>
-          <t>狙击镜渲染纹理尺寸</t>
+          <t>FOV平滑时间</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="J163" s="0" t="inlineStr">
         <is>
-          <t>scopeCameraFov</t>
+          <t>shakeDamping</t>
         </is>
       </c>
       <c r="L163" s="0" t="inlineStr">
@@ -3897,99 +3897,99 @@
       </c>
       <c r="N163" s="0" t="inlineStr">
         <is>
-          <t>狙击镜相机FOV</t>
+          <t>震动衰减速度</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="J164" s="0" t="inlineStr">
         <is>
-          <t>defaultOrthographicSize</t>
+          <t>scopeRenderSize</t>
         </is>
       </c>
       <c r="L164" s="0" t="inlineStr">
         <is>
-          <t>float</t>
+          <t>int</t>
         </is>
       </c>
       <c r="N164" s="0" t="inlineStr">
         <is>
-          <t>默认正交尺寸</t>
+          <t>狙击镜渲染纹理尺寸</t>
         </is>
       </c>
     </row>
     <row r="165">
-      <c r="B165" s="0" t="inlineStr">
-        <is>
-          <t>cfg.Ballistic</t>
-        </is>
-      </c>
-      <c r="G165" s="0" t="inlineStr">
-        <is>
-          <t>弹道全局配置</t>
-        </is>
-      </c>
-      <c r="H165" s="0" t="inlineStr">
-        <is>
-          <t>c</t>
+      <c r="J165" s="0" t="inlineStr">
+        <is>
+          <t>scopeCameraFov</t>
+        </is>
+      </c>
+      <c r="L165" s="0" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="N165" s="0" t="inlineStr">
+        <is>
+          <t>狙击镜相机FOV</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="J166" s="0" t="inlineStr">
         <is>
-          <t>id</t>
+          <t>defaultOrthographicSize</t>
         </is>
       </c>
       <c r="L166" s="0" t="inlineStr">
         <is>
-          <t>int</t>
+          <t>float</t>
         </is>
       </c>
       <c r="N166" s="0" t="inlineStr">
         <is>
-          <t>配置ID</t>
+          <t>默认正交尺寸</t>
         </is>
       </c>
     </row>
     <row r="167">
-      <c r="J167" s="0" t="inlineStr">
-        <is>
-          <t>tracerRadius</t>
-        </is>
-      </c>
-      <c r="L167" s="0" t="inlineStr">
-        <is>
-          <t>float</t>
-        </is>
-      </c>
-      <c r="N167" s="0" t="inlineStr">
-        <is>
-          <t>Tracer射线检测半径</t>
+      <c r="B167" s="0" t="inlineStr">
+        <is>
+          <t>cfg.Ballistic</t>
+        </is>
+      </c>
+      <c r="G167" s="0" t="inlineStr">
+        <is>
+          <t>弹道全局配置</t>
+        </is>
+      </c>
+      <c r="H167" s="0" t="inlineStr">
+        <is>
+          <t>c</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="J168" s="0" t="inlineStr">
         <is>
-          <t>tracerStartWidth</t>
+          <t>id</t>
         </is>
       </c>
       <c r="L168" s="0" t="inlineStr">
         <is>
-          <t>float</t>
+          <t>int</t>
         </is>
       </c>
       <c r="N168" s="0" t="inlineStr">
         <is>
-          <t>Tracer起始宽度</t>
+          <t>配置ID</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="J169" s="0" t="inlineStr">
         <is>
-          <t>tracerEndWidth</t>
+          <t>tracerRadius</t>
         </is>
       </c>
       <c r="L169" s="0" t="inlineStr">
@@ -3999,14 +3999,14 @@
       </c>
       <c r="N169" s="0" t="inlineStr">
         <is>
-          <t>Tracer结束宽度</t>
+          <t>Tracer射线检测半径</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="J170" s="0" t="inlineStr">
         <is>
-          <t>tracerTailLength</t>
+          <t>tracerStartWidth</t>
         </is>
       </c>
       <c r="L170" s="0" t="inlineStr">
@@ -4016,235 +4016,235 @@
       </c>
       <c r="N170" s="0" t="inlineStr">
         <is>
-          <t>Tracer尾迹长度</t>
+          <t>Tracer起始宽度</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="J171" s="0" t="inlineStr">
         <is>
-          <t>maxActiveTracers</t>
+          <t>tracerEndWidth</t>
         </is>
       </c>
       <c r="L171" s="0" t="inlineStr">
         <is>
-          <t>int</t>
+          <t>float</t>
         </is>
       </c>
       <c r="N171" s="0" t="inlineStr">
         <is>
-          <t>最大同时存在Tracer数量</t>
+          <t>Tracer结束宽度</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="J172" s="0" t="inlineStr">
         <is>
-          <t>hitLayers</t>
+          <t>tracerTailLength</t>
         </is>
       </c>
       <c r="L172" s="0" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>float</t>
         </is>
       </c>
       <c r="N172" s="0" t="inlineStr">
         <is>
-          <t>默认命中层级</t>
+          <t>Tracer尾迹长度</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="J173" s="0" t="inlineStr">
         <is>
-          <t>tracerStartColor</t>
+          <t>maxActiveTracers</t>
         </is>
       </c>
       <c r="L173" s="0" t="inlineStr">
         <is>
-          <t>cfg.Color#sep=,</t>
+          <t>int</t>
         </is>
       </c>
       <c r="N173" s="0" t="inlineStr">
         <is>
-          <t>Tracer起始颜色</t>
+          <t>最大同时存在Tracer数量</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="J174" s="0" t="inlineStr">
         <is>
-          <t>tracerEndColor</t>
+          <t>hitLayers</t>
         </is>
       </c>
       <c r="L174" s="0" t="inlineStr">
         <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="N174" s="0" t="inlineStr">
+        <is>
+          <t>默认命中层级</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="J175" s="0" t="inlineStr">
+        <is>
+          <t>tracerStartColor</t>
+        </is>
+      </c>
+      <c r="L175" s="0" t="inlineStr">
+        <is>
           <t>cfg.Color#sep=,</t>
         </is>
       </c>
-      <c r="N174" s="0" t="inlineStr">
-        <is>
-          <t>Tracer结束颜色</t>
-        </is>
-      </c>
-    </row>
-    <row r="175">
-      <c r="B175" s="0" t="inlineStr">
-        <is>
-          <t>cfg.UiConfig</t>
-        </is>
-      </c>
-      <c r="G175" s="0" t="inlineStr">
-        <is>
-          <t>UI全局配置</t>
-        </is>
-      </c>
-      <c r="H175" s="0" t="inlineStr">
-        <is>
-          <t>c</t>
+      <c r="N175" s="0" t="inlineStr">
+        <is>
+          <t>Tracer起始颜色</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="J176" s="0" t="inlineStr">
         <is>
-          <t>id</t>
+          <t>tracerEndColor</t>
         </is>
       </c>
       <c r="L176" s="0" t="inlineStr">
         <is>
-          <t>int</t>
+          <t>cfg.Color#sep=,</t>
         </is>
       </c>
       <c r="N176" s="0" t="inlineStr">
         <is>
-          <t>配置ID</t>
+          <t>Tracer结束颜色</t>
         </is>
       </c>
     </row>
     <row r="177">
-      <c r="J177" s="0" t="inlineStr">
-        <is>
-          <t>damageNumberPoolSize</t>
-        </is>
-      </c>
-      <c r="L177" s="0" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="N177" s="0" t="inlineStr">
-        <is>
-          <t>伤害数字对象池大小</t>
+      <c r="B177" s="0" t="inlineStr">
+        <is>
+          <t>cfg.UiConfig</t>
+        </is>
+      </c>
+      <c r="G177" s="0" t="inlineStr">
+        <is>
+          <t>UI全局配置</t>
+        </is>
+      </c>
+      <c r="H177" s="0" t="inlineStr">
+        <is>
+          <t>c</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="J178" s="0" t="inlineStr">
         <is>
-          <t>damageNumberFadeDuration</t>
+          <t>id</t>
         </is>
       </c>
       <c r="L178" s="0" t="inlineStr">
         <is>
-          <t>float</t>
+          <t>int</t>
         </is>
       </c>
       <c r="N178" s="0" t="inlineStr">
         <is>
-          <t>伤害数字渐隐时间</t>
+          <t>配置ID</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="J179" s="0" t="inlineStr">
         <is>
-          <t>damageNumberMoveOffset</t>
+          <t>damageNumberPoolSize</t>
         </is>
       </c>
       <c r="L179" s="0" t="inlineStr">
         <is>
-          <t>float</t>
+          <t>int</t>
         </is>
       </c>
       <c r="N179" s="0" t="inlineStr">
         <is>
-          <t>伤害数字上浮偏移</t>
+          <t>伤害数字对象池大小</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="J180" s="0" t="inlineStr">
         <is>
-          <t>damageNumberNormalColor</t>
+          <t>damageNumberFadeDuration</t>
         </is>
       </c>
       <c r="L180" s="0" t="inlineStr">
         <is>
-          <t>cfg.Color#sep=,</t>
+          <t>float</t>
         </is>
       </c>
       <c r="N180" s="0" t="inlineStr">
         <is>
-          <t>普通伤害数字颜色</t>
+          <t>伤害数字渐隐时间</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="J181" s="0" t="inlineStr">
         <is>
-          <t>damageNumberCriticalColor</t>
+          <t>damageNumberMoveOffset</t>
         </is>
       </c>
       <c r="L181" s="0" t="inlineStr">
         <is>
-          <t>cfg.Color#sep=,</t>
+          <t>float</t>
         </is>
       </c>
       <c r="N181" s="0" t="inlineStr">
         <is>
-          <t>暴击伤害数字颜色</t>
+          <t>伤害数字上浮偏移</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="J182" s="0" t="inlineStr">
         <is>
-          <t>damageNumberNormalFontSize</t>
+          <t>damageNumberNormalColor</t>
         </is>
       </c>
       <c r="L182" s="0" t="inlineStr">
         <is>
-          <t>int</t>
+          <t>cfg.Color#sep=,</t>
         </is>
       </c>
       <c r="N182" s="0" t="inlineStr">
         <is>
-          <t>普通伤害数字字体大小</t>
+          <t>普通伤害数字颜色</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="J183" s="0" t="inlineStr">
         <is>
-          <t>damageNumberCriticalFontSize</t>
+          <t>damageNumberCriticalColor</t>
         </is>
       </c>
       <c r="L183" s="0" t="inlineStr">
         <is>
-          <t>int</t>
+          <t>cfg.Color#sep=,</t>
         </is>
       </c>
       <c r="N183" s="0" t="inlineStr">
         <is>
-          <t>暴击伤害数字字体大小</t>
+          <t>暴击伤害数字颜色</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="J184" s="0" t="inlineStr">
         <is>
-          <t>hitMarkerPoolSize</t>
+          <t>damageNumberNormalFontSize</t>
         </is>
       </c>
       <c r="L184" s="0" t="inlineStr">
@@ -4254,99 +4254,99 @@
       </c>
       <c r="N184" s="0" t="inlineStr">
         <is>
-          <t>命中标记对象池大小</t>
+          <t>普通伤害数字字体大小</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="J185" s="0" t="inlineStr">
         <is>
-          <t>hitMarkerDuration</t>
+          <t>damageNumberCriticalFontSize</t>
         </is>
       </c>
       <c r="L185" s="0" t="inlineStr">
         <is>
-          <t>float</t>
+          <t>int</t>
         </is>
       </c>
       <c r="N185" s="0" t="inlineStr">
         <is>
-          <t>命中标记显示时间</t>
+          <t>暴击伤害数字字体大小</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="J186" s="0" t="inlineStr">
         <is>
-          <t>hitMarkerSize</t>
+          <t>hitMarkerPoolSize</t>
         </is>
       </c>
       <c r="L186" s="0" t="inlineStr">
         <is>
-          <t>float</t>
+          <t>int</t>
         </is>
       </c>
       <c r="N186" s="0" t="inlineStr">
         <is>
-          <t>命中标记大小</t>
+          <t>命中标记对象池大小</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="J187" s="0" t="inlineStr">
         <is>
-          <t>hitMarkerNormalColor</t>
+          <t>hitMarkerDuration</t>
         </is>
       </c>
       <c r="L187" s="0" t="inlineStr">
         <is>
-          <t>cfg.Color#sep=,</t>
+          <t>float</t>
         </is>
       </c>
       <c r="N187" s="0" t="inlineStr">
         <is>
-          <t>普通命中标记颜色</t>
+          <t>命中标记显示时间</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="J188" s="0" t="inlineStr">
         <is>
-          <t>hitMarkerCriticalColor</t>
+          <t>hitMarkerSize</t>
         </is>
       </c>
       <c r="L188" s="0" t="inlineStr">
         <is>
-          <t>cfg.Color#sep=,</t>
+          <t>float</t>
         </is>
       </c>
       <c r="N188" s="0" t="inlineStr">
         <is>
-          <t>暴击命中标记颜色</t>
+          <t>命中标记大小</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="J189" s="0" t="inlineStr">
         <is>
-          <t>indicatorFadeSpeed</t>
+          <t>hitMarkerNormalColor</t>
         </is>
       </c>
       <c r="L189" s="0" t="inlineStr">
         <is>
-          <t>float</t>
+          <t>cfg.Color#sep=,</t>
         </is>
       </c>
       <c r="N189" s="0" t="inlineStr">
         <is>
-          <t>受击指示器淡出速度</t>
+          <t>普通命中标记颜色</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="J190" s="0" t="inlineStr">
         <is>
-          <t>indicatorColor</t>
+          <t>hitMarkerCriticalColor</t>
         </is>
       </c>
       <c r="L190" s="0" t="inlineStr">
@@ -4356,133 +4356,133 @@
       </c>
       <c r="N190" s="0" t="inlineStr">
         <is>
-          <t>受击指示器颜色</t>
+          <t>暴击命中标记颜色</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="J191" s="0" t="inlineStr">
         <is>
-          <t>loadingTextFormat</t>
+          <t>indicatorFadeSpeed</t>
         </is>
       </c>
       <c r="L191" s="0" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>float</t>
         </is>
       </c>
       <c r="N191" s="0" t="inlineStr">
         <is>
-          <t>加载进度文本格式</t>
+          <t>受击指示器淡出速度</t>
         </is>
       </c>
     </row>
     <row r="192">
-      <c r="B192" s="0" t="inlineStr">
-        <is>
-          <t>cfg.Pickup</t>
-        </is>
-      </c>
-      <c r="G192" s="0" t="inlineStr">
-        <is>
-          <t>拾取物配置</t>
-        </is>
-      </c>
-      <c r="H192" s="0" t="inlineStr">
-        <is>
-          <t>c</t>
+      <c r="J192" s="0" t="inlineStr">
+        <is>
+          <t>indicatorColor</t>
+        </is>
+      </c>
+      <c r="L192" s="0" t="inlineStr">
+        <is>
+          <t>cfg.Color#sep=,</t>
+        </is>
+      </c>
+      <c r="N192" s="0" t="inlineStr">
+        <is>
+          <t>受击指示器颜色</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="J193" s="0" t="inlineStr">
         <is>
-          <t>id</t>
+          <t>loadingTextFormat</t>
         </is>
       </c>
       <c r="L193" s="0" t="inlineStr">
         <is>
-          <t>int</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N193" s="0" t="inlineStr">
         <is>
-          <t>配置ID</t>
+          <t>加载进度文本格式</t>
         </is>
       </c>
     </row>
     <row r="194">
-      <c r="J194" s="0" t="inlineStr">
-        <is>
-          <t>colliderRadius</t>
-        </is>
-      </c>
-      <c r="L194" s="0" t="inlineStr">
-        <is>
-          <t>float</t>
-        </is>
-      </c>
-      <c r="N194" s="0" t="inlineStr">
-        <is>
-          <t>拾取物碰撞体半径</t>
+      <c r="B194" s="0" t="inlineStr">
+        <is>
+          <t>cfg.Pickup</t>
+        </is>
+      </c>
+      <c r="G194" s="0" t="inlineStr">
+        <is>
+          <t>拾取物配置</t>
+        </is>
+      </c>
+      <c r="H194" s="0" t="inlineStr">
+        <is>
+          <t>c</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="J195" s="0" t="inlineStr">
         <is>
-          <t>visualScale</t>
+          <t>id</t>
         </is>
       </c>
       <c r="L195" s="0" t="inlineStr">
         <is>
-          <t>float</t>
+          <t>int</t>
         </is>
       </c>
       <c r="N195" s="0" t="inlineStr">
         <is>
-          <t>拾取物视觉缩放</t>
+          <t>配置ID</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="J196" s="0" t="inlineStr">
         <is>
-          <t>sortingOrder</t>
+          <t>colliderRadius</t>
         </is>
       </c>
       <c r="L196" s="0" t="inlineStr">
         <is>
-          <t>int</t>
+          <t>float</t>
         </is>
       </c>
       <c r="N196" s="0" t="inlineStr">
         <is>
-          <t>拾取物渲染排序</t>
+          <t>拾取物碰撞体半径</t>
         </is>
       </c>
     </row>
     <row r="197">
-      <c r="B197" s="0" t="inlineStr">
-        <is>
-          <t>cfg.Building</t>
-        </is>
-      </c>
-      <c r="G197" s="0" t="inlineStr">
-        <is>
-          <t>建筑配置</t>
-        </is>
-      </c>
-      <c r="I197" s="0" t="inlineStr">
-        <is>
-          <t>c</t>
+      <c r="J197" s="0" t="inlineStr">
+        <is>
+          <t>visualScale</t>
+        </is>
+      </c>
+      <c r="L197" s="0" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="N197" s="0" t="inlineStr">
+        <is>
+          <t>拾取物视觉缩放</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="J198" s="0" t="inlineStr">
         <is>
-          <t>id</t>
+          <t>sortingOrder</t>
         </is>
       </c>
       <c r="L198" s="0" t="inlineStr">
@@ -4492,65 +4492,65 @@
       </c>
       <c r="N198" s="0" t="inlineStr">
         <is>
-          <t>建筑ID</t>
+          <t>拾取物渲染排序</t>
         </is>
       </c>
     </row>
     <row r="199">
-      <c r="J199" s="0" t="inlineStr">
-        <is>
-          <t>name</t>
-        </is>
-      </c>
-      <c r="L199" s="0" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="N199" s="0" t="inlineStr">
-        <is>
-          <t>名称</t>
+      <c r="B199" s="0" t="inlineStr">
+        <is>
+          <t>cfg.Building</t>
+        </is>
+      </c>
+      <c r="G199" s="0" t="inlineStr">
+        <is>
+          <t>建筑配置</t>
+        </is>
+      </c>
+      <c r="I199" s="0" t="inlineStr">
+        <is>
+          <t>c</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="J200" s="0" t="inlineStr">
         <is>
-          <t>desc</t>
+          <t>id</t>
         </is>
       </c>
       <c r="L200" s="0" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>int</t>
         </is>
       </c>
       <c r="N200" s="0" t="inlineStr">
         <is>
-          <t>描述</t>
+          <t>建筑ID</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="J201" s="0" t="inlineStr">
         <is>
-          <t>buildingType</t>
+          <t>name</t>
         </is>
       </c>
       <c r="L201" s="0" t="inlineStr">
         <is>
-          <t>cfg.EBuildingType</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N201" s="0" t="inlineStr">
         <is>
-          <t>建筑类型</t>
+          <t>名称</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="J202" s="0" t="inlineStr">
         <is>
-          <t>icon</t>
+          <t>desc</t>
         </is>
       </c>
       <c r="L202" s="0" t="inlineStr">
@@ -4560,167 +4560,167 @@
       </c>
       <c r="N202" s="0" t="inlineStr">
         <is>
-          <t>图标</t>
+          <t>描述</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="J203" s="0" t="inlineStr">
         <is>
-          <t>maxLevel</t>
+          <t>buildingType</t>
         </is>
       </c>
       <c r="L203" s="0" t="inlineStr">
         <is>
-          <t>int</t>
+          <t>cfg.EBuildingType</t>
         </is>
       </c>
       <c r="N203" s="0" t="inlineStr">
         <is>
-          <t>最大等级</t>
+          <t>建筑类型</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="J204" s="0" t="inlineStr">
         <is>
-          <t>buildCostGold</t>
+          <t>icon</t>
         </is>
       </c>
       <c r="L204" s="0" t="inlineStr">
         <is>
-          <t>int</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N204" s="0" t="inlineStr">
         <is>
-          <t>建造金币</t>
+          <t>图标</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="J205" s="0" t="inlineStr">
         <is>
-          <t>buildCostItems</t>
+          <t>maxLevel</t>
         </is>
       </c>
       <c r="L205" s="0" t="inlineStr">
         <is>
-          <t>(list#sep=;),cfg.ItemExchange#sep=,</t>
+          <t>int</t>
         </is>
       </c>
       <c r="N205" s="0" t="inlineStr">
         <is>
-          <t>建造材料</t>
+          <t>最大等级</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="J206" s="0" t="inlineStr">
         <is>
-          <t>buildTime</t>
+          <t>buildCostGold</t>
         </is>
       </c>
       <c r="L206" s="0" t="inlineStr">
         <is>
-          <t>float</t>
+          <t>int</t>
         </is>
       </c>
       <c r="N206" s="0" t="inlineStr">
         <is>
-          <t>建造耗时</t>
+          <t>建造金币</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="J207" s="0" t="inlineStr">
         <is>
-          <t>upgradeCostGold</t>
+          <t>buildCostItems</t>
         </is>
       </c>
       <c r="L207" s="0" t="inlineStr">
         <is>
-          <t>int</t>
+          <t>(list#sep=;),cfg.ItemExchange#sep=,</t>
         </is>
       </c>
       <c r="N207" s="0" t="inlineStr">
         <is>
-          <t>升级金币</t>
+          <t>建造材料</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="J208" s="0" t="inlineStr">
         <is>
-          <t>upgradeCostItems</t>
+          <t>buildTime</t>
         </is>
       </c>
       <c r="L208" s="0" t="inlineStr">
         <is>
-          <t>(list#sep=;),cfg.ItemExchange#sep=,</t>
+          <t>float</t>
         </is>
       </c>
       <c r="N208" s="0" t="inlineStr">
         <is>
-          <t>升级材料</t>
+          <t>建造耗时</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="J209" s="0" t="inlineStr">
         <is>
-          <t>upgradeTime</t>
+          <t>upgradeCostGold</t>
         </is>
       </c>
       <c r="L209" s="0" t="inlineStr">
         <is>
-          <t>float</t>
+          <t>int</t>
         </is>
       </c>
       <c r="N209" s="0" t="inlineStr">
         <is>
-          <t>升级耗时</t>
+          <t>升级金币</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="J210" s="0" t="inlineStr">
         <is>
-          <t>productionSlotCount</t>
+          <t>upgradeCostItems</t>
         </is>
       </c>
       <c r="L210" s="0" t="inlineStr">
         <is>
-          <t>int</t>
+          <t>(list#sep=;),cfg.ItemExchange#sep=,</t>
         </is>
       </c>
       <c r="N210" s="0" t="inlineStr">
         <is>
-          <t>生产槽位</t>
+          <t>升级材料</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="J211" s="0" t="inlineStr">
         <is>
-          <t>unlockLevel</t>
+          <t>upgradeTime</t>
         </is>
       </c>
       <c r="L211" s="0" t="inlineStr">
         <is>
-          <t>int</t>
+          <t>float</t>
         </is>
       </c>
       <c r="N211" s="0" t="inlineStr">
         <is>
-          <t>解锁等级</t>
+          <t>升级耗时</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="J212" s="0" t="inlineStr">
         <is>
-          <t>footprintX</t>
+          <t>productionSlotCount</t>
         </is>
       </c>
       <c r="L212" s="0" t="inlineStr">
@@ -4730,14 +4730,14 @@
       </c>
       <c r="N212" s="0" t="inlineStr">
         <is>
-          <t>占地格数X(1m格)</t>
+          <t>生产槽位</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="J213" s="0" t="inlineStr">
         <is>
-          <t>maxCount</t>
+          <t>unlockLevel</t>
         </is>
       </c>
       <c r="L213" s="0" t="inlineStr">
@@ -4747,14 +4747,14 @@
       </c>
       <c r="N213" s="0" t="inlineStr">
         <is>
-          <t>数量上限-基础值(默认1)</t>
+          <t>解锁等级</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="J214" s="0" t="inlineStr">
         <is>
-          <t>maxCountPerPlayerLevel</t>
+          <t>footprintX</t>
         </is>
       </c>
       <c r="L214" s="0" t="inlineStr">
@@ -4764,14 +4764,14 @@
       </c>
       <c r="N214" s="0" t="inlineStr">
         <is>
-          <t>数量上限-玩家等级解锁:玩家每升1级上限+N(默认0)</t>
+          <t>占地格数X(1m格)</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="J215" s="0" t="inlineStr">
         <is>
-          <t>maxCountUpgradeLevel</t>
+          <t>maxCount</t>
         </is>
       </c>
       <c r="L215" s="0" t="inlineStr">
@@ -4781,14 +4781,14 @@
       </c>
       <c r="N215" s="0" t="inlineStr">
         <is>
-          <t>数量上限-升级解锁(默认方式):同类建筑每有1座达到该等级上限+1,0=不启用</t>
+          <t>数量上限-基础值(默认1)</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="J216" s="0" t="inlineStr">
         <is>
-          <t>maxCountSlotBaseCost</t>
+          <t>maxCountPerPlayerLevel</t>
         </is>
       </c>
       <c r="L216" s="0" t="inlineStr">
@@ -4798,14 +4798,14 @@
       </c>
       <c r="N216" s="0" t="inlineStr">
         <is>
-          <t>数量上限-购买解锁:购买1个栏位的金币基础价,0=不可购买</t>
+          <t>数量上限-玩家等级解锁:玩家每升1级上限+N(默认0)</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="J217" s="0" t="inlineStr">
         <is>
-          <t>maxCountSlotCostGrow</t>
+          <t>maxCountUpgradeLevel</t>
         </is>
       </c>
       <c r="L217" s="0" t="inlineStr">
@@ -4815,14 +4815,14 @@
       </c>
       <c r="N217" s="0" t="inlineStr">
         <is>
-          <t>数量上限-购买解锁:每已购1个栏位价格+N(线性涨价)</t>
+          <t>数量上限-升级解锁(默认方式):同类建筑每有1座达到该等级上限+1,0=不启用</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="J218" s="0" t="inlineStr">
         <is>
-          <t>footprintZ</t>
+          <t>maxCountSlotBaseCost</t>
         </is>
       </c>
       <c r="L218" s="0" t="inlineStr">
@@ -4832,31 +4832,31 @@
       </c>
       <c r="N218" s="0" t="inlineStr">
         <is>
-          <t>占地格数Z(1m格)</t>
+          <t>数量上限-购买解锁:购买1个栏位的金币基础价,0=不可购买</t>
         </is>
       </c>
     </row>
     <row r="219">
-      <c r="B219" s="0" t="inlineStr">
-        <is>
-          <t>cfg.Production</t>
-        </is>
-      </c>
-      <c r="G219" s="0" t="inlineStr">
-        <is>
-          <t>生产配方</t>
-        </is>
-      </c>
-      <c r="I219" s="0" t="inlineStr">
-        <is>
-          <t>c</t>
+      <c r="J219" s="0" t="inlineStr">
+        <is>
+          <t>maxCountSlotCostGrow</t>
+        </is>
+      </c>
+      <c r="L219" s="0" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="N219" s="0" t="inlineStr">
+        <is>
+          <t>数量上限-购买解锁:每已购1个栏位价格+N(线性涨价)</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="J220" s="0" t="inlineStr">
         <is>
-          <t>id</t>
+          <t>footprintZ</t>
         </is>
       </c>
       <c r="L220" s="0" t="inlineStr">
@@ -4866,99 +4866,99 @@
       </c>
       <c r="N220" s="0" t="inlineStr">
         <is>
-          <t>配方ID</t>
+          <t>占地格数Z(1m格)</t>
         </is>
       </c>
     </row>
     <row r="221">
-      <c r="J221" s="0" t="inlineStr">
-        <is>
-          <t>name</t>
-        </is>
-      </c>
-      <c r="L221" s="0" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="N221" s="0" t="inlineStr">
-        <is>
-          <t>名称</t>
+      <c r="B221" s="0" t="inlineStr">
+        <is>
+          <t>cfg.Production</t>
+        </is>
+      </c>
+      <c r="G221" s="0" t="inlineStr">
+        <is>
+          <t>生产配方</t>
+        </is>
+      </c>
+      <c r="I221" s="0" t="inlineStr">
+        <is>
+          <t>c</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="J222" s="0" t="inlineStr">
         <is>
-          <t>desc</t>
+          <t>id</t>
         </is>
       </c>
       <c r="L222" s="0" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>int</t>
         </is>
       </c>
       <c r="N222" s="0" t="inlineStr">
         <is>
-          <t>描述</t>
+          <t>配方ID</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="J223" s="0" t="inlineStr">
         <is>
-          <t>buildingId</t>
+          <t>name</t>
         </is>
       </c>
       <c r="L223" s="0" t="inlineStr">
         <is>
-          <t>int</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N223" s="0" t="inlineStr">
         <is>
-          <t>建筑ID</t>
+          <t>名称</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="J224" s="0" t="inlineStr">
         <is>
-          <t>levelRequired</t>
+          <t>desc</t>
         </is>
       </c>
       <c r="L224" s="0" t="inlineStr">
         <is>
-          <t>int</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N224" s="0" t="inlineStr">
         <is>
-          <t>等级要求</t>
+          <t>描述</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="J225" s="0" t="inlineStr">
         <is>
-          <t>inputItems</t>
+          <t>buildingId</t>
         </is>
       </c>
       <c r="L225" s="0" t="inlineStr">
         <is>
-          <t>(list#sep=;),cfg.ItemExchange#sep=,</t>
+          <t>int</t>
         </is>
       </c>
       <c r="N225" s="0" t="inlineStr">
         <is>
-          <t>输入材料</t>
+          <t>建筑ID</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="J226" s="0" t="inlineStr">
         <is>
-          <t>outputItemId</t>
+          <t>levelRequired</t>
         </is>
       </c>
       <c r="L226" s="0" t="inlineStr">
@@ -4968,116 +4968,116 @@
       </c>
       <c r="N226" s="0" t="inlineStr">
         <is>
-          <t>产出物品</t>
+          <t>等级要求</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="J227" s="0" t="inlineStr">
         <is>
-          <t>outputCount</t>
+          <t>inputItems</t>
         </is>
       </c>
       <c r="L227" s="0" t="inlineStr">
         <is>
-          <t>int</t>
+          <t>(list#sep=;),cfg.ItemExchange#sep=,</t>
         </is>
       </c>
       <c r="N227" s="0" t="inlineStr">
         <is>
-          <t>产出数量</t>
+          <t>输入材料</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="J228" s="0" t="inlineStr">
         <is>
-          <t>productionTime</t>
+          <t>outputItemId</t>
         </is>
       </c>
       <c r="L228" s="0" t="inlineStr">
         <is>
-          <t>float</t>
+          <t>int</t>
         </is>
       </c>
       <c r="N228" s="0" t="inlineStr">
         <is>
-          <t>生产耗时</t>
+          <t>产出物品</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="J229" s="0" t="inlineStr">
         <is>
-          <t>icon</t>
+          <t>outputCount</t>
         </is>
       </c>
       <c r="L229" s="0" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>int</t>
         </is>
       </c>
       <c r="N229" s="0" t="inlineStr">
         <is>
-          <t>图标</t>
+          <t>产出数量</t>
         </is>
       </c>
     </row>
     <row r="230">
-      <c r="B230" s="0" t="inlineStr">
-        <is>
-          <t>cfg.Order</t>
-        </is>
-      </c>
-      <c r="G230" s="0" t="inlineStr">
-        <is>
-          <t>订单配置</t>
-        </is>
-      </c>
-      <c r="I230" s="0" t="inlineStr">
-        <is>
-          <t>c</t>
+      <c r="J230" s="0" t="inlineStr">
+        <is>
+          <t>productionTime</t>
+        </is>
+      </c>
+      <c r="L230" s="0" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="N230" s="0" t="inlineStr">
+        <is>
+          <t>生产耗时</t>
         </is>
       </c>
     </row>
     <row r="231">
       <c r="J231" s="0" t="inlineStr">
         <is>
-          <t>id</t>
+          <t>icon</t>
         </is>
       </c>
       <c r="L231" s="0" t="inlineStr">
         <is>
-          <t>int</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N231" s="0" t="inlineStr">
         <is>
-          <t>订单ID</t>
+          <t>图标</t>
         </is>
       </c>
     </row>
     <row r="232">
-      <c r="J232" s="0" t="inlineStr">
-        <is>
-          <t>requiredItems</t>
-        </is>
-      </c>
-      <c r="L232" s="0" t="inlineStr">
-        <is>
-          <t>(list#sep=;),cfg.ItemExchange#sep=,</t>
-        </is>
-      </c>
-      <c r="N232" s="0" t="inlineStr">
-        <is>
-          <t>需求物品</t>
+      <c r="B232" s="0" t="inlineStr">
+        <is>
+          <t>cfg.Order</t>
+        </is>
+      </c>
+      <c r="G232" s="0" t="inlineStr">
+        <is>
+          <t>订单配置</t>
+        </is>
+      </c>
+      <c r="I232" s="0" t="inlineStr">
+        <is>
+          <t>c</t>
         </is>
       </c>
     </row>
     <row r="233">
       <c r="J233" s="0" t="inlineStr">
         <is>
-          <t>rewardGold</t>
+          <t>id</t>
         </is>
       </c>
       <c r="L233" s="0" t="inlineStr">
@@ -5087,14 +5087,14 @@
       </c>
       <c r="N233" s="0" t="inlineStr">
         <is>
-          <t>奖励金币</t>
+          <t>订单ID</t>
         </is>
       </c>
     </row>
     <row r="234">
       <c r="J234" s="0" t="inlineStr">
         <is>
-          <t>rewardItems</t>
+          <t>requiredItems</t>
         </is>
       </c>
       <c r="L234" s="0" t="inlineStr">
@@ -5104,14 +5104,14 @@
       </c>
       <c r="N234" s="0" t="inlineStr">
         <is>
-          <t>奖励物品</t>
+          <t>需求物品</t>
         </is>
       </c>
     </row>
     <row r="235">
       <c r="J235" s="0" t="inlineStr">
         <is>
-          <t>rewardExp</t>
+          <t>rewardGold</t>
         </is>
       </c>
       <c r="L235" s="0" t="inlineStr">
@@ -5121,31 +5121,31 @@
       </c>
       <c r="N235" s="0" t="inlineStr">
         <is>
-          <t>奖励经验</t>
+          <t>奖励金币</t>
         </is>
       </c>
     </row>
     <row r="236">
       <c r="J236" s="0" t="inlineStr">
         <is>
-          <t>timeLimit</t>
+          <t>rewardItems</t>
         </is>
       </c>
       <c r="L236" s="0" t="inlineStr">
         <is>
-          <t>float</t>
+          <t>(list#sep=;),cfg.ItemExchange#sep=,</t>
         </is>
       </c>
       <c r="N236" s="0" t="inlineStr">
         <is>
-          <t>时限</t>
+          <t>奖励物品</t>
         </is>
       </c>
     </row>
     <row r="237">
       <c r="J237" s="0" t="inlineStr">
         <is>
-          <t>weight</t>
+          <t>rewardExp</t>
         </is>
       </c>
       <c r="L237" s="0" t="inlineStr">
@@ -5155,48 +5155,48 @@
       </c>
       <c r="N237" s="0" t="inlineStr">
         <is>
-          <t>权重</t>
+          <t>奖励经验</t>
         </is>
       </c>
     </row>
     <row r="238">
       <c r="J238" s="0" t="inlineStr">
         <is>
-          <t>minPlayerLevel</t>
+          <t>timeLimit</t>
         </is>
       </c>
       <c r="L238" s="0" t="inlineStr">
         <is>
-          <t>int</t>
+          <t>float</t>
         </is>
       </c>
       <c r="N238" s="0" t="inlineStr">
         <is>
-          <t>最低等级</t>
+          <t>时限</t>
         </is>
       </c>
     </row>
     <row r="239">
-      <c r="B239" s="0" t="inlineStr">
-        <is>
-          <t>cfg.SimTimeConfig</t>
-        </is>
-      </c>
-      <c r="G239" s="0" t="inlineStr">
-        <is>
-          <t>经营时间配置</t>
-        </is>
-      </c>
-      <c r="I239" s="0" t="inlineStr">
-        <is>
-          <t>c</t>
+      <c r="J239" s="0" t="inlineStr">
+        <is>
+          <t>weight</t>
+        </is>
+      </c>
+      <c r="L239" s="0" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="N239" s="0" t="inlineStr">
+        <is>
+          <t>权重</t>
         </is>
       </c>
     </row>
     <row r="240">
       <c r="J240" s="0" t="inlineStr">
         <is>
-          <t>id</t>
+          <t>minPlayerLevel</t>
         </is>
       </c>
       <c r="L240" s="0" t="inlineStr">
@@ -5206,48 +5206,48 @@
       </c>
       <c r="N240" s="0" t="inlineStr">
         <is>
-          <t>ID</t>
+          <t>最低等级</t>
         </is>
       </c>
     </row>
     <row r="241">
-      <c r="J241" s="0" t="inlineStr">
-        <is>
-          <t>baseSpeed</t>
-        </is>
-      </c>
-      <c r="L241" s="0" t="inlineStr">
-        <is>
-          <t>float</t>
-        </is>
-      </c>
-      <c r="N241" s="0" t="inlineStr">
-        <is>
-          <t>基础速度</t>
+      <c r="B241" s="0" t="inlineStr">
+        <is>
+          <t>cfg.SimTimeConfig</t>
+        </is>
+      </c>
+      <c r="G241" s="0" t="inlineStr">
+        <is>
+          <t>经营时间配置</t>
+        </is>
+      </c>
+      <c r="I241" s="0" t="inlineStr">
+        <is>
+          <t>c</t>
         </is>
       </c>
     </row>
     <row r="242">
       <c r="J242" s="0" t="inlineStr">
         <is>
-          <t>fastSpeed</t>
+          <t>id</t>
         </is>
       </c>
       <c r="L242" s="0" t="inlineStr">
         <is>
-          <t>float</t>
+          <t>int</t>
         </is>
       </c>
       <c r="N242" s="0" t="inlineStr">
         <is>
-          <t>加速速度</t>
+          <t>ID</t>
         </is>
       </c>
     </row>
     <row r="243">
       <c r="J243" s="0" t="inlineStr">
         <is>
-          <t>maxSpeed</t>
+          <t>baseSpeed</t>
         </is>
       </c>
       <c r="L243" s="0" t="inlineStr">
@@ -5257,14 +5257,14 @@
       </c>
       <c r="N243" s="0" t="inlineStr">
         <is>
-          <t>最大速度</t>
+          <t>基础速度</t>
         </is>
       </c>
     </row>
     <row r="244">
       <c r="J244" s="0" t="inlineStr">
         <is>
-          <t>orderRefreshInterval</t>
+          <t>fastSpeed</t>
         </is>
       </c>
       <c r="L244" s="0" t="inlineStr">
@@ -5274,48 +5274,48 @@
       </c>
       <c r="N244" s="0" t="inlineStr">
         <is>
-          <t>订单刷新间隔</t>
+          <t>加速速度</t>
         </is>
       </c>
     </row>
     <row r="245">
       <c r="J245" s="0" t="inlineStr">
         <is>
-          <t>maxOrderCount</t>
+          <t>maxSpeed</t>
         </is>
       </c>
       <c r="L245" s="0" t="inlineStr">
         <is>
-          <t>int</t>
+          <t>float</t>
         </is>
       </c>
       <c r="N245" s="0" t="inlineStr">
         <is>
-          <t>最大订单数</t>
+          <t>最大速度</t>
         </is>
       </c>
     </row>
     <row r="246">
-      <c r="B246" s="0" t="inlineStr">
-        <is>
-          <t>cfg.Camera3D</t>
-        </is>
-      </c>
-      <c r="G246" s="0" t="inlineStr">
-        <is>
-          <t>3D摄像机配置</t>
-        </is>
-      </c>
-      <c r="I246" s="0" t="inlineStr">
-        <is>
-          <t>c</t>
+      <c r="J246" s="0" t="inlineStr">
+        <is>
+          <t>orderRefreshInterval</t>
+        </is>
+      </c>
+      <c r="L246" s="0" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="N246" s="0" t="inlineStr">
+        <is>
+          <t>订单刷新间隔</t>
         </is>
       </c>
     </row>
     <row r="247">
       <c r="J247" s="0" t="inlineStr">
         <is>
-          <t>id</t>
+          <t>maxOrderCount</t>
         </is>
       </c>
       <c r="L247" s="0" t="inlineStr">
@@ -5325,48 +5325,48 @@
       </c>
       <c r="N247" s="0" t="inlineStr">
         <is>
-          <t>配置ID</t>
+          <t>最大订单数</t>
         </is>
       </c>
     </row>
     <row r="248">
-      <c r="J248" s="0" t="inlineStr">
-        <is>
-          <t>pitchAngle</t>
-        </is>
-      </c>
-      <c r="L248" s="0" t="inlineStr">
-        <is>
-          <t>float</t>
-        </is>
-      </c>
-      <c r="N248" s="0" t="inlineStr">
-        <is>
-          <t>俯视角度</t>
+      <c r="B248" s="0" t="inlineStr">
+        <is>
+          <t>cfg.Camera3D</t>
+        </is>
+      </c>
+      <c r="G248" s="0" t="inlineStr">
+        <is>
+          <t>3D摄像机配置</t>
+        </is>
+      </c>
+      <c r="I248" s="0" t="inlineStr">
+        <is>
+          <t>c</t>
         </is>
       </c>
     </row>
     <row r="249">
       <c r="J249" s="0" t="inlineStr">
         <is>
-          <t>initialHeight</t>
+          <t>id</t>
         </is>
       </c>
       <c r="L249" s="0" t="inlineStr">
         <is>
-          <t>float</t>
+          <t>int</t>
         </is>
       </c>
       <c r="N249" s="0" t="inlineStr">
         <is>
-          <t>初始高度</t>
+          <t>配置ID</t>
         </is>
       </c>
     </row>
     <row r="250">
       <c r="J250" s="0" t="inlineStr">
         <is>
-          <t>initialDistance</t>
+          <t>pitchAngle</t>
         </is>
       </c>
       <c r="L250" s="0" t="inlineStr">
@@ -5376,14 +5376,14 @@
       </c>
       <c r="N250" s="0" t="inlineStr">
         <is>
-          <t>初始距离</t>
+          <t>俯视角度</t>
         </is>
       </c>
     </row>
     <row r="251">
       <c r="J251" s="0" t="inlineStr">
         <is>
-          <t>fov</t>
+          <t>initialHeight</t>
         </is>
       </c>
       <c r="L251" s="0" t="inlineStr">
@@ -5393,14 +5393,14 @@
       </c>
       <c r="N251" s="0" t="inlineStr">
         <is>
-          <t>视场角</t>
+          <t>初始高度</t>
         </is>
       </c>
     </row>
     <row r="252">
       <c r="J252" s="0" t="inlineStr">
         <is>
-          <t>minZoom</t>
+          <t>initialDistance</t>
         </is>
       </c>
       <c r="L252" s="0" t="inlineStr">
@@ -5410,14 +5410,14 @@
       </c>
       <c r="N252" s="0" t="inlineStr">
         <is>
-          <t>最小缩放</t>
+          <t>初始距离</t>
         </is>
       </c>
     </row>
     <row r="253">
       <c r="J253" s="0" t="inlineStr">
         <is>
-          <t>maxZoom</t>
+          <t>fov</t>
         </is>
       </c>
       <c r="L253" s="0" t="inlineStr">
@@ -5427,14 +5427,14 @@
       </c>
       <c r="N253" s="0" t="inlineStr">
         <is>
-          <t>最大缩放</t>
+          <t>视场角</t>
         </is>
       </c>
     </row>
     <row r="254">
       <c r="J254" s="0" t="inlineStr">
         <is>
-          <t>moveSpeed</t>
+          <t>minZoom</t>
         </is>
       </c>
       <c r="L254" s="0" t="inlineStr">
@@ -5444,14 +5444,14 @@
       </c>
       <c r="N254" s="0" t="inlineStr">
         <is>
-          <t>移动速度</t>
+          <t>最小缩放</t>
         </is>
       </c>
     </row>
     <row r="255">
       <c r="J255" s="0" t="inlineStr">
         <is>
-          <t>zoomSpeed</t>
+          <t>maxZoom</t>
         </is>
       </c>
       <c r="L255" s="0" t="inlineStr">
@@ -5461,14 +5461,14 @@
       </c>
       <c r="N255" s="0" t="inlineStr">
         <is>
-          <t>缩放速度</t>
+          <t>最大缩放</t>
         </is>
       </c>
     </row>
     <row r="256">
       <c r="J256" s="0" t="inlineStr">
         <is>
-          <t>maxRotationAngle</t>
+          <t>moveSpeed</t>
         </is>
       </c>
       <c r="L256" s="0" t="inlineStr">
@@ -5478,14 +5478,14 @@
       </c>
       <c r="N256" s="0" t="inlineStr">
         <is>
-          <t>最大旋转角度</t>
+          <t>移动速度</t>
         </is>
       </c>
     </row>
     <row r="257">
       <c r="J257" s="0" t="inlineStr">
         <is>
-          <t>rotationSpeed</t>
+          <t>zoomSpeed</t>
         </is>
       </c>
       <c r="L257" s="0" t="inlineStr">
@@ -5495,72 +5495,83 @@
       </c>
       <c r="N257" s="0" t="inlineStr">
         <is>
-          <t>旋转速度</t>
+          <t>缩放速度</t>
         </is>
       </c>
     </row>
     <row r="258">
       <c r="J258" s="0" t="inlineStr">
         <is>
+          <t>maxRotationAngle</t>
+        </is>
+      </c>
+      <c r="L258" s="0" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="N258" s="0" t="inlineStr">
+        <is>
+          <t>最大旋转角度</t>
+        </is>
+      </c>
+    </row>
+    <row r="259">
+      <c r="J259" s="0" t="inlineStr">
+        <is>
+          <t>rotationSpeed</t>
+        </is>
+      </c>
+      <c r="L259" s="0" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="N259" s="0" t="inlineStr">
+        <is>
+          <t>旋转速度</t>
+        </is>
+      </c>
+    </row>
+    <row r="260">
+      <c r="J260" s="0" t="inlineStr">
+        <is>
           <t>followSmoothTime</t>
         </is>
       </c>
-      <c r="L258" s="0" t="inlineStr">
-        <is>
-          <t>float</t>
-        </is>
-      </c>
-      <c r="N258" s="0" t="inlineStr">
+      <c r="L260" s="0" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="N260" s="0" t="inlineStr">
         <is>
           <t>跟随平滑时间</t>
         </is>
       </c>
     </row>
-    <row r="260">
-      <c r="B260" s="0" t="inlineStr">
+    <row r="261"/>
+    <row r="262">
+      <c r="B262" s="0" t="inlineStr">
         <is>
           <t>cfg.LootContainer</t>
         </is>
       </c>
-      <c r="G260" s="0" t="inlineStr">
+      <c r="G262" s="0" t="inlineStr">
         <is>
           <t>容器掉落记录</t>
         </is>
       </c>
-      <c r="I260" s="0" t="inlineStr">
+      <c r="I262" s="0" t="inlineStr">
         <is>
           <t>c</t>
-        </is>
-      </c>
-    </row>
-    <row r="261">
-      <c r="J261" s="0" t="inlineStr">
-        <is>
-          <t>id</t>
-        </is>
-      </c>
-      <c r="L261" s="0" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-    </row>
-    <row r="262">
-      <c r="J262" s="0" t="inlineStr">
-        <is>
-          <t>containerId</t>
-        </is>
-      </c>
-      <c r="L262" s="0" t="inlineStr">
-        <is>
-          <t>int</t>
         </is>
       </c>
     </row>
     <row r="263">
       <c r="J263" s="0" t="inlineStr">
         <is>
-          <t>itemId</t>
+          <t>id</t>
         </is>
       </c>
       <c r="L263" s="0" t="inlineStr">
@@ -5572,7 +5583,7 @@
     <row r="264">
       <c r="J264" s="0" t="inlineStr">
         <is>
-          <t>weight</t>
+          <t>containerId</t>
         </is>
       </c>
       <c r="L264" s="0" t="inlineStr">
@@ -5584,7 +5595,7 @@
     <row r="265">
       <c r="J265" s="0" t="inlineStr">
         <is>
-          <t>minCount</t>
+          <t>itemId</t>
         </is>
       </c>
       <c r="L265" s="0" t="inlineStr">
@@ -5596,156 +5607,147 @@
     <row r="266">
       <c r="J266" s="0" t="inlineStr">
         <is>
+          <t>weight</t>
+        </is>
+      </c>
+      <c r="L266" s="0" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+    </row>
+    <row r="267">
+      <c r="J267" s="0" t="inlineStr">
+        <is>
+          <t>minCount</t>
+        </is>
+      </c>
+      <c r="L267" s="0" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+    </row>
+    <row r="268">
+      <c r="J268" s="0" t="inlineStr">
+        <is>
           <t>maxCount</t>
         </is>
       </c>
-      <c r="L266" s="0" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-    </row>
-    <row r="268">
-      <c r="B268" s="0" t="inlineStr">
+      <c r="L268" s="0" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+    </row>
+    <row r="269"/>
+    <row r="270">
+      <c r="B270" s="0" t="inlineStr">
         <is>
           <t>cfg.Note</t>
         </is>
       </c>
-      <c r="G268" s="0" t="inlineStr">
+      <c r="G270" s="0" t="inlineStr">
         <is>
           <t>小纸条记录</t>
         </is>
       </c>
-      <c r="I268" s="0" t="inlineStr">
+      <c r="I270" s="0" t="inlineStr">
         <is>
           <t>c</t>
-        </is>
-      </c>
-    </row>
-    <row r="269">
-      <c r="J269" s="0" t="inlineStr">
-        <is>
-          <t>id</t>
-        </is>
-      </c>
-      <c r="L269" s="0" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="N269" s="0" t="inlineStr">
-        <is>
-          <t>纸条ID</t>
-        </is>
-      </c>
-    </row>
-    <row r="270">
-      <c r="J270" s="0" t="inlineStr">
-        <is>
-          <t>title</t>
-        </is>
-      </c>
-      <c r="L270" s="0" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="N270" s="0" t="inlineStr">
-        <is>
-          <t>标题</t>
         </is>
       </c>
     </row>
     <row r="271">
       <c r="J271" s="0" t="inlineStr">
         <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="L271" s="0" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="N271" s="0" t="inlineStr">
+        <is>
+          <t>纸条ID</t>
+        </is>
+      </c>
+    </row>
+    <row r="272">
+      <c r="J272" s="0" t="inlineStr">
+        <is>
+          <t>title</t>
+        </is>
+      </c>
+      <c r="L272" s="0" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="N272" s="0" t="inlineStr">
+        <is>
+          <t>标题</t>
+        </is>
+      </c>
+    </row>
+    <row r="273">
+      <c r="J273" s="0" t="inlineStr">
+        <is>
           <t>content</t>
         </is>
       </c>
-      <c r="L271" s="0" t="inlineStr">
+      <c r="L273" s="0" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="N271" s="0" t="inlineStr">
+      <c r="N273" s="0" t="inlineStr">
         <is>
           <t>正文(支持
 换行)</t>
         </is>
       </c>
     </row>
-    <row r="272">
-      <c r="B272" s="0" t="inlineStr">
+    <row r="274">
+      <c r="B274" s="0" t="inlineStr">
         <is>
           <t>cfg.PlayerLevel</t>
         </is>
       </c>
-      <c r="G272" s="0" t="inlineStr">
+      <c r="G274" s="0" t="inlineStr">
         <is>
           <t>玩家等级经验表</t>
         </is>
       </c>
-      <c r="I272" s="0" t="inlineStr">
+      <c r="I274" s="0" t="inlineStr">
         <is>
           <t>c</t>
         </is>
       </c>
     </row>
-    <row r="273">
-      <c r="J273" s="0" t="inlineStr">
+    <row r="275">
+      <c r="J275" s="0" t="inlineStr">
         <is>
           <t>level</t>
         </is>
       </c>
-      <c r="L273" s="0" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="N273" s="0" t="inlineStr">
+      <c r="L275" s="0" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="N275" s="0" t="inlineStr">
         <is>
           <t>等级</t>
-        </is>
-      </c>
-    </row>
-    <row r="274">
-      <c r="J274" s="0" t="inlineStr">
-        <is>
-          <t>expToNext</t>
-        </is>
-      </c>
-      <c r="L274" s="0" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="N274" s="0" t="inlineStr">
-        <is>
-          <t>升到下一级所需经验</t>
-        </is>
-      </c>
-    </row>
-    <row r="275">
-      <c r="B275" s="0" t="inlineStr">
-        <is>
-          <t>cfg.Unlock</t>
-        </is>
-      </c>
-      <c r="G275" s="0" t="inlineStr">
-        <is>
-          <t>内容解锁表</t>
-        </is>
-      </c>
-      <c r="I275" s="0" t="inlineStr">
-        <is>
-          <t>c</t>
         </is>
       </c>
     </row>
     <row r="276">
       <c r="J276" s="0" t="inlineStr">
         <is>
-          <t>id</t>
+          <t>expToNext</t>
         </is>
       </c>
       <c r="L276" s="0" t="inlineStr">
@@ -5755,31 +5757,31 @@
       </c>
       <c r="N276" s="0" t="inlineStr">
         <is>
-          <t>解锁ID</t>
+          <t>升到下一级所需经验</t>
         </is>
       </c>
     </row>
     <row r="277">
-      <c r="J277" s="0" t="inlineStr">
-        <is>
-          <t>contentType</t>
-        </is>
-      </c>
-      <c r="L277" s="0" t="inlineStr">
-        <is>
-          <t>cfg.UnlockContentType</t>
-        </is>
-      </c>
-      <c r="N277" s="0" t="inlineStr">
-        <is>
-          <t>内容类型</t>
+      <c r="B277" s="0" t="inlineStr">
+        <is>
+          <t>cfg.Unlock</t>
+        </is>
+      </c>
+      <c r="G277" s="0" t="inlineStr">
+        <is>
+          <t>内容解锁表</t>
+        </is>
+      </c>
+      <c r="I277" s="0" t="inlineStr">
+        <is>
+          <t>c</t>
         </is>
       </c>
     </row>
     <row r="278">
       <c r="J278" s="0" t="inlineStr">
         <is>
-          <t>targetId</t>
+          <t>id</t>
         </is>
       </c>
       <c r="L278" s="0" t="inlineStr">
@@ -5789,31 +5791,31 @@
       </c>
       <c r="N278" s="0" t="inlineStr">
         <is>
-          <t>目标ID（关卡/武器）</t>
+          <t>解锁ID</t>
         </is>
       </c>
     </row>
     <row r="279">
       <c r="J279" s="0" t="inlineStr">
         <is>
-          <t>requirePlayerLevel</t>
+          <t>contentType</t>
         </is>
       </c>
       <c r="L279" s="0" t="inlineStr">
         <is>
-          <t>int</t>
+          <t>cfg.UnlockContentType</t>
         </is>
       </c>
       <c r="N279" s="0" t="inlineStr">
         <is>
-          <t>要求玩家等级(0=无)</t>
+          <t>内容类型</t>
         </is>
       </c>
     </row>
     <row r="280">
       <c r="J280" s="0" t="inlineStr">
         <is>
-          <t>requireCompleteLevelId</t>
+          <t>targetId</t>
         </is>
       </c>
       <c r="L280" s="0" t="inlineStr">
@@ -5823,14 +5825,14 @@
       </c>
       <c r="N280" s="0" t="inlineStr">
         <is>
-          <t>要求通关关卡ID(0=无)</t>
+          <t>目标ID（关卡/武器）</t>
         </is>
       </c>
     </row>
     <row r="281">
       <c r="J281" s="0" t="inlineStr">
         <is>
-          <t>costGold</t>
+          <t>requirePlayerLevel</t>
         </is>
       </c>
       <c r="L281" s="0" t="inlineStr">
@@ -5840,116 +5842,116 @@
       </c>
       <c r="N281" s="0" t="inlineStr">
         <is>
-          <t>解锁花费金币(0=免费)</t>
+          <t>要求玩家等级(0=无)</t>
         </is>
       </c>
     </row>
     <row r="282">
       <c r="J282" s="0" t="inlineStr">
         <is>
-          <t>comment</t>
+          <t>requireCompleteLevelId</t>
         </is>
       </c>
       <c r="L282" s="0" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>int</t>
         </is>
       </c>
       <c r="N282" s="0" t="inlineStr">
         <is>
-          <t>备注</t>
+          <t>要求通关关卡ID(0=无)</t>
         </is>
       </c>
     </row>
     <row r="283">
-      <c r="B283" s="0" t="inlineStr">
-        <is>
-          <t>cfg.Npc</t>
-        </is>
-      </c>
-      <c r="G283" s="0" t="inlineStr">
-        <is>
-          <t>NPC记录</t>
-        </is>
-      </c>
-      <c r="I283" s="0" t="inlineStr">
-        <is>
-          <t>c</t>
+      <c r="J283" s="0" t="inlineStr">
+        <is>
+          <t>costGold</t>
+        </is>
+      </c>
+      <c r="L283" s="0" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="N283" s="0" t="inlineStr">
+        <is>
+          <t>解锁花费金币(0=免费)</t>
         </is>
       </c>
     </row>
     <row r="284">
       <c r="J284" s="0" t="inlineStr">
         <is>
-          <t>id</t>
+          <t>comment</t>
         </is>
       </c>
       <c r="L284" s="0" t="inlineStr">
         <is>
-          <t>int</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N284" s="0" t="inlineStr">
         <is>
-          <t>NPC ID</t>
+          <t>备注</t>
         </is>
       </c>
     </row>
     <row r="285">
-      <c r="J285" s="0" t="inlineStr">
-        <is>
-          <t>name</t>
-        </is>
-      </c>
-      <c r="L285" s="0" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="N285" s="0" t="inlineStr">
-        <is>
-          <t>显示名</t>
+      <c r="B285" s="0" t="inlineStr">
+        <is>
+          <t>cfg.Npc</t>
+        </is>
+      </c>
+      <c r="G285" s="0" t="inlineStr">
+        <is>
+          <t>NPC记录</t>
+        </is>
+      </c>
+      <c r="I285" s="0" t="inlineStr">
+        <is>
+          <t>c</t>
         </is>
       </c>
     </row>
     <row r="286">
       <c r="J286" s="0" t="inlineStr">
         <is>
-          <t>role</t>
+          <t>id</t>
         </is>
       </c>
       <c r="L286" s="0" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>int</t>
         </is>
       </c>
       <c r="N286" s="0" t="inlineStr">
         <is>
-          <t>身份/职业</t>
+          <t>NPC ID</t>
         </is>
       </c>
     </row>
     <row r="287">
       <c r="J287" s="0" t="inlineStr">
         <is>
-          <t>moveSpeed</t>
+          <t>name</t>
         </is>
       </c>
       <c r="L287" s="0" t="inlineStr">
         <is>
-          <t>float</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N287" s="0" t="inlineStr">
         <is>
-          <t>移动速度(0=站桩)</t>
+          <t>显示名</t>
         </is>
       </c>
     </row>
     <row r="288">
       <c r="J288" s="0" t="inlineStr">
         <is>
-          <t>patrolPath</t>
+          <t>role</t>
         </is>
       </c>
       <c r="L288" s="0" t="inlineStr">
@@ -5959,65 +5961,65 @@
       </c>
       <c r="N288" s="0" t="inlineStr">
         <is>
-          <t>巡逻路径(x,z|x,z 空=不巡逻)</t>
+          <t>身份/职业</t>
         </is>
       </c>
     </row>
     <row r="289">
       <c r="J289" s="0" t="inlineStr">
         <is>
+          <t>moveSpeed</t>
+        </is>
+      </c>
+      <c r="L289" s="0" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="N289" s="0" t="inlineStr">
+        <is>
+          <t>移动速度(0=站桩)</t>
+        </is>
+      </c>
+    </row>
+    <row r="290">
+      <c r="J290" s="0" t="inlineStr">
+        <is>
+          <t>patrolPath</t>
+        </is>
+      </c>
+      <c r="L290" s="0" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="N290" s="0" t="inlineStr">
+        <is>
+          <t>巡逻路径(x,z|x,z 空=不巡逻)</t>
+        </is>
+      </c>
+    </row>
+    <row r="291">
+      <c r="J291" s="0" t="inlineStr">
+        <is>
           <t>dialogueId</t>
         </is>
       </c>
-      <c r="L289" s="0" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="N289" s="0" t="inlineStr">
+      <c r="L291" s="0" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="N291" s="0" t="inlineStr">
         <is>
           <t>对话ID(预留,0=无)</t>
-        </is>
-      </c>
-    </row>
-    <row r="290">
-      <c r="J290" t="inlineStr">
-        <is>
-          <t>consoleType</t>
-        </is>
-      </c>
-      <c r="L290" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="N290" t="inlineStr">
-        <is>
-          <t>操作台类型(0=无 1=技能树)</t>
-        </is>
-      </c>
-    </row>
-    <row r="291">
-      <c r="B291" s="0" t="inlineStr">
-        <is>
-          <t>cfg.Dialogue</t>
-        </is>
-      </c>
-      <c r="G291" s="0" t="inlineStr">
-        <is>
-          <t>对话头</t>
-        </is>
-      </c>
-      <c r="I291" s="0" t="inlineStr">
-        <is>
-          <t>c</t>
         </is>
       </c>
     </row>
     <row r="292">
       <c r="J292" s="0" t="inlineStr">
         <is>
-          <t>id</t>
+          <t>consoleType</t>
         </is>
       </c>
       <c r="L292" s="0" t="inlineStr">
@@ -6027,31 +6029,31 @@
       </c>
       <c r="N292" s="0" t="inlineStr">
         <is>
-          <t>对话ID</t>
+          <t>操作台类型(0=无 1=技能树)</t>
         </is>
       </c>
     </row>
     <row r="293">
-      <c r="J293" s="0" t="inlineStr">
-        <is>
-          <t>name</t>
-        </is>
-      </c>
-      <c r="L293" s="0" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="N293" s="0" t="inlineStr">
-        <is>
-          <t>注释名(不显示)</t>
+      <c r="B293" s="0" t="inlineStr">
+        <is>
+          <t>cfg.Dialogue</t>
+        </is>
+      </c>
+      <c r="G293" s="0" t="inlineStr">
+        <is>
+          <t>对话头</t>
+        </is>
+      </c>
+      <c r="I293" s="0" t="inlineStr">
+        <is>
+          <t>c</t>
         </is>
       </c>
     </row>
     <row r="294">
       <c r="J294" s="0" t="inlineStr">
         <is>
-          <t>startNode</t>
+          <t>id</t>
         </is>
       </c>
       <c r="L294" s="0" t="inlineStr">
@@ -6061,31 +6063,31 @@
       </c>
       <c r="N294" s="0" t="inlineStr">
         <is>
-          <t>起始节点ID</t>
+          <t>对话ID</t>
         </is>
       </c>
     </row>
     <row r="295">
       <c r="J295" s="0" t="inlineStr">
         <is>
-          <t>onceOnly</t>
+          <t>name</t>
         </is>
       </c>
       <c r="L295" s="0" t="inlineStr">
         <is>
-          <t>bool</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N295" s="0" t="inlineStr">
         <is>
-          <t>只触发一次</t>
+          <t>注释名(不显示)</t>
         </is>
       </c>
     </row>
     <row r="296">
       <c r="J296" s="0" t="inlineStr">
         <is>
-          <t>priority</t>
+          <t>startNode</t>
         </is>
       </c>
       <c r="L296" s="0" t="inlineStr">
@@ -6095,31 +6097,31 @@
       </c>
       <c r="N296" s="0" t="inlineStr">
         <is>
-          <t>优先级(大优先)</t>
+          <t>起始节点ID</t>
         </is>
       </c>
     </row>
     <row r="297">
-      <c r="B297" s="0" t="inlineStr">
-        <is>
-          <t>cfg.DialogueNode</t>
-        </is>
-      </c>
-      <c r="G297" s="0" t="inlineStr">
-        <is>
-          <t>对话节点</t>
-        </is>
-      </c>
-      <c r="I297" s="0" t="inlineStr">
-        <is>
-          <t>c</t>
+      <c r="J297" s="0" t="inlineStr">
+        <is>
+          <t>onceOnly</t>
+        </is>
+      </c>
+      <c r="L297" s="0" t="inlineStr">
+        <is>
+          <t>bool</t>
+        </is>
+      </c>
+      <c r="N297" s="0" t="inlineStr">
+        <is>
+          <t>只触发一次</t>
         </is>
       </c>
     </row>
     <row r="298">
       <c r="J298" s="0" t="inlineStr">
         <is>
-          <t>id</t>
+          <t>priority</t>
         </is>
       </c>
       <c r="L298" s="0" t="inlineStr">
@@ -6129,65 +6131,65 @@
       </c>
       <c r="N298" s="0" t="inlineStr">
         <is>
-          <t>节点ID</t>
+          <t>优先级(大优先)</t>
         </is>
       </c>
     </row>
     <row r="299">
-      <c r="J299" s="0" t="inlineStr">
-        <is>
-          <t>dialogueId</t>
-        </is>
-      </c>
-      <c r="L299" s="0" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="N299" s="0" t="inlineStr">
-        <is>
-          <t>所属对话</t>
+      <c r="B299" s="0" t="inlineStr">
+        <is>
+          <t>cfg.DialogueNode</t>
+        </is>
+      </c>
+      <c r="G299" s="0" t="inlineStr">
+        <is>
+          <t>对话节点</t>
+        </is>
+      </c>
+      <c r="I299" s="0" t="inlineStr">
+        <is>
+          <t>c</t>
         </is>
       </c>
     </row>
     <row r="300">
       <c r="J300" s="0" t="inlineStr">
         <is>
-          <t>type</t>
+          <t>id</t>
         </is>
       </c>
       <c r="L300" s="0" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>int</t>
         </is>
       </c>
       <c r="N300" s="0" t="inlineStr">
         <is>
-          <t>类型(line/choice/setflag/end)</t>
+          <t>节点ID</t>
         </is>
       </c>
     </row>
     <row r="301">
       <c r="J301" s="0" t="inlineStr">
         <is>
-          <t>speaker</t>
+          <t>dialogueId</t>
         </is>
       </c>
       <c r="L301" s="0" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>int</t>
         </is>
       </c>
       <c r="N301" s="0" t="inlineStr">
         <is>
-          <t>说话人</t>
+          <t>所属对话</t>
         </is>
       </c>
     </row>
     <row r="302">
       <c r="J302" s="0" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>type</t>
         </is>
       </c>
       <c r="L302" s="0" t="inlineStr">
@@ -6197,14 +6199,14 @@
       </c>
       <c r="N302" s="0" t="inlineStr">
         <is>
-          <t>正文</t>
+          <t>类型(line/choice/setflag/end)</t>
         </is>
       </c>
     </row>
     <row r="303">
       <c r="J303" s="0" t="inlineStr">
         <is>
-          <t>choices</t>
+          <t>speaker</t>
         </is>
       </c>
       <c r="L303" s="0" t="inlineStr">
@@ -6214,14 +6216,14 @@
       </c>
       <c r="N303" s="0" t="inlineStr">
         <is>
-          <t>选项(文本-&gt;节点|...)</t>
+          <t>说话人</t>
         </is>
       </c>
     </row>
     <row r="304">
       <c r="J304" s="0" t="inlineStr">
         <is>
-          <t>condition</t>
+          <t>text</t>
         </is>
       </c>
       <c r="L304" s="0" t="inlineStr">
@@ -6231,14 +6233,14 @@
       </c>
       <c r="N304" s="0" t="inlineStr">
         <is>
-          <t>进入条件</t>
+          <t>正文</t>
         </is>
       </c>
     </row>
     <row r="305">
       <c r="J305" s="0" t="inlineStr">
         <is>
-          <t>action</t>
+          <t>choices</t>
         </is>
       </c>
       <c r="L305" s="0" t="inlineStr">
@@ -6248,31 +6250,31 @@
       </c>
       <c r="N305" s="0" t="inlineStr">
         <is>
-          <t>到达动作</t>
+          <t>选项(文本-&gt;节点|...)</t>
         </is>
       </c>
     </row>
     <row r="306">
       <c r="J306" s="0" t="inlineStr">
         <is>
-          <t>next</t>
+          <t>condition</t>
         </is>
       </c>
       <c r="L306" s="0" t="inlineStr">
         <is>
-          <t>int</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N306" s="0" t="inlineStr">
         <is>
-          <t>下一节点(0=结束)</t>
+          <t>进入条件</t>
         </is>
       </c>
     </row>
     <row r="307">
       <c r="J307" s="0" t="inlineStr">
         <is>
-          <t>voiceClip</t>
+          <t>action</t>
         </is>
       </c>
       <c r="L307" s="0" t="inlineStr">
@@ -6280,96 +6282,96 @@
           <t>string</t>
         </is>
       </c>
+      <c r="N307" s="0" t="inlineStr">
+        <is>
+          <t>到达动作</t>
+        </is>
+      </c>
     </row>
     <row r="308">
-      <c r="B308" s="0" t="inlineStr">
-        <is>
-          <t>cfg.Quest</t>
-        </is>
-      </c>
-      <c r="G308" s="0" t="inlineStr">
-        <is>
-          <t>任务定义</t>
-        </is>
-      </c>
-      <c r="I308" s="0" t="inlineStr">
-        <is>
-          <t>c</t>
+      <c r="J308" s="0" t="inlineStr">
+        <is>
+          <t>next</t>
+        </is>
+      </c>
+      <c r="L308" s="0" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="N308" s="0" t="inlineStr">
+        <is>
+          <t>下一节点(0=结束)</t>
         </is>
       </c>
     </row>
     <row r="309">
       <c r="J309" s="0" t="inlineStr">
         <is>
-          <t>id</t>
+          <t>voiceClip</t>
         </is>
       </c>
       <c r="L309" s="0" t="inlineStr">
         <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="N309" s="0" t="inlineStr">
-        <is>
-          <t>任务ID</t>
+          <t>string</t>
         </is>
       </c>
     </row>
     <row r="310">
-      <c r="J310" s="0" t="inlineStr">
-        <is>
-          <t>name</t>
-        </is>
-      </c>
-      <c r="L310" s="0" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="N310" s="0" t="inlineStr">
-        <is>
-          <t>显示名</t>
+      <c r="B310" s="0" t="inlineStr">
+        <is>
+          <t>cfg.Quest</t>
+        </is>
+      </c>
+      <c r="G310" s="0" t="inlineStr">
+        <is>
+          <t>任务定义</t>
+        </is>
+      </c>
+      <c r="I310" s="0" t="inlineStr">
+        <is>
+          <t>c</t>
         </is>
       </c>
     </row>
     <row r="311">
       <c r="J311" s="0" t="inlineStr">
         <is>
-          <t>desc</t>
+          <t>id</t>
         </is>
       </c>
       <c r="L311" s="0" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>int</t>
         </is>
       </c>
       <c r="N311" s="0" t="inlineStr">
         <is>
-          <t>描述</t>
+          <t>任务ID</t>
         </is>
       </c>
     </row>
     <row r="312">
       <c r="J312" s="0" t="inlineStr">
         <is>
-          <t>giverNpc</t>
+          <t>name</t>
         </is>
       </c>
       <c r="L312" s="0" t="inlineStr">
         <is>
-          <t>int</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N312" s="0" t="inlineStr">
         <is>
-          <t>发布NPC(0=任务板)</t>
+          <t>显示名</t>
         </is>
       </c>
     </row>
     <row r="313">
       <c r="J313" s="0" t="inlineStr">
         <is>
-          <t>prereq</t>
+          <t>desc</t>
         </is>
       </c>
       <c r="L313" s="0" t="inlineStr">
@@ -6379,65 +6381,65 @@
       </c>
       <c r="N313" s="0" t="inlineStr">
         <is>
-          <t>接取条件表达式(空=无)</t>
+          <t>描述</t>
         </is>
       </c>
     </row>
     <row r="314">
       <c r="J314" s="0" t="inlineStr">
         <is>
-          <t>rewards</t>
+          <t>giverNpc</t>
         </is>
       </c>
       <c r="L314" s="0" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>int</t>
         </is>
       </c>
       <c r="N314" s="0" t="inlineStr">
         <is>
-          <t>奖励(gold:200|exp:50|item:3001:2)</t>
+          <t>发布NPC(0=任务板)</t>
         </is>
       </c>
     </row>
     <row r="315">
       <c r="J315" s="0" t="inlineStr">
         <is>
-          <t>nextQuest</t>
+          <t>prereq</t>
         </is>
       </c>
       <c r="L315" s="0" t="inlineStr">
         <is>
-          <t>int</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N315" s="0" t="inlineStr">
         <is>
-          <t>后继任务(0=无)</t>
+          <t>接取条件表达式(空=无)</t>
         </is>
       </c>
     </row>
     <row r="316">
-      <c r="B316" s="0" t="inlineStr">
-        <is>
-          <t>cfg.QuestObjective</t>
-        </is>
-      </c>
-      <c r="G316" s="0" t="inlineStr">
-        <is>
-          <t>任务目标</t>
-        </is>
-      </c>
-      <c r="I316" s="0" t="inlineStr">
-        <is>
-          <t>c</t>
+      <c r="J316" s="0" t="inlineStr">
+        <is>
+          <t>rewards</t>
+        </is>
+      </c>
+      <c r="L316" s="0" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="N316" s="0" t="inlineStr">
+        <is>
+          <t>奖励(gold:200|exp:50|item:3001:2)</t>
         </is>
       </c>
     </row>
     <row r="317">
       <c r="J317" s="0" t="inlineStr">
         <is>
-          <t>id</t>
+          <t>nextQuest</t>
         </is>
       </c>
       <c r="L317" s="0" t="inlineStr">
@@ -6447,82 +6449,82 @@
       </c>
       <c r="N317" s="0" t="inlineStr">
         <is>
-          <t>目标ID</t>
+          <t>后继任务(0=无)</t>
         </is>
       </c>
     </row>
     <row r="318">
-      <c r="J318" s="0" t="inlineStr">
-        <is>
-          <t>questId</t>
-        </is>
-      </c>
-      <c r="L318" s="0" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="N318" s="0" t="inlineStr">
-        <is>
-          <t>所属任务</t>
+      <c r="B318" s="0" t="inlineStr">
+        <is>
+          <t>cfg.QuestObjective</t>
+        </is>
+      </c>
+      <c r="G318" s="0" t="inlineStr">
+        <is>
+          <t>任务目标</t>
+        </is>
+      </c>
+      <c r="I318" s="0" t="inlineStr">
+        <is>
+          <t>c</t>
         </is>
       </c>
     </row>
     <row r="319">
       <c r="J319" s="0" t="inlineStr">
         <is>
-          <t>type</t>
+          <t>id</t>
         </is>
       </c>
       <c r="L319" s="0" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>int</t>
         </is>
       </c>
       <c r="N319" s="0" t="inlineStr">
         <is>
-          <t>类型(kill/collect/extract/flag)</t>
+          <t>目标ID</t>
         </is>
       </c>
     </row>
     <row r="320">
       <c r="J320" s="0" t="inlineStr">
         <is>
-          <t>targetId</t>
+          <t>questId</t>
         </is>
       </c>
       <c r="L320" s="0" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>int</t>
         </is>
       </c>
       <c r="N320" s="0" t="inlineStr">
         <is>
-          <t>目标ID/标志键</t>
+          <t>所属任务</t>
         </is>
       </c>
     </row>
     <row r="321">
       <c r="J321" s="0" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>type</t>
         </is>
       </c>
       <c r="L321" s="0" t="inlineStr">
         <is>
-          <t>int</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N321" s="0" t="inlineStr">
         <is>
-          <t>需求数(extract恒1)</t>
+          <t>类型(kill/collect/extract/flag)</t>
         </is>
       </c>
     </row>
     <row r="322">
       <c r="J322" s="0" t="inlineStr">
         <is>
-          <t>desc</t>
+          <t>targetId</t>
         </is>
       </c>
       <c r="L322" s="0" t="inlineStr">
@@ -6532,31 +6534,31 @@
       </c>
       <c r="N322" s="0" t="inlineStr">
         <is>
-          <t>目标一行描述</t>
+          <t>目标ID/标志键</t>
         </is>
       </c>
     </row>
     <row r="323">
-      <c r="B323" s="0" t="inlineStr">
-        <is>
-          <t>cfg.Localization</t>
-        </is>
-      </c>
-      <c r="G323" s="0" t="inlineStr">
-        <is>
-          <t>本地化词条</t>
-        </is>
-      </c>
-      <c r="I323" s="0" t="inlineStr">
-        <is>
-          <t>c</t>
+      <c r="J323" s="0" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="L323" s="0" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="N323" s="0" t="inlineStr">
+        <is>
+          <t>需求数(extract恒1)</t>
         </is>
       </c>
     </row>
     <row r="324">
       <c r="J324" s="0" t="inlineStr">
         <is>
-          <t>key</t>
+          <t>desc</t>
         </is>
       </c>
       <c r="L324" s="0" t="inlineStr">
@@ -6566,31 +6568,31 @@
       </c>
       <c r="N324" s="0" t="inlineStr">
         <is>
-          <t>词条Key</t>
+          <t>目标一行描述</t>
         </is>
       </c>
     </row>
     <row r="325">
-      <c r="J325" s="0" t="inlineStr">
-        <is>
-          <t>en</t>
-        </is>
-      </c>
-      <c r="L325" s="0" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="N325" s="0" t="inlineStr">
-        <is>
-          <t>英文(必填/兜底)</t>
+      <c r="B325" s="0" t="inlineStr">
+        <is>
+          <t>cfg.Localization</t>
+        </is>
+      </c>
+      <c r="G325" s="0" t="inlineStr">
+        <is>
+          <t>本地化词条</t>
+        </is>
+      </c>
+      <c r="I325" s="0" t="inlineStr">
+        <is>
+          <t>c</t>
         </is>
       </c>
     </row>
     <row r="326">
       <c r="J326" s="0" t="inlineStr">
         <is>
-          <t>zh_cn</t>
+          <t>key</t>
         </is>
       </c>
       <c r="L326" s="0" t="inlineStr">
@@ -6600,14 +6602,14 @@
       </c>
       <c r="N326" s="0" t="inlineStr">
         <is>
-          <t>简体中文</t>
+          <t>词条Key</t>
         </is>
       </c>
     </row>
     <row r="327">
       <c r="J327" s="0" t="inlineStr">
         <is>
-          <t>zh_tw</t>
+          <t>en</t>
         </is>
       </c>
       <c r="L327" s="0" t="inlineStr">
@@ -6617,14 +6619,14 @@
       </c>
       <c r="N327" s="0" t="inlineStr">
         <is>
-          <t>繁体中文</t>
+          <t>英文(必填/兜底)</t>
         </is>
       </c>
     </row>
     <row r="328">
       <c r="J328" s="0" t="inlineStr">
         <is>
-          <t>ja</t>
+          <t>zh_cn</t>
         </is>
       </c>
       <c r="L328" s="0" t="inlineStr">
@@ -6634,14 +6636,14 @@
       </c>
       <c r="N328" s="0" t="inlineStr">
         <is>
-          <t>日文</t>
+          <t>简体中文</t>
         </is>
       </c>
     </row>
     <row r="329">
       <c r="J329" s="0" t="inlineStr">
         <is>
-          <t>ko</t>
+          <t>zh_tw</t>
         </is>
       </c>
       <c r="L329" s="0" t="inlineStr">
@@ -6651,150 +6653,150 @@
       </c>
       <c r="N329" s="0" t="inlineStr">
         <is>
-          <t>韩文</t>
+          <t>繁体中文</t>
         </is>
       </c>
     </row>
     <row r="330">
-      <c r="B330" s="0" t="inlineStr">
-        <is>
-          <t>cfg.Companion</t>
-        </is>
-      </c>
-      <c r="G330" s="0" t="inlineStr">
-        <is>
-          <t>队友人设卡</t>
-        </is>
-      </c>
-      <c r="H330" s="0" t="inlineStr">
-        <is>
-          <t>c</t>
+      <c r="J330" s="0" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="L330" s="0" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="N330" s="0" t="inlineStr">
+        <is>
+          <t>日文</t>
         </is>
       </c>
     </row>
     <row r="331">
       <c r="J331" s="0" t="inlineStr">
         <is>
-          <t>id</t>
+          <t>ko</t>
         </is>
       </c>
       <c r="L331" s="0" t="inlineStr">
         <is>
-          <t>int</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N331" s="0" t="inlineStr">
         <is>
-          <t>队友ID</t>
+          <t>韩文</t>
         </is>
       </c>
     </row>
     <row r="332">
-      <c r="J332" s="0" t="inlineStr">
-        <is>
-          <t>nameKey</t>
-        </is>
-      </c>
-      <c r="L332" s="0" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="N332" s="0" t="inlineStr">
-        <is>
-          <t>呼号本地化键</t>
+      <c r="B332" s="0" t="inlineStr">
+        <is>
+          <t>cfg.Companion</t>
+        </is>
+      </c>
+      <c r="G332" s="0" t="inlineStr">
+        <is>
+          <t>队友人设卡</t>
+        </is>
+      </c>
+      <c r="H332" s="0" t="inlineStr">
+        <is>
+          <t>c</t>
         </is>
       </c>
     </row>
     <row r="333">
       <c r="J333" s="0" t="inlineStr">
         <is>
-          <t>personaPrompt</t>
+          <t>id</t>
         </is>
       </c>
       <c r="L333" s="0" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>int</t>
         </is>
       </c>
       <c r="N333" s="0" t="inlineStr">
         <is>
-          <t>LLM 人设 system prompt(英文)</t>
+          <t>队友ID</t>
         </is>
       </c>
     </row>
     <row r="334">
       <c r="J334" s="0" t="inlineStr">
         <is>
-          <t>weaponConfigId</t>
+          <t>nameKey</t>
         </is>
       </c>
       <c r="L334" s="0" t="inlineStr">
         <is>
-          <t>int</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N334" s="0" t="inlineStr">
         <is>
-          <t>持有武器</t>
+          <t>呼号本地化键</t>
         </is>
       </c>
     </row>
     <row r="335">
       <c r="J335" s="0" t="inlineStr">
         <is>
-          <t>maxHp</t>
+          <t>personaPrompt</t>
         </is>
       </c>
       <c r="L335" s="0" t="inlineStr">
         <is>
-          <t>int</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N335" s="0" t="inlineStr">
         <is>
-          <t>最大HP</t>
+          <t>LLM 人设 system prompt(英文)</t>
         </is>
       </c>
     </row>
     <row r="336">
       <c r="J336" s="0" t="inlineStr">
         <is>
-          <t>moveSpeed</t>
+          <t>weaponConfigId</t>
         </is>
       </c>
       <c r="L336" s="0" t="inlineStr">
         <is>
-          <t>float</t>
+          <t>int</t>
         </is>
       </c>
       <c r="N336" s="0" t="inlineStr">
         <is>
-          <t>移动速度</t>
+          <t>持有武器</t>
         </is>
       </c>
     </row>
     <row r="337">
       <c r="J337" s="0" t="inlineStr">
         <is>
-          <t>followStopDist</t>
+          <t>maxHp</t>
         </is>
       </c>
       <c r="L337" s="0" t="inlineStr">
         <is>
-          <t>float</t>
+          <t>int</t>
         </is>
       </c>
       <c r="N337" s="0" t="inlineStr">
         <is>
-          <t>跟随到位距离</t>
+          <t>最大HP</t>
         </is>
       </c>
     </row>
     <row r="338">
       <c r="J338" s="0" t="inlineStr">
         <is>
-          <t>engageMinDist</t>
+          <t>moveSpeed</t>
         </is>
       </c>
       <c r="L338" s="0" t="inlineStr">
@@ -6804,14 +6806,14 @@
       </c>
       <c r="N338" s="0" t="inlineStr">
         <is>
-          <t>最小交战距离</t>
+          <t>移动速度</t>
         </is>
       </c>
     </row>
     <row r="339">
       <c r="J339" s="0" t="inlineStr">
         <is>
-          <t>retreatHpRatio</t>
+          <t>followStopDist</t>
         </is>
       </c>
       <c r="L339" s="0" t="inlineStr">
@@ -6821,14 +6823,14 @@
       </c>
       <c r="N339" s="0" t="inlineStr">
         <is>
-          <t>撤退血量比例</t>
+          <t>跟随到位距离</t>
         </is>
       </c>
     </row>
     <row r="340">
       <c r="J340" s="0" t="inlineStr">
         <is>
-          <t>idleChatMinInterval</t>
+          <t>engageMinDist</t>
         </is>
       </c>
       <c r="L340" s="0" t="inlineStr">
@@ -6838,14 +6840,14 @@
       </c>
       <c r="N340" s="0" t="inlineStr">
         <is>
-          <t>安全闲聊最小间隔s</t>
+          <t>最小交战距离</t>
         </is>
       </c>
     </row>
     <row r="341">
       <c r="J341" s="0" t="inlineStr">
         <is>
-          <t>idleChatMaxInterval</t>
+          <t>retreatHpRatio</t>
         </is>
       </c>
       <c r="L341" s="0" t="inlineStr">
@@ -6855,14 +6857,14 @@
       </c>
       <c r="N341" s="0" t="inlineStr">
         <is>
-          <t>安全闲聊最大间隔s</t>
+          <t>撤退血量比例</t>
         </is>
       </c>
     </row>
     <row r="342">
       <c r="J342" s="0" t="inlineStr">
         <is>
-          <t>llmRequestInterval</t>
+          <t>idleChatMinInterval</t>
         </is>
       </c>
       <c r="L342" s="0" t="inlineStr">
@@ -6872,31 +6874,31 @@
       </c>
       <c r="N342" s="0" t="inlineStr">
         <is>
-          <t>LLM 全局最小请求间隔s</t>
+          <t>安全闲聊最小间隔s</t>
         </is>
       </c>
     </row>
     <row r="343">
       <c r="J343" s="0" t="inlineStr">
         <is>
-          <t>llmBudgetPerRun</t>
+          <t>idleChatMaxInterval</t>
         </is>
       </c>
       <c r="L343" s="0" t="inlineStr">
         <is>
-          <t>int</t>
+          <t>float</t>
         </is>
       </c>
       <c r="N343" s="0" t="inlineStr">
         <is>
-          <t>单局 LLM 请求限额</t>
+          <t>安全闲聊最大间隔s</t>
         </is>
       </c>
     </row>
     <row r="344">
       <c r="J344" s="0" t="inlineStr">
         <is>
-          <t>llmTimeout</t>
+          <t>llmRequestInterval</t>
         </is>
       </c>
       <c r="L344" s="0" t="inlineStr">
@@ -6906,31 +6908,31 @@
       </c>
       <c r="N344" s="0" t="inlineStr">
         <is>
-          <t>LLM 超时s</t>
+          <t>LLM 全局最小请求间隔s</t>
         </is>
       </c>
     </row>
     <row r="345">
       <c r="J345" s="0" t="inlineStr">
         <is>
-          <t>intentTtl</t>
+          <t>llmBudgetPerRun</t>
         </is>
       </c>
       <c r="L345" s="0" t="inlineStr">
         <is>
-          <t>float</t>
+          <t>int</t>
         </is>
       </c>
       <c r="N345" s="0" t="inlineStr">
         <is>
-          <t>意图 TTL s</t>
+          <t>单局 LLM 请求限额</t>
         </is>
       </c>
     </row>
     <row r="346">
       <c r="J346" s="0" t="inlineStr">
         <is>
-          <t>offlineProbeInterval</t>
+          <t>llmTimeout</t>
         </is>
       </c>
       <c r="L346" s="0" t="inlineStr">
@@ -6940,14 +6942,14 @@
       </c>
       <c r="N346" s="0" t="inlineStr">
         <is>
-          <t>离线恢复探测间隔s</t>
+          <t>LLM 超时s</t>
         </is>
       </c>
     </row>
     <row r="347">
       <c r="J347" s="0" t="inlineStr">
         <is>
-          <t>decisionIntervalSafe</t>
+          <t>intentTtl</t>
         </is>
       </c>
       <c r="L347" s="0" t="inlineStr">
@@ -6957,14 +6959,14 @@
       </c>
       <c r="N347" s="0" t="inlineStr">
         <is>
-          <t>安全决策间隔s(M5)</t>
+          <t>意图 TTL s</t>
         </is>
       </c>
     </row>
     <row r="348">
       <c r="J348" s="0" t="inlineStr">
         <is>
-          <t>decisionIntervalCombat</t>
+          <t>offlineProbeInterval</t>
         </is>
       </c>
       <c r="L348" s="0" t="inlineStr">
@@ -6974,14 +6976,14 @@
       </c>
       <c r="N348" s="0" t="inlineStr">
         <is>
-          <t>战斗决策间隔s(M5)</t>
+          <t>离线恢复探测间隔s</t>
         </is>
       </c>
     </row>
     <row r="349">
       <c r="J349" s="0" t="inlineStr">
         <is>
-          <t>decisionTimeout</t>
+          <t>decisionIntervalSafe</t>
         </is>
       </c>
       <c r="L349" s="0" t="inlineStr">
@@ -6991,31 +6993,31 @@
       </c>
       <c r="N349" s="0" t="inlineStr">
         <is>
-          <t>决策响应超时s(M5)</t>
+          <t>安全决策间隔s(M5)</t>
         </is>
       </c>
     </row>
     <row r="350">
       <c r="J350" s="0" t="inlineStr">
         <is>
-          <t>controlBudgetPerRun</t>
+          <t>decisionIntervalCombat</t>
         </is>
       </c>
       <c r="L350" s="0" t="inlineStr">
         <is>
-          <t>int</t>
+          <t>float</t>
         </is>
       </c>
       <c r="N350" s="0" t="inlineStr">
         <is>
-          <t>单局操控决策限额(M5)</t>
+          <t>战斗决策间隔s(M5)</t>
         </is>
       </c>
     </row>
     <row r="351">
       <c r="J351" s="0" t="inlineStr">
         <is>
-          <t>proactiveEngageDist</t>
+          <t>decisionTimeout</t>
         </is>
       </c>
       <c r="L351" s="0" t="inlineStr">
@@ -7025,38 +7027,48 @@
       </c>
       <c r="N351" s="0" t="inlineStr">
         <is>
-          <t>主动开火警戒半径m</t>
+          <t>决策响应超时s(M5)</t>
         </is>
       </c>
     </row>
     <row r="352">
       <c r="J352" s="0" t="inlineStr">
         <is>
-          <t>conversationHold</t>
+          <t>controlBudgetPerRun</t>
         </is>
       </c>
       <c r="L352" s="0" t="inlineStr">
         <is>
-          <t>float</t>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="N352" s="0" t="inlineStr">
+        <is>
+          <t>单局操控决策限额(M5)</t>
         </is>
       </c>
     </row>
     <row r="353">
       <c r="J353" s="0" t="inlineStr">
         <is>
-          <t>postCombatCalm</t>
+          <t>proactiveEngageDist</t>
         </is>
       </c>
       <c r="L353" s="0" t="inlineStr">
         <is>
           <t>float</t>
+        </is>
+      </c>
+      <c r="N353" s="0" t="inlineStr">
+        <is>
+          <t>主动开火警戒半径m</t>
         </is>
       </c>
     </row>
     <row r="354">
       <c r="J354" s="0" t="inlineStr">
         <is>
-          <t>dirHintInterval</t>
+          <t>conversationHold</t>
         </is>
       </c>
       <c r="L354" s="0" t="inlineStr">
@@ -7068,19 +7080,19 @@
     <row r="355">
       <c r="J355" s="0" t="inlineStr">
         <is>
-          <t>offlineFailThreshold</t>
+          <t>postCombatCalm</t>
         </is>
       </c>
       <c r="L355" s="0" t="inlineStr">
         <is>
-          <t>int</t>
+          <t>float</t>
         </is>
       </c>
     </row>
     <row r="356">
       <c r="J356" s="0" t="inlineStr">
         <is>
-          <t>decisionSayInterval</t>
+          <t>dirHintInterval</t>
         </is>
       </c>
       <c r="L356" s="0" t="inlineStr">
@@ -7092,7 +7104,7 @@
     <row r="357">
       <c r="J357" s="0" t="inlineStr">
         <is>
-          <t>maxReportEntries</t>
+          <t>offlineFailThreshold</t>
         </is>
       </c>
       <c r="L357" s="0" t="inlineStr">
@@ -7104,7 +7116,7 @@
     <row r="358">
       <c r="J358" s="0" t="inlineStr">
         <is>
-          <t>leashDist</t>
+          <t>decisionSayInterval</t>
         </is>
       </c>
       <c r="L358" s="0" t="inlineStr">
@@ -7116,19 +7128,19 @@
     <row r="359">
       <c r="J359" s="0" t="inlineStr">
         <is>
-          <t>leashStopDist</t>
+          <t>maxReportEntries</t>
         </is>
       </c>
       <c r="L359" s="0" t="inlineStr">
         <is>
-          <t>float</t>
+          <t>int</t>
         </is>
       </c>
     </row>
     <row r="360">
       <c r="J360" s="0" t="inlineStr">
         <is>
-          <t>spawnOffsetX</t>
+          <t>leashDist</t>
         </is>
       </c>
       <c r="L360" s="0" t="inlineStr">
@@ -7140,7 +7152,7 @@
     <row r="361">
       <c r="J361" s="0" t="inlineStr">
         <is>
-          <t>spawnOffsetZ</t>
+          <t>leashStopDist</t>
         </is>
       </c>
       <c r="L361" s="0" t="inlineStr">
@@ -7150,200 +7162,205 @@
       </c>
     </row>
     <row r="362">
-      <c r="B362" s="0" t="inlineStr">
-        <is>
-          <t>cfg.CompanionBark</t>
-        </is>
-      </c>
-      <c r="G362" s="0" t="inlineStr">
-        <is>
-          <t>队友本地台词</t>
-        </is>
-      </c>
-      <c r="H362" s="0" t="inlineStr">
-        <is>
-          <t>c</t>
+      <c r="J362" s="0" t="inlineStr">
+        <is>
+          <t>spawnOffsetX</t>
+        </is>
+      </c>
+      <c r="L362" s="0" t="inlineStr">
+        <is>
+          <t>float</t>
         </is>
       </c>
     </row>
     <row r="363">
       <c r="J363" s="0" t="inlineStr">
         <is>
-          <t>id</t>
+          <t>spawnOffsetZ</t>
         </is>
       </c>
       <c r="L363" s="0" t="inlineStr">
         <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="N363" s="0" t="inlineStr">
-        <is>
-          <t>ID</t>
+          <t>float</t>
         </is>
       </c>
     </row>
     <row r="364">
-      <c r="J364" s="0" t="inlineStr">
-        <is>
-          <t>trigger</t>
-        </is>
-      </c>
-      <c r="L364" s="0" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="N364" s="0" t="inlineStr">
-        <is>
-          <t>触发键</t>
+      <c r="B364" s="0" t="inlineStr">
+        <is>
+          <t>cfg.CompanionBark</t>
+        </is>
+      </c>
+      <c r="G364" s="0" t="inlineStr">
+        <is>
+          <t>队友本地台词</t>
+        </is>
+      </c>
+      <c r="H364" s="0" t="inlineStr">
+        <is>
+          <t>c</t>
         </is>
       </c>
     </row>
     <row r="365">
       <c r="J365" s="0" t="inlineStr">
         <is>
-          <t>textKey</t>
+          <t>id</t>
         </is>
       </c>
       <c r="L365" s="0" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>int</t>
         </is>
       </c>
       <c r="N365" s="0" t="inlineStr">
         <is>
-          <t>台词本地化键</t>
+          <t>ID</t>
         </is>
       </c>
     </row>
     <row r="366">
       <c r="J366" s="0" t="inlineStr">
         <is>
-          <t>weight</t>
+          <t>trigger</t>
         </is>
       </c>
       <c r="L366" s="0" t="inlineStr">
         <is>
-          <t>int</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N366" s="0" t="inlineStr">
         <is>
-          <t>随机权重</t>
+          <t>触发键</t>
         </is>
       </c>
     </row>
     <row r="367">
       <c r="J367" s="0" t="inlineStr">
         <is>
-          <t>cooldown</t>
+          <t>textKey</t>
         </is>
       </c>
       <c r="L367" s="0" t="inlineStr">
         <is>
-          <t>float</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N367" s="0" t="inlineStr">
         <is>
-          <t>单键冷却s(0=不限)</t>
+          <t>台词本地化键</t>
         </is>
       </c>
     </row>
     <row r="368">
-      <c r="B368" s="0" t="inlineStr">
-        <is>
-          <t>cfg.Audio</t>
-        </is>
-      </c>
-      <c r="G368" s="0" t="inlineStr">
-        <is>
-          <t>音频条目</t>
-        </is>
-      </c>
-      <c r="H368" s="0" t="inlineStr">
-        <is>
-          <t>c</t>
+      <c r="J368" s="0" t="inlineStr">
+        <is>
+          <t>weight</t>
+        </is>
+      </c>
+      <c r="L368" s="0" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="N368" s="0" t="inlineStr">
+        <is>
+          <t>随机权重</t>
         </is>
       </c>
     </row>
     <row r="369">
       <c r="J369" s="0" t="inlineStr">
         <is>
-          <t>id</t>
+          <t>cooldown</t>
         </is>
       </c>
       <c r="L369" s="0" t="inlineStr">
         <is>
-          <t>int</t>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="N369" s="0" t="inlineStr">
+        <is>
+          <t>单键冷却s(0=不限)</t>
         </is>
       </c>
     </row>
     <row r="370">
-      <c r="J370" s="0" t="inlineStr">
-        <is>
-          <t>name</t>
-        </is>
-      </c>
-      <c r="L370" s="0" t="inlineStr">
-        <is>
-          <t>string</t>
+      <c r="J370" t="inlineStr">
+        <is>
+          <t>minTier</t>
+        </is>
+      </c>
+      <c r="L370" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="N370" t="inlineStr">
+        <is>
+          <t>最低好感档位(1-4)</t>
         </is>
       </c>
     </row>
     <row r="371">
-      <c r="J371" s="0" t="inlineStr">
-        <is>
-          <t>audioType</t>
-        </is>
-      </c>
-      <c r="L371" s="0" t="inlineStr">
-        <is>
-          <t>string</t>
+      <c r="B371" s="0" t="inlineStr">
+        <is>
+          <t>cfg.Audio</t>
+        </is>
+      </c>
+      <c r="G371" s="0" t="inlineStr">
+        <is>
+          <t>音频条目</t>
+        </is>
+      </c>
+      <c r="H371" s="0" t="inlineStr">
+        <is>
+          <t>c</t>
         </is>
       </c>
     </row>
     <row r="372">
       <c r="J372" s="0" t="inlineStr">
         <is>
-          <t>volume</t>
+          <t>id</t>
         </is>
       </c>
       <c r="L372" s="0" t="inlineStr">
         <is>
-          <t>float</t>
+          <t>int</t>
         </is>
       </c>
     </row>
     <row r="373">
       <c r="J373" s="0" t="inlineStr">
         <is>
-          <t>loop</t>
+          <t>name</t>
         </is>
       </c>
       <c r="L373" s="0" t="inlineStr">
         <is>
-          <t>bool</t>
+          <t>string</t>
         </is>
       </c>
     </row>
     <row r="374">
       <c r="J374" s="0" t="inlineStr">
         <is>
-          <t>spatial</t>
+          <t>audioType</t>
         </is>
       </c>
       <c r="L374" s="0" t="inlineStr">
         <is>
-          <t>bool</t>
+          <t>string</t>
         </is>
       </c>
     </row>
     <row r="375">
       <c r="J375" s="0" t="inlineStr">
         <is>
-          <t>minDist</t>
+          <t>volume</t>
         </is>
       </c>
       <c r="L375" s="0" t="inlineStr">
@@ -7355,65 +7372,55 @@
     <row r="376">
       <c r="J376" s="0" t="inlineStr">
         <is>
-          <t>maxDist</t>
+          <t>loop</t>
         </is>
       </c>
       <c r="L376" s="0" t="inlineStr">
         <is>
-          <t>float</t>
+          <t>bool</t>
         </is>
       </c>
     </row>
     <row r="377">
       <c r="J377" s="0" t="inlineStr">
         <is>
-          <t>sceneKey</t>
+          <t>spatial</t>
         </is>
       </c>
       <c r="L377" s="0" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>bool</t>
         </is>
       </c>
     </row>
     <row r="378">
-      <c r="B378" s="0" t="inlineStr">
-        <is>
-          <t>cfg.Skill</t>
-        </is>
-      </c>
-      <c r="G378" s="0" t="inlineStr">
-        <is>
-          <t>技能节点</t>
-        </is>
-      </c>
-      <c r="I378" s="0" t="inlineStr">
-        <is>
-          <t>c</t>
+      <c r="J378" s="0" t="inlineStr">
+        <is>
+          <t>minDist</t>
+        </is>
+      </c>
+      <c r="L378" s="0" t="inlineStr">
+        <is>
+          <t>float</t>
         </is>
       </c>
     </row>
     <row r="379">
       <c r="J379" s="0" t="inlineStr">
         <is>
-          <t>id</t>
+          <t>maxDist</t>
         </is>
       </c>
       <c r="L379" s="0" t="inlineStr">
         <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="N379" s="0" t="inlineStr">
-        <is>
-          <t>技能ID</t>
+          <t>float</t>
         </is>
       </c>
     </row>
     <row r="380">
       <c r="J380" s="0" t="inlineStr">
         <is>
-          <t>nameKey</t>
+          <t>sceneKey</t>
         </is>
       </c>
       <c r="L380" s="0" t="inlineStr">
@@ -7421,33 +7428,28 @@
           <t>string</t>
         </is>
       </c>
-      <c r="N380" s="0" t="inlineStr">
-        <is>
-          <t>名称词条键</t>
-        </is>
-      </c>
     </row>
     <row r="381">
-      <c r="J381" s="0" t="inlineStr">
-        <is>
-          <t>descKey</t>
-        </is>
-      </c>
-      <c r="L381" s="0" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="N381" s="0" t="inlineStr">
-        <is>
-          <t>描述词条键</t>
+      <c r="B381" s="0" t="inlineStr">
+        <is>
+          <t>cfg.Skill</t>
+        </is>
+      </c>
+      <c r="G381" s="0" t="inlineStr">
+        <is>
+          <t>技能节点</t>
+        </is>
+      </c>
+      <c r="I381" s="0" t="inlineStr">
+        <is>
+          <t>c</t>
         </is>
       </c>
     </row>
     <row r="382">
       <c r="J382" s="0" t="inlineStr">
         <is>
-          <t>branch</t>
+          <t>id</t>
         </is>
       </c>
       <c r="L382" s="0" t="inlineStr">
@@ -7457,160 +7459,585 @@
       </c>
       <c r="N382" s="0" t="inlineStr">
         <is>
-          <t>分支(1战斗2生存3经营)</t>
+          <t>技能ID</t>
         </is>
       </c>
     </row>
     <row r="383">
       <c r="J383" s="0" t="inlineStr">
         <is>
-          <t>maxLevel</t>
+          <t>nameKey</t>
         </is>
       </c>
       <c r="L383" s="0" t="inlineStr">
         <is>
-          <t>int</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N383" s="0" t="inlineStr">
         <is>
-          <t>最大等级</t>
+          <t>名称词条键</t>
         </is>
       </c>
     </row>
     <row r="384">
       <c r="J384" s="0" t="inlineStr">
         <is>
-          <t>effectType</t>
+          <t>descKey</t>
         </is>
       </c>
       <c r="L384" s="0" t="inlineStr">
         <is>
-          <t>cfg.ESkillEffect</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N384" s="0" t="inlineStr">
         <is>
-          <t>效果类型</t>
+          <t>描述词条键</t>
         </is>
       </c>
     </row>
     <row r="385">
       <c r="J385" s="0" t="inlineStr">
         <is>
-          <t>effectValue</t>
+          <t>branch</t>
         </is>
       </c>
       <c r="L385" s="0" t="inlineStr">
         <is>
-          <t>float</t>
+          <t>int</t>
         </is>
       </c>
       <c r="N385" s="0" t="inlineStr">
         <is>
-          <t>每级效果值</t>
+          <t>分支(1战斗2生存3经营)</t>
         </is>
       </c>
     </row>
     <row r="386">
       <c r="J386" s="0" t="inlineStr">
         <is>
-          <t>costItems</t>
+          <t>maxLevel</t>
         </is>
       </c>
       <c r="L386" s="0" t="inlineStr">
         <is>
-          <t>(list#sep=;),cfg.ItemExchange#sep=,</t>
+          <t>int</t>
         </is>
       </c>
       <c r="N386" s="0" t="inlineStr">
         <is>
-          <t>每级材料消耗</t>
+          <t>最大等级</t>
         </is>
       </c>
     </row>
     <row r="387">
       <c r="J387" s="0" t="inlineStr">
         <is>
-          <t>costGold</t>
+          <t>effectType</t>
         </is>
       </c>
       <c r="L387" s="0" t="inlineStr">
         <is>
-          <t>long</t>
+          <t>cfg.ESkillEffect</t>
         </is>
       </c>
       <c r="N387" s="0" t="inlineStr">
         <is>
-          <t>每级金币消耗</t>
+          <t>效果类型</t>
         </is>
       </c>
     </row>
     <row r="388">
       <c r="J388" s="0" t="inlineStr">
         <is>
-          <t>prereqSkillId</t>
+          <t>effectValue</t>
         </is>
       </c>
       <c r="L388" s="0" t="inlineStr">
         <is>
-          <t>int</t>
+          <t>float</t>
         </is>
       </c>
       <c r="N388" s="0" t="inlineStr">
         <is>
-          <t>前置技能(需满级,0=无)</t>
+          <t>每级效果值</t>
         </is>
       </c>
     </row>
     <row r="389">
       <c r="J389" s="0" t="inlineStr">
         <is>
-          <t>row</t>
+          <t>costItems</t>
         </is>
       </c>
       <c r="L389" s="0" t="inlineStr">
         <is>
-          <t>int</t>
+          <t>(list#sep=;),cfg.ItemExchange#sep=,</t>
         </is>
       </c>
       <c r="N389" s="0" t="inlineStr">
         <is>
-          <t>树UI行</t>
+          <t>每级材料消耗</t>
         </is>
       </c>
     </row>
     <row r="390">
       <c r="J390" s="0" t="inlineStr">
         <is>
-          <t>col</t>
+          <t>costGold</t>
         </is>
       </c>
       <c r="L390" s="0" t="inlineStr">
         <is>
-          <t>int</t>
+          <t>long</t>
         </is>
       </c>
       <c r="N390" s="0" t="inlineStr">
         <is>
-          <t>树UI列</t>
+          <t>每级金币消耗</t>
         </is>
       </c>
     </row>
     <row r="391">
       <c r="J391" s="0" t="inlineStr">
         <is>
+          <t>prereqSkillId</t>
+        </is>
+      </c>
+      <c r="L391" s="0" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="N391" s="0" t="inlineStr">
+        <is>
+          <t>前置技能(需满级,0=无)</t>
+        </is>
+      </c>
+    </row>
+    <row r="392">
+      <c r="J392" s="0" t="inlineStr">
+        <is>
+          <t>row</t>
+        </is>
+      </c>
+      <c r="L392" s="0" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="N392" s="0" t="inlineStr">
+        <is>
+          <t>树UI行</t>
+        </is>
+      </c>
+    </row>
+    <row r="393">
+      <c r="J393" s="0" t="inlineStr">
+        <is>
+          <t>col</t>
+        </is>
+      </c>
+      <c r="L393" s="0" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="N393" s="0" t="inlineStr">
+        <is>
+          <t>树UI列</t>
+        </is>
+      </c>
+    </row>
+    <row r="394">
+      <c r="J394" s="0" t="inlineStr">
+        <is>
           <t>icon</t>
         </is>
       </c>
-      <c r="L391" s="0" t="inlineStr">
+      <c r="L394" s="0" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="N391" s="0" t="inlineStr">
+      <c r="N394" s="0" t="inlineStr">
         <is>
           <t>图标资源地址</t>
+        </is>
+      </c>
+    </row>
+    <row r="395">
+      <c r="B395" t="inlineStr">
+        <is>
+          <t>cfg.CompanionAffinityTier</t>
+        </is>
+      </c>
+      <c r="G395" t="inlineStr">
+        <is>
+          <t>好感档位表</t>
+        </is>
+      </c>
+      <c r="I395" t="inlineStr">
+        <is>
+          <t>c</t>
+        </is>
+      </c>
+    </row>
+    <row r="396">
+      <c r="J396" t="inlineStr">
+        <is>
+          <t>tier</t>
+        </is>
+      </c>
+      <c r="L396" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="N396" t="inlineStr">
+        <is>
+          <t>档位(1-4)</t>
+        </is>
+      </c>
+    </row>
+    <row r="397">
+      <c r="J397" t="inlineStr">
+        <is>
+          <t>nameKey</t>
+        </is>
+      </c>
+      <c r="L397" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="N397" t="inlineStr">
+        <is>
+          <t>档位名词条键</t>
+        </is>
+      </c>
+    </row>
+    <row r="398">
+      <c r="J398" t="inlineStr">
+        <is>
+          <t>threshold</t>
+        </is>
+      </c>
+      <c r="L398" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="N398" t="inlineStr">
+        <is>
+          <t>到达该档所需累计好感</t>
+        </is>
+      </c>
+    </row>
+    <row r="399">
+      <c r="J399" t="inlineStr">
+        <is>
+          <t>descKey</t>
+        </is>
+      </c>
+      <c r="L399" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="N399" t="inlineStr">
+        <is>
+          <t>档位人格描述词条键</t>
+        </is>
+      </c>
+    </row>
+    <row r="400">
+      <c r="B400" t="inlineStr">
+        <is>
+          <t>cfg.CompanionAffinityGain</t>
+        </is>
+      </c>
+      <c r="G400" t="inlineStr">
+        <is>
+          <t>好感获取规则表</t>
+        </is>
+      </c>
+      <c r="I400" t="inlineStr">
+        <is>
+          <t>c</t>
+        </is>
+      </c>
+    </row>
+    <row r="401">
+      <c r="J401" t="inlineStr">
+        <is>
+          <t>source</t>
+        </is>
+      </c>
+      <c r="L401" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="N401" t="inlineStr">
+        <is>
+          <t>来源标识(chat/extract/protect)</t>
+        </is>
+      </c>
+    </row>
+    <row r="402">
+      <c r="J402" t="inlineStr">
+        <is>
+          <t>value</t>
+        </is>
+      </c>
+      <c r="L402" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="N402" t="inlineStr">
+        <is>
+          <t>好感数值</t>
+        </is>
+      </c>
+    </row>
+    <row r="403">
+      <c r="J403" t="inlineStr">
+        <is>
+          <t>cooldownSec</t>
+        </is>
+      </c>
+      <c r="L403" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="N403" t="inlineStr">
+        <is>
+          <t>冷却秒(0=无)</t>
+        </is>
+      </c>
+    </row>
+    <row r="404">
+      <c r="J404" t="inlineStr">
+        <is>
+          <t>perRunCap</t>
+        </is>
+      </c>
+      <c r="L404" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="N404" t="inlineStr">
+        <is>
+          <t>每局上限(0=无限制)</t>
+        </is>
+      </c>
+    </row>
+    <row r="405">
+      <c r="B405" t="inlineStr">
+        <is>
+          <t>cfg.CompanionPersona</t>
+        </is>
+      </c>
+      <c r="G405" t="inlineStr">
+        <is>
+          <t>队友分档人格提示表</t>
+        </is>
+      </c>
+      <c r="I405" t="inlineStr">
+        <is>
+          <t>c</t>
+        </is>
+      </c>
+    </row>
+    <row r="406">
+      <c r="J406" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="L406" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="N406" t="inlineStr">
+        <is>
+          <t>唯一ID(companionId*10+tier)</t>
+        </is>
+      </c>
+    </row>
+    <row r="407">
+      <c r="J407" t="inlineStr">
+        <is>
+          <t>companionId</t>
+        </is>
+      </c>
+      <c r="L407" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="N407" t="inlineStr">
+        <is>
+          <t>队友ID</t>
+        </is>
+      </c>
+    </row>
+    <row r="408">
+      <c r="J408" t="inlineStr">
+        <is>
+          <t>tier</t>
+        </is>
+      </c>
+      <c r="L408" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="N408" t="inlineStr">
+        <is>
+          <t>好感档位</t>
+        </is>
+      </c>
+    </row>
+    <row r="409">
+      <c r="J409" t="inlineStr">
+        <is>
+          <t>promptAdd</t>
+        </is>
+      </c>
+      <c r="L409" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="N409" t="inlineStr">
+        <is>
+          <t>追加给LLM的关系姿态文本(英文)</t>
+        </is>
+      </c>
+    </row>
+    <row r="410">
+      <c r="B410" t="inlineStr">
+        <is>
+          <t>cfg.CompanionMemoryRule</t>
+        </is>
+      </c>
+      <c r="G410" t="inlineStr">
+        <is>
+          <t>队友记忆规则表</t>
+        </is>
+      </c>
+      <c r="I410" t="inlineStr">
+        <is>
+          <t>c</t>
+        </is>
+      </c>
+    </row>
+    <row r="411">
+      <c r="J411" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="L411" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="N411" t="inlineStr">
+        <is>
+          <t>规则ID</t>
+        </is>
+      </c>
+    </row>
+    <row r="412">
+      <c r="J412" t="inlineStr">
+        <is>
+          <t>memoryType</t>
+        </is>
+      </c>
+      <c r="L412" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="N412" t="inlineStr">
+        <is>
+          <t>记忆类型</t>
+        </is>
+      </c>
+    </row>
+    <row r="413">
+      <c r="J413" t="inlineStr">
+        <is>
+          <t>minTier</t>
+        </is>
+      </c>
+      <c r="L413" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="N413" t="inlineStr">
+        <is>
+          <t>生效最低档位</t>
+        </is>
+      </c>
+    </row>
+    <row r="414">
+      <c r="J414" t="inlineStr">
+        <is>
+          <t>maxCount</t>
+        </is>
+      </c>
+      <c r="L414" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="N414" t="inlineStr">
+        <is>
+          <t>容量上限</t>
+        </is>
+      </c>
+    </row>
+    <row r="415">
+      <c r="J415" t="inlineStr">
+        <is>
+          <t>sampleRule</t>
+        </is>
+      </c>
+      <c r="L415" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="N415" t="inlineStr">
+        <is>
+          <t>采样规则(fifo/random_forget/random_evict)</t>
+        </is>
+      </c>
+    </row>
+    <row r="416">
+      <c r="J416" t="inlineStr">
+        <is>
+          <t>writeChance</t>
+        </is>
+      </c>
+      <c r="L416" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="N416" t="inlineStr">
+        <is>
+          <t>写入概率(0-1)</t>
         </is>
       </c>
     </row>
